--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan51\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D132E7B6-90EB-42E2-B216-D607FBFE2513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DCEA5B9-58ED-463B-9F4B-3853FAC5D635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2939" uniqueCount="873">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -802,13 +802,13 @@
     <t>elc_spv_POL_004</t>
   </si>
   <si>
-    <t>solar electricity near Wroclaw (cluster 4)</t>
+    <t>solar electricity near Warsaw (cluster 4)</t>
   </si>
   <si>
     <t>elc_spv_POL_005</t>
   </si>
   <si>
-    <t>solar electricity near Wroclaw (cluster 5)</t>
+    <t>solar electricity near Siedlce (cluster 5)</t>
   </si>
   <si>
     <t>elc_spv_POL_006</t>
@@ -820,253 +820,307 @@
     <t>elc_spv_POL_007</t>
   </si>
   <si>
-    <t>solar electricity near Olsztyn (cluster 7)</t>
+    <t>solar electricity near Rzeszow (cluster 7)</t>
   </si>
   <si>
     <t>elc_spv_POL_008</t>
   </si>
   <si>
-    <t>solar electricity near Slupsk (cluster 8)</t>
+    <t>solar electricity near Olsztyn (cluster 8)</t>
   </si>
   <si>
     <t>elc_spv_POL_009</t>
   </si>
   <si>
-    <t>solar electricity near Olsztyn (cluster 9)</t>
+    <t>solar electricity near Szczecin (cluster 9)</t>
   </si>
   <si>
     <t>elc_spv_POL_010</t>
   </si>
   <si>
-    <t>solar electricity near Legnica (cluster 10)</t>
+    <t>solar electricity near Slupsk (cluster 10)</t>
   </si>
   <si>
     <t>elc_spv_POL_011</t>
   </si>
   <si>
-    <t>solar electricity near Gdansk (cluster 11)</t>
+    <t>solar electricity near Olsztyn (cluster 11)</t>
   </si>
   <si>
     <t>elc_spv_POL_012</t>
   </si>
   <si>
-    <t>solar electricity near Lomza (cluster 12)</t>
+    <t>solar electricity near Legnica (cluster 12)</t>
   </si>
   <si>
     <t>elc_spv_POL_013</t>
   </si>
   <si>
-    <t>solar electricity near Zielona Gora (cluster 13)</t>
+    <t>solar electricity near Gdansk (cluster 13)</t>
   </si>
   <si>
     <t>elc_spv_POL_014</t>
   </si>
   <si>
-    <t>solar electricity near Szczecin (cluster 14)</t>
+    <t>solar electricity near Warsaw (cluster 14)</t>
   </si>
   <si>
     <t>elc_spv_POL_015</t>
   </si>
   <si>
-    <t>solar electricity near Rzeszow (cluster 15)</t>
+    <t>solar electricity near Lomza (cluster 15)</t>
   </si>
   <si>
     <t>elc_spv_POL_016</t>
   </si>
   <si>
-    <t>solar electricity near Suwalki (cluster 16)</t>
+    <t>solar electricity near Rybnik (cluster 16)</t>
   </si>
   <si>
     <t>elc_spv_POL_017</t>
   </si>
   <si>
-    <t>solar electricity near Lodz (cluster 17)</t>
+    <t>solar electricity near Zielona Gora (cluster 17)</t>
   </si>
   <si>
     <t>elc_spv_POL_018</t>
   </si>
   <si>
-    <t>solar electricity near Lodz (cluster 18)</t>
+    <t>solar electricity near Szczecin (cluster 18)</t>
   </si>
   <si>
     <t>elc_spv_POL_019</t>
   </si>
   <si>
-    <t>solar electricity near Zamosc (cluster 19)</t>
+    <t>solar electricity near Lublin (cluster 19)</t>
   </si>
   <si>
     <t>elc_spv_POL_020</t>
   </si>
   <si>
-    <t>solar electricity near Koszalin (cluster 20)</t>
+    <t>solar electricity near Suwalki (cluster 20)</t>
   </si>
   <si>
     <t>elc_spv_POL_021</t>
   </si>
   <si>
-    <t>solar electricity near Zielona Gora (cluster 21)</t>
+    <t>solar electricity near Rzeszow (cluster 21)</t>
   </si>
   <si>
     <t>elc_spv_POL_022</t>
   </si>
   <si>
-    <t>solar electricity near Katowice (cluster 22)</t>
+    <t>solar electricity near Lodz (cluster 22)</t>
   </si>
   <si>
     <t>elc_spv_POL_023</t>
   </si>
   <si>
-    <t>solar electricity near Tarnow (cluster 23)</t>
+    <t>solar electricity near Warsaw (cluster 23)</t>
   </si>
   <si>
     <t>elc_spv_POL_024</t>
   </si>
   <si>
-    <t>solar electricity near Lublin (cluster 24)</t>
+    <t>solar electricity near Koszalin (cluster 24)</t>
   </si>
   <si>
     <t>elc_spv_POL_025</t>
   </si>
   <si>
-    <t>solar electricity near Rzeszow (cluster 25)</t>
+    <t>solar electricity near Koszalin (cluster 25)</t>
   </si>
   <si>
     <t>elc_spv_POL_026</t>
   </si>
   <si>
-    <t>solar electricity near Kielce (cluster 26)</t>
+    <t>solar electricity near Zielona Gora (cluster 26)</t>
   </si>
   <si>
     <t>elc_spv_POL_027</t>
   </si>
   <si>
-    <t>solar electricity near Mielec (cluster 27)</t>
+    <t>solar electricity near Katowice (cluster 27)</t>
   </si>
   <si>
     <t>elc_spv_POL_028</t>
   </si>
   <si>
-    <t>solar electricity near Stalowa Wola (cluster 28)</t>
+    <t>solar electricity near Kedzierzyn-Kozle (cluster 28)</t>
   </si>
   <si>
     <t>elc_spv_POL_029</t>
   </si>
   <si>
-    <t>solar electricity near Czestochowa (cluster 29)</t>
+    <t>solar electricity near Krakow (cluster 29)</t>
   </si>
   <si>
     <t>elc_spv_POL_030</t>
   </si>
   <si>
-    <t>solar electricity near Torun (cluster 30)</t>
+    <t>solar electricity near Tarnow (cluster 30)</t>
   </si>
   <si>
     <t>elc_spv_POL_031</t>
   </si>
   <si>
-    <t>solar electricity near Ostrowiec Swietokrzyski (cluster 31)</t>
+    <t>solar electricity near Chelm (cluster 31)</t>
   </si>
   <si>
     <t>elc_spv_POL_032</t>
   </si>
   <si>
-    <t>solar electricity near Opole (cluster 32)</t>
+    <t>solar electricity near Radom (cluster 32)</t>
   </si>
   <si>
     <t>elc_spv_POL_033</t>
   </si>
   <si>
-    <t>solar electricity near Konin (cluster 33)</t>
+    <t>solar electricity near Mielec (cluster 33)</t>
   </si>
   <si>
     <t>elc_spv_POL_034</t>
   </si>
   <si>
-    <t>solar electricity near Koszalin (cluster 34)</t>
+    <t>solar electricity near Rzeszow (cluster 34)</t>
   </si>
   <si>
     <t>elc_spv_POL_035</t>
   </si>
   <si>
-    <t>solar electricity near Warsaw (cluster 35)</t>
+    <t>solar electricity near Czestochowa (cluster 35)</t>
   </si>
   <si>
     <t>elc_spv_POL_036</t>
   </si>
   <si>
-    <t>solar electricity near Katowice (cluster 36)</t>
+    <t>solar electricity near Pila (cluster 36)</t>
   </si>
   <si>
     <t>elc_spv_POL_037</t>
   </si>
   <si>
-    <t>solar electricity near Elk (cluster 37)</t>
+    <t>solar electricity near Torun (cluster 37)</t>
   </si>
   <si>
     <t>elc_spv_POL_038</t>
   </si>
   <si>
-    <t>solar electricity near Poznan (cluster 38)</t>
+    <t>solar electricity near Skarzysko-Kamienna (cluster 38)</t>
   </si>
   <si>
     <t>elc_spv_POL_039</t>
   </si>
   <si>
-    <t>solar electricity near Opole (cluster 39)</t>
+    <t>solar electricity near Wroclaw (cluster 39)</t>
   </si>
   <si>
     <t>elc_spv_POL_040</t>
   </si>
   <si>
-    <t>solar electricity near Szczecin (cluster 40)</t>
+    <t>solar electricity near Konin (cluster 40)</t>
   </si>
   <si>
     <t>elc_spv_POL_041</t>
   </si>
   <si>
-    <t>solar electricity near Krakow (cluster 41)</t>
+    <t>solar electricity near Kalisz (cluster 41)</t>
   </si>
   <si>
     <t>elc_spv_POL_042</t>
   </si>
   <si>
-    <t>solar electricity near Krakow (cluster 42)</t>
+    <t>solar electricity near Koszalin (cluster 42)</t>
   </si>
   <si>
     <t>elc_spv_POL_043</t>
   </si>
   <si>
-    <t>solar electricity near Elblag (cluster 43)</t>
+    <t>solar electricity near Walbrzych (cluster 43)</t>
   </si>
   <si>
     <t>elc_spv_POL_044</t>
   </si>
   <si>
-    <t>solar electricity near Plock (cluster 44)</t>
+    <t>solar electricity near Warsaw (cluster 44)</t>
   </si>
   <si>
     <t>elc_spv_POL_045</t>
   </si>
   <si>
-    <t>solar electricity near Wroclaw (cluster 45)</t>
+    <t>solar electricity near Lodz (cluster 45)</t>
   </si>
   <si>
     <t>elc_spv_POL_046</t>
   </si>
   <si>
-    <t>solar electricity near Gdansk (cluster 46)</t>
+    <t>solar electricity near Elk (cluster 46)</t>
   </si>
   <si>
     <t>elc_spv_POL_047</t>
   </si>
   <si>
-    <t>solar electricity near Krakow (cluster 47)</t>
+    <t>solar electricity near Poznan (cluster 47)</t>
   </si>
   <si>
     <t>elc_spv_POL_048</t>
   </si>
   <si>
-    <t>solar electricity near Lublin (cluster 48)</t>
+    <t>solar electricity near Opole (cluster 48)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_049</t>
+  </si>
+  <si>
+    <t>solar electricity near Gdansk (cluster 49)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_050</t>
+  </si>
+  <si>
+    <t>solar electricity near Szczecin (cluster 50)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_051</t>
+  </si>
+  <si>
+    <t>solar electricity near Krakow (cluster 51)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_052</t>
+  </si>
+  <si>
+    <t>solar electricity near Krakow (cluster 52)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_053</t>
+  </si>
+  <si>
+    <t>solar electricity near Grudziadz (cluster 53)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_054</t>
+  </si>
+  <si>
+    <t>solar electricity near Plock (cluster 54)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_055</t>
+  </si>
+  <si>
+    <t>solar electricity near Wroclaw (cluster 55)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_056</t>
+  </si>
+  <si>
+    <t>solar electricity near Gdansk (cluster 56)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_057</t>
+  </si>
+  <si>
+    <t>solar electricity near Lublin (cluster 57)</t>
   </si>
   <si>
     <t>elc_wof_POL_001</t>
@@ -1084,7 +1138,7 @@
     <t>elc_wof_POL_003</t>
   </si>
   <si>
-    <t>wind offshore electricity near Koszalin (cluster 3)</t>
+    <t>wind offshore electricity near Szczecin (cluster 3)</t>
   </si>
   <si>
     <t>elc_wof_POL_004</t>
@@ -1102,13 +1156,13 @@
     <t>elc_wof_POL_006</t>
   </si>
   <si>
-    <t>wind offshore electricity near Koszalin (cluster 6)</t>
+    <t>wind offshore electricity near Slupsk (cluster 6)</t>
   </si>
   <si>
     <t>elc_wof_POL_007</t>
   </si>
   <si>
-    <t>wind offshore electricity near Koszalin (cluster 7)</t>
+    <t>wind offshore electricity near Slupsk (cluster 7)</t>
   </si>
   <si>
     <t>elc_wof_POL_008</t>
@@ -1150,253 +1204,325 @@
     <t>elc_won_POL_004</t>
   </si>
   <si>
-    <t>wind onshore electricity near Legnica (cluster 4)</t>
+    <t>wind onshore electricity near Warsaw (cluster 4)</t>
   </si>
   <si>
     <t>elc_won_POL_005</t>
   </si>
   <si>
-    <t>wind onshore electricity near Wroclaw (cluster 5)</t>
+    <t>wind onshore electricity near Siedlce (cluster 5)</t>
   </si>
   <si>
     <t>elc_won_POL_006</t>
   </si>
   <si>
-    <t>wind onshore electricity near Wroclaw (cluster 6)</t>
+    <t>wind onshore electricity near Legnica (cluster 6)</t>
   </si>
   <si>
     <t>elc_won_POL_007</t>
   </si>
   <si>
-    <t>wind onshore electricity near Olsztyn (cluster 7)</t>
+    <t>wind onshore electricity near Rzeszow (cluster 7)</t>
   </si>
   <si>
     <t>elc_won_POL_008</t>
   </si>
   <si>
-    <t>wind onshore electricity near Slupsk (cluster 8)</t>
+    <t>wind onshore electricity near Olsztyn (cluster 8)</t>
   </si>
   <si>
     <t>elc_won_POL_009</t>
   </si>
   <si>
-    <t>wind onshore electricity near Olsztyn (cluster 9)</t>
+    <t>wind onshore electricity near Szczecin (cluster 9)</t>
   </si>
   <si>
     <t>elc_won_POL_010</t>
   </si>
   <si>
-    <t>wind onshore electricity near Legnica (cluster 10)</t>
+    <t>wind onshore electricity near Slupsk (cluster 10)</t>
   </si>
   <si>
     <t>elc_won_POL_011</t>
   </si>
   <si>
-    <t>wind onshore electricity near Gdansk (cluster 11)</t>
+    <t>wind onshore electricity near Olsztyn (cluster 11)</t>
   </si>
   <si>
     <t>elc_won_POL_012</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lomza (cluster 12)</t>
+    <t>wind onshore electricity near Legnica (cluster 12)</t>
   </si>
   <si>
     <t>elc_won_POL_013</t>
   </si>
   <si>
-    <t>wind onshore electricity near Zielona Gora (cluster 13)</t>
+    <t>wind onshore electricity near Gdansk (cluster 13)</t>
   </si>
   <si>
     <t>elc_won_POL_014</t>
   </si>
   <si>
-    <t>wind onshore electricity near Szczecin (cluster 14)</t>
+    <t>wind onshore electricity near Warsaw (cluster 14)</t>
   </si>
   <si>
     <t>elc_won_POL_015</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rzeszow (cluster 15)</t>
+    <t>wind onshore electricity near Lomza (cluster 15)</t>
   </si>
   <si>
     <t>elc_won_POL_016</t>
   </si>
   <si>
-    <t>wind onshore electricity near Suwalki (cluster 16)</t>
+    <t>wind onshore electricity near Rybnik (cluster 16)</t>
   </si>
   <si>
     <t>elc_won_POL_017</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lodz (cluster 17)</t>
+    <t>wind onshore electricity near Zielona Gora (cluster 17)</t>
   </si>
   <si>
     <t>elc_won_POL_018</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lodz (cluster 18)</t>
+    <t>wind onshore electricity near Szczecin (cluster 18)</t>
   </si>
   <si>
     <t>elc_won_POL_019</t>
   </si>
   <si>
-    <t>wind onshore electricity near Zamosc (cluster 19)</t>
+    <t>wind onshore electricity near Lublin (cluster 19)</t>
   </si>
   <si>
     <t>elc_won_POL_020</t>
   </si>
   <si>
-    <t>wind onshore electricity near Koszalin (cluster 20)</t>
+    <t>wind onshore electricity near Suwalki (cluster 20)</t>
   </si>
   <si>
     <t>elc_won_POL_021</t>
   </si>
   <si>
-    <t>wind onshore electricity near Zielona Gora (cluster 21)</t>
+    <t>wind onshore electricity near Rzeszow (cluster 21)</t>
   </si>
   <si>
     <t>elc_won_POL_022</t>
   </si>
   <si>
-    <t>wind onshore electricity near Tarnow (cluster 22)</t>
+    <t>wind onshore electricity near Lodz (cluster 22)</t>
   </si>
   <si>
     <t>elc_won_POL_023</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lublin (cluster 23)</t>
+    <t>wind onshore electricity near Warsaw (cluster 23)</t>
   </si>
   <si>
     <t>elc_won_POL_024</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rzeszow (cluster 24)</t>
+    <t>wind onshore electricity near Koszalin (cluster 24)</t>
   </si>
   <si>
     <t>elc_won_POL_025</t>
   </si>
   <si>
-    <t>wind onshore electricity near Radom (cluster 25)</t>
+    <t>wind onshore electricity near Koszalin (cluster 25)</t>
   </si>
   <si>
     <t>elc_won_POL_026</t>
   </si>
   <si>
-    <t>wind onshore electricity near Mielec (cluster 26)</t>
+    <t>wind onshore electricity near Zielona Gora (cluster 26)</t>
   </si>
   <si>
     <t>elc_won_POL_027</t>
   </si>
   <si>
-    <t>wind onshore electricity near Stalowa Wola (cluster 27)</t>
+    <t>wind onshore electricity near Katowice (cluster 27)</t>
   </si>
   <si>
     <t>elc_won_POL_028</t>
   </si>
   <si>
-    <t>wind onshore electricity near Czestochowa (cluster 28)</t>
+    <t>wind onshore electricity near Kedzierzyn-Kozle (cluster 28)</t>
   </si>
   <si>
     <t>elc_won_POL_029</t>
   </si>
   <si>
-    <t>wind onshore electricity near Torun (cluster 29)</t>
+    <t>wind onshore electricity near Krakow (cluster 29)</t>
   </si>
   <si>
     <t>elc_won_POL_030</t>
   </si>
   <si>
-    <t>wind onshore electricity near Radom (cluster 30)</t>
+    <t>wind onshore electricity near Tarnow (cluster 30)</t>
   </si>
   <si>
     <t>elc_won_POL_031</t>
   </si>
   <si>
-    <t>wind onshore electricity near Konin (cluster 31)</t>
+    <t>wind onshore electricity near Chelm (cluster 31)</t>
   </si>
   <si>
     <t>elc_won_POL_032</t>
   </si>
   <si>
-    <t>wind onshore electricity near Koszalin (cluster 32)</t>
+    <t>wind onshore electricity near Radom (cluster 32)</t>
   </si>
   <si>
     <t>elc_won_POL_033</t>
   </si>
   <si>
-    <t>wind onshore electricity near Warsaw (cluster 33)</t>
+    <t>wind onshore electricity near Mielec (cluster 33)</t>
   </si>
   <si>
     <t>elc_won_POL_034</t>
   </si>
   <si>
-    <t>wind onshore electricity near Katowice (cluster 34)</t>
+    <t>wind onshore electricity near Rzeszow (cluster 34)</t>
   </si>
   <si>
     <t>elc_won_POL_035</t>
   </si>
   <si>
-    <t>wind onshore electricity near Elk (cluster 35)</t>
+    <t>wind onshore electricity near Czestochowa (cluster 35)</t>
   </si>
   <si>
     <t>elc_won_POL_036</t>
   </si>
   <si>
-    <t>wind onshore electricity near Poznan (cluster 36)</t>
+    <t>wind onshore electricity near Pila (cluster 36)</t>
   </si>
   <si>
     <t>elc_won_POL_037</t>
   </si>
   <si>
-    <t>wind onshore electricity near Kedzierzyn-Kozle (cluster 37)</t>
+    <t>wind onshore electricity near Torun (cluster 37)</t>
   </si>
   <si>
     <t>elc_won_POL_038</t>
   </si>
   <si>
-    <t>wind onshore electricity near Szczecin (cluster 38)</t>
+    <t>wind onshore electricity near Skarzysko-Kamienna (cluster 38)</t>
   </si>
   <si>
     <t>elc_won_POL_039</t>
   </si>
   <si>
-    <t>wind onshore electricity near Krakow (cluster 39)</t>
+    <t>wind onshore electricity near Wroclaw (cluster 39)</t>
   </si>
   <si>
     <t>elc_won_POL_040</t>
   </si>
   <si>
-    <t>wind onshore electricity near Elblag (cluster 40)</t>
+    <t>wind onshore electricity near Konin (cluster 40)</t>
   </si>
   <si>
     <t>elc_won_POL_041</t>
   </si>
   <si>
-    <t>wind onshore electricity near Plock (cluster 41)</t>
+    <t>wind onshore electricity near Kalisz (cluster 41)</t>
   </si>
   <si>
     <t>elc_won_POL_042</t>
   </si>
   <si>
-    <t>wind onshore electricity near Kalisz (cluster 42)</t>
+    <t>wind onshore electricity near Koszalin (cluster 42)</t>
   </si>
   <si>
     <t>elc_won_POL_043</t>
   </si>
   <si>
-    <t>wind onshore electricity near Gdansk (cluster 43)</t>
+    <t>wind onshore electricity near Walbrzych (cluster 43)</t>
   </si>
   <si>
     <t>elc_won_POL_044</t>
   </si>
   <si>
-    <t>wind onshore electricity near Krakow (cluster 44)</t>
+    <t>wind onshore electricity near Warsaw (cluster 44)</t>
   </si>
   <si>
     <t>elc_won_POL_045</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lublin (cluster 45)</t>
+    <t>wind onshore electricity near Lodz (cluster 45)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_046</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Elk (cluster 46)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_047</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Poznan (cluster 47)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_048</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Opole (cluster 48)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_049</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Gdansk (cluster 49)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_050</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Szczecin (cluster 50)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_051</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Krakow (cluster 51)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_052</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Krakow (cluster 52)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_053</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Grudziadz (cluster 53)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_054</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Plock (cluster 54)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_055</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Wroclaw (cluster 55)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_056</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Gdansk (cluster 56)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_057</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Lublin (cluster 57)</t>
   </si>
   <si>
     <t>~fi_comm</t>
@@ -1423,276 +1549,348 @@
     <t>grid node -- way/111615226-220 (Legnica, 74 km)</t>
   </si>
   <si>
-    <t>e_Bydgoszcz_POL</t>
+    <t>e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/194903381-400 (Chelm, 4 km)</t>
+  </si>
+  <si>
+    <t>e_Debica_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/191038569-220 (Tarnow, 5 km)</t>
+  </si>
+  <si>
+    <t>e_Elk_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/303870256-400 (Elk, 8 km)</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/86494356-400 (Gdansk, 54 km)</t>
+  </si>
+  <si>
+    <t>e_Giszowiec_POL</t>
+  </si>
+  <si>
+    <t>grid node -- PL55-220 (Katowice, 8 km)</t>
+  </si>
+  <si>
+    <t>e_GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>grid node -- PL18-400 (Gorzow Wielkopolski, 15 km)</t>
+  </si>
+  <si>
+    <t>e_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/170259740-220 (Elk, 6 km)</t>
+  </si>
+  <si>
+    <t>e_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/46092396-400 (Grudziadz, 6 km)</t>
+  </si>
+  <si>
+    <t>e_Kalisz_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/255293403-400 (Kalisz, 21 km)</t>
+  </si>
+  <si>
+    <t>e_KamienPomorski_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/165763717-220 (Szczecin, 15 km)</t>
+  </si>
+  <si>
+    <t>e_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/185454704-220 (Gliwice, 28 km)</t>
+  </si>
+  <si>
+    <t>e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/199098050-220 (Kielce, 16 km)</t>
+  </si>
+  <si>
+    <t>e_Kolno_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/121656686-400 (Lomza, 31 km)</t>
+  </si>
+  <si>
+    <t>e_Konin_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/255284259-220 (Konin, 10 km)</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/175406958-400 (Koszalin, 10 km)</t>
+  </si>
+  <si>
+    <t>e_Krakow_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/189501431-400 (Krakow, 13 km)</t>
+  </si>
+  <si>
+    <t>e_Krapkowice_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/336990960-220 (Opole, 7 km)</t>
+  </si>
+  <si>
+    <t>e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>grid node -- PL7-400 (Grudziadz, 8 km)</t>
+  </si>
+  <si>
+    <t>e_Legnica_POL</t>
+  </si>
+  <si>
+    <t>grid node -- PL34-400 (Wroclaw, 43 km)</t>
+  </si>
+  <si>
+    <t>e_Lukow_POL</t>
+  </si>
+  <si>
+    <t>grid node -- PL27-400 (Siedlce, 8 km)</t>
+  </si>
+  <si>
+    <t>e_Miastko_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/178838661-220 (Koszalin, 40 km)</t>
+  </si>
+  <si>
+    <t>e_Mikolow_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/183945016-220 (Katowice, 19 km)</t>
+  </si>
+  <si>
+    <t>e_NowaSol_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/180535363-220 (Lubin, 33 km)</t>
+  </si>
+  <si>
+    <t>e_Nowogard_POL</t>
+  </si>
+  <si>
+    <t>grid node -- PL8-220 (Szczecin, 29 km)</t>
+  </si>
+  <si>
+    <t>e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/101915790-220 (Olsztyn, 4 km)</t>
+  </si>
+  <si>
+    <t>e_Opole_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/255277953-400 (Opole, 10 km)</t>
+  </si>
+  <si>
+    <t>e_OstrowMazowiecka_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/121656686-220 (Lomza, 31 km)</t>
+  </si>
+  <si>
+    <t>e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/254235846-400 (Ostrowiec Swietokrzyski, 4 km)</t>
+  </si>
+  <si>
+    <t>e_Otwock_POL</t>
+  </si>
+  <si>
+    <t>grid node -- PL26-400 (Warsaw, 53 km)</t>
+  </si>
+  <si>
+    <t>e_PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/293484891-400 (Piotrkow Trybunalski, 26 km)</t>
+  </si>
+  <si>
+    <t>e_Plock_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/658600169-400 (Plock, 4 km)</t>
+  </si>
+  <si>
+    <t>e_Police_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/39428977-220 (Szczecin, 27 km)</t>
+  </si>
+  <si>
+    <t>e_Pulawy_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/88544449-220 (Lublin, 46 km)</t>
+  </si>
+  <si>
+    <t>e_Radom_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/173582810-400 (Radom, 35 km)</t>
+  </si>
+  <si>
+    <t>e_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/171917072-400 (Czestochowa, 41 km)</t>
+  </si>
+  <si>
+    <t>e_Rumia_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/112614319-400 (Gdansk, 4 km)</t>
+  </si>
+  <si>
+    <t>e_Rybnik_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/139452056-400 (Gliwice, 20 km)</t>
+  </si>
+  <si>
+    <t>e_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/215282393-400 (Rzeszow, 20 km)</t>
+  </si>
+  <si>
+    <t>e_Sanok_POL</t>
+  </si>
+  <si>
+    <t>grid node -- PL62-400 (Rzeszow, 32 km)</t>
+  </si>
+  <si>
+    <t>e_SiemianowiceSlaski_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/40946790-220 (Katowice, 19 km)</t>
+  </si>
+  <si>
+    <t>e_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>grid node -- relation/18085709-400 (Slupsk, 10 km)</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/133537926-220 (Katowice, 22 km)</t>
+  </si>
+  <si>
+    <t>e_Staszow_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/199098053-400 (Mielec, 19 km)</t>
+  </si>
+  <si>
+    <t>e_Swarzedz_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/32036484-220 (Poznan, 11 km)</t>
+  </si>
+  <si>
+    <t>e_Swidnik_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/170249563-220 (Lublin, 6 km)</t>
+  </si>
+  <si>
+    <t>e_Tczew_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/385098015-400 (Gdansk, 45 km)</t>
+  </si>
+  <si>
+    <t>e_TomaszowLubelski_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/170368942-220 (Zamosc, 8 km)</t>
+  </si>
+  <si>
+    <t>e_Torun_POL</t>
   </si>
   <si>
     <t>grid node -- PL15-400 (Bydgoszcz, 10 km)</t>
   </si>
   <si>
-    <t>e_Chelm_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/194903381-400 (Chelm, 4 km)</t>
-  </si>
-  <si>
-    <t>e_Czestochowa_POL</t>
+    <t>e_Ustka_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/255314292 (Slupsk, 10 km)</t>
+  </si>
+  <si>
+    <t>e_Wagrowiec_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/238640596-220 (Pila, 12 km)</t>
+  </si>
+  <si>
+    <t>e_Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/276291999-220 (Walbrzych, 11 km)</t>
+  </si>
+  <si>
+    <t>e_Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/245964556-220 (Wloclawek, 10 km)</t>
+  </si>
+  <si>
+    <t>e_Wloszczowa_POL</t>
   </si>
   <si>
     <t>grid node -- way/216060722-220 (Czestochowa, 4 km)</t>
   </si>
   <si>
-    <t>e_Debica_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/198635989-220 (Rzeszow, 6 km)</t>
-  </si>
-  <si>
-    <t>e_Elk_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/303870256-400 (Elk, 8 km)</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/112614319-400 (Gdansk, 4 km)</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/86494356-400 (Gdansk, 54 km)</t>
-  </si>
-  <si>
-    <t>e_Gliwice_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/293489607-400 (Katowice, 21 km)</t>
-  </si>
-  <si>
-    <t>e_GorzowWielkopolski_POL</t>
-  </si>
-  <si>
-    <t>grid node -- PL18-400 (Gorzow Wielkopolski, 15 km)</t>
-  </si>
-  <si>
-    <t>e_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/170259740-220 (Elk, 6 km)</t>
-  </si>
-  <si>
-    <t>e_Grudziadz_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/46092396-400 (Grudziadz, 6 km)</t>
-  </si>
-  <si>
-    <t>e_Katowice_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/40946790-220 (Katowice, 19 km)</t>
-  </si>
-  <si>
-    <t>e_KedzierzynKozle_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/336990960-220 (Opole, 7 km)</t>
-  </si>
-  <si>
-    <t>e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/199098050-220 (Kielce, 16 km)</t>
-  </si>
-  <si>
-    <t>e_Konin_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/255284259-220 (Konin, 10 km)</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/178838661-220 (Koszalin, 40 km)</t>
-  </si>
-  <si>
-    <t>e_Krakow_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/87667718-220 (Krakow, 12 km)</t>
-  </si>
-  <si>
-    <t>e_Krosno_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/166838338-400 (Rzeszow, 40 km)</t>
-  </si>
-  <si>
-    <t>e_Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>grid node -- PL7-400 (Grudziadz, 8 km)</t>
-  </si>
-  <si>
-    <t>e_Legnica_POL</t>
-  </si>
-  <si>
-    <t>grid node -- PL34-400 (Wroclaw, 43 km)</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/121656686-220 (Lomza, 31 km)</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/180535363-220 (Lubin, 33 km)</t>
-  </si>
-  <si>
-    <t>e_Mielec_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/199098053-220 (Mielec, 19 km)</t>
-  </si>
-  <si>
-    <t>e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>grid node -- PL36-400 (Wroclaw, 46 km)</t>
-  </si>
-  <si>
-    <t>e_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/101915790-220 (Olsztyn, 4 km)</t>
-  </si>
-  <si>
-    <t>e_Opole_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/255277953-400 (Opole, 10 km)</t>
-  </si>
-  <si>
-    <t>e_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/254235846-400 (Ostrowiec Swietokrzyski, 4 km)</t>
-  </si>
-  <si>
-    <t>e_PiotrkowTrybunalsk_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/170316833-220 (Piotrkow Trybunalski, 3 km)</t>
-  </si>
-  <si>
-    <t>e_Plock_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/658600169-400 (Plock, 4 km)</t>
-  </si>
-  <si>
-    <t>e_Police_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/165763717-220 (Szczecin, 15 km)</t>
-  </si>
-  <si>
-    <t>e_Poznan_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/32036484-220 (Poznan, 11 km)</t>
-  </si>
-  <si>
-    <t>e_Pulawy_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/88544449-220 (Lublin, 46 km)</t>
-  </si>
-  <si>
-    <t>e_Radomsko_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/171917072-400 (Czestochowa, 41 km)</t>
-  </si>
-  <si>
-    <t>e_Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/215282393-400 (Rzeszow, 20 km)</t>
-  </si>
-  <si>
-    <t>e_Slupsk_POL</t>
-  </si>
-  <si>
-    <t>grid node -- relation/18085709-400 (Slupsk, 10 km)</t>
-  </si>
-  <si>
-    <t>e_Sosnowiec_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/183945016-220 (Katowice, 19 km)</t>
-  </si>
-  <si>
-    <t>e_Swidnica_POL</t>
-  </si>
-  <si>
-    <t>grid node -- PL46-220 (Wroclaw, 58 km)</t>
-  </si>
-  <si>
-    <t>e_Szczecin_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/39428977-400 (Szczecin, 27 km)</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/191038569-220 (Tarnow, 5 km)</t>
-  </si>
-  <si>
-    <t>e_Ustka_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/255314292 (Slupsk, 10 km)</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL</t>
+    <t>e_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/79033485-400 (Wroclaw, 13 km)</t>
+  </si>
+  <si>
+    <t>e_Zabki_POL</t>
   </si>
   <si>
     <t>grid node -- way/29115701-220 (Warsaw, 9 km)</t>
   </si>
   <si>
-    <t>e_Wloclawek_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/245964556-220 (Wloclawek, 10 km)</t>
-  </si>
-  <si>
-    <t>e_Wroclaw_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/79033485-400 (Wroclaw, 13 km)</t>
-  </si>
-  <si>
-    <t>e_Zamosc_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/173613665-220 (Zamosc, 3 km)</t>
-  </si>
-  <si>
     <t>e_ZielonaGora_POL</t>
   </si>
   <si>
     <t>grid node -- way/158232924-220 (Zielona Gora, 15 km)</t>
   </si>
   <si>
+    <t>e_Zory_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/139452056-220 (Gliwice, 20 km)</t>
+  </si>
+  <si>
     <t>h_Bialystok_POL</t>
   </si>
   <si>
@@ -1711,277 +1909,349 @@
     <t>heat at grid node -- way/111615226-220 (Legnica, 74 km)</t>
   </si>
   <si>
-    <t>h_Bydgoszcz_POL</t>
+    <t>h_Chelm_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/194903381-400 (Chelm, 4 km)</t>
+  </si>
+  <si>
+    <t>h_Debica_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/191038569-220 (Tarnow, 5 km)</t>
+  </si>
+  <si>
+    <t>h_Elk_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/303870256-400 (Elk, 8 km)</t>
+  </si>
+  <si>
+    <t>h_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/86494356-400 (Gdansk, 54 km)</t>
+  </si>
+  <si>
+    <t>h_Giszowiec_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- PL55-220 (Katowice, 8 km)</t>
+  </si>
+  <si>
+    <t>h_GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- PL18-400 (Gorzow Wielkopolski, 15 km)</t>
+  </si>
+  <si>
+    <t>h_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/170259740-220 (Elk, 6 km)</t>
+  </si>
+  <si>
+    <t>h_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/46092396-400 (Grudziadz, 6 km)</t>
+  </si>
+  <si>
+    <t>h_Kalisz_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/255293403-400 (Kalisz, 21 km)</t>
+  </si>
+  <si>
+    <t>h_KamienPomorski_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/165763717-220 (Szczecin, 15 km)</t>
+  </si>
+  <si>
+    <t>h_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/185454704-220 (Gliwice, 28 km)</t>
+  </si>
+  <si>
+    <t>h_Kielce_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/199098050-220 (Kielce, 16 km)</t>
+  </si>
+  <si>
+    <t>h_Kolno_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/121656686-400 (Lomza, 31 km)</t>
+  </si>
+  <si>
+    <t>h_Konin_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/255284259-220 (Konin, 10 km)</t>
+  </si>
+  <si>
+    <t>h_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/175406958-400 (Koszalin, 10 km)</t>
+  </si>
+  <si>
+    <t>h_Krakow_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/189501431-400 (Krakow, 13 km)</t>
+  </si>
+  <si>
+    <t>h_Krapkowice_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/336990960-220 (Opole, 7 km)</t>
+  </si>
+  <si>
+    <t>h_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- PL7-400 (Grudziadz, 8 km)</t>
+  </si>
+  <si>
+    <t>h_Legnica_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- PL34-400 (Wroclaw, 43 km)</t>
+  </si>
+  <si>
+    <t>h_Lukow_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- PL27-400 (Siedlce, 8 km)</t>
+  </si>
+  <si>
+    <t>h_Miastko_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/178838661-220 (Koszalin, 40 km)</t>
+  </si>
+  <si>
+    <t>h_Mikolow_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/183945016-220 (Katowice, 19 km)</t>
+  </si>
+  <si>
+    <t>h_NowaSol_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/180535363-220 (Lubin, 33 km)</t>
+  </si>
+  <si>
+    <t>h_Nowogard_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- PL8-220 (Szczecin, 29 km)</t>
+  </si>
+  <si>
+    <t>h_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/101915790-220 (Olsztyn, 4 km)</t>
+  </si>
+  <si>
+    <t>h_Opole_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/255277953-400 (Opole, 10 km)</t>
+  </si>
+  <si>
+    <t>h_OstrowMazowiecka_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/121656686-220 (Lomza, 31 km)</t>
+  </si>
+  <si>
+    <t>h_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/254235846-400 (Ostrowiec Swietokrzyski, 4 km)</t>
+  </si>
+  <si>
+    <t>h_Otwock_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- PL26-400 (Warsaw, 53 km)</t>
+  </si>
+  <si>
+    <t>h_PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/293484891-400 (Piotrkow Trybunalski, 26 km)</t>
+  </si>
+  <si>
+    <t>h_Plock_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/658600169-400 (Plock, 4 km)</t>
+  </si>
+  <si>
+    <t>h_Police_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/39428977-220 (Szczecin, 27 km)</t>
+  </si>
+  <si>
+    <t>h_Pulawy_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/88544449-220 (Lublin, 46 km)</t>
+  </si>
+  <si>
+    <t>h_Radom_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/173582810-400 (Radom, 35 km)</t>
+  </si>
+  <si>
+    <t>h_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/171917072-400 (Czestochowa, 41 km)</t>
+  </si>
+  <si>
+    <t>h_Rumia_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/112614319-400 (Gdansk, 4 km)</t>
+  </si>
+  <si>
+    <t>h_Rybnik_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/139452056-400 (Gliwice, 20 km)</t>
+  </si>
+  <si>
+    <t>h_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/215282393-400 (Rzeszow, 20 km)</t>
+  </si>
+  <si>
+    <t>h_Sanok_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- PL62-400 (Rzeszow, 32 km)</t>
+  </si>
+  <si>
+    <t>h_SiemianowiceSlaski_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/40946790-220 (Katowice, 19 km)</t>
+  </si>
+  <si>
+    <t>h_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- relation/18085709-400 (Slupsk, 10 km)</t>
+  </si>
+  <si>
+    <t>h_Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/133537926-220 (Katowice, 22 km)</t>
+  </si>
+  <si>
+    <t>h_Staszow_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/199098053-400 (Mielec, 19 km)</t>
+  </si>
+  <si>
+    <t>h_Swarzedz_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/32036484-220 (Poznan, 11 km)</t>
+  </si>
+  <si>
+    <t>h_Swidnik_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/170249563-220 (Lublin, 6 km)</t>
+  </si>
+  <si>
+    <t>h_Tczew_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/385098015-400 (Gdansk, 45 km)</t>
+  </si>
+  <si>
+    <t>h_TomaszowLubelski_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/170368942-220 (Zamosc, 8 km)</t>
+  </si>
+  <si>
+    <t>h_Torun_POL</t>
   </si>
   <si>
     <t>heat at grid node -- PL15-400 (Bydgoszcz, 10 km)</t>
   </si>
   <si>
-    <t>h_Chelm_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/194903381-400 (Chelm, 4 km)</t>
-  </si>
-  <si>
-    <t>h_Czestochowa_POL</t>
+    <t>h_Ustka_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/255314292 (Slupsk, 10 km)</t>
+  </si>
+  <si>
+    <t>h_Wagrowiec_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/238640596-220 (Pila, 12 km)</t>
+  </si>
+  <si>
+    <t>h_Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/276291999-220 (Walbrzych, 11 km)</t>
+  </si>
+  <si>
+    <t>h_Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/245964556-220 (Wloclawek, 10 km)</t>
+  </si>
+  <si>
+    <t>h_Wloszczowa_POL</t>
   </si>
   <si>
     <t>heat at grid node -- way/216060722-220 (Czestochowa, 4 km)</t>
   </si>
   <si>
-    <t>h_Debica_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/198635989-220 (Rzeszow, 6 km)</t>
-  </si>
-  <si>
-    <t>h_Elk_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/303870256-400 (Elk, 8 km)</t>
-  </si>
-  <si>
-    <t>h_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/112614319-400 (Gdansk, 4 km)</t>
-  </si>
-  <si>
-    <t>h_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/86494356-400 (Gdansk, 54 km)</t>
-  </si>
-  <si>
-    <t>h_Gliwice_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/293489607-400 (Katowice, 21 km)</t>
-  </si>
-  <si>
-    <t>h_GorzowWielkopolski_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- PL18-400 (Gorzow Wielkopolski, 15 km)</t>
-  </si>
-  <si>
-    <t>h_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/170259740-220 (Elk, 6 km)</t>
-  </si>
-  <si>
-    <t>h_Grudziadz_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/46092396-400 (Grudziadz, 6 km)</t>
-  </si>
-  <si>
-    <t>h_Katowice_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/40946790-220 (Katowice, 19 km)</t>
-  </si>
-  <si>
-    <t>h_KedzierzynKozle_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/336990960-220 (Opole, 7 km)</t>
-  </si>
-  <si>
-    <t>h_Kielce_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/199098050-220 (Kielce, 16 km)</t>
-  </si>
-  <si>
-    <t>h_Konin_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/255284259-220 (Konin, 10 km)</t>
-  </si>
-  <si>
-    <t>h_Koszalin_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/178838661-220 (Koszalin, 40 km)</t>
-  </si>
-  <si>
-    <t>h_Krakow_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/87667718-220 (Krakow, 12 km)</t>
-  </si>
-  <si>
-    <t>h_Krosno_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/166838338-400 (Rzeszow, 40 km)</t>
-  </si>
-  <si>
-    <t>h_Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- PL7-400 (Grudziadz, 8 km)</t>
-  </si>
-  <si>
-    <t>h_Legnica_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- PL34-400 (Wroclaw, 43 km)</t>
-  </si>
-  <si>
-    <t>h_Lomza_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/121656686-220 (Lomza, 31 km)</t>
-  </si>
-  <si>
-    <t>h_Lubin_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/180535363-220 (Lubin, 33 km)</t>
-  </si>
-  <si>
-    <t>h_Mielec_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/199098053-220 (Mielec, 19 km)</t>
-  </si>
-  <si>
-    <t>h_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- PL36-400 (Wroclaw, 46 km)</t>
-  </si>
-  <si>
-    <t>h_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/101915790-220 (Olsztyn, 4 km)</t>
-  </si>
-  <si>
-    <t>h_Opole_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/255277953-400 (Opole, 10 km)</t>
-  </si>
-  <si>
-    <t>h_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/254235846-400 (Ostrowiec Swietokrzyski, 4 km)</t>
-  </si>
-  <si>
-    <t>h_PiotrkowTrybunalsk_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/170316833-220 (Piotrkow Trybunalski, 3 km)</t>
-  </si>
-  <si>
-    <t>h_Plock_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/658600169-400 (Plock, 4 km)</t>
-  </si>
-  <si>
-    <t>h_Police_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/165763717-220 (Szczecin, 15 km)</t>
-  </si>
-  <si>
-    <t>h_Poznan_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/32036484-220 (Poznan, 11 km)</t>
-  </si>
-  <si>
-    <t>h_Pulawy_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/88544449-220 (Lublin, 46 km)</t>
-  </si>
-  <si>
-    <t>h_Radomsko_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/171917072-400 (Czestochowa, 41 km)</t>
-  </si>
-  <si>
-    <t>h_Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/215282393-400 (Rzeszow, 20 km)</t>
-  </si>
-  <si>
-    <t>h_Slupsk_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- relation/18085709-400 (Slupsk, 10 km)</t>
-  </si>
-  <si>
-    <t>h_Sosnowiec_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/183945016-220 (Katowice, 19 km)</t>
-  </si>
-  <si>
-    <t>h_Swidnica_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- PL46-220 (Wroclaw, 58 km)</t>
-  </si>
-  <si>
-    <t>h_Szczecin_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/39428977-400 (Szczecin, 27 km)</t>
-  </si>
-  <si>
-    <t>h_Tarnow_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/191038569-220 (Tarnow, 5 km)</t>
-  </si>
-  <si>
-    <t>h_Ustka_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/255314292 (Slupsk, 10 km)</t>
-  </si>
-  <si>
-    <t>h_Warsaw_POL</t>
+    <t>h_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/79033485-400 (Wroclaw, 13 km)</t>
+  </si>
+  <si>
+    <t>h_Zabki_POL</t>
   </si>
   <si>
     <t>heat at grid node -- way/29115701-220 (Warsaw, 9 km)</t>
   </si>
   <si>
-    <t>h_Wloclawek_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/245964556-220 (Wloclawek, 10 km)</t>
-  </si>
-  <si>
-    <t>h_Wroclaw_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/79033485-400 (Wroclaw, 13 km)</t>
-  </si>
-  <si>
-    <t>h_Zamosc_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/173613665-220 (Zamosc, 3 km)</t>
-  </si>
-  <si>
     <t>h_ZielonaGora_POL</t>
   </si>
   <si>
     <t>heat at grid node -- way/158232924-220 (Zielona Gora, 15 km)</t>
   </si>
   <si>
-    <t>co2_Bydgoszcz_POL</t>
+    <t>h_Zory_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/139452056-220 (Gliwice, 20 km)</t>
+  </si>
+  <si>
+    <t>co2_Torun_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- PL15-400 (Bydgoszcz, 10 km)</t>
@@ -2002,22 +2272,34 @@
     <t>co2 captured at grid node -- PL18-400 (Gorzow Wielkopolski, 15 km)</t>
   </si>
   <si>
+    <t>co2_Otwock_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- PL26-400 (Warsaw, 53 km)</t>
+  </si>
+  <si>
+    <t>co2_Lukow_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- PL27-400 (Siedlce, 8 km)</t>
+  </si>
+  <si>
     <t>co2_Legnica_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- PL34-400 (Wroclaw, 43 km)</t>
   </si>
   <si>
-    <t>co2_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- PL36-400 (Wroclaw, 46 km)</t>
-  </si>
-  <si>
-    <t>co2_Swidnica_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- PL46-220 (Wroclaw, 58 km)</t>
+    <t>co2_Giszowiec_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- PL55-220 (Katowice, 8 km)</t>
+  </si>
+  <si>
+    <t>co2_Sanok_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- PL62-400 (Rzeszow, 32 km)</t>
   </si>
   <si>
     <t>co2_Kwidzyn_POL</t>
@@ -2026,6 +2308,12 @@
     <t>co2 captured at grid node -- PL7-400 (Grudziadz, 8 km)</t>
   </si>
   <si>
+    <t>co2_Nowogard_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- PL8-220 (Szczecin, 29 km)</t>
+  </si>
+  <si>
     <t>co2_Slupsk_POL</t>
   </si>
   <si>
@@ -2044,187 +2332,247 @@
     <t>co2 captured at grid node -- way/111615226-220 (Legnica, 74 km)</t>
   </si>
   <si>
-    <t>co2_Gdansk_POL</t>
+    <t>co2_Rumia_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/112614319-400 (Gdansk, 4 km)</t>
   </si>
   <si>
-    <t>co2_Lomza_POL</t>
+    <t>co2_OstrowMazowiecka_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/121656686-220 (Lomza, 31 km)</t>
   </si>
   <si>
+    <t>co2_Kolno_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/121656686-400 (Lomza, 31 km)</t>
+  </si>
+  <si>
+    <t>co2_Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/133537926-220 (Katowice, 22 km)</t>
+  </si>
+  <si>
+    <t>co2_Zory_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/139452056-220 (Gliwice, 20 km)</t>
+  </si>
+  <si>
+    <t>co2_Rybnik_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/139452056-400 (Gliwice, 20 km)</t>
+  </si>
+  <si>
     <t>co2_ZielonaGora_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/158232924-220 (Zielona Gora, 15 km)</t>
   </si>
   <si>
+    <t>co2_KamienPomorski_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/165763717-220 (Szczecin, 15 km)</t>
+  </si>
+  <si>
+    <t>co2_Swidnik_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/170249563-220 (Lublin, 6 km)</t>
+  </si>
+  <si>
+    <t>co2_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/170259740-220 (Elk, 6 km)</t>
+  </si>
+  <si>
+    <t>co2_TomaszowLubelski_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/170368942-220 (Zamosc, 8 km)</t>
+  </si>
+  <si>
+    <t>co2_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/171917072-400 (Czestochowa, 41 km)</t>
+  </si>
+  <si>
+    <t>co2_Radom_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/173582810-400 (Radom, 35 km)</t>
+  </si>
+  <si>
+    <t>co2_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/175406958-400 (Koszalin, 10 km)</t>
+  </si>
+  <si>
+    <t>co2_Miastko_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/178838661-220 (Koszalin, 40 km)</t>
+  </si>
+  <si>
+    <t>co2_NowaSol_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/180535363-220 (Lubin, 33 km)</t>
+  </si>
+  <si>
+    <t>co2_Mikolow_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/183945016-220 (Katowice, 19 km)</t>
+  </si>
+  <si>
+    <t>co2_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/185454704-220 (Gliwice, 28 km)</t>
+  </si>
+  <si>
+    <t>co2_Krakow_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/189501431-400 (Krakow, 13 km)</t>
+  </si>
+  <si>
+    <t>co2_Debica_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/191038569-220 (Tarnow, 5 km)</t>
+  </si>
+  <si>
+    <t>co2_Chelm_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/194903381-400 (Chelm, 4 km)</t>
+  </si>
+  <si>
+    <t>co2_Kielce_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/199098050-220 (Kielce, 16 km)</t>
+  </si>
+  <si>
+    <t>co2_Staszow_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/199098053-400 (Mielec, 19 km)</t>
+  </si>
+  <si>
+    <t>co2_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/215282393-400 (Rzeszow, 20 km)</t>
+  </si>
+  <si>
+    <t>co2_Wloszczowa_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/216060722-220 (Czestochowa, 4 km)</t>
+  </si>
+  <si>
+    <t>co2_Wagrowiec_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/238640596-220 (Pila, 12 km)</t>
+  </si>
+  <si>
+    <t>co2_Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/245964556-220 (Wloclawek, 10 km)</t>
+  </si>
+  <si>
+    <t>co2_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/254235846-400 (Ostrowiec Swietokrzyski, 4 km)</t>
+  </si>
+  <si>
+    <t>co2_Opole_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/255277953-400 (Opole, 10 km)</t>
+  </si>
+  <si>
+    <t>co2_Konin_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/255284259-220 (Konin, 10 km)</t>
+  </si>
+  <si>
+    <t>co2_Kalisz_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/255293403-400 (Kalisz, 21 km)</t>
+  </si>
+  <si>
+    <t>co2_Ustka_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/255314292 (Slupsk, 10 km)</t>
+  </si>
+  <si>
+    <t>co2_Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/276291999-220 (Walbrzych, 11 km)</t>
+  </si>
+  <si>
+    <t>co2_Zabki_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/29115701-220 (Warsaw, 9 km)</t>
+  </si>
+  <si>
+    <t>co2_PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/293484891-400 (Piotrkow Trybunalski, 26 km)</t>
+  </si>
+  <si>
+    <t>co2_Elk_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/303870256-400 (Elk, 8 km)</t>
+  </si>
+  <si>
+    <t>co2_Swarzedz_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/32036484-220 (Poznan, 11 km)</t>
+  </si>
+  <si>
+    <t>co2_Krapkowice_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/336990960-220 (Opole, 7 km)</t>
+  </si>
+  <si>
+    <t>co2_Tczew_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/385098015-400 (Gdansk, 45 km)</t>
+  </si>
+  <si>
     <t>co2_Police_POL</t>
   </si>
   <si>
-    <t>co2 captured at grid node -- way/165763717-220 (Szczecin, 15 km)</t>
-  </si>
-  <si>
-    <t>co2_Krosno_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/166838338-400 (Rzeszow, 40 km)</t>
-  </si>
-  <si>
-    <t>co2_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/170259740-220 (Elk, 6 km)</t>
-  </si>
-  <si>
-    <t>co2_PiotrkowTrybunalsk_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/170316833-220 (Piotrkow Trybunalski, 3 km)</t>
-  </si>
-  <si>
-    <t>co2_Radomsko_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/171917072-400 (Czestochowa, 41 km)</t>
-  </si>
-  <si>
-    <t>co2_Zamosc_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/173613665-220 (Zamosc, 3 km)</t>
-  </si>
-  <si>
-    <t>co2_Koszalin_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/178838661-220 (Koszalin, 40 km)</t>
-  </si>
-  <si>
-    <t>co2_Lubin_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/180535363-220 (Lubin, 33 km)</t>
-  </si>
-  <si>
-    <t>co2_Sosnowiec_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/183945016-220 (Katowice, 19 km)</t>
-  </si>
-  <si>
-    <t>co2_Tarnow_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/191038569-220 (Tarnow, 5 km)</t>
-  </si>
-  <si>
-    <t>co2_Chelm_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/194903381-400 (Chelm, 4 km)</t>
-  </si>
-  <si>
-    <t>co2_Debica_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/198635989-220 (Rzeszow, 6 km)</t>
-  </si>
-  <si>
-    <t>co2_Kielce_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/199098050-220 (Kielce, 16 km)</t>
-  </si>
-  <si>
-    <t>co2_Mielec_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/199098053-220 (Mielec, 19 km)</t>
-  </si>
-  <si>
-    <t>co2_Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/215282393-400 (Rzeszow, 20 km)</t>
-  </si>
-  <si>
-    <t>co2_Czestochowa_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/216060722-220 (Czestochowa, 4 km)</t>
-  </si>
-  <si>
-    <t>co2_Wloclawek_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/245964556-220 (Wloclawek, 10 km)</t>
-  </si>
-  <si>
-    <t>co2_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/254235846-400 (Ostrowiec Swietokrzyski, 4 km)</t>
-  </si>
-  <si>
-    <t>co2_Opole_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/255277953-400 (Opole, 10 km)</t>
-  </si>
-  <si>
-    <t>co2_Konin_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/255284259-220 (Konin, 10 km)</t>
-  </si>
-  <si>
-    <t>co2_Ustka_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/255314292 (Slupsk, 10 km)</t>
-  </si>
-  <si>
-    <t>co2_Warsaw_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/29115701-220 (Warsaw, 9 km)</t>
-  </si>
-  <si>
-    <t>co2_Gliwice_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/293489607-400 (Katowice, 21 km)</t>
-  </si>
-  <si>
-    <t>co2_Elk_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/303870256-400 (Elk, 8 km)</t>
-  </si>
-  <si>
-    <t>co2_Poznan_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/32036484-220 (Poznan, 11 km)</t>
-  </si>
-  <si>
-    <t>co2_KedzierzynKozle_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/336990960-220 (Opole, 7 km)</t>
-  </si>
-  <si>
-    <t>co2_Szczecin_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/39428977-400 (Szczecin, 27 km)</t>
-  </si>
-  <si>
-    <t>co2_Katowice_POL</t>
+    <t>co2 captured at grid node -- way/39428977-220 (Szczecin, 27 km)</t>
+  </si>
+  <si>
+    <t>co2_SiemianowiceSlaski_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/40946790-220 (Katowice, 19 km)</t>
@@ -2260,148 +2608,10 @@
     <t>co2 captured at grid node -- way/86494356-400 (Gdansk, 54 km)</t>
   </si>
   <si>
-    <t>co2_Krakow_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/87667718-220 (Krakow, 12 km)</t>
-  </si>
-  <si>
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/88544449-220 (Lublin, 46 km)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11072_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11072.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11074_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11074.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11075_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11075.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11076_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11076.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11077_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11077.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11078_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11078.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11079_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11079.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11080_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11080.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11081_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11081.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11082_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11082.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11083_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11083.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11084_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11084.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11085_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11085.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11086_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11086.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11087_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11087.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11088_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11088.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11089_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11089.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11090_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11090.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11091_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11091.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11092_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11092.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11093_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11093.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11094_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11094.0 (OGCI/catalogue)</t>
   </si>
   <si>
     <t>co2s_T1_POL</t>
@@ -4482,9 +4692,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4522,7 +4732,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4628,7 +4838,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4770,7 +4980,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4779,15 +4989,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H5"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="16.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.06640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.9296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.53125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8">
@@ -4844,13 +5054,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0F7B196-FB77-4156-A72F-6197B3013C84}">
-  <dimension ref="B3:H82"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE1DB511-6C08-417A-B3CF-DA0D0FA32E5C}">
+  <dimension ref="B3:H72"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="3" spans="2:8">
       <c r="B3" t="s">
-        <v>452</v>
+        <v>494</v>
       </c>
     </row>
     <row r="4" spans="2:8">
@@ -4881,19 +5091,19 @@
         <v>192</v>
       </c>
       <c r="C5" t="s">
-        <v>646</v>
+        <v>736</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>647</v>
+        <v>737</v>
       </c>
       <c r="F5" t="s">
         <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H5" t="s">
         <v>195</v>
@@ -4904,19 +5114,19 @@
         <v>192</v>
       </c>
       <c r="C6" t="s">
-        <v>649</v>
+        <v>739</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>650</v>
+        <v>740</v>
       </c>
       <c r="F6" t="s">
         <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H6" t="s">
         <v>195</v>
@@ -4927,19 +5137,19 @@
         <v>192</v>
       </c>
       <c r="C7" t="s">
-        <v>651</v>
+        <v>741</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>652</v>
+        <v>742</v>
       </c>
       <c r="F7" t="s">
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H7" t="s">
         <v>195</v>
@@ -4950,19 +5160,19 @@
         <v>192</v>
       </c>
       <c r="C8" t="s">
-        <v>653</v>
+        <v>743</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>654</v>
+        <v>744</v>
       </c>
       <c r="F8" t="s">
         <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H8" t="s">
         <v>195</v>
@@ -4973,19 +5183,19 @@
         <v>192</v>
       </c>
       <c r="C9" t="s">
-        <v>655</v>
+        <v>745</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>656</v>
+        <v>746</v>
       </c>
       <c r="F9" t="s">
         <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H9" t="s">
         <v>195</v>
@@ -4996,19 +5206,19 @@
         <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>657</v>
+        <v>747</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>658</v>
+        <v>748</v>
       </c>
       <c r="F10" t="s">
         <v>26</v>
       </c>
       <c r="G10" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H10" t="s">
         <v>195</v>
@@ -5019,19 +5229,19 @@
         <v>192</v>
       </c>
       <c r="C11" t="s">
-        <v>659</v>
+        <v>749</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>660</v>
+        <v>750</v>
       </c>
       <c r="F11" t="s">
         <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H11" t="s">
         <v>195</v>
@@ -5042,19 +5252,19 @@
         <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>661</v>
+        <v>751</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>662</v>
+        <v>752</v>
       </c>
       <c r="F12" t="s">
         <v>26</v>
       </c>
       <c r="G12" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H12" t="s">
         <v>195</v>
@@ -5065,19 +5275,19 @@
         <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>663</v>
+        <v>753</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>664</v>
+        <v>754</v>
       </c>
       <c r="F13" t="s">
         <v>26</v>
       </c>
       <c r="G13" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H13" t="s">
         <v>195</v>
@@ -5088,19 +5298,19 @@
         <v>192</v>
       </c>
       <c r="C14" t="s">
-        <v>665</v>
+        <v>755</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>666</v>
+        <v>756</v>
       </c>
       <c r="F14" t="s">
         <v>26</v>
       </c>
       <c r="G14" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H14" t="s">
         <v>195</v>
@@ -5111,19 +5321,19 @@
         <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>667</v>
+        <v>757</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>668</v>
+        <v>758</v>
       </c>
       <c r="F15" t="s">
         <v>26</v>
       </c>
       <c r="G15" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H15" t="s">
         <v>195</v>
@@ -5134,19 +5344,19 @@
         <v>192</v>
       </c>
       <c r="C16" t="s">
-        <v>669</v>
+        <v>759</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>670</v>
+        <v>760</v>
       </c>
       <c r="F16" t="s">
         <v>26</v>
       </c>
       <c r="G16" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H16" t="s">
         <v>195</v>
@@ -5157,19 +5367,19 @@
         <v>192</v>
       </c>
       <c r="C17" t="s">
-        <v>671</v>
+        <v>761</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>672</v>
+        <v>762</v>
       </c>
       <c r="F17" t="s">
         <v>26</v>
       </c>
       <c r="G17" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H17" t="s">
         <v>195</v>
@@ -5180,19 +5390,19 @@
         <v>192</v>
       </c>
       <c r="C18" t="s">
-        <v>673</v>
+        <v>763</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>674</v>
+        <v>764</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
       </c>
       <c r="G18" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H18" t="s">
         <v>195</v>
@@ -5203,19 +5413,19 @@
         <v>192</v>
       </c>
       <c r="C19" t="s">
-        <v>675</v>
+        <v>765</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>676</v>
+        <v>766</v>
       </c>
       <c r="F19" t="s">
         <v>26</v>
       </c>
       <c r="G19" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H19" t="s">
         <v>195</v>
@@ -5226,19 +5436,19 @@
         <v>192</v>
       </c>
       <c r="C20" t="s">
-        <v>677</v>
+        <v>767</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>678</v>
+        <v>768</v>
       </c>
       <c r="F20" t="s">
         <v>26</v>
       </c>
       <c r="G20" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H20" t="s">
         <v>195</v>
@@ -5249,19 +5459,19 @@
         <v>192</v>
       </c>
       <c r="C21" t="s">
-        <v>679</v>
+        <v>769</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>680</v>
+        <v>770</v>
       </c>
       <c r="F21" t="s">
         <v>26</v>
       </c>
       <c r="G21" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H21" t="s">
         <v>195</v>
@@ -5272,19 +5482,19 @@
         <v>192</v>
       </c>
       <c r="C22" t="s">
-        <v>681</v>
+        <v>771</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>682</v>
+        <v>772</v>
       </c>
       <c r="F22" t="s">
         <v>26</v>
       </c>
       <c r="G22" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H22" t="s">
         <v>195</v>
@@ -5295,19 +5505,19 @@
         <v>192</v>
       </c>
       <c r="C23" t="s">
-        <v>683</v>
+        <v>773</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>684</v>
+        <v>774</v>
       </c>
       <c r="F23" t="s">
         <v>26</v>
       </c>
       <c r="G23" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H23" t="s">
         <v>195</v>
@@ -5318,19 +5528,19 @@
         <v>192</v>
       </c>
       <c r="C24" t="s">
-        <v>685</v>
+        <v>775</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>686</v>
+        <v>776</v>
       </c>
       <c r="F24" t="s">
         <v>26</v>
       </c>
       <c r="G24" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H24" t="s">
         <v>195</v>
@@ -5341,19 +5551,19 @@
         <v>192</v>
       </c>
       <c r="C25" t="s">
-        <v>687</v>
+        <v>777</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>688</v>
+        <v>778</v>
       </c>
       <c r="F25" t="s">
         <v>26</v>
       </c>
       <c r="G25" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H25" t="s">
         <v>195</v>
@@ -5364,19 +5574,19 @@
         <v>192</v>
       </c>
       <c r="C26" t="s">
-        <v>689</v>
+        <v>779</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>690</v>
+        <v>780</v>
       </c>
       <c r="F26" t="s">
         <v>26</v>
       </c>
       <c r="G26" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H26" t="s">
         <v>195</v>
@@ -5387,19 +5597,19 @@
         <v>192</v>
       </c>
       <c r="C27" t="s">
-        <v>691</v>
+        <v>781</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>692</v>
+        <v>782</v>
       </c>
       <c r="F27" t="s">
         <v>26</v>
       </c>
       <c r="G27" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H27" t="s">
         <v>195</v>
@@ -5410,19 +5620,19 @@
         <v>192</v>
       </c>
       <c r="C28" t="s">
-        <v>693</v>
+        <v>783</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>694</v>
+        <v>784</v>
       </c>
       <c r="F28" t="s">
         <v>26</v>
       </c>
       <c r="G28" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H28" t="s">
         <v>195</v>
@@ -5433,19 +5643,19 @@
         <v>192</v>
       </c>
       <c r="C29" t="s">
-        <v>695</v>
+        <v>785</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>696</v>
+        <v>786</v>
       </c>
       <c r="F29" t="s">
         <v>26</v>
       </c>
       <c r="G29" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H29" t="s">
         <v>195</v>
@@ -5456,19 +5666,19 @@
         <v>192</v>
       </c>
       <c r="C30" t="s">
-        <v>697</v>
+        <v>787</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>698</v>
+        <v>788</v>
       </c>
       <c r="F30" t="s">
         <v>26</v>
       </c>
       <c r="G30" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H30" t="s">
         <v>195</v>
@@ -5479,19 +5689,19 @@
         <v>192</v>
       </c>
       <c r="C31" t="s">
-        <v>699</v>
+        <v>789</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>700</v>
+        <v>790</v>
       </c>
       <c r="F31" t="s">
         <v>26</v>
       </c>
       <c r="G31" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H31" t="s">
         <v>195</v>
@@ -5502,19 +5712,19 @@
         <v>192</v>
       </c>
       <c r="C32" t="s">
-        <v>701</v>
+        <v>791</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>702</v>
+        <v>792</v>
       </c>
       <c r="F32" t="s">
         <v>26</v>
       </c>
       <c r="G32" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H32" t="s">
         <v>195</v>
@@ -5525,19 +5735,19 @@
         <v>192</v>
       </c>
       <c r="C33" t="s">
-        <v>703</v>
+        <v>793</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>704</v>
+        <v>794</v>
       </c>
       <c r="F33" t="s">
         <v>26</v>
       </c>
       <c r="G33" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H33" t="s">
         <v>195</v>
@@ -5548,19 +5758,19 @@
         <v>192</v>
       </c>
       <c r="C34" t="s">
-        <v>705</v>
+        <v>795</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>706</v>
+        <v>796</v>
       </c>
       <c r="F34" t="s">
         <v>26</v>
       </c>
       <c r="G34" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H34" t="s">
         <v>195</v>
@@ -5571,19 +5781,19 @@
         <v>192</v>
       </c>
       <c r="C35" t="s">
-        <v>707</v>
+        <v>797</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>708</v>
+        <v>798</v>
       </c>
       <c r="F35" t="s">
         <v>26</v>
       </c>
       <c r="G35" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H35" t="s">
         <v>195</v>
@@ -5594,19 +5804,19 @@
         <v>192</v>
       </c>
       <c r="C36" t="s">
-        <v>709</v>
+        <v>799</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>710</v>
+        <v>800</v>
       </c>
       <c r="F36" t="s">
         <v>26</v>
       </c>
       <c r="G36" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H36" t="s">
         <v>195</v>
@@ -5617,19 +5827,19 @@
         <v>192</v>
       </c>
       <c r="C37" t="s">
-        <v>711</v>
+        <v>801</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>712</v>
+        <v>802</v>
       </c>
       <c r="F37" t="s">
         <v>26</v>
       </c>
       <c r="G37" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H37" t="s">
         <v>195</v>
@@ -5640,19 +5850,19 @@
         <v>192</v>
       </c>
       <c r="C38" t="s">
-        <v>713</v>
+        <v>803</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>714</v>
+        <v>804</v>
       </c>
       <c r="F38" t="s">
         <v>26</v>
       </c>
       <c r="G38" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H38" t="s">
         <v>195</v>
@@ -5663,19 +5873,19 @@
         <v>192</v>
       </c>
       <c r="C39" t="s">
-        <v>715</v>
+        <v>805</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>716</v>
+        <v>806</v>
       </c>
       <c r="F39" t="s">
         <v>26</v>
       </c>
       <c r="G39" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H39" t="s">
         <v>195</v>
@@ -5686,19 +5896,19 @@
         <v>192</v>
       </c>
       <c r="C40" t="s">
-        <v>717</v>
+        <v>807</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>718</v>
+        <v>808</v>
       </c>
       <c r="F40" t="s">
         <v>26</v>
       </c>
       <c r="G40" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H40" t="s">
         <v>195</v>
@@ -5709,19 +5919,19 @@
         <v>192</v>
       </c>
       <c r="C41" t="s">
-        <v>719</v>
+        <v>809</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>720</v>
+        <v>810</v>
       </c>
       <c r="F41" t="s">
         <v>26</v>
       </c>
       <c r="G41" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H41" t="s">
         <v>195</v>
@@ -5732,19 +5942,19 @@
         <v>192</v>
       </c>
       <c r="C42" t="s">
-        <v>721</v>
+        <v>811</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>722</v>
+        <v>812</v>
       </c>
       <c r="F42" t="s">
         <v>26</v>
       </c>
       <c r="G42" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H42" t="s">
         <v>195</v>
@@ -5755,19 +5965,19 @@
         <v>192</v>
       </c>
       <c r="C43" t="s">
-        <v>723</v>
+        <v>813</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>724</v>
+        <v>814</v>
       </c>
       <c r="F43" t="s">
         <v>26</v>
       </c>
       <c r="G43" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H43" t="s">
         <v>195</v>
@@ -5778,19 +5988,19 @@
         <v>192</v>
       </c>
       <c r="C44" t="s">
-        <v>725</v>
+        <v>815</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>726</v>
+        <v>816</v>
       </c>
       <c r="F44" t="s">
         <v>26</v>
       </c>
       <c r="G44" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H44" t="s">
         <v>195</v>
@@ -5801,19 +6011,19 @@
         <v>192</v>
       </c>
       <c r="C45" t="s">
-        <v>727</v>
+        <v>817</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>728</v>
+        <v>818</v>
       </c>
       <c r="F45" t="s">
         <v>26</v>
       </c>
       <c r="G45" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H45" t="s">
         <v>195</v>
@@ -5824,19 +6034,19 @@
         <v>192</v>
       </c>
       <c r="C46" t="s">
-        <v>729</v>
+        <v>819</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>730</v>
+        <v>820</v>
       </c>
       <c r="F46" t="s">
         <v>26</v>
       </c>
       <c r="G46" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H46" t="s">
         <v>195</v>
@@ -5847,19 +6057,19 @@
         <v>192</v>
       </c>
       <c r="C47" t="s">
-        <v>731</v>
+        <v>821</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>732</v>
+        <v>822</v>
       </c>
       <c r="F47" t="s">
         <v>26</v>
       </c>
       <c r="G47" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H47" t="s">
         <v>195</v>
@@ -5870,19 +6080,19 @@
         <v>192</v>
       </c>
       <c r="C48" t="s">
-        <v>733</v>
+        <v>823</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>734</v>
+        <v>824</v>
       </c>
       <c r="F48" t="s">
         <v>26</v>
       </c>
       <c r="G48" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H48" t="s">
         <v>195</v>
@@ -5893,19 +6103,19 @@
         <v>192</v>
       </c>
       <c r="C49" t="s">
-        <v>735</v>
+        <v>825</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>736</v>
+        <v>826</v>
       </c>
       <c r="F49" t="s">
         <v>26</v>
       </c>
       <c r="G49" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H49" t="s">
         <v>195</v>
@@ -5916,19 +6126,19 @@
         <v>192</v>
       </c>
       <c r="C50" t="s">
-        <v>737</v>
+        <v>827</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>738</v>
+        <v>828</v>
       </c>
       <c r="F50" t="s">
         <v>26</v>
       </c>
       <c r="G50" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H50" t="s">
         <v>195</v>
@@ -5939,19 +6149,19 @@
         <v>192</v>
       </c>
       <c r="C51" t="s">
-        <v>739</v>
+        <v>829</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>740</v>
+        <v>830</v>
       </c>
       <c r="F51" t="s">
         <v>26</v>
       </c>
       <c r="G51" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H51" t="s">
         <v>195</v>
@@ -5962,19 +6172,19 @@
         <v>192</v>
       </c>
       <c r="C52" t="s">
-        <v>741</v>
+        <v>831</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>742</v>
+        <v>832</v>
       </c>
       <c r="F52" t="s">
         <v>26</v>
       </c>
       <c r="G52" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H52" t="s">
         <v>195</v>
@@ -5985,19 +6195,19 @@
         <v>192</v>
       </c>
       <c r="C53" t="s">
-        <v>743</v>
+        <v>833</v>
       </c>
       <c r="D53" t="s">
         <v>243</v>
       </c>
       <c r="E53" t="s">
-        <v>744</v>
+        <v>834</v>
       </c>
       <c r="F53" t="s">
         <v>26</v>
       </c>
       <c r="G53" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H53" t="s">
         <v>195</v>
@@ -6008,19 +6218,19 @@
         <v>192</v>
       </c>
       <c r="C54" t="s">
-        <v>745</v>
+        <v>835</v>
       </c>
       <c r="D54" t="s">
         <v>243</v>
       </c>
       <c r="E54" t="s">
-        <v>746</v>
+        <v>836</v>
       </c>
       <c r="F54" t="s">
         <v>26</v>
       </c>
       <c r="G54" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H54" t="s">
         <v>195</v>
@@ -6031,19 +6241,19 @@
         <v>192</v>
       </c>
       <c r="C55" t="s">
-        <v>747</v>
+        <v>837</v>
       </c>
       <c r="D55" t="s">
         <v>243</v>
       </c>
       <c r="E55" t="s">
-        <v>748</v>
+        <v>838</v>
       </c>
       <c r="F55" t="s">
         <v>26</v>
       </c>
       <c r="G55" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H55" t="s">
         <v>195</v>
@@ -6054,19 +6264,19 @@
         <v>192</v>
       </c>
       <c r="C56" t="s">
-        <v>749</v>
+        <v>839</v>
       </c>
       <c r="D56" t="s">
         <v>243</v>
       </c>
       <c r="E56" t="s">
-        <v>750</v>
+        <v>840</v>
       </c>
       <c r="F56" t="s">
         <v>26</v>
       </c>
       <c r="G56" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H56" t="s">
         <v>195</v>
@@ -6077,19 +6287,19 @@
         <v>192</v>
       </c>
       <c r="C57" t="s">
-        <v>751</v>
+        <v>841</v>
       </c>
       <c r="D57" t="s">
         <v>243</v>
       </c>
       <c r="E57" t="s">
-        <v>752</v>
+        <v>842</v>
       </c>
       <c r="F57" t="s">
         <v>26</v>
       </c>
       <c r="G57" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H57" t="s">
         <v>195</v>
@@ -6100,19 +6310,19 @@
         <v>192</v>
       </c>
       <c r="C58" t="s">
-        <v>753</v>
+        <v>843</v>
       </c>
       <c r="D58" t="s">
         <v>243</v>
       </c>
       <c r="E58" t="s">
-        <v>754</v>
+        <v>844</v>
       </c>
       <c r="F58" t="s">
         <v>26</v>
       </c>
       <c r="G58" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H58" t="s">
         <v>195</v>
@@ -6123,19 +6333,19 @@
         <v>192</v>
       </c>
       <c r="C59" t="s">
-        <v>755</v>
+        <v>845</v>
       </c>
       <c r="D59" t="s">
         <v>243</v>
       </c>
       <c r="E59" t="s">
-        <v>756</v>
+        <v>846</v>
       </c>
       <c r="F59" t="s">
         <v>26</v>
       </c>
       <c r="G59" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H59" t="s">
         <v>195</v>
@@ -6146,19 +6356,19 @@
         <v>192</v>
       </c>
       <c r="C60" t="s">
-        <v>757</v>
+        <v>847</v>
       </c>
       <c r="D60" t="s">
         <v>243</v>
       </c>
       <c r="E60" t="s">
-        <v>758</v>
+        <v>848</v>
       </c>
       <c r="F60" t="s">
         <v>26</v>
       </c>
       <c r="G60" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H60" t="s">
         <v>195</v>
@@ -6169,19 +6379,19 @@
         <v>192</v>
       </c>
       <c r="C61" t="s">
-        <v>759</v>
+        <v>849</v>
       </c>
       <c r="D61" t="s">
         <v>243</v>
       </c>
       <c r="E61" t="s">
-        <v>760</v>
+        <v>850</v>
       </c>
       <c r="F61" t="s">
         <v>26</v>
       </c>
       <c r="G61" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H61" t="s">
         <v>195</v>
@@ -6192,19 +6402,19 @@
         <v>192</v>
       </c>
       <c r="C62" t="s">
-        <v>761</v>
+        <v>851</v>
       </c>
       <c r="D62" t="s">
         <v>243</v>
       </c>
       <c r="E62" t="s">
-        <v>762</v>
+        <v>852</v>
       </c>
       <c r="F62" t="s">
         <v>26</v>
       </c>
       <c r="G62" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H62" t="s">
         <v>195</v>
@@ -6215,19 +6425,19 @@
         <v>192</v>
       </c>
       <c r="C63" t="s">
-        <v>763</v>
+        <v>853</v>
       </c>
       <c r="D63" t="s">
         <v>243</v>
       </c>
       <c r="E63" t="s">
-        <v>764</v>
+        <v>854</v>
       </c>
       <c r="F63" t="s">
         <v>26</v>
       </c>
       <c r="G63" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H63" t="s">
         <v>195</v>
@@ -6238,19 +6448,19 @@
         <v>192</v>
       </c>
       <c r="C64" t="s">
-        <v>765</v>
+        <v>855</v>
       </c>
       <c r="D64" t="s">
         <v>243</v>
       </c>
       <c r="E64" t="s">
-        <v>766</v>
+        <v>856</v>
       </c>
       <c r="F64" t="s">
         <v>26</v>
       </c>
       <c r="G64" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H64" t="s">
         <v>195</v>
@@ -6261,19 +6471,19 @@
         <v>192</v>
       </c>
       <c r="C65" t="s">
-        <v>767</v>
+        <v>857</v>
       </c>
       <c r="D65" t="s">
         <v>243</v>
       </c>
       <c r="E65" t="s">
-        <v>768</v>
+        <v>858</v>
       </c>
       <c r="F65" t="s">
         <v>26</v>
       </c>
       <c r="G65" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H65" t="s">
         <v>195</v>
@@ -6284,19 +6494,19 @@
         <v>192</v>
       </c>
       <c r="C66" t="s">
-        <v>769</v>
+        <v>859</v>
       </c>
       <c r="D66" t="s">
         <v>243</v>
       </c>
       <c r="E66" t="s">
-        <v>770</v>
+        <v>860</v>
       </c>
       <c r="F66" t="s">
         <v>26</v>
       </c>
       <c r="G66" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H66" t="s">
         <v>195</v>
@@ -6307,19 +6517,19 @@
         <v>192</v>
       </c>
       <c r="C67" t="s">
-        <v>771</v>
+        <v>861</v>
       </c>
       <c r="D67" t="s">
         <v>243</v>
       </c>
       <c r="E67" t="s">
-        <v>772</v>
+        <v>862</v>
       </c>
       <c r="F67" t="s">
         <v>26</v>
       </c>
       <c r="G67" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H67" t="s">
         <v>195</v>
@@ -6330,19 +6540,19 @@
         <v>192</v>
       </c>
       <c r="C68" t="s">
-        <v>773</v>
+        <v>863</v>
       </c>
       <c r="D68" t="s">
         <v>243</v>
       </c>
       <c r="E68" t="s">
-        <v>774</v>
+        <v>864</v>
       </c>
       <c r="F68" t="s">
         <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H68" t="s">
         <v>195</v>
@@ -6353,19 +6563,19 @@
         <v>192</v>
       </c>
       <c r="C69" t="s">
-        <v>775</v>
+        <v>865</v>
       </c>
       <c r="D69" t="s">
         <v>243</v>
       </c>
       <c r="E69" t="s">
-        <v>776</v>
+        <v>866</v>
       </c>
       <c r="F69" t="s">
         <v>26</v>
       </c>
       <c r="G69" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H69" t="s">
         <v>195</v>
@@ -6376,19 +6586,19 @@
         <v>192</v>
       </c>
       <c r="C70" t="s">
-        <v>777</v>
+        <v>867</v>
       </c>
       <c r="D70" t="s">
         <v>243</v>
       </c>
       <c r="E70" t="s">
-        <v>778</v>
+        <v>868</v>
       </c>
       <c r="F70" t="s">
         <v>26</v>
       </c>
       <c r="G70" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H70" t="s">
         <v>195</v>
@@ -6399,19 +6609,19 @@
         <v>192</v>
       </c>
       <c r="C71" t="s">
-        <v>779</v>
+        <v>869</v>
       </c>
       <c r="D71" t="s">
         <v>243</v>
       </c>
       <c r="E71" t="s">
-        <v>780</v>
+        <v>870</v>
       </c>
       <c r="F71" t="s">
         <v>26</v>
       </c>
       <c r="G71" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H71" t="s">
         <v>195</v>
@@ -6422,251 +6632,21 @@
         <v>192</v>
       </c>
       <c r="C72" t="s">
-        <v>781</v>
+        <v>871</v>
       </c>
       <c r="D72" t="s">
         <v>243</v>
       </c>
       <c r="E72" t="s">
-        <v>782</v>
+        <v>872</v>
       </c>
       <c r="F72" t="s">
         <v>26</v>
       </c>
       <c r="G72" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="H72" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="73" spans="2:8">
-      <c r="B73" t="s">
-        <v>192</v>
-      </c>
-      <c r="C73" t="s">
-        <v>783</v>
-      </c>
-      <c r="D73" t="s">
-        <v>243</v>
-      </c>
-      <c r="E73" t="s">
-        <v>784</v>
-      </c>
-      <c r="F73" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" t="s">
-        <v>648</v>
-      </c>
-      <c r="H73" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="74" spans="2:8">
-      <c r="B74" t="s">
-        <v>192</v>
-      </c>
-      <c r="C74" t="s">
-        <v>785</v>
-      </c>
-      <c r="D74" t="s">
-        <v>243</v>
-      </c>
-      <c r="E74" t="s">
-        <v>786</v>
-      </c>
-      <c r="F74" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" t="s">
-        <v>648</v>
-      </c>
-      <c r="H74" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="75" spans="2:8">
-      <c r="B75" t="s">
-        <v>192</v>
-      </c>
-      <c r="C75" t="s">
-        <v>787</v>
-      </c>
-      <c r="D75" t="s">
-        <v>243</v>
-      </c>
-      <c r="E75" t="s">
-        <v>788</v>
-      </c>
-      <c r="F75" t="s">
-        <v>26</v>
-      </c>
-      <c r="G75" t="s">
-        <v>648</v>
-      </c>
-      <c r="H75" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="76" spans="2:8">
-      <c r="B76" t="s">
-        <v>192</v>
-      </c>
-      <c r="C76" t="s">
-        <v>789</v>
-      </c>
-      <c r="D76" t="s">
-        <v>243</v>
-      </c>
-      <c r="E76" t="s">
-        <v>790</v>
-      </c>
-      <c r="F76" t="s">
-        <v>26</v>
-      </c>
-      <c r="G76" t="s">
-        <v>648</v>
-      </c>
-      <c r="H76" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="77" spans="2:8">
-      <c r="B77" t="s">
-        <v>192</v>
-      </c>
-      <c r="C77" t="s">
-        <v>791</v>
-      </c>
-      <c r="D77" t="s">
-        <v>243</v>
-      </c>
-      <c r="E77" t="s">
-        <v>792</v>
-      </c>
-      <c r="F77" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" t="s">
-        <v>648</v>
-      </c>
-      <c r="H77" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="78" spans="2:8">
-      <c r="B78" t="s">
-        <v>192</v>
-      </c>
-      <c r="C78" t="s">
-        <v>793</v>
-      </c>
-      <c r="D78" t="s">
-        <v>243</v>
-      </c>
-      <c r="E78" t="s">
-        <v>794</v>
-      </c>
-      <c r="F78" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" t="s">
-        <v>648</v>
-      </c>
-      <c r="H78" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="79" spans="2:8">
-      <c r="B79" t="s">
-        <v>192</v>
-      </c>
-      <c r="C79" t="s">
-        <v>795</v>
-      </c>
-      <c r="D79" t="s">
-        <v>243</v>
-      </c>
-      <c r="E79" t="s">
-        <v>796</v>
-      </c>
-      <c r="F79" t="s">
-        <v>26</v>
-      </c>
-      <c r="G79" t="s">
-        <v>648</v>
-      </c>
-      <c r="H79" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="80" spans="2:8">
-      <c r="B80" t="s">
-        <v>192</v>
-      </c>
-      <c r="C80" t="s">
-        <v>797</v>
-      </c>
-      <c r="D80" t="s">
-        <v>243</v>
-      </c>
-      <c r="E80" t="s">
-        <v>798</v>
-      </c>
-      <c r="F80" t="s">
-        <v>26</v>
-      </c>
-      <c r="G80" t="s">
-        <v>648</v>
-      </c>
-      <c r="H80" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8">
-      <c r="B81" t="s">
-        <v>192</v>
-      </c>
-      <c r="C81" t="s">
-        <v>799</v>
-      </c>
-      <c r="D81" t="s">
-        <v>243</v>
-      </c>
-      <c r="E81" t="s">
-        <v>800</v>
-      </c>
-      <c r="F81" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" t="s">
-        <v>648</v>
-      </c>
-      <c r="H81" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="82" spans="2:8">
-      <c r="B82" t="s">
-        <v>192</v>
-      </c>
-      <c r="C82" t="s">
-        <v>801</v>
-      </c>
-      <c r="D82" t="s">
-        <v>243</v>
-      </c>
-      <c r="E82" t="s">
-        <v>802</v>
-      </c>
-      <c r="F82" t="s">
-        <v>26</v>
-      </c>
-      <c r="G82" t="s">
-        <v>648</v>
-      </c>
-      <c r="H82" t="s">
         <v>195</v>
       </c>
     </row>
@@ -6676,13 +6656,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88C1B4F-C4AD-47BE-9F7D-63B8ADA6B425}">
-  <dimension ref="B3:I52"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8675A9A-2614-46E3-A9BA-5DAD67EC3D7E}">
+  <dimension ref="B3:I64"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>452</v>
+        <v>494</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -6716,13 +6696,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>550</v>
+        <v>616</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>551</v>
+        <v>617</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -6731,7 +6711,7 @@
         <v>232</v>
       </c>
       <c r="H5" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I5" t="s">
         <v>247</v>
@@ -6742,13 +6722,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>552</v>
+        <v>618</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>553</v>
+        <v>619</v>
       </c>
       <c r="F6" t="s">
         <v>233</v>
@@ -6757,7 +6737,7 @@
         <v>232</v>
       </c>
       <c r="H6" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I6" t="s">
         <v>247</v>
@@ -6768,13 +6748,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>554</v>
+        <v>620</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>555</v>
+        <v>621</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -6783,7 +6763,7 @@
         <v>232</v>
       </c>
       <c r="H7" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I7" t="s">
         <v>247</v>
@@ -6794,13 +6774,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>556</v>
+        <v>622</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>557</v>
+        <v>623</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -6809,7 +6789,7 @@
         <v>232</v>
       </c>
       <c r="H8" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I8" t="s">
         <v>247</v>
@@ -6820,13 +6800,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>558</v>
+        <v>624</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>559</v>
+        <v>625</v>
       </c>
       <c r="F9" t="s">
         <v>233</v>
@@ -6835,7 +6815,7 @@
         <v>232</v>
       </c>
       <c r="H9" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I9" t="s">
         <v>247</v>
@@ -6846,13 +6826,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>560</v>
+        <v>626</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>561</v>
+        <v>627</v>
       </c>
       <c r="F10" t="s">
         <v>233</v>
@@ -6861,7 +6841,7 @@
         <v>232</v>
       </c>
       <c r="H10" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I10" t="s">
         <v>247</v>
@@ -6872,13 +6852,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>562</v>
+        <v>628</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>563</v>
+        <v>629</v>
       </c>
       <c r="F11" t="s">
         <v>233</v>
@@ -6887,7 +6867,7 @@
         <v>232</v>
       </c>
       <c r="H11" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I11" t="s">
         <v>247</v>
@@ -6898,13 +6878,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>564</v>
+        <v>630</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>565</v>
+        <v>631</v>
       </c>
       <c r="F12" t="s">
         <v>233</v>
@@ -6913,7 +6893,7 @@
         <v>232</v>
       </c>
       <c r="H12" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I12" t="s">
         <v>247</v>
@@ -6924,13 +6904,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>566</v>
+        <v>632</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>567</v>
+        <v>633</v>
       </c>
       <c r="F13" t="s">
         <v>233</v>
@@ -6939,7 +6919,7 @@
         <v>232</v>
       </c>
       <c r="H13" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I13" t="s">
         <v>247</v>
@@ -6950,13 +6930,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>568</v>
+        <v>634</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>569</v>
+        <v>635</v>
       </c>
       <c r="F14" t="s">
         <v>233</v>
@@ -6965,7 +6945,7 @@
         <v>232</v>
       </c>
       <c r="H14" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I14" t="s">
         <v>247</v>
@@ -6976,13 +6956,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>570</v>
+        <v>636</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>571</v>
+        <v>637</v>
       </c>
       <c r="F15" t="s">
         <v>233</v>
@@ -6991,7 +6971,7 @@
         <v>232</v>
       </c>
       <c r="H15" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I15" t="s">
         <v>247</v>
@@ -7002,13 +6982,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>572</v>
+        <v>638</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>573</v>
+        <v>639</v>
       </c>
       <c r="F16" t="s">
         <v>233</v>
@@ -7017,7 +6997,7 @@
         <v>232</v>
       </c>
       <c r="H16" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I16" t="s">
         <v>247</v>
@@ -7028,13 +7008,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>574</v>
+        <v>640</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>575</v>
+        <v>641</v>
       </c>
       <c r="F17" t="s">
         <v>233</v>
@@ -7043,7 +7023,7 @@
         <v>232</v>
       </c>
       <c r="H17" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I17" t="s">
         <v>247</v>
@@ -7054,13 +7034,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>576</v>
+        <v>642</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>577</v>
+        <v>643</v>
       </c>
       <c r="F18" t="s">
         <v>233</v>
@@ -7069,7 +7049,7 @@
         <v>232</v>
       </c>
       <c r="H18" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I18" t="s">
         <v>247</v>
@@ -7080,13 +7060,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>578</v>
+        <v>644</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>579</v>
+        <v>645</v>
       </c>
       <c r="F19" t="s">
         <v>233</v>
@@ -7095,7 +7075,7 @@
         <v>232</v>
       </c>
       <c r="H19" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I19" t="s">
         <v>247</v>
@@ -7106,13 +7086,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>580</v>
+        <v>646</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>581</v>
+        <v>647</v>
       </c>
       <c r="F20" t="s">
         <v>233</v>
@@ -7121,7 +7101,7 @@
         <v>232</v>
       </c>
       <c r="H20" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I20" t="s">
         <v>247</v>
@@ -7132,13 +7112,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>582</v>
+        <v>648</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>583</v>
+        <v>649</v>
       </c>
       <c r="F21" t="s">
         <v>233</v>
@@ -7147,7 +7127,7 @@
         <v>232</v>
       </c>
       <c r="H21" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I21" t="s">
         <v>247</v>
@@ -7158,13 +7138,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>584</v>
+        <v>650</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>585</v>
+        <v>651</v>
       </c>
       <c r="F22" t="s">
         <v>233</v>
@@ -7173,7 +7153,7 @@
         <v>232</v>
       </c>
       <c r="H22" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I22" t="s">
         <v>247</v>
@@ -7184,13 +7164,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>586</v>
+        <v>652</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>587</v>
+        <v>653</v>
       </c>
       <c r="F23" t="s">
         <v>233</v>
@@ -7199,7 +7179,7 @@
         <v>232</v>
       </c>
       <c r="H23" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I23" t="s">
         <v>247</v>
@@ -7210,13 +7190,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>588</v>
+        <v>654</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>589</v>
+        <v>655</v>
       </c>
       <c r="F24" t="s">
         <v>233</v>
@@ -7225,7 +7205,7 @@
         <v>232</v>
       </c>
       <c r="H24" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I24" t="s">
         <v>247</v>
@@ -7236,13 +7216,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>590</v>
+        <v>656</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>591</v>
+        <v>657</v>
       </c>
       <c r="F25" t="s">
         <v>233</v>
@@ -7251,7 +7231,7 @@
         <v>232</v>
       </c>
       <c r="H25" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I25" t="s">
         <v>247</v>
@@ -7262,13 +7242,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>592</v>
+        <v>658</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>593</v>
+        <v>659</v>
       </c>
       <c r="F26" t="s">
         <v>233</v>
@@ -7277,7 +7257,7 @@
         <v>232</v>
       </c>
       <c r="H26" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I26" t="s">
         <v>247</v>
@@ -7288,13 +7268,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>594</v>
+        <v>660</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>595</v>
+        <v>661</v>
       </c>
       <c r="F27" t="s">
         <v>233</v>
@@ -7303,7 +7283,7 @@
         <v>232</v>
       </c>
       <c r="H27" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I27" t="s">
         <v>247</v>
@@ -7314,13 +7294,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>596</v>
+        <v>662</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>597</v>
+        <v>663</v>
       </c>
       <c r="F28" t="s">
         <v>233</v>
@@ -7329,7 +7309,7 @@
         <v>232</v>
       </c>
       <c r="H28" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I28" t="s">
         <v>247</v>
@@ -7340,13 +7320,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>598</v>
+        <v>664</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>599</v>
+        <v>665</v>
       </c>
       <c r="F29" t="s">
         <v>233</v>
@@ -7355,7 +7335,7 @@
         <v>232</v>
       </c>
       <c r="H29" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I29" t="s">
         <v>247</v>
@@ -7366,13 +7346,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>600</v>
+        <v>666</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>601</v>
+        <v>667</v>
       </c>
       <c r="F30" t="s">
         <v>233</v>
@@ -7381,7 +7361,7 @@
         <v>232</v>
       </c>
       <c r="H30" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I30" t="s">
         <v>247</v>
@@ -7392,13 +7372,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>602</v>
+        <v>668</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>603</v>
+        <v>669</v>
       </c>
       <c r="F31" t="s">
         <v>233</v>
@@ -7407,7 +7387,7 @@
         <v>232</v>
       </c>
       <c r="H31" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I31" t="s">
         <v>247</v>
@@ -7418,13 +7398,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>604</v>
+        <v>670</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>605</v>
+        <v>671</v>
       </c>
       <c r="F32" t="s">
         <v>233</v>
@@ -7433,7 +7413,7 @@
         <v>232</v>
       </c>
       <c r="H32" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I32" t="s">
         <v>247</v>
@@ -7444,13 +7424,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>606</v>
+        <v>672</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>607</v>
+        <v>673</v>
       </c>
       <c r="F33" t="s">
         <v>233</v>
@@ -7459,7 +7439,7 @@
         <v>232</v>
       </c>
       <c r="H33" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I33" t="s">
         <v>247</v>
@@ -7470,13 +7450,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>608</v>
+        <v>674</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>609</v>
+        <v>675</v>
       </c>
       <c r="F34" t="s">
         <v>233</v>
@@ -7485,7 +7465,7 @@
         <v>232</v>
       </c>
       <c r="H34" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I34" t="s">
         <v>247</v>
@@ -7496,13 +7476,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>610</v>
+        <v>676</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>611</v>
+        <v>677</v>
       </c>
       <c r="F35" t="s">
         <v>233</v>
@@ -7511,7 +7491,7 @@
         <v>232</v>
       </c>
       <c r="H35" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I35" t="s">
         <v>247</v>
@@ -7522,13 +7502,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>612</v>
+        <v>678</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>613</v>
+        <v>679</v>
       </c>
       <c r="F36" t="s">
         <v>233</v>
@@ -7537,7 +7517,7 @@
         <v>232</v>
       </c>
       <c r="H36" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I36" t="s">
         <v>247</v>
@@ -7548,13 +7528,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>614</v>
+        <v>680</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>615</v>
+        <v>681</v>
       </c>
       <c r="F37" t="s">
         <v>233</v>
@@ -7563,7 +7543,7 @@
         <v>232</v>
       </c>
       <c r="H37" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I37" t="s">
         <v>247</v>
@@ -7574,13 +7554,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>616</v>
+        <v>682</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>617</v>
+        <v>683</v>
       </c>
       <c r="F38" t="s">
         <v>233</v>
@@ -7589,7 +7569,7 @@
         <v>232</v>
       </c>
       <c r="H38" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I38" t="s">
         <v>247</v>
@@ -7600,13 +7580,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>618</v>
+        <v>684</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>619</v>
+        <v>685</v>
       </c>
       <c r="F39" t="s">
         <v>233</v>
@@ -7615,7 +7595,7 @@
         <v>232</v>
       </c>
       <c r="H39" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I39" t="s">
         <v>247</v>
@@ -7626,13 +7606,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>620</v>
+        <v>686</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>621</v>
+        <v>687</v>
       </c>
       <c r="F40" t="s">
         <v>233</v>
@@ -7641,7 +7621,7 @@
         <v>232</v>
       </c>
       <c r="H40" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I40" t="s">
         <v>247</v>
@@ -7652,13 +7632,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>622</v>
+        <v>688</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>623</v>
+        <v>689</v>
       </c>
       <c r="F41" t="s">
         <v>233</v>
@@ -7667,7 +7647,7 @@
         <v>232</v>
       </c>
       <c r="H41" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I41" t="s">
         <v>247</v>
@@ -7678,13 +7658,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>624</v>
+        <v>690</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>625</v>
+        <v>691</v>
       </c>
       <c r="F42" t="s">
         <v>233</v>
@@ -7693,7 +7673,7 @@
         <v>232</v>
       </c>
       <c r="H42" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I42" t="s">
         <v>247</v>
@@ -7704,13 +7684,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>626</v>
+        <v>692</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>627</v>
+        <v>693</v>
       </c>
       <c r="F43" t="s">
         <v>233</v>
@@ -7719,7 +7699,7 @@
         <v>232</v>
       </c>
       <c r="H43" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I43" t="s">
         <v>247</v>
@@ -7730,13 +7710,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>628</v>
+        <v>694</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>629</v>
+        <v>695</v>
       </c>
       <c r="F44" t="s">
         <v>233</v>
@@ -7745,7 +7725,7 @@
         <v>232</v>
       </c>
       <c r="H44" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I44" t="s">
         <v>247</v>
@@ -7756,13 +7736,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>630</v>
+        <v>696</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>631</v>
+        <v>697</v>
       </c>
       <c r="F45" t="s">
         <v>233</v>
@@ -7771,7 +7751,7 @@
         <v>232</v>
       </c>
       <c r="H45" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I45" t="s">
         <v>247</v>
@@ -7782,13 +7762,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>632</v>
+        <v>698</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>633</v>
+        <v>699</v>
       </c>
       <c r="F46" t="s">
         <v>233</v>
@@ -7797,7 +7777,7 @@
         <v>232</v>
       </c>
       <c r="H46" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I46" t="s">
         <v>247</v>
@@ -7808,13 +7788,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>634</v>
+        <v>700</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>635</v>
+        <v>701</v>
       </c>
       <c r="F47" t="s">
         <v>233</v>
@@ -7823,7 +7803,7 @@
         <v>232</v>
       </c>
       <c r="H47" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I47" t="s">
         <v>247</v>
@@ -7834,13 +7814,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>636</v>
+        <v>702</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>637</v>
+        <v>703</v>
       </c>
       <c r="F48" t="s">
         <v>233</v>
@@ -7849,7 +7829,7 @@
         <v>232</v>
       </c>
       <c r="H48" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I48" t="s">
         <v>247</v>
@@ -7860,13 +7840,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>638</v>
+        <v>704</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>639</v>
+        <v>705</v>
       </c>
       <c r="F49" t="s">
         <v>233</v>
@@ -7875,7 +7855,7 @@
         <v>232</v>
       </c>
       <c r="H49" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I49" t="s">
         <v>247</v>
@@ -7886,13 +7866,13 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>640</v>
+        <v>706</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>641</v>
+        <v>707</v>
       </c>
       <c r="F50" t="s">
         <v>233</v>
@@ -7901,7 +7881,7 @@
         <v>232</v>
       </c>
       <c r="H50" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I50" t="s">
         <v>247</v>
@@ -7912,13 +7892,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>642</v>
+        <v>708</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>643</v>
+        <v>709</v>
       </c>
       <c r="F51" t="s">
         <v>233</v>
@@ -7927,7 +7907,7 @@
         <v>232</v>
       </c>
       <c r="H51" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I51" t="s">
         <v>247</v>
@@ -7938,13 +7918,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>644</v>
+        <v>710</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>645</v>
+        <v>711</v>
       </c>
       <c r="F52" t="s">
         <v>233</v>
@@ -7953,9 +7933,321 @@
         <v>232</v>
       </c>
       <c r="H52" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I52" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9">
+      <c r="B53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" t="s">
+        <v>712</v>
+      </c>
+      <c r="D53" t="s">
+        <v>243</v>
+      </c>
+      <c r="E53" t="s">
+        <v>713</v>
+      </c>
+      <c r="F53" t="s">
+        <v>233</v>
+      </c>
+      <c r="G53" t="s">
+        <v>232</v>
+      </c>
+      <c r="H53" t="s">
+        <v>497</v>
+      </c>
+      <c r="I53" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9">
+      <c r="B54" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" t="s">
+        <v>714</v>
+      </c>
+      <c r="D54" t="s">
+        <v>243</v>
+      </c>
+      <c r="E54" t="s">
+        <v>715</v>
+      </c>
+      <c r="F54" t="s">
+        <v>233</v>
+      </c>
+      <c r="G54" t="s">
+        <v>232</v>
+      </c>
+      <c r="H54" t="s">
+        <v>497</v>
+      </c>
+      <c r="I54" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9">
+      <c r="B55" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" t="s">
+        <v>716</v>
+      </c>
+      <c r="D55" t="s">
+        <v>243</v>
+      </c>
+      <c r="E55" t="s">
+        <v>717</v>
+      </c>
+      <c r="F55" t="s">
+        <v>233</v>
+      </c>
+      <c r="G55" t="s">
+        <v>232</v>
+      </c>
+      <c r="H55" t="s">
+        <v>497</v>
+      </c>
+      <c r="I55" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9">
+      <c r="B56" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" t="s">
+        <v>718</v>
+      </c>
+      <c r="D56" t="s">
+        <v>243</v>
+      </c>
+      <c r="E56" t="s">
+        <v>719</v>
+      </c>
+      <c r="F56" t="s">
+        <v>233</v>
+      </c>
+      <c r="G56" t="s">
+        <v>232</v>
+      </c>
+      <c r="H56" t="s">
+        <v>497</v>
+      </c>
+      <c r="I56" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9">
+      <c r="B57" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" t="s">
+        <v>720</v>
+      </c>
+      <c r="D57" t="s">
+        <v>243</v>
+      </c>
+      <c r="E57" t="s">
+        <v>721</v>
+      </c>
+      <c r="F57" t="s">
+        <v>233</v>
+      </c>
+      <c r="G57" t="s">
+        <v>232</v>
+      </c>
+      <c r="H57" t="s">
+        <v>497</v>
+      </c>
+      <c r="I57" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9">
+      <c r="B58" t="s">
+        <v>17</v>
+      </c>
+      <c r="C58" t="s">
+        <v>722</v>
+      </c>
+      <c r="D58" t="s">
+        <v>243</v>
+      </c>
+      <c r="E58" t="s">
+        <v>723</v>
+      </c>
+      <c r="F58" t="s">
+        <v>233</v>
+      </c>
+      <c r="G58" t="s">
+        <v>232</v>
+      </c>
+      <c r="H58" t="s">
+        <v>497</v>
+      </c>
+      <c r="I58" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9">
+      <c r="B59" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" t="s">
+        <v>724</v>
+      </c>
+      <c r="D59" t="s">
+        <v>243</v>
+      </c>
+      <c r="E59" t="s">
+        <v>725</v>
+      </c>
+      <c r="F59" t="s">
+        <v>233</v>
+      </c>
+      <c r="G59" t="s">
+        <v>232</v>
+      </c>
+      <c r="H59" t="s">
+        <v>497</v>
+      </c>
+      <c r="I59" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9">
+      <c r="B60" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60" t="s">
+        <v>726</v>
+      </c>
+      <c r="D60" t="s">
+        <v>243</v>
+      </c>
+      <c r="E60" t="s">
+        <v>727</v>
+      </c>
+      <c r="F60" t="s">
+        <v>233</v>
+      </c>
+      <c r="G60" t="s">
+        <v>232</v>
+      </c>
+      <c r="H60" t="s">
+        <v>497</v>
+      </c>
+      <c r="I60" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9">
+      <c r="B61" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" t="s">
+        <v>728</v>
+      </c>
+      <c r="D61" t="s">
+        <v>243</v>
+      </c>
+      <c r="E61" t="s">
+        <v>729</v>
+      </c>
+      <c r="F61" t="s">
+        <v>233</v>
+      </c>
+      <c r="G61" t="s">
+        <v>232</v>
+      </c>
+      <c r="H61" t="s">
+        <v>497</v>
+      </c>
+      <c r="I61" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9">
+      <c r="B62" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" t="s">
+        <v>730</v>
+      </c>
+      <c r="D62" t="s">
+        <v>243</v>
+      </c>
+      <c r="E62" t="s">
+        <v>731</v>
+      </c>
+      <c r="F62" t="s">
+        <v>233</v>
+      </c>
+      <c r="G62" t="s">
+        <v>232</v>
+      </c>
+      <c r="H62" t="s">
+        <v>497</v>
+      </c>
+      <c r="I62" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9">
+      <c r="B63" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" t="s">
+        <v>732</v>
+      </c>
+      <c r="D63" t="s">
+        <v>243</v>
+      </c>
+      <c r="E63" t="s">
+        <v>733</v>
+      </c>
+      <c r="F63" t="s">
+        <v>233</v>
+      </c>
+      <c r="G63" t="s">
+        <v>232</v>
+      </c>
+      <c r="H63" t="s">
+        <v>497</v>
+      </c>
+      <c r="I63" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9">
+      <c r="B64" t="s">
+        <v>17</v>
+      </c>
+      <c r="C64" t="s">
+        <v>734</v>
+      </c>
+      <c r="D64" t="s">
+        <v>243</v>
+      </c>
+      <c r="E64" t="s">
+        <v>735</v>
+      </c>
+      <c r="F64" t="s">
+        <v>233</v>
+      </c>
+      <c r="G64" t="s">
+        <v>232</v>
+      </c>
+      <c r="H64" t="s">
+        <v>497</v>
+      </c>
+      <c r="I64" t="s">
         <v>247</v>
       </c>
     </row>
@@ -7965,13 +8257,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D5B8311-A7E9-42EF-B49B-10C96D5F9BB3}">
-  <dimension ref="B3:I52"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11AE27F4-6BCB-4E70-944E-6E03C6A66E34}">
+  <dimension ref="B3:I64"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>452</v>
+        <v>494</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -8005,13 +8297,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>453</v>
+        <v>495</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>454</v>
+        <v>496</v>
       </c>
       <c r="F5" t="s">
         <v>25</v>
@@ -8020,7 +8312,7 @@
         <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I5" t="s">
         <v>247</v>
@@ -8031,13 +8323,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>456</v>
+        <v>498</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>457</v>
+        <v>499</v>
       </c>
       <c r="F6" t="s">
         <v>25</v>
@@ -8046,7 +8338,7 @@
         <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I6" t="s">
         <v>247</v>
@@ -8057,13 +8349,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>458</v>
+        <v>500</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>459</v>
+        <v>501</v>
       </c>
       <c r="F7" t="s">
         <v>25</v>
@@ -8072,7 +8364,7 @@
         <v>35</v>
       </c>
       <c r="H7" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I7" t="s">
         <v>247</v>
@@ -8083,13 +8375,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>460</v>
+        <v>502</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>461</v>
+        <v>503</v>
       </c>
       <c r="F8" t="s">
         <v>25</v>
@@ -8098,7 +8390,7 @@
         <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I8" t="s">
         <v>247</v>
@@ -8109,13 +8401,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>462</v>
+        <v>504</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>463</v>
+        <v>505</v>
       </c>
       <c r="F9" t="s">
         <v>25</v>
@@ -8124,7 +8416,7 @@
         <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I9" t="s">
         <v>247</v>
@@ -8135,13 +8427,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>464</v>
+        <v>506</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>465</v>
+        <v>507</v>
       </c>
       <c r="F10" t="s">
         <v>25</v>
@@ -8150,7 +8442,7 @@
         <v>35</v>
       </c>
       <c r="H10" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I10" t="s">
         <v>247</v>
@@ -8161,13 +8453,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>466</v>
+        <v>508</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>467</v>
+        <v>509</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
@@ -8176,7 +8468,7 @@
         <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I11" t="s">
         <v>247</v>
@@ -8187,13 +8479,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>468</v>
+        <v>510</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>469</v>
+        <v>511</v>
       </c>
       <c r="F12" t="s">
         <v>25</v>
@@ -8202,7 +8494,7 @@
         <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I12" t="s">
         <v>247</v>
@@ -8213,13 +8505,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>470</v>
+        <v>512</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>471</v>
+        <v>513</v>
       </c>
       <c r="F13" t="s">
         <v>25</v>
@@ -8228,7 +8520,7 @@
         <v>35</v>
       </c>
       <c r="H13" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I13" t="s">
         <v>247</v>
@@ -8239,13 +8531,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>472</v>
+        <v>514</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>473</v>
+        <v>515</v>
       </c>
       <c r="F14" t="s">
         <v>25</v>
@@ -8254,7 +8546,7 @@
         <v>35</v>
       </c>
       <c r="H14" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I14" t="s">
         <v>247</v>
@@ -8265,13 +8557,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>474</v>
+        <v>516</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>475</v>
+        <v>517</v>
       </c>
       <c r="F15" t="s">
         <v>25</v>
@@ -8280,7 +8572,7 @@
         <v>35</v>
       </c>
       <c r="H15" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I15" t="s">
         <v>247</v>
@@ -8291,13 +8583,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>476</v>
+        <v>518</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>477</v>
+        <v>519</v>
       </c>
       <c r="F16" t="s">
         <v>25</v>
@@ -8306,7 +8598,7 @@
         <v>35</v>
       </c>
       <c r="H16" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I16" t="s">
         <v>247</v>
@@ -8317,13 +8609,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>478</v>
+        <v>520</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>479</v>
+        <v>521</v>
       </c>
       <c r="F17" t="s">
         <v>25</v>
@@ -8332,7 +8624,7 @@
         <v>35</v>
       </c>
       <c r="H17" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I17" t="s">
         <v>247</v>
@@ -8343,13 +8635,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>480</v>
+        <v>522</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>481</v>
+        <v>523</v>
       </c>
       <c r="F18" t="s">
         <v>25</v>
@@ -8358,7 +8650,7 @@
         <v>35</v>
       </c>
       <c r="H18" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I18" t="s">
         <v>247</v>
@@ -8369,13 +8661,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>482</v>
+        <v>524</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>483</v>
+        <v>525</v>
       </c>
       <c r="F19" t="s">
         <v>25</v>
@@ -8384,7 +8676,7 @@
         <v>35</v>
       </c>
       <c r="H19" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I19" t="s">
         <v>247</v>
@@ -8395,13 +8687,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>484</v>
+        <v>526</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>485</v>
+        <v>527</v>
       </c>
       <c r="F20" t="s">
         <v>25</v>
@@ -8410,7 +8702,7 @@
         <v>35</v>
       </c>
       <c r="H20" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I20" t="s">
         <v>247</v>
@@ -8421,13 +8713,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>486</v>
+        <v>528</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>487</v>
+        <v>529</v>
       </c>
       <c r="F21" t="s">
         <v>25</v>
@@ -8436,7 +8728,7 @@
         <v>35</v>
       </c>
       <c r="H21" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I21" t="s">
         <v>247</v>
@@ -8447,13 +8739,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>488</v>
+        <v>530</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>489</v>
+        <v>531</v>
       </c>
       <c r="F22" t="s">
         <v>25</v>
@@ -8462,7 +8754,7 @@
         <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I22" t="s">
         <v>247</v>
@@ -8473,13 +8765,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>490</v>
+        <v>532</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>491</v>
+        <v>533</v>
       </c>
       <c r="F23" t="s">
         <v>25</v>
@@ -8488,7 +8780,7 @@
         <v>35</v>
       </c>
       <c r="H23" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I23" t="s">
         <v>247</v>
@@ -8499,13 +8791,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>492</v>
+        <v>534</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>493</v>
+        <v>535</v>
       </c>
       <c r="F24" t="s">
         <v>25</v>
@@ -8514,7 +8806,7 @@
         <v>35</v>
       </c>
       <c r="H24" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I24" t="s">
         <v>247</v>
@@ -8525,13 +8817,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>494</v>
+        <v>536</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>495</v>
+        <v>537</v>
       </c>
       <c r="F25" t="s">
         <v>25</v>
@@ -8540,7 +8832,7 @@
         <v>35</v>
       </c>
       <c r="H25" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I25" t="s">
         <v>247</v>
@@ -8551,22 +8843,22 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>496</v>
+        <v>538</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
+        <v>539</v>
+      </c>
+      <c r="F26" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" t="s">
+        <v>35</v>
+      </c>
+      <c r="H26" t="s">
         <v>497</v>
-      </c>
-      <c r="F26" t="s">
-        <v>25</v>
-      </c>
-      <c r="G26" t="s">
-        <v>35</v>
-      </c>
-      <c r="H26" t="s">
-        <v>455</v>
       </c>
       <c r="I26" t="s">
         <v>247</v>
@@ -8577,13 +8869,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>498</v>
+        <v>540</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>499</v>
+        <v>541</v>
       </c>
       <c r="F27" t="s">
         <v>25</v>
@@ -8592,7 +8884,7 @@
         <v>35</v>
       </c>
       <c r="H27" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I27" t="s">
         <v>247</v>
@@ -8603,13 +8895,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>500</v>
+        <v>542</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>501</v>
+        <v>543</v>
       </c>
       <c r="F28" t="s">
         <v>25</v>
@@ -8618,7 +8910,7 @@
         <v>35</v>
       </c>
       <c r="H28" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I28" t="s">
         <v>247</v>
@@ -8629,13 +8921,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>502</v>
+        <v>544</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>503</v>
+        <v>545</v>
       </c>
       <c r="F29" t="s">
         <v>25</v>
@@ -8644,7 +8936,7 @@
         <v>35</v>
       </c>
       <c r="H29" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I29" t="s">
         <v>247</v>
@@ -8655,13 +8947,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>504</v>
+        <v>546</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>505</v>
+        <v>547</v>
       </c>
       <c r="F30" t="s">
         <v>25</v>
@@ -8670,7 +8962,7 @@
         <v>35</v>
       </c>
       <c r="H30" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I30" t="s">
         <v>247</v>
@@ -8681,13 +8973,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>506</v>
+        <v>548</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>507</v>
+        <v>549</v>
       </c>
       <c r="F31" t="s">
         <v>25</v>
@@ -8696,7 +8988,7 @@
         <v>35</v>
       </c>
       <c r="H31" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I31" t="s">
         <v>247</v>
@@ -8707,13 +8999,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>508</v>
+        <v>550</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>509</v>
+        <v>551</v>
       </c>
       <c r="F32" t="s">
         <v>25</v>
@@ -8722,7 +9014,7 @@
         <v>35</v>
       </c>
       <c r="H32" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I32" t="s">
         <v>247</v>
@@ -8733,13 +9025,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>510</v>
+        <v>552</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>511</v>
+        <v>553</v>
       </c>
       <c r="F33" t="s">
         <v>25</v>
@@ -8748,7 +9040,7 @@
         <v>35</v>
       </c>
       <c r="H33" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I33" t="s">
         <v>247</v>
@@ -8759,13 +9051,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>512</v>
+        <v>554</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>513</v>
+        <v>555</v>
       </c>
       <c r="F34" t="s">
         <v>25</v>
@@ -8774,7 +9066,7 @@
         <v>35</v>
       </c>
       <c r="H34" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I34" t="s">
         <v>247</v>
@@ -8785,13 +9077,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>514</v>
+        <v>556</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>515</v>
+        <v>557</v>
       </c>
       <c r="F35" t="s">
         <v>25</v>
@@ -8800,7 +9092,7 @@
         <v>35</v>
       </c>
       <c r="H35" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I35" t="s">
         <v>247</v>
@@ -8811,13 +9103,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>516</v>
+        <v>558</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>517</v>
+        <v>559</v>
       </c>
       <c r="F36" t="s">
         <v>25</v>
@@ -8826,7 +9118,7 @@
         <v>35</v>
       </c>
       <c r="H36" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I36" t="s">
         <v>247</v>
@@ -8837,13 +9129,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>518</v>
+        <v>560</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>519</v>
+        <v>561</v>
       </c>
       <c r="F37" t="s">
         <v>25</v>
@@ -8852,7 +9144,7 @@
         <v>35</v>
       </c>
       <c r="H37" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I37" t="s">
         <v>247</v>
@@ -8863,13 +9155,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>520</v>
+        <v>562</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>521</v>
+        <v>563</v>
       </c>
       <c r="F38" t="s">
         <v>25</v>
@@ -8878,7 +9170,7 @@
         <v>35</v>
       </c>
       <c r="H38" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I38" t="s">
         <v>247</v>
@@ -8889,13 +9181,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>522</v>
+        <v>564</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>523</v>
+        <v>565</v>
       </c>
       <c r="F39" t="s">
         <v>25</v>
@@ -8904,7 +9196,7 @@
         <v>35</v>
       </c>
       <c r="H39" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I39" t="s">
         <v>247</v>
@@ -8915,13 +9207,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>524</v>
+        <v>566</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>525</v>
+        <v>567</v>
       </c>
       <c r="F40" t="s">
         <v>25</v>
@@ -8930,7 +9222,7 @@
         <v>35</v>
       </c>
       <c r="H40" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I40" t="s">
         <v>247</v>
@@ -8941,13 +9233,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>526</v>
+        <v>568</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>527</v>
+        <v>569</v>
       </c>
       <c r="F41" t="s">
         <v>25</v>
@@ -8956,7 +9248,7 @@
         <v>35</v>
       </c>
       <c r="H41" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I41" t="s">
         <v>247</v>
@@ -8967,13 +9259,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>528</v>
+        <v>570</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>529</v>
+        <v>571</v>
       </c>
       <c r="F42" t="s">
         <v>25</v>
@@ -8982,7 +9274,7 @@
         <v>35</v>
       </c>
       <c r="H42" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I42" t="s">
         <v>247</v>
@@ -8993,13 +9285,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>530</v>
+        <v>572</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>531</v>
+        <v>573</v>
       </c>
       <c r="F43" t="s">
         <v>25</v>
@@ -9008,7 +9300,7 @@
         <v>35</v>
       </c>
       <c r="H43" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I43" t="s">
         <v>247</v>
@@ -9019,13 +9311,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>532</v>
+        <v>574</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>533</v>
+        <v>575</v>
       </c>
       <c r="F44" t="s">
         <v>25</v>
@@ -9034,7 +9326,7 @@
         <v>35</v>
       </c>
       <c r="H44" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I44" t="s">
         <v>247</v>
@@ -9045,13 +9337,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>534</v>
+        <v>576</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>535</v>
+        <v>577</v>
       </c>
       <c r="F45" t="s">
         <v>25</v>
@@ -9060,7 +9352,7 @@
         <v>35</v>
       </c>
       <c r="H45" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I45" t="s">
         <v>247</v>
@@ -9071,13 +9363,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>536</v>
+        <v>578</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>537</v>
+        <v>579</v>
       </c>
       <c r="F46" t="s">
         <v>25</v>
@@ -9086,7 +9378,7 @@
         <v>35</v>
       </c>
       <c r="H46" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I46" t="s">
         <v>247</v>
@@ -9097,13 +9389,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>538</v>
+        <v>580</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>539</v>
+        <v>581</v>
       </c>
       <c r="F47" t="s">
         <v>25</v>
@@ -9112,7 +9404,7 @@
         <v>35</v>
       </c>
       <c r="H47" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I47" t="s">
         <v>247</v>
@@ -9123,13 +9415,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>540</v>
+        <v>582</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>541</v>
+        <v>583</v>
       </c>
       <c r="F48" t="s">
         <v>25</v>
@@ -9138,7 +9430,7 @@
         <v>35</v>
       </c>
       <c r="H48" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I48" t="s">
         <v>247</v>
@@ -9149,13 +9441,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>542</v>
+        <v>584</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>543</v>
+        <v>585</v>
       </c>
       <c r="F49" t="s">
         <v>25</v>
@@ -9164,7 +9456,7 @@
         <v>35</v>
       </c>
       <c r="H49" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I49" t="s">
         <v>247</v>
@@ -9175,13 +9467,13 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>544</v>
+        <v>586</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>545</v>
+        <v>587</v>
       </c>
       <c r="F50" t="s">
         <v>25</v>
@@ -9190,7 +9482,7 @@
         <v>35</v>
       </c>
       <c r="H50" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I50" t="s">
         <v>247</v>
@@ -9201,13 +9493,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>546</v>
+        <v>588</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>547</v>
+        <v>589</v>
       </c>
       <c r="F51" t="s">
         <v>25</v>
@@ -9216,7 +9508,7 @@
         <v>35</v>
       </c>
       <c r="H51" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I51" t="s">
         <v>247</v>
@@ -9227,13 +9519,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>548</v>
+        <v>590</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>549</v>
+        <v>591</v>
       </c>
       <c r="F52" t="s">
         <v>25</v>
@@ -9242,9 +9534,321 @@
         <v>35</v>
       </c>
       <c r="H52" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="I52" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9">
+      <c r="B53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" t="s">
+        <v>592</v>
+      </c>
+      <c r="D53" t="s">
+        <v>243</v>
+      </c>
+      <c r="E53" t="s">
+        <v>593</v>
+      </c>
+      <c r="F53" t="s">
+        <v>25</v>
+      </c>
+      <c r="G53" t="s">
+        <v>35</v>
+      </c>
+      <c r="H53" t="s">
+        <v>497</v>
+      </c>
+      <c r="I53" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9">
+      <c r="B54" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" t="s">
+        <v>594</v>
+      </c>
+      <c r="D54" t="s">
+        <v>243</v>
+      </c>
+      <c r="E54" t="s">
+        <v>595</v>
+      </c>
+      <c r="F54" t="s">
+        <v>25</v>
+      </c>
+      <c r="G54" t="s">
+        <v>35</v>
+      </c>
+      <c r="H54" t="s">
+        <v>497</v>
+      </c>
+      <c r="I54" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9">
+      <c r="B55" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" t="s">
+        <v>596</v>
+      </c>
+      <c r="D55" t="s">
+        <v>243</v>
+      </c>
+      <c r="E55" t="s">
+        <v>597</v>
+      </c>
+      <c r="F55" t="s">
+        <v>25</v>
+      </c>
+      <c r="G55" t="s">
+        <v>35</v>
+      </c>
+      <c r="H55" t="s">
+        <v>497</v>
+      </c>
+      <c r="I55" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9">
+      <c r="B56" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" t="s">
+        <v>598</v>
+      </c>
+      <c r="D56" t="s">
+        <v>243</v>
+      </c>
+      <c r="E56" t="s">
+        <v>599</v>
+      </c>
+      <c r="F56" t="s">
+        <v>25</v>
+      </c>
+      <c r="G56" t="s">
+        <v>35</v>
+      </c>
+      <c r="H56" t="s">
+        <v>497</v>
+      </c>
+      <c r="I56" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9">
+      <c r="B57" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" t="s">
+        <v>600</v>
+      </c>
+      <c r="D57" t="s">
+        <v>243</v>
+      </c>
+      <c r="E57" t="s">
+        <v>601</v>
+      </c>
+      <c r="F57" t="s">
+        <v>25</v>
+      </c>
+      <c r="G57" t="s">
+        <v>35</v>
+      </c>
+      <c r="H57" t="s">
+        <v>497</v>
+      </c>
+      <c r="I57" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9">
+      <c r="B58" t="s">
+        <v>17</v>
+      </c>
+      <c r="C58" t="s">
+        <v>602</v>
+      </c>
+      <c r="D58" t="s">
+        <v>243</v>
+      </c>
+      <c r="E58" t="s">
+        <v>603</v>
+      </c>
+      <c r="F58" t="s">
+        <v>25</v>
+      </c>
+      <c r="G58" t="s">
+        <v>35</v>
+      </c>
+      <c r="H58" t="s">
+        <v>497</v>
+      </c>
+      <c r="I58" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9">
+      <c r="B59" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" t="s">
+        <v>604</v>
+      </c>
+      <c r="D59" t="s">
+        <v>243</v>
+      </c>
+      <c r="E59" t="s">
+        <v>605</v>
+      </c>
+      <c r="F59" t="s">
+        <v>25</v>
+      </c>
+      <c r="G59" t="s">
+        <v>35</v>
+      </c>
+      <c r="H59" t="s">
+        <v>497</v>
+      </c>
+      <c r="I59" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9">
+      <c r="B60" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60" t="s">
+        <v>606</v>
+      </c>
+      <c r="D60" t="s">
+        <v>243</v>
+      </c>
+      <c r="E60" t="s">
+        <v>607</v>
+      </c>
+      <c r="F60" t="s">
+        <v>25</v>
+      </c>
+      <c r="G60" t="s">
+        <v>35</v>
+      </c>
+      <c r="H60" t="s">
+        <v>497</v>
+      </c>
+      <c r="I60" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9">
+      <c r="B61" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" t="s">
+        <v>608</v>
+      </c>
+      <c r="D61" t="s">
+        <v>243</v>
+      </c>
+      <c r="E61" t="s">
+        <v>609</v>
+      </c>
+      <c r="F61" t="s">
+        <v>25</v>
+      </c>
+      <c r="G61" t="s">
+        <v>35</v>
+      </c>
+      <c r="H61" t="s">
+        <v>497</v>
+      </c>
+      <c r="I61" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9">
+      <c r="B62" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" t="s">
+        <v>610</v>
+      </c>
+      <c r="D62" t="s">
+        <v>243</v>
+      </c>
+      <c r="E62" t="s">
+        <v>611</v>
+      </c>
+      <c r="F62" t="s">
+        <v>25</v>
+      </c>
+      <c r="G62" t="s">
+        <v>35</v>
+      </c>
+      <c r="H62" t="s">
+        <v>497</v>
+      </c>
+      <c r="I62" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9">
+      <c r="B63" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" t="s">
+        <v>612</v>
+      </c>
+      <c r="D63" t="s">
+        <v>243</v>
+      </c>
+      <c r="E63" t="s">
+        <v>613</v>
+      </c>
+      <c r="F63" t="s">
+        <v>25</v>
+      </c>
+      <c r="G63" t="s">
+        <v>35</v>
+      </c>
+      <c r="H63" t="s">
+        <v>497</v>
+      </c>
+      <c r="I63" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9">
+      <c r="B64" t="s">
+        <v>17</v>
+      </c>
+      <c r="C64" t="s">
+        <v>614</v>
+      </c>
+      <c r="D64" t="s">
+        <v>243</v>
+      </c>
+      <c r="E64" t="s">
+        <v>615</v>
+      </c>
+      <c r="F64" t="s">
+        <v>25</v>
+      </c>
+      <c r="G64" t="s">
+        <v>35</v>
+      </c>
+      <c r="H64" t="s">
+        <v>497</v>
+      </c>
+      <c r="I64" t="s">
         <v>247</v>
       </c>
     </row>
@@ -9255,20 +9859,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:S107"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="B3:S128"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.06640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.06640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.19921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:19" ht="17.25" thickBot="1">
+    <row r="3" spans="2:19" ht="18" thickBot="1">
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
@@ -9287,7 +9891,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="2:19" ht="15" thickTop="1" thickBot="1">
+    <row r="4" spans="2:19" ht="16.5" thickTop="1" thickBot="1">
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
@@ -10173,7 +10777,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="30" spans="2:19" ht="17.25" thickBot="1">
+    <row r="30" spans="2:19" ht="18" thickBot="1">
       <c r="B30" s="3" t="s">
         <v>212</v>
       </c>
@@ -10201,7 +10805,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="31" spans="2:19" ht="15" thickTop="1" thickBot="1">
+    <row r="31" spans="2:19" ht="16.5" thickTop="1" thickBot="1">
       <c r="B31" s="5" t="s">
         <v>172</v>
       </c>
@@ -10380,7 +10984,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="38" spans="2:19" ht="17.25" thickBot="1">
+    <row r="38" spans="2:19" ht="18" thickBot="1">
       <c r="B38" s="3" t="s">
         <v>8</v>
       </c>
@@ -10408,7 +11012,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="39" spans="2:19" ht="15" thickTop="1" thickBot="1">
+    <row r="39" spans="2:19" ht="16.5" thickTop="1" thickBot="1">
       <c r="B39" s="5" t="s">
         <v>218</v>
       </c>
@@ -12085,6 +12689,489 @@
         <v>35</v>
       </c>
       <c r="S107" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="108" spans="13:19">
+      <c r="M108" t="s">
+        <v>17</v>
+      </c>
+      <c r="N108" t="s">
+        <v>452</v>
+      </c>
+      <c r="O108" t="s">
+        <v>243</v>
+      </c>
+      <c r="P108" t="s">
+        <v>453</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>25</v>
+      </c>
+      <c r="R108" t="s">
+        <v>35</v>
+      </c>
+      <c r="S108" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="109" spans="13:19">
+      <c r="M109" t="s">
+        <v>17</v>
+      </c>
+      <c r="N109" t="s">
+        <v>454</v>
+      </c>
+      <c r="O109" t="s">
+        <v>243</v>
+      </c>
+      <c r="P109" t="s">
+        <v>455</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>25</v>
+      </c>
+      <c r="R109" t="s">
+        <v>35</v>
+      </c>
+      <c r="S109" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="110" spans="13:19">
+      <c r="M110" t="s">
+        <v>17</v>
+      </c>
+      <c r="N110" t="s">
+        <v>456</v>
+      </c>
+      <c r="O110" t="s">
+        <v>243</v>
+      </c>
+      <c r="P110" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>25</v>
+      </c>
+      <c r="R110" t="s">
+        <v>35</v>
+      </c>
+      <c r="S110" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="111" spans="13:19">
+      <c r="M111" t="s">
+        <v>17</v>
+      </c>
+      <c r="N111" t="s">
+        <v>458</v>
+      </c>
+      <c r="O111" t="s">
+        <v>243</v>
+      </c>
+      <c r="P111" t="s">
+        <v>459</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>25</v>
+      </c>
+      <c r="R111" t="s">
+        <v>35</v>
+      </c>
+      <c r="S111" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="112" spans="13:19">
+      <c r="M112" t="s">
+        <v>17</v>
+      </c>
+      <c r="N112" t="s">
+        <v>460</v>
+      </c>
+      <c r="O112" t="s">
+        <v>243</v>
+      </c>
+      <c r="P112" t="s">
+        <v>461</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>25</v>
+      </c>
+      <c r="R112" t="s">
+        <v>35</v>
+      </c>
+      <c r="S112" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="113" spans="13:19">
+      <c r="M113" t="s">
+        <v>17</v>
+      </c>
+      <c r="N113" t="s">
+        <v>462</v>
+      </c>
+      <c r="O113" t="s">
+        <v>243</v>
+      </c>
+      <c r="P113" t="s">
+        <v>463</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>25</v>
+      </c>
+      <c r="R113" t="s">
+        <v>35</v>
+      </c>
+      <c r="S113" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="114" spans="13:19">
+      <c r="M114" t="s">
+        <v>17</v>
+      </c>
+      <c r="N114" t="s">
+        <v>464</v>
+      </c>
+      <c r="O114" t="s">
+        <v>243</v>
+      </c>
+      <c r="P114" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>25</v>
+      </c>
+      <c r="R114" t="s">
+        <v>35</v>
+      </c>
+      <c r="S114" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="115" spans="13:19">
+      <c r="M115" t="s">
+        <v>17</v>
+      </c>
+      <c r="N115" t="s">
+        <v>466</v>
+      </c>
+      <c r="O115" t="s">
+        <v>243</v>
+      </c>
+      <c r="P115" t="s">
+        <v>467</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>25</v>
+      </c>
+      <c r="R115" t="s">
+        <v>35</v>
+      </c>
+      <c r="S115" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="116" spans="13:19">
+      <c r="M116" t="s">
+        <v>17</v>
+      </c>
+      <c r="N116" t="s">
+        <v>468</v>
+      </c>
+      <c r="O116" t="s">
+        <v>243</v>
+      </c>
+      <c r="P116" t="s">
+        <v>469</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>25</v>
+      </c>
+      <c r="R116" t="s">
+        <v>35</v>
+      </c>
+      <c r="S116" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="117" spans="13:19">
+      <c r="M117" t="s">
+        <v>17</v>
+      </c>
+      <c r="N117" t="s">
+        <v>470</v>
+      </c>
+      <c r="O117" t="s">
+        <v>243</v>
+      </c>
+      <c r="P117" t="s">
+        <v>471</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>25</v>
+      </c>
+      <c r="R117" t="s">
+        <v>35</v>
+      </c>
+      <c r="S117" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="118" spans="13:19">
+      <c r="M118" t="s">
+        <v>17</v>
+      </c>
+      <c r="N118" t="s">
+        <v>472</v>
+      </c>
+      <c r="O118" t="s">
+        <v>243</v>
+      </c>
+      <c r="P118" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>25</v>
+      </c>
+      <c r="R118" t="s">
+        <v>35</v>
+      </c>
+      <c r="S118" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="119" spans="13:19">
+      <c r="M119" t="s">
+        <v>17</v>
+      </c>
+      <c r="N119" t="s">
+        <v>474</v>
+      </c>
+      <c r="O119" t="s">
+        <v>243</v>
+      </c>
+      <c r="P119" t="s">
+        <v>475</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>25</v>
+      </c>
+      <c r="R119" t="s">
+        <v>35</v>
+      </c>
+      <c r="S119" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="120" spans="13:19">
+      <c r="M120" t="s">
+        <v>17</v>
+      </c>
+      <c r="N120" t="s">
+        <v>476</v>
+      </c>
+      <c r="O120" t="s">
+        <v>243</v>
+      </c>
+      <c r="P120" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>25</v>
+      </c>
+      <c r="R120" t="s">
+        <v>35</v>
+      </c>
+      <c r="S120" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="121" spans="13:19">
+      <c r="M121" t="s">
+        <v>17</v>
+      </c>
+      <c r="N121" t="s">
+        <v>478</v>
+      </c>
+      <c r="O121" t="s">
+        <v>243</v>
+      </c>
+      <c r="P121" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>25</v>
+      </c>
+      <c r="R121" t="s">
+        <v>35</v>
+      </c>
+      <c r="S121" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="122" spans="13:19">
+      <c r="M122" t="s">
+        <v>17</v>
+      </c>
+      <c r="N122" t="s">
+        <v>480</v>
+      </c>
+      <c r="O122" t="s">
+        <v>243</v>
+      </c>
+      <c r="P122" t="s">
+        <v>481</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>25</v>
+      </c>
+      <c r="R122" t="s">
+        <v>35</v>
+      </c>
+      <c r="S122" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="123" spans="13:19">
+      <c r="M123" t="s">
+        <v>17</v>
+      </c>
+      <c r="N123" t="s">
+        <v>482</v>
+      </c>
+      <c r="O123" t="s">
+        <v>243</v>
+      </c>
+      <c r="P123" t="s">
+        <v>483</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>25</v>
+      </c>
+      <c r="R123" t="s">
+        <v>35</v>
+      </c>
+      <c r="S123" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="124" spans="13:19">
+      <c r="M124" t="s">
+        <v>17</v>
+      </c>
+      <c r="N124" t="s">
+        <v>484</v>
+      </c>
+      <c r="O124" t="s">
+        <v>243</v>
+      </c>
+      <c r="P124" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>25</v>
+      </c>
+      <c r="R124" t="s">
+        <v>35</v>
+      </c>
+      <c r="S124" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="125" spans="13:19">
+      <c r="M125" t="s">
+        <v>17</v>
+      </c>
+      <c r="N125" t="s">
+        <v>486</v>
+      </c>
+      <c r="O125" t="s">
+        <v>243</v>
+      </c>
+      <c r="P125" t="s">
+        <v>487</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>25</v>
+      </c>
+      <c r="R125" t="s">
+        <v>35</v>
+      </c>
+      <c r="S125" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="126" spans="13:19">
+      <c r="M126" t="s">
+        <v>17</v>
+      </c>
+      <c r="N126" t="s">
+        <v>488</v>
+      </c>
+      <c r="O126" t="s">
+        <v>243</v>
+      </c>
+      <c r="P126" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>25</v>
+      </c>
+      <c r="R126" t="s">
+        <v>35</v>
+      </c>
+      <c r="S126" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="127" spans="13:19">
+      <c r="M127" t="s">
+        <v>17</v>
+      </c>
+      <c r="N127" t="s">
+        <v>490</v>
+      </c>
+      <c r="O127" t="s">
+        <v>243</v>
+      </c>
+      <c r="P127" t="s">
+        <v>491</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>25</v>
+      </c>
+      <c r="R127" t="s">
+        <v>35</v>
+      </c>
+      <c r="S127" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="128" spans="13:19">
+      <c r="M128" t="s">
+        <v>17</v>
+      </c>
+      <c r="N128" t="s">
+        <v>492</v>
+      </c>
+      <c r="O128" t="s">
+        <v>243</v>
+      </c>
+      <c r="P128" t="s">
+        <v>493</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>25</v>
+      </c>
+      <c r="R128" t="s">
+        <v>35</v>
+      </c>
+      <c r="S128" t="s">
         <v>247</v>
       </c>
     </row>
@@ -12099,15 +13186,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A39735C-B147-4873-BE33-BF7570891F36}">
   <dimension ref="B3:G33"/>
-  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="6" customWidth="1"/>
-    <col min="2" max="2" width="11.86328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3984375" style="6"/>
-    <col min="4" max="4" width="14.1328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.86328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.86328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.3984375" style="6"/>
+    <col min="1" max="1" width="9.140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="6"/>
+    <col min="4" max="4" width="14.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:7">
@@ -12138,7 +13225,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="14.25">
+    <row r="12" spans="2:7" ht="15">
       <c r="B12" s="7" t="s">
         <v>42</v>
       </c>
@@ -12158,7 +13245,7 @@
         <v>msy5_2050</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="14.25">
+    <row r="13" spans="2:7" ht="15">
       <c r="B13" s="9">
         <v>1</v>
       </c>
@@ -12166,7 +13253,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="14.25">
+    <row r="14" spans="2:7" ht="15">
       <c r="B14" s="9">
         <v>5</v>
       </c>
@@ -12186,7 +13273,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="14.25">
+    <row r="15" spans="2:7" ht="15">
       <c r="B15" s="9">
         <v>5</v>
       </c>
@@ -12206,7 +13293,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="14.25">
+    <row r="16" spans="2:7" ht="15">
       <c r="B16" s="9">
         <v>10</v>
       </c>
@@ -12226,7 +13313,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="14.25">
+    <row r="17" spans="2:7" ht="15">
       <c r="B17" s="9">
         <v>10</v>
       </c>
@@ -12246,7 +13333,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="14.25">
+    <row r="18" spans="2:7" ht="15">
       <c r="B18" s="9">
         <v>10</v>
       </c>
@@ -12266,7 +13353,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="14.25">
+    <row r="19" spans="2:7" ht="15">
       <c r="B19" s="9">
         <v>10</v>
       </c>
@@ -12282,7 +13369,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="14.25">
+    <row r="20" spans="2:7" ht="15">
       <c r="B20" s="9">
         <v>10</v>
       </c>
@@ -12294,7 +13381,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="14.25">
+    <row r="21" spans="2:7" ht="15">
       <c r="B21" s="9">
         <v>10</v>
       </c>
@@ -12302,7 +13389,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="14.25">
+    <row r="22" spans="2:7" ht="15">
       <c r="B22" s="9">
         <v>10</v>
       </c>
@@ -12310,7 +13397,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="14.25">
+    <row r="23" spans="2:7" ht="15">
       <c r="B23" s="9">
         <v>10</v>
       </c>
@@ -12318,7 +13405,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="14.25">
+    <row r="24" spans="2:7" ht="15">
       <c r="B24" s="9">
         <v>10</v>
       </c>
@@ -12326,46 +13413,46 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="14.25">
+    <row r="25" spans="2:7" ht="15">
       <c r="B25" s="9"/>
       <c r="D25" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="14.25">
+    <row r="26" spans="2:7" ht="15">
       <c r="B26" s="9"/>
       <c r="D26" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="14.25">
+    <row r="27" spans="2:7" ht="15">
       <c r="B27" s="9"/>
       <c r="D27" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14.25">
+    <row r="28" spans="2:7" ht="15">
       <c r="B28" s="9"/>
       <c r="D28" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="14.25">
+    <row r="29" spans="2:7" ht="15">
       <c r="B29" s="9"/>
       <c r="D29" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="14.25">
+    <row r="30" spans="2:7" ht="15">
       <c r="B30" s="9"/>
     </row>
-    <row r="31" spans="2:7" ht="14.25">
+    <row r="31" spans="2:7" ht="15">
       <c r="B31" s="9"/>
     </row>
-    <row r="32" spans="2:7" ht="14.25">
+    <row r="32" spans="2:7" ht="15">
       <c r="B32" s="9"/>
     </row>
-    <row r="33" spans="2:2" ht="14.25">
+    <row r="33" spans="2:2" ht="15">
       <c r="B33" s="9"/>
     </row>
   </sheetData>
@@ -12377,21 +13464,21 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
   <dimension ref="B1:N42"/>
-  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" style="11"/>
-    <col min="2" max="2" width="8.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.1328125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.46484375" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.46484375" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.9296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.9296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.1328125" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.53125" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.73046875" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.3984375" style="11"/>
+    <col min="1" max="1" width="11.42578125" style="11"/>
+    <col min="2" max="2" width="8.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.42578125" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="12.75">
@@ -12623,7 +13710,7 @@
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
     </row>
-    <row r="21" spans="2:14" ht="14.25">
+    <row r="21" spans="2:14" ht="15">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -12638,7 +13725,7 @@
       <c r="M21"/>
       <c r="N21"/>
     </row>
-    <row r="22" spans="2:14" ht="14.25">
+    <row r="22" spans="2:14" ht="15">
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
@@ -12653,7 +13740,7 @@
       <c r="M22"/>
       <c r="N22"/>
     </row>
-    <row r="23" spans="2:14" ht="14.25">
+    <row r="23" spans="2:14" ht="15">
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
@@ -12668,7 +13755,7 @@
       <c r="M23"/>
       <c r="N23"/>
     </row>
-    <row r="24" spans="2:14" ht="14.25">
+    <row r="24" spans="2:14" ht="15">
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
@@ -12683,7 +13770,7 @@
       <c r="M24"/>
       <c r="N24"/>
     </row>
-    <row r="25" spans="2:14" ht="14.25">
+    <row r="25" spans="2:14" ht="15">
       <c r="B25"/>
       <c r="C25"/>
       <c r="D25"/>
@@ -12698,7 +13785,7 @@
       <c r="M25"/>
       <c r="N25"/>
     </row>
-    <row r="26" spans="2:14" ht="14.25">
+    <row r="26" spans="2:14" ht="15">
       <c r="B26"/>
       <c r="C26"/>
       <c r="D26"/>
@@ -12713,7 +13800,7 @@
       <c r="M26"/>
       <c r="N26"/>
     </row>
-    <row r="27" spans="2:14" ht="14.25">
+    <row r="27" spans="2:14" ht="15">
       <c r="B27"/>
       <c r="C27"/>
       <c r="D27"/>
@@ -12728,7 +13815,7 @@
       <c r="M27"/>
       <c r="N27"/>
     </row>
-    <row r="28" spans="2:14" ht="14.25">
+    <row r="28" spans="2:14" ht="15">
       <c r="B28"/>
       <c r="C28"/>
       <c r="D28"/>
@@ -12743,7 +13830,7 @@
       <c r="M28"/>
       <c r="N28"/>
     </row>
-    <row r="29" spans="2:14" ht="14.25">
+    <row r="29" spans="2:14" ht="15">
       <c r="B29"/>
       <c r="C29"/>
       <c r="D29"/>
@@ -12758,7 +13845,7 @@
       <c r="M29"/>
       <c r="N29"/>
     </row>
-    <row r="30" spans="2:14" ht="14.25">
+    <row r="30" spans="2:14" ht="15">
       <c r="B30"/>
       <c r="C30"/>
       <c r="D30"/>
@@ -12773,7 +13860,7 @@
       <c r="M30"/>
       <c r="N30"/>
     </row>
-    <row r="31" spans="2:14" ht="14.25">
+    <row r="31" spans="2:14" ht="15">
       <c r="B31"/>
       <c r="C31"/>
       <c r="D31"/>
@@ -12788,7 +13875,7 @@
       <c r="M31"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="2:14" ht="14.25">
+    <row r="32" spans="2:14" ht="15">
       <c r="B32"/>
       <c r="C32"/>
       <c r="D32"/>
@@ -12803,7 +13890,7 @@
       <c r="M32"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="2:14" ht="14.25">
+    <row r="33" spans="2:14" ht="15">
       <c r="B33"/>
       <c r="C33"/>
       <c r="D33"/>
@@ -12818,7 +13905,7 @@
       <c r="M33"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="2:14" ht="14.25">
+    <row r="34" spans="2:14" ht="15">
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
@@ -12833,7 +13920,7 @@
       <c r="M34"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="2:14" ht="14.25">
+    <row r="35" spans="2:14" ht="15">
       <c r="B35"/>
       <c r="C35"/>
       <c r="D35"/>
@@ -12848,7 +13935,7 @@
       <c r="M35"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="2:14" ht="14.25">
+    <row r="36" spans="2:14" ht="15">
       <c r="B36"/>
       <c r="C36"/>
       <c r="D36"/>
@@ -12863,7 +13950,7 @@
       <c r="M36"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="2:14" ht="14.25">
+    <row r="37" spans="2:14" ht="15">
       <c r="B37"/>
       <c r="C37"/>
       <c r="D37"/>
@@ -12878,7 +13965,7 @@
       <c r="M37"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="2:14" ht="14.25">
+    <row r="38" spans="2:14" ht="15">
       <c r="B38"/>
       <c r="C38"/>
       <c r="D38"/>
@@ -12893,7 +13980,7 @@
       <c r="M38"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="2:14" ht="14.25">
+    <row r="39" spans="2:14" ht="15">
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
@@ -12908,7 +13995,7 @@
       <c r="M39"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="2:14" ht="14.25">
+    <row r="40" spans="2:14" ht="15">
       <c r="B40"/>
       <c r="C40"/>
       <c r="D40"/>
@@ -12923,7 +14010,7 @@
       <c r="M40"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="2:14" ht="14.25">
+    <row r="41" spans="2:14" ht="15">
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
@@ -12938,7 +14025,7 @@
       <c r="M41"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="2:14" ht="14.25">
+    <row r="42" spans="2:14" ht="15">
       <c r="B42"/>
       <c r="C42"/>
       <c r="D42"/>
@@ -12963,25 +14050,25 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EBD23C-EA82-4040-97D7-F532F0547462}">
   <dimension ref="A2:N102"/>
-  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" style="11"/>
-    <col min="2" max="2" width="12.73046875" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.3984375" style="11"/>
-    <col min="5" max="5" width="13.53125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.59765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.3984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.9296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.3984375" style="11"/>
-    <col min="12" max="12" width="17.19921875" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.73046875" style="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.3984375" style="11"/>
+    <col min="1" max="1" width="11.42578125" style="11"/>
+    <col min="2" max="2" width="12.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.42578125" style="11"/>
+    <col min="5" max="5" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="11"/>
+    <col min="12" max="12" width="17.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" ht="17.25" thickBot="1">
+    <row r="2" spans="1:14" ht="18" thickBot="1">
       <c r="A2" s="13"/>
       <c r="B2" s="20" t="s">
         <v>68</v>
@@ -12995,7 +14082,7 @@
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14" ht="15" thickTop="1" thickBot="1">
+    <row r="3" spans="1:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="A3" s="13"/>
       <c r="B3" s="4" t="s">
         <v>70</v>
@@ -13028,7 +14115,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="13.15">
+    <row r="4" spans="1:14" ht="12.75">
       <c r="A4" s="13"/>
       <c r="B4" s="19" t="s">
         <v>134</v>
@@ -13053,7 +14140,7 @@
         <v>1055.55</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="13.15">
+    <row r="5" spans="1:14" ht="12.75">
       <c r="A5" s="13"/>
       <c r="B5" s="19" t="s">
         <v>72</v>
@@ -13080,7 +14167,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="13.15">
+    <row r="6" spans="1:14" ht="12.75">
       <c r="A6" s="13"/>
       <c r="B6" s="19" t="s">
         <v>73</v>
@@ -13101,7 +14188,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="13.15">
+    <row r="7" spans="1:14" ht="12.75">
       <c r="A7" s="13"/>
       <c r="B7" s="19" t="s">
         <v>74</v>
@@ -13122,7 +14209,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="13.15">
+    <row r="8" spans="1:14" ht="12.75">
       <c r="A8" s="13"/>
       <c r="B8" s="19" t="s">
         <v>75</v>
@@ -13149,7 +14236,7 @@
         <v>1.05555</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="13.15">
+    <row r="9" spans="1:14" ht="12.75">
       <c r="A9" s="13"/>
       <c r="B9" s="19" t="s">
         <v>76</v>
@@ -13176,7 +14263,7 @@
         <v>4.1868000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="13.15">
+    <row r="10" spans="1:14" ht="12.75">
       <c r="A10" s="13"/>
       <c r="B10" s="19" t="s">
         <v>78</v>
@@ -13203,7 +14290,7 @@
         <v>41.868000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="13.15">
+    <row r="11" spans="1:14" ht="12.75">
       <c r="A11" s="13"/>
       <c r="B11" s="19" t="s">
         <v>71</v>
@@ -13230,7 +14317,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="13.15">
+    <row r="12" spans="1:14" ht="12.75">
       <c r="A12" s="13"/>
       <c r="B12" s="19" t="s">
         <v>82</v>
@@ -13257,7 +14344,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="13.15">
+    <row r="13" spans="1:14" ht="12.75">
       <c r="A13" s="13"/>
       <c r="B13" s="19" t="s">
         <v>85</v>
@@ -13284,7 +14371,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="13.15">
+    <row r="14" spans="1:14" ht="12.75">
       <c r="A14" s="13"/>
       <c r="B14" s="19" t="s">
         <v>87</v>
@@ -13311,7 +14398,7 @@
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="13.15">
+    <row r="15" spans="1:14" ht="12.75">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>90</v>
@@ -13338,7 +14425,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="13.15">
+    <row r="16" spans="1:14" ht="12.75">
       <c r="A16" s="13"/>
       <c r="B16" s="19" t="s">
         <v>93</v>
@@ -13365,7 +14452,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="13.15">
+    <row r="17" spans="1:14" ht="12.75">
       <c r="A17" s="13"/>
       <c r="B17" s="19" t="s">
         <v>95</v>
@@ -13392,7 +14479,7 @@
         <v>37.68</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="13.15">
+    <row r="18" spans="1:14" ht="12.75">
       <c r="B18" s="19" t="s">
         <v>97</v>
       </c>
@@ -13418,7 +14505,7 @@
         <v>2139.4548</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="13.15">
+    <row r="19" spans="1:14" ht="12.75">
       <c r="B19" s="19" t="s">
         <v>99</v>
       </c>
@@ -13444,7 +14531,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="13.15">
+    <row r="20" spans="1:14" ht="12.75">
       <c r="B20" s="19" t="s">
         <v>101</v>
       </c>
@@ -13470,7 +14557,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="13.15">
+    <row r="21" spans="1:14" ht="12.75">
       <c r="B21" s="19" t="s">
         <v>103</v>
       </c>
@@ -13496,7 +14583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="13.15">
+    <row r="22" spans="1:14" ht="12.75">
       <c r="B22" s="19" t="s">
         <v>106</v>
       </c>
@@ -13522,7 +14609,7 @@
         <v>31.536000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="13.15">
+    <row r="23" spans="1:14" ht="12.75">
       <c r="B23" s="19" t="s">
         <v>109</v>
       </c>
@@ -13548,7 +14635,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="13.15">
+    <row r="24" spans="1:14" ht="12.75">
       <c r="B24" s="19" t="s">
         <v>112</v>
       </c>
@@ -13574,7 +14661,7 @@
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="13.15">
+    <row r="25" spans="1:14" ht="12.75">
       <c r="B25" s="19" t="s">
         <v>114</v>
       </c>
@@ -13600,7 +14687,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="13.15">
+    <row r="26" spans="1:14" ht="12.75">
       <c r="B26" s="19" t="s">
         <v>116</v>
       </c>
@@ -13617,7 +14704,7 @@
         <v>1.4198999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="13.15">
+    <row r="27" spans="1:14" ht="12.75">
       <c r="B27" s="19" t="s">
         <v>118</v>
       </c>
@@ -13634,7 +14721,7 @@
         <v>1.3986000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="13.15">
+    <row r="28" spans="1:14" ht="12.75">
       <c r="B28" s="19" t="s">
         <v>121</v>
       </c>
@@ -13651,7 +14738,7 @@
         <v>1.3727</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="13.15">
+    <row r="29" spans="1:14" ht="12.75">
       <c r="B29" s="19" t="s">
         <v>123</v>
       </c>
@@ -13668,7 +14755,7 @@
         <v>1.3369</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="13.15">
+    <row r="30" spans="1:14" ht="12.75">
       <c r="B30" s="19" t="s">
         <v>124</v>
       </c>
@@ -13685,7 +14772,7 @@
         <v>1.2967</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="13.15">
+    <row r="31" spans="1:14" ht="12.75">
       <c r="B31" s="19" t="s">
         <v>126</v>
       </c>
@@ -13702,7 +14789,7 @@
         <v>1.2583</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="13.15">
+    <row r="32" spans="1:14" ht="12.75">
       <c r="B32" s="19" t="s">
         <v>128</v>
       </c>
@@ -13719,7 +14806,7 @@
         <v>1.2253000000000001</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="13.15">
+    <row r="33" spans="2:9" ht="12.75">
       <c r="B33" s="19" t="s">
         <v>130</v>
       </c>
@@ -13736,7 +14823,7 @@
         <v>1.2023999999999999</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="13.15">
+    <row r="34" spans="2:9" ht="12.75">
       <c r="B34" s="19" t="s">
         <v>132</v>
       </c>
@@ -13753,7 +14840,7 @@
         <v>1.1931</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="13.15">
+    <row r="35" spans="2:9" ht="12.75">
       <c r="B35" s="19" t="s">
         <v>133</v>
       </c>
@@ -13770,7 +14857,7 @@
         <v>1.1793</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="13.15">
+    <row r="36" spans="2:9" ht="12.75">
       <c r="B36" s="19" t="s">
         <v>134</v>
       </c>
@@ -13787,7 +14874,7 @@
         <v>1.1552</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="13.15">
+    <row r="37" spans="2:9" ht="12.75">
       <c r="B37" s="19" t="s">
         <v>135</v>
       </c>
@@ -13804,7 +14891,7 @@
         <v>1.1334</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="13.15">
+    <row r="38" spans="2:9" ht="12.75">
       <c r="B38" s="19" t="s">
         <v>136</v>
       </c>
@@ -13821,7 +14908,7 @@
         <v>1.1136999999999999</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="13.15">
+    <row r="39" spans="2:9" ht="12.75">
       <c r="B39" s="19" t="s">
         <v>137</v>
       </c>
@@ -13838,7 +14925,7 @@
         <v>1.0934999999999999</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="13.15">
+    <row r="40" spans="2:9" ht="12.75">
       <c r="B40" s="19" t="s">
         <v>138</v>
       </c>
@@ -13855,7 +14942,7 @@
         <v>1.0831</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="13.15">
+    <row r="41" spans="2:9" ht="12.75">
       <c r="B41" s="19" t="s">
         <v>139</v>
       </c>
@@ -13872,7 +14959,7 @@
         <v>1.0719000000000001</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="13.15">
+    <row r="42" spans="2:9" ht="12.75">
       <c r="B42" s="19" t="s">
         <v>140</v>
       </c>
@@ -13889,7 +14976,7 @@
         <v>1.0519000000000001</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="13.15">
+    <row r="43" spans="2:9" ht="12.75">
       <c r="B43" s="19" t="s">
         <v>141</v>
       </c>
@@ -13906,7 +14993,7 @@
         <v>1.0274000000000001</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="13.15">
+    <row r="44" spans="2:9" ht="12.75">
       <c r="B44" s="19" t="s">
         <v>142</v>
       </c>
@@ -13923,7 +15010,7 @@
         <v>1.0091000000000001</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="13.15">
+    <row r="45" spans="2:9" ht="12.75">
       <c r="B45" s="19" t="s">
         <v>143</v>
       </c>
@@ -13940,7 +15027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="13.15">
+    <row r="46" spans="2:9" ht="12.75">
       <c r="B46" s="19" t="s">
         <v>144</v>
       </c>
@@ -13957,7 +15044,7 @@
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="13.15">
+    <row r="47" spans="2:9" ht="12.75">
       <c r="B47" s="19" t="s">
         <v>145</v>
       </c>
@@ -13974,7 +15061,7 @@
         <v>0.97809999999999997</v>
       </c>
     </row>
-    <row r="48" spans="2:9" ht="13.15">
+    <row r="48" spans="2:9" ht="12.75">
       <c r="B48" s="19" t="s">
         <v>146</v>
       </c>
@@ -13991,7 +15078,7 @@
         <v>0.96499999999999997</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="13.15">
+    <row r="49" spans="2:9" ht="12.75">
       <c r="B49" s="19" t="s">
         <v>147</v>
       </c>
@@ -14008,7 +15095,7 @@
         <v>0.94910000000000005</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="13.15">
+    <row r="50" spans="2:9" ht="12.75">
       <c r="B50" s="19" t="s">
         <v>148</v>
       </c>
@@ -14025,7 +15112,7 @@
         <v>0.92969999999999997</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="13.15">
+    <row r="51" spans="2:9" ht="12.75">
       <c r="B51" s="19" t="s">
         <v>149</v>
       </c>
@@ -14045,7 +15132,7 @@
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="13.15">
+    <row r="52" spans="2:9" ht="12.75">
       <c r="B52" s="19" t="s">
         <v>150</v>
       </c>
@@ -14059,7 +15146,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="13.15">
+    <row r="53" spans="2:9" ht="12.75">
       <c r="B53" s="19" t="s">
         <v>151</v>
       </c>
@@ -14073,7 +15160,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="13.15">
+    <row r="54" spans="2:9" ht="12.75">
       <c r="B54" s="19" t="s">
         <v>152</v>
       </c>
@@ -14539,12 +15626,12 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="99" spans="5:10" ht="17.25" thickBot="1">
+    <row r="99" spans="5:10" ht="18" thickBot="1">
       <c r="E99" s="20" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="100" spans="5:10" ht="15" thickTop="1" thickBot="1">
+    <row r="100" spans="5:10" ht="16.5" thickTop="1" thickBot="1">
       <c r="E100" s="4" t="s">
         <v>49</v>
       </c>
@@ -14564,7 +15651,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="101" spans="5:10" ht="14.25">
+    <row r="101" spans="5:10" ht="15">
       <c r="E101"/>
       <c r="F101" s="21" t="s">
         <v>189</v>
@@ -14580,7 +15667,7 @@
         <v>1.201442041042708</v>
       </c>
     </row>
-    <row r="102" spans="5:10" ht="14.25">
+    <row r="102" spans="5:10" ht="15">
       <c r="E102"/>
       <c r="F102" s="21" t="s">
         <v>191</v>
@@ -14603,19 +15690,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE1F0D2-7682-484B-9627-54FDDA96E26C}">
   <dimension ref="B3:D33"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="2" width="8.86328125" style="6"/>
-    <col min="3" max="3" width="20.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.86328125" style="6"/>
+    <col min="1" max="2" width="8.85546875" style="6"/>
+    <col min="3" max="3" width="20.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" ht="17.25" thickBot="1">
+    <row r="3" spans="2:4" ht="18" thickBot="1">
       <c r="B3" s="20" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="15" thickTop="1" thickBot="1">
+    <row r="4" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
       <c r="B4" s="4" t="s">
         <v>51</v>
       </c>
@@ -14807,12 +15894,12 @@
         <v>170</v>
       </c>
     </row>
-    <row r="25" spans="2:4" ht="17.25" thickBot="1">
+    <row r="25" spans="2:4" ht="18" thickBot="1">
       <c r="B25" s="20" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="15" thickTop="1" thickBot="1">
+    <row r="26" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
       <c r="B26" s="4" t="s">
         <v>172</v>
       </c>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan51\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DCEA5B9-58ED-463B-9F4B-3853FAC5D635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D132E7B6-90EB-42E2-B216-D607FBFE2513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2939" uniqueCount="873">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="803">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -802,13 +802,13 @@
     <t>elc_spv_POL_004</t>
   </si>
   <si>
-    <t>solar electricity near Warsaw (cluster 4)</t>
+    <t>solar electricity near Wroclaw (cluster 4)</t>
   </si>
   <si>
     <t>elc_spv_POL_005</t>
   </si>
   <si>
-    <t>solar electricity near Siedlce (cluster 5)</t>
+    <t>solar electricity near Wroclaw (cluster 5)</t>
   </si>
   <si>
     <t>elc_spv_POL_006</t>
@@ -820,307 +820,253 @@
     <t>elc_spv_POL_007</t>
   </si>
   <si>
-    <t>solar electricity near Rzeszow (cluster 7)</t>
+    <t>solar electricity near Olsztyn (cluster 7)</t>
   </si>
   <si>
     <t>elc_spv_POL_008</t>
   </si>
   <si>
-    <t>solar electricity near Olsztyn (cluster 8)</t>
+    <t>solar electricity near Slupsk (cluster 8)</t>
   </si>
   <si>
     <t>elc_spv_POL_009</t>
   </si>
   <si>
-    <t>solar electricity near Szczecin (cluster 9)</t>
+    <t>solar electricity near Olsztyn (cluster 9)</t>
   </si>
   <si>
     <t>elc_spv_POL_010</t>
   </si>
   <si>
-    <t>solar electricity near Slupsk (cluster 10)</t>
+    <t>solar electricity near Legnica (cluster 10)</t>
   </si>
   <si>
     <t>elc_spv_POL_011</t>
   </si>
   <si>
-    <t>solar electricity near Olsztyn (cluster 11)</t>
+    <t>solar electricity near Gdansk (cluster 11)</t>
   </si>
   <si>
     <t>elc_spv_POL_012</t>
   </si>
   <si>
-    <t>solar electricity near Legnica (cluster 12)</t>
+    <t>solar electricity near Lomza (cluster 12)</t>
   </si>
   <si>
     <t>elc_spv_POL_013</t>
   </si>
   <si>
-    <t>solar electricity near Gdansk (cluster 13)</t>
+    <t>solar electricity near Zielona Gora (cluster 13)</t>
   </si>
   <si>
     <t>elc_spv_POL_014</t>
   </si>
   <si>
-    <t>solar electricity near Warsaw (cluster 14)</t>
+    <t>solar electricity near Szczecin (cluster 14)</t>
   </si>
   <si>
     <t>elc_spv_POL_015</t>
   </si>
   <si>
-    <t>solar electricity near Lomza (cluster 15)</t>
+    <t>solar electricity near Rzeszow (cluster 15)</t>
   </si>
   <si>
     <t>elc_spv_POL_016</t>
   </si>
   <si>
-    <t>solar electricity near Rybnik (cluster 16)</t>
+    <t>solar electricity near Suwalki (cluster 16)</t>
   </si>
   <si>
     <t>elc_spv_POL_017</t>
   </si>
   <si>
-    <t>solar electricity near Zielona Gora (cluster 17)</t>
+    <t>solar electricity near Lodz (cluster 17)</t>
   </si>
   <si>
     <t>elc_spv_POL_018</t>
   </si>
   <si>
-    <t>solar electricity near Szczecin (cluster 18)</t>
+    <t>solar electricity near Lodz (cluster 18)</t>
   </si>
   <si>
     <t>elc_spv_POL_019</t>
   </si>
   <si>
-    <t>solar electricity near Lublin (cluster 19)</t>
+    <t>solar electricity near Zamosc (cluster 19)</t>
   </si>
   <si>
     <t>elc_spv_POL_020</t>
   </si>
   <si>
-    <t>solar electricity near Suwalki (cluster 20)</t>
+    <t>solar electricity near Koszalin (cluster 20)</t>
   </si>
   <si>
     <t>elc_spv_POL_021</t>
   </si>
   <si>
-    <t>solar electricity near Rzeszow (cluster 21)</t>
+    <t>solar electricity near Zielona Gora (cluster 21)</t>
   </si>
   <si>
     <t>elc_spv_POL_022</t>
   </si>
   <si>
-    <t>solar electricity near Lodz (cluster 22)</t>
+    <t>solar electricity near Katowice (cluster 22)</t>
   </si>
   <si>
     <t>elc_spv_POL_023</t>
   </si>
   <si>
-    <t>solar electricity near Warsaw (cluster 23)</t>
+    <t>solar electricity near Tarnow (cluster 23)</t>
   </si>
   <si>
     <t>elc_spv_POL_024</t>
   </si>
   <si>
-    <t>solar electricity near Koszalin (cluster 24)</t>
+    <t>solar electricity near Lublin (cluster 24)</t>
   </si>
   <si>
     <t>elc_spv_POL_025</t>
   </si>
   <si>
-    <t>solar electricity near Koszalin (cluster 25)</t>
+    <t>solar electricity near Rzeszow (cluster 25)</t>
   </si>
   <si>
     <t>elc_spv_POL_026</t>
   </si>
   <si>
-    <t>solar electricity near Zielona Gora (cluster 26)</t>
+    <t>solar electricity near Kielce (cluster 26)</t>
   </si>
   <si>
     <t>elc_spv_POL_027</t>
   </si>
   <si>
-    <t>solar electricity near Katowice (cluster 27)</t>
+    <t>solar electricity near Mielec (cluster 27)</t>
   </si>
   <si>
     <t>elc_spv_POL_028</t>
   </si>
   <si>
-    <t>solar electricity near Kedzierzyn-Kozle (cluster 28)</t>
+    <t>solar electricity near Stalowa Wola (cluster 28)</t>
   </si>
   <si>
     <t>elc_spv_POL_029</t>
   </si>
   <si>
-    <t>solar electricity near Krakow (cluster 29)</t>
+    <t>solar electricity near Czestochowa (cluster 29)</t>
   </si>
   <si>
     <t>elc_spv_POL_030</t>
   </si>
   <si>
-    <t>solar electricity near Tarnow (cluster 30)</t>
+    <t>solar electricity near Torun (cluster 30)</t>
   </si>
   <si>
     <t>elc_spv_POL_031</t>
   </si>
   <si>
-    <t>solar electricity near Chelm (cluster 31)</t>
+    <t>solar electricity near Ostrowiec Swietokrzyski (cluster 31)</t>
   </si>
   <si>
     <t>elc_spv_POL_032</t>
   </si>
   <si>
-    <t>solar electricity near Radom (cluster 32)</t>
+    <t>solar electricity near Opole (cluster 32)</t>
   </si>
   <si>
     <t>elc_spv_POL_033</t>
   </si>
   <si>
-    <t>solar electricity near Mielec (cluster 33)</t>
+    <t>solar electricity near Konin (cluster 33)</t>
   </si>
   <si>
     <t>elc_spv_POL_034</t>
   </si>
   <si>
-    <t>solar electricity near Rzeszow (cluster 34)</t>
+    <t>solar electricity near Koszalin (cluster 34)</t>
   </si>
   <si>
     <t>elc_spv_POL_035</t>
   </si>
   <si>
-    <t>solar electricity near Czestochowa (cluster 35)</t>
+    <t>solar electricity near Warsaw (cluster 35)</t>
   </si>
   <si>
     <t>elc_spv_POL_036</t>
   </si>
   <si>
-    <t>solar electricity near Pila (cluster 36)</t>
+    <t>solar electricity near Katowice (cluster 36)</t>
   </si>
   <si>
     <t>elc_spv_POL_037</t>
   </si>
   <si>
-    <t>solar electricity near Torun (cluster 37)</t>
+    <t>solar electricity near Elk (cluster 37)</t>
   </si>
   <si>
     <t>elc_spv_POL_038</t>
   </si>
   <si>
-    <t>solar electricity near Skarzysko-Kamienna (cluster 38)</t>
+    <t>solar electricity near Poznan (cluster 38)</t>
   </si>
   <si>
     <t>elc_spv_POL_039</t>
   </si>
   <si>
-    <t>solar electricity near Wroclaw (cluster 39)</t>
+    <t>solar electricity near Opole (cluster 39)</t>
   </si>
   <si>
     <t>elc_spv_POL_040</t>
   </si>
   <si>
-    <t>solar electricity near Konin (cluster 40)</t>
+    <t>solar electricity near Szczecin (cluster 40)</t>
   </si>
   <si>
     <t>elc_spv_POL_041</t>
   </si>
   <si>
-    <t>solar electricity near Kalisz (cluster 41)</t>
+    <t>solar electricity near Krakow (cluster 41)</t>
   </si>
   <si>
     <t>elc_spv_POL_042</t>
   </si>
   <si>
-    <t>solar electricity near Koszalin (cluster 42)</t>
+    <t>solar electricity near Krakow (cluster 42)</t>
   </si>
   <si>
     <t>elc_spv_POL_043</t>
   </si>
   <si>
-    <t>solar electricity near Walbrzych (cluster 43)</t>
+    <t>solar electricity near Elblag (cluster 43)</t>
   </si>
   <si>
     <t>elc_spv_POL_044</t>
   </si>
   <si>
-    <t>solar electricity near Warsaw (cluster 44)</t>
+    <t>solar electricity near Plock (cluster 44)</t>
   </si>
   <si>
     <t>elc_spv_POL_045</t>
   </si>
   <si>
-    <t>solar electricity near Lodz (cluster 45)</t>
+    <t>solar electricity near Wroclaw (cluster 45)</t>
   </si>
   <si>
     <t>elc_spv_POL_046</t>
   </si>
   <si>
-    <t>solar electricity near Elk (cluster 46)</t>
+    <t>solar electricity near Gdansk (cluster 46)</t>
   </si>
   <si>
     <t>elc_spv_POL_047</t>
   </si>
   <si>
-    <t>solar electricity near Poznan (cluster 47)</t>
+    <t>solar electricity near Krakow (cluster 47)</t>
   </si>
   <si>
     <t>elc_spv_POL_048</t>
   </si>
   <si>
-    <t>solar electricity near Opole (cluster 48)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_049</t>
-  </si>
-  <si>
-    <t>solar electricity near Gdansk (cluster 49)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_050</t>
-  </si>
-  <si>
-    <t>solar electricity near Szczecin (cluster 50)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_051</t>
-  </si>
-  <si>
-    <t>solar electricity near Krakow (cluster 51)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_052</t>
-  </si>
-  <si>
-    <t>solar electricity near Krakow (cluster 52)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_053</t>
-  </si>
-  <si>
-    <t>solar electricity near Grudziadz (cluster 53)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_054</t>
-  </si>
-  <si>
-    <t>solar electricity near Plock (cluster 54)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_055</t>
-  </si>
-  <si>
-    <t>solar electricity near Wroclaw (cluster 55)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_056</t>
-  </si>
-  <si>
-    <t>solar electricity near Gdansk (cluster 56)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_057</t>
-  </si>
-  <si>
-    <t>solar electricity near Lublin (cluster 57)</t>
+    <t>solar electricity near Lublin (cluster 48)</t>
   </si>
   <si>
     <t>elc_wof_POL_001</t>
@@ -1138,7 +1084,7 @@
     <t>elc_wof_POL_003</t>
   </si>
   <si>
-    <t>wind offshore electricity near Szczecin (cluster 3)</t>
+    <t>wind offshore electricity near Koszalin (cluster 3)</t>
   </si>
   <si>
     <t>elc_wof_POL_004</t>
@@ -1156,13 +1102,13 @@
     <t>elc_wof_POL_006</t>
   </si>
   <si>
-    <t>wind offshore electricity near Slupsk (cluster 6)</t>
+    <t>wind offshore electricity near Koszalin (cluster 6)</t>
   </si>
   <si>
     <t>elc_wof_POL_007</t>
   </si>
   <si>
-    <t>wind offshore electricity near Slupsk (cluster 7)</t>
+    <t>wind offshore electricity near Koszalin (cluster 7)</t>
   </si>
   <si>
     <t>elc_wof_POL_008</t>
@@ -1204,325 +1150,253 @@
     <t>elc_won_POL_004</t>
   </si>
   <si>
-    <t>wind onshore electricity near Warsaw (cluster 4)</t>
+    <t>wind onshore electricity near Legnica (cluster 4)</t>
   </si>
   <si>
     <t>elc_won_POL_005</t>
   </si>
   <si>
-    <t>wind onshore electricity near Siedlce (cluster 5)</t>
+    <t>wind onshore electricity near Wroclaw (cluster 5)</t>
   </si>
   <si>
     <t>elc_won_POL_006</t>
   </si>
   <si>
-    <t>wind onshore electricity near Legnica (cluster 6)</t>
+    <t>wind onshore electricity near Wroclaw (cluster 6)</t>
   </si>
   <si>
     <t>elc_won_POL_007</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rzeszow (cluster 7)</t>
+    <t>wind onshore electricity near Olsztyn (cluster 7)</t>
   </si>
   <si>
     <t>elc_won_POL_008</t>
   </si>
   <si>
-    <t>wind onshore electricity near Olsztyn (cluster 8)</t>
+    <t>wind onshore electricity near Slupsk (cluster 8)</t>
   </si>
   <si>
     <t>elc_won_POL_009</t>
   </si>
   <si>
-    <t>wind onshore electricity near Szczecin (cluster 9)</t>
+    <t>wind onshore electricity near Olsztyn (cluster 9)</t>
   </si>
   <si>
     <t>elc_won_POL_010</t>
   </si>
   <si>
-    <t>wind onshore electricity near Slupsk (cluster 10)</t>
+    <t>wind onshore electricity near Legnica (cluster 10)</t>
   </si>
   <si>
     <t>elc_won_POL_011</t>
   </si>
   <si>
-    <t>wind onshore electricity near Olsztyn (cluster 11)</t>
+    <t>wind onshore electricity near Gdansk (cluster 11)</t>
   </si>
   <si>
     <t>elc_won_POL_012</t>
   </si>
   <si>
-    <t>wind onshore electricity near Legnica (cluster 12)</t>
+    <t>wind onshore electricity near Lomza (cluster 12)</t>
   </si>
   <si>
     <t>elc_won_POL_013</t>
   </si>
   <si>
-    <t>wind onshore electricity near Gdansk (cluster 13)</t>
+    <t>wind onshore electricity near Zielona Gora (cluster 13)</t>
   </si>
   <si>
     <t>elc_won_POL_014</t>
   </si>
   <si>
-    <t>wind onshore electricity near Warsaw (cluster 14)</t>
+    <t>wind onshore electricity near Szczecin (cluster 14)</t>
   </si>
   <si>
     <t>elc_won_POL_015</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lomza (cluster 15)</t>
+    <t>wind onshore electricity near Rzeszow (cluster 15)</t>
   </si>
   <si>
     <t>elc_won_POL_016</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rybnik (cluster 16)</t>
+    <t>wind onshore electricity near Suwalki (cluster 16)</t>
   </si>
   <si>
     <t>elc_won_POL_017</t>
   </si>
   <si>
-    <t>wind onshore electricity near Zielona Gora (cluster 17)</t>
+    <t>wind onshore electricity near Lodz (cluster 17)</t>
   </si>
   <si>
     <t>elc_won_POL_018</t>
   </si>
   <si>
-    <t>wind onshore electricity near Szczecin (cluster 18)</t>
+    <t>wind onshore electricity near Lodz (cluster 18)</t>
   </si>
   <si>
     <t>elc_won_POL_019</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lublin (cluster 19)</t>
+    <t>wind onshore electricity near Zamosc (cluster 19)</t>
   </si>
   <si>
     <t>elc_won_POL_020</t>
   </si>
   <si>
-    <t>wind onshore electricity near Suwalki (cluster 20)</t>
+    <t>wind onshore electricity near Koszalin (cluster 20)</t>
   </si>
   <si>
     <t>elc_won_POL_021</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rzeszow (cluster 21)</t>
+    <t>wind onshore electricity near Zielona Gora (cluster 21)</t>
   </si>
   <si>
     <t>elc_won_POL_022</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lodz (cluster 22)</t>
+    <t>wind onshore electricity near Tarnow (cluster 22)</t>
   </si>
   <si>
     <t>elc_won_POL_023</t>
   </si>
   <si>
-    <t>wind onshore electricity near Warsaw (cluster 23)</t>
+    <t>wind onshore electricity near Lublin (cluster 23)</t>
   </si>
   <si>
     <t>elc_won_POL_024</t>
   </si>
   <si>
-    <t>wind onshore electricity near Koszalin (cluster 24)</t>
+    <t>wind onshore electricity near Rzeszow (cluster 24)</t>
   </si>
   <si>
     <t>elc_won_POL_025</t>
   </si>
   <si>
-    <t>wind onshore electricity near Koszalin (cluster 25)</t>
+    <t>wind onshore electricity near Radom (cluster 25)</t>
   </si>
   <si>
     <t>elc_won_POL_026</t>
   </si>
   <si>
-    <t>wind onshore electricity near Zielona Gora (cluster 26)</t>
+    <t>wind onshore electricity near Mielec (cluster 26)</t>
   </si>
   <si>
     <t>elc_won_POL_027</t>
   </si>
   <si>
-    <t>wind onshore electricity near Katowice (cluster 27)</t>
+    <t>wind onshore electricity near Stalowa Wola (cluster 27)</t>
   </si>
   <si>
     <t>elc_won_POL_028</t>
   </si>
   <si>
-    <t>wind onshore electricity near Kedzierzyn-Kozle (cluster 28)</t>
+    <t>wind onshore electricity near Czestochowa (cluster 28)</t>
   </si>
   <si>
     <t>elc_won_POL_029</t>
   </si>
   <si>
-    <t>wind onshore electricity near Krakow (cluster 29)</t>
+    <t>wind onshore electricity near Torun (cluster 29)</t>
   </si>
   <si>
     <t>elc_won_POL_030</t>
   </si>
   <si>
-    <t>wind onshore electricity near Tarnow (cluster 30)</t>
+    <t>wind onshore electricity near Radom (cluster 30)</t>
   </si>
   <si>
     <t>elc_won_POL_031</t>
   </si>
   <si>
-    <t>wind onshore electricity near Chelm (cluster 31)</t>
+    <t>wind onshore electricity near Konin (cluster 31)</t>
   </si>
   <si>
     <t>elc_won_POL_032</t>
   </si>
   <si>
-    <t>wind onshore electricity near Radom (cluster 32)</t>
+    <t>wind onshore electricity near Koszalin (cluster 32)</t>
   </si>
   <si>
     <t>elc_won_POL_033</t>
   </si>
   <si>
-    <t>wind onshore electricity near Mielec (cluster 33)</t>
+    <t>wind onshore electricity near Warsaw (cluster 33)</t>
   </si>
   <si>
     <t>elc_won_POL_034</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rzeszow (cluster 34)</t>
+    <t>wind onshore electricity near Katowice (cluster 34)</t>
   </si>
   <si>
     <t>elc_won_POL_035</t>
   </si>
   <si>
-    <t>wind onshore electricity near Czestochowa (cluster 35)</t>
+    <t>wind onshore electricity near Elk (cluster 35)</t>
   </si>
   <si>
     <t>elc_won_POL_036</t>
   </si>
   <si>
-    <t>wind onshore electricity near Pila (cluster 36)</t>
+    <t>wind onshore electricity near Poznan (cluster 36)</t>
   </si>
   <si>
     <t>elc_won_POL_037</t>
   </si>
   <si>
-    <t>wind onshore electricity near Torun (cluster 37)</t>
+    <t>wind onshore electricity near Kedzierzyn-Kozle (cluster 37)</t>
   </si>
   <si>
     <t>elc_won_POL_038</t>
   </si>
   <si>
-    <t>wind onshore electricity near Skarzysko-Kamienna (cluster 38)</t>
+    <t>wind onshore electricity near Szczecin (cluster 38)</t>
   </si>
   <si>
     <t>elc_won_POL_039</t>
   </si>
   <si>
-    <t>wind onshore electricity near Wroclaw (cluster 39)</t>
+    <t>wind onshore electricity near Krakow (cluster 39)</t>
   </si>
   <si>
     <t>elc_won_POL_040</t>
   </si>
   <si>
-    <t>wind onshore electricity near Konin (cluster 40)</t>
+    <t>wind onshore electricity near Elblag (cluster 40)</t>
   </si>
   <si>
     <t>elc_won_POL_041</t>
   </si>
   <si>
-    <t>wind onshore electricity near Kalisz (cluster 41)</t>
+    <t>wind onshore electricity near Plock (cluster 41)</t>
   </si>
   <si>
     <t>elc_won_POL_042</t>
   </si>
   <si>
-    <t>wind onshore electricity near Koszalin (cluster 42)</t>
+    <t>wind onshore electricity near Kalisz (cluster 42)</t>
   </si>
   <si>
     <t>elc_won_POL_043</t>
   </si>
   <si>
-    <t>wind onshore electricity near Walbrzych (cluster 43)</t>
+    <t>wind onshore electricity near Gdansk (cluster 43)</t>
   </si>
   <si>
     <t>elc_won_POL_044</t>
   </si>
   <si>
-    <t>wind onshore electricity near Warsaw (cluster 44)</t>
+    <t>wind onshore electricity near Krakow (cluster 44)</t>
   </si>
   <si>
     <t>elc_won_POL_045</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lodz (cluster 45)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_046</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Elk (cluster 46)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_047</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Poznan (cluster 47)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_048</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Opole (cluster 48)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_049</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Gdansk (cluster 49)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_050</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Szczecin (cluster 50)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_051</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Krakow (cluster 51)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_052</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Krakow (cluster 52)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_053</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Grudziadz (cluster 53)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_054</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Plock (cluster 54)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_055</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Wroclaw (cluster 55)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_056</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Gdansk (cluster 56)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_057</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Lublin (cluster 57)</t>
+    <t>wind onshore electricity near Lublin (cluster 45)</t>
   </si>
   <si>
     <t>~fi_comm</t>
@@ -1549,310 +1423,250 @@
     <t>grid node -- way/111615226-220 (Legnica, 74 km)</t>
   </si>
   <si>
+    <t>e_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>grid node -- PL15-400 (Bydgoszcz, 10 km)</t>
+  </si>
+  <si>
     <t>e_Chelm_POL</t>
   </si>
   <si>
     <t>grid node -- way/194903381-400 (Chelm, 4 km)</t>
   </si>
   <si>
+    <t>e_Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/216060722-220 (Czestochowa, 4 km)</t>
+  </si>
+  <si>
     <t>e_Debica_POL</t>
   </si>
   <si>
+    <t>grid node -- way/198635989-220 (Rzeszow, 6 km)</t>
+  </si>
+  <si>
+    <t>e_Elk_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/303870256-400 (Elk, 8 km)</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/112614319-400 (Gdansk, 4 km)</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/86494356-400 (Gdansk, 54 km)</t>
+  </si>
+  <si>
+    <t>e_Gliwice_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/293489607-400 (Katowice, 21 km)</t>
+  </si>
+  <si>
+    <t>e_GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>grid node -- PL18-400 (Gorzow Wielkopolski, 15 km)</t>
+  </si>
+  <si>
+    <t>e_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/170259740-220 (Elk, 6 km)</t>
+  </si>
+  <si>
+    <t>e_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/46092396-400 (Grudziadz, 6 km)</t>
+  </si>
+  <si>
+    <t>e_Katowice_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/40946790-220 (Katowice, 19 km)</t>
+  </si>
+  <si>
+    <t>e_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/336990960-220 (Opole, 7 km)</t>
+  </si>
+  <si>
+    <t>e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/199098050-220 (Kielce, 16 km)</t>
+  </si>
+  <si>
+    <t>e_Konin_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/255284259-220 (Konin, 10 km)</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/178838661-220 (Koszalin, 40 km)</t>
+  </si>
+  <si>
+    <t>e_Krakow_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/87667718-220 (Krakow, 12 km)</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/166838338-400 (Rzeszow, 40 km)</t>
+  </si>
+  <si>
+    <t>e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>grid node -- PL7-400 (Grudziadz, 8 km)</t>
+  </si>
+  <si>
+    <t>e_Legnica_POL</t>
+  </si>
+  <si>
+    <t>grid node -- PL34-400 (Wroclaw, 43 km)</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/121656686-220 (Lomza, 31 km)</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/180535363-220 (Lubin, 33 km)</t>
+  </si>
+  <si>
+    <t>e_Mielec_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/199098053-220 (Mielec, 19 km)</t>
+  </si>
+  <si>
+    <t>e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>grid node -- PL36-400 (Wroclaw, 46 km)</t>
+  </si>
+  <si>
+    <t>e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/101915790-220 (Olsztyn, 4 km)</t>
+  </si>
+  <si>
+    <t>e_Opole_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/255277953-400 (Opole, 10 km)</t>
+  </si>
+  <si>
+    <t>e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/254235846-400 (Ostrowiec Swietokrzyski, 4 km)</t>
+  </si>
+  <si>
+    <t>e_PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/170316833-220 (Piotrkow Trybunalski, 3 km)</t>
+  </si>
+  <si>
+    <t>e_Plock_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/658600169-400 (Plock, 4 km)</t>
+  </si>
+  <si>
+    <t>e_Police_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/165763717-220 (Szczecin, 15 km)</t>
+  </si>
+  <si>
+    <t>e_Poznan_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/32036484-220 (Poznan, 11 km)</t>
+  </si>
+  <si>
+    <t>e_Pulawy_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/88544449-220 (Lublin, 46 km)</t>
+  </si>
+  <si>
+    <t>e_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/171917072-400 (Czestochowa, 41 km)</t>
+  </si>
+  <si>
+    <t>e_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/215282393-400 (Rzeszow, 20 km)</t>
+  </si>
+  <si>
+    <t>e_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>grid node -- relation/18085709-400 (Slupsk, 10 km)</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/183945016-220 (Katowice, 19 km)</t>
+  </si>
+  <si>
+    <t>e_Swidnica_POL</t>
+  </si>
+  <si>
+    <t>grid node -- PL46-220 (Wroclaw, 58 km)</t>
+  </si>
+  <si>
+    <t>e_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/39428977-400 (Szczecin, 27 km)</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL</t>
+  </si>
+  <si>
     <t>grid node -- way/191038569-220 (Tarnow, 5 km)</t>
   </si>
   <si>
-    <t>e_Elk_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/303870256-400 (Elk, 8 km)</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/86494356-400 (Gdansk, 54 km)</t>
-  </si>
-  <si>
-    <t>e_Giszowiec_POL</t>
-  </si>
-  <si>
-    <t>grid node -- PL55-220 (Katowice, 8 km)</t>
-  </si>
-  <si>
-    <t>e_GorzowWielkopolski_POL</t>
-  </si>
-  <si>
-    <t>grid node -- PL18-400 (Gorzow Wielkopolski, 15 km)</t>
-  </si>
-  <si>
-    <t>e_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/170259740-220 (Elk, 6 km)</t>
-  </si>
-  <si>
-    <t>e_Grudziadz_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/46092396-400 (Grudziadz, 6 km)</t>
-  </si>
-  <si>
-    <t>e_Kalisz_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/255293403-400 (Kalisz, 21 km)</t>
-  </si>
-  <si>
-    <t>e_KamienPomorski_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/165763717-220 (Szczecin, 15 km)</t>
-  </si>
-  <si>
-    <t>e_KedzierzynKozle_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/185454704-220 (Gliwice, 28 km)</t>
-  </si>
-  <si>
-    <t>e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/199098050-220 (Kielce, 16 km)</t>
-  </si>
-  <si>
-    <t>e_Kolno_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/121656686-400 (Lomza, 31 km)</t>
-  </si>
-  <si>
-    <t>e_Konin_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/255284259-220 (Konin, 10 km)</t>
-  </si>
-  <si>
-    <t>e_Koszalin_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/175406958-400 (Koszalin, 10 km)</t>
-  </si>
-  <si>
-    <t>e_Krakow_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/189501431-400 (Krakow, 13 km)</t>
-  </si>
-  <si>
-    <t>e_Krapkowice_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/336990960-220 (Opole, 7 km)</t>
-  </si>
-  <si>
-    <t>e_Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>grid node -- PL7-400 (Grudziadz, 8 km)</t>
-  </si>
-  <si>
-    <t>e_Legnica_POL</t>
-  </si>
-  <si>
-    <t>grid node -- PL34-400 (Wroclaw, 43 km)</t>
-  </si>
-  <si>
-    <t>e_Lukow_POL</t>
-  </si>
-  <si>
-    <t>grid node -- PL27-400 (Siedlce, 8 km)</t>
-  </si>
-  <si>
-    <t>e_Miastko_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/178838661-220 (Koszalin, 40 km)</t>
-  </si>
-  <si>
-    <t>e_Mikolow_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/183945016-220 (Katowice, 19 km)</t>
-  </si>
-  <si>
-    <t>e_NowaSol_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/180535363-220 (Lubin, 33 km)</t>
-  </si>
-  <si>
-    <t>e_Nowogard_POL</t>
-  </si>
-  <si>
-    <t>grid node -- PL8-220 (Szczecin, 29 km)</t>
-  </si>
-  <si>
-    <t>e_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/101915790-220 (Olsztyn, 4 km)</t>
-  </si>
-  <si>
-    <t>e_Opole_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/255277953-400 (Opole, 10 km)</t>
-  </si>
-  <si>
-    <t>e_OstrowMazowiecka_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/121656686-220 (Lomza, 31 km)</t>
-  </si>
-  <si>
-    <t>e_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/254235846-400 (Ostrowiec Swietokrzyski, 4 km)</t>
-  </si>
-  <si>
-    <t>e_Otwock_POL</t>
-  </si>
-  <si>
-    <t>grid node -- PL26-400 (Warsaw, 53 km)</t>
-  </si>
-  <si>
-    <t>e_PiotrkowTrybunalsk_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/293484891-400 (Piotrkow Trybunalski, 26 km)</t>
-  </si>
-  <si>
-    <t>e_Plock_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/658600169-400 (Plock, 4 km)</t>
-  </si>
-  <si>
-    <t>e_Police_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/39428977-220 (Szczecin, 27 km)</t>
-  </si>
-  <si>
-    <t>e_Pulawy_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/88544449-220 (Lublin, 46 km)</t>
-  </si>
-  <si>
-    <t>e_Radom_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/173582810-400 (Radom, 35 km)</t>
-  </si>
-  <si>
-    <t>e_Radomsko_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/171917072-400 (Czestochowa, 41 km)</t>
-  </si>
-  <si>
-    <t>e_Rumia_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/112614319-400 (Gdansk, 4 km)</t>
-  </si>
-  <si>
-    <t>e_Rybnik_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/139452056-400 (Gliwice, 20 km)</t>
-  </si>
-  <si>
-    <t>e_Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/215282393-400 (Rzeszow, 20 km)</t>
-  </si>
-  <si>
-    <t>e_Sanok_POL</t>
-  </si>
-  <si>
-    <t>grid node -- PL62-400 (Rzeszow, 32 km)</t>
-  </si>
-  <si>
-    <t>e_SiemianowiceSlaski_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/40946790-220 (Katowice, 19 km)</t>
-  </si>
-  <si>
-    <t>e_Slupsk_POL</t>
-  </si>
-  <si>
-    <t>grid node -- relation/18085709-400 (Slupsk, 10 km)</t>
-  </si>
-  <si>
-    <t>e_Sosnowiec_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/133537926-220 (Katowice, 22 km)</t>
-  </si>
-  <si>
-    <t>e_Staszow_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/199098053-400 (Mielec, 19 km)</t>
-  </si>
-  <si>
-    <t>e_Swarzedz_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/32036484-220 (Poznan, 11 km)</t>
-  </si>
-  <si>
-    <t>e_Swidnik_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/170249563-220 (Lublin, 6 km)</t>
-  </si>
-  <si>
-    <t>e_Tczew_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/385098015-400 (Gdansk, 45 km)</t>
-  </si>
-  <si>
-    <t>e_TomaszowLubelski_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/170368942-220 (Zamosc, 8 km)</t>
-  </si>
-  <si>
-    <t>e_Torun_POL</t>
-  </si>
-  <si>
-    <t>grid node -- PL15-400 (Bydgoszcz, 10 km)</t>
-  </si>
-  <si>
     <t>e_Ustka_POL</t>
   </si>
   <si>
     <t>grid node -- way/255314292 (Slupsk, 10 km)</t>
   </si>
   <si>
-    <t>e_Wagrowiec_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/238640596-220 (Pila, 12 km)</t>
-  </si>
-  <si>
-    <t>e_Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/276291999-220 (Walbrzych, 11 km)</t>
+    <t>e_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/29115701-220 (Warsaw, 9 km)</t>
   </si>
   <si>
     <t>e_Wloclawek_POL</t>
@@ -1861,22 +1675,16 @@
     <t>grid node -- way/245964556-220 (Wloclawek, 10 km)</t>
   </si>
   <si>
-    <t>e_Wloszczowa_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/216060722-220 (Czestochowa, 4 km)</t>
-  </si>
-  <si>
     <t>e_Wroclaw_POL</t>
   </si>
   <si>
     <t>grid node -- way/79033485-400 (Wroclaw, 13 km)</t>
   </si>
   <si>
-    <t>e_Zabki_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/29115701-220 (Warsaw, 9 km)</t>
+    <t>e_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/173613665-220 (Zamosc, 3 km)</t>
   </si>
   <si>
     <t>e_ZielonaGora_POL</t>
@@ -1885,12 +1693,6 @@
     <t>grid node -- way/158232924-220 (Zielona Gora, 15 km)</t>
   </si>
   <si>
-    <t>e_Zory_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/139452056-220 (Gliwice, 20 km)</t>
-  </si>
-  <si>
     <t>h_Bialystok_POL</t>
   </si>
   <si>
@@ -1909,310 +1711,250 @@
     <t>heat at grid node -- way/111615226-220 (Legnica, 74 km)</t>
   </si>
   <si>
+    <t>h_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- PL15-400 (Bydgoszcz, 10 km)</t>
+  </si>
+  <si>
     <t>h_Chelm_POL</t>
   </si>
   <si>
     <t>heat at grid node -- way/194903381-400 (Chelm, 4 km)</t>
   </si>
   <si>
+    <t>h_Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/216060722-220 (Czestochowa, 4 km)</t>
+  </si>
+  <si>
     <t>h_Debica_POL</t>
   </si>
   <si>
+    <t>heat at grid node -- way/198635989-220 (Rzeszow, 6 km)</t>
+  </si>
+  <si>
+    <t>h_Elk_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/303870256-400 (Elk, 8 km)</t>
+  </si>
+  <si>
+    <t>h_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/112614319-400 (Gdansk, 4 km)</t>
+  </si>
+  <si>
+    <t>h_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/86494356-400 (Gdansk, 54 km)</t>
+  </si>
+  <si>
+    <t>h_Gliwice_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/293489607-400 (Katowice, 21 km)</t>
+  </si>
+  <si>
+    <t>h_GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- PL18-400 (Gorzow Wielkopolski, 15 km)</t>
+  </si>
+  <si>
+    <t>h_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/170259740-220 (Elk, 6 km)</t>
+  </si>
+  <si>
+    <t>h_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/46092396-400 (Grudziadz, 6 km)</t>
+  </si>
+  <si>
+    <t>h_Katowice_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/40946790-220 (Katowice, 19 km)</t>
+  </si>
+  <si>
+    <t>h_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/336990960-220 (Opole, 7 km)</t>
+  </si>
+  <si>
+    <t>h_Kielce_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/199098050-220 (Kielce, 16 km)</t>
+  </si>
+  <si>
+    <t>h_Konin_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/255284259-220 (Konin, 10 km)</t>
+  </si>
+  <si>
+    <t>h_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/178838661-220 (Koszalin, 40 km)</t>
+  </si>
+  <si>
+    <t>h_Krakow_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/87667718-220 (Krakow, 12 km)</t>
+  </si>
+  <si>
+    <t>h_Krosno_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/166838338-400 (Rzeszow, 40 km)</t>
+  </si>
+  <si>
+    <t>h_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- PL7-400 (Grudziadz, 8 km)</t>
+  </si>
+  <si>
+    <t>h_Legnica_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- PL34-400 (Wroclaw, 43 km)</t>
+  </si>
+  <si>
+    <t>h_Lomza_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/121656686-220 (Lomza, 31 km)</t>
+  </si>
+  <si>
+    <t>h_Lubin_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/180535363-220 (Lubin, 33 km)</t>
+  </si>
+  <si>
+    <t>h_Mielec_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/199098053-220 (Mielec, 19 km)</t>
+  </si>
+  <si>
+    <t>h_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- PL36-400 (Wroclaw, 46 km)</t>
+  </si>
+  <si>
+    <t>h_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/101915790-220 (Olsztyn, 4 km)</t>
+  </si>
+  <si>
+    <t>h_Opole_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/255277953-400 (Opole, 10 km)</t>
+  </si>
+  <si>
+    <t>h_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/254235846-400 (Ostrowiec Swietokrzyski, 4 km)</t>
+  </si>
+  <si>
+    <t>h_PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/170316833-220 (Piotrkow Trybunalski, 3 km)</t>
+  </si>
+  <si>
+    <t>h_Plock_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/658600169-400 (Plock, 4 km)</t>
+  </si>
+  <si>
+    <t>h_Police_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/165763717-220 (Szczecin, 15 km)</t>
+  </si>
+  <si>
+    <t>h_Poznan_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/32036484-220 (Poznan, 11 km)</t>
+  </si>
+  <si>
+    <t>h_Pulawy_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/88544449-220 (Lublin, 46 km)</t>
+  </si>
+  <si>
+    <t>h_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/171917072-400 (Czestochowa, 41 km)</t>
+  </si>
+  <si>
+    <t>h_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/215282393-400 (Rzeszow, 20 km)</t>
+  </si>
+  <si>
+    <t>h_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- relation/18085709-400 (Slupsk, 10 km)</t>
+  </si>
+  <si>
+    <t>h_Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/183945016-220 (Katowice, 19 km)</t>
+  </si>
+  <si>
+    <t>h_Swidnica_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- PL46-220 (Wroclaw, 58 km)</t>
+  </si>
+  <si>
+    <t>h_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/39428977-400 (Szczecin, 27 km)</t>
+  </si>
+  <si>
+    <t>h_Tarnow_POL</t>
+  </si>
+  <si>
     <t>heat at grid node -- way/191038569-220 (Tarnow, 5 km)</t>
   </si>
   <si>
-    <t>h_Elk_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/303870256-400 (Elk, 8 km)</t>
-  </si>
-  <si>
-    <t>h_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/86494356-400 (Gdansk, 54 km)</t>
-  </si>
-  <si>
-    <t>h_Giszowiec_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- PL55-220 (Katowice, 8 km)</t>
-  </si>
-  <si>
-    <t>h_GorzowWielkopolski_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- PL18-400 (Gorzow Wielkopolski, 15 km)</t>
-  </si>
-  <si>
-    <t>h_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/170259740-220 (Elk, 6 km)</t>
-  </si>
-  <si>
-    <t>h_Grudziadz_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/46092396-400 (Grudziadz, 6 km)</t>
-  </si>
-  <si>
-    <t>h_Kalisz_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/255293403-400 (Kalisz, 21 km)</t>
-  </si>
-  <si>
-    <t>h_KamienPomorski_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/165763717-220 (Szczecin, 15 km)</t>
-  </si>
-  <si>
-    <t>h_KedzierzynKozle_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/185454704-220 (Gliwice, 28 km)</t>
-  </si>
-  <si>
-    <t>h_Kielce_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/199098050-220 (Kielce, 16 km)</t>
-  </si>
-  <si>
-    <t>h_Kolno_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/121656686-400 (Lomza, 31 km)</t>
-  </si>
-  <si>
-    <t>h_Konin_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/255284259-220 (Konin, 10 km)</t>
-  </si>
-  <si>
-    <t>h_Koszalin_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/175406958-400 (Koszalin, 10 km)</t>
-  </si>
-  <si>
-    <t>h_Krakow_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/189501431-400 (Krakow, 13 km)</t>
-  </si>
-  <si>
-    <t>h_Krapkowice_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/336990960-220 (Opole, 7 km)</t>
-  </si>
-  <si>
-    <t>h_Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- PL7-400 (Grudziadz, 8 km)</t>
-  </si>
-  <si>
-    <t>h_Legnica_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- PL34-400 (Wroclaw, 43 km)</t>
-  </si>
-  <si>
-    <t>h_Lukow_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- PL27-400 (Siedlce, 8 km)</t>
-  </si>
-  <si>
-    <t>h_Miastko_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/178838661-220 (Koszalin, 40 km)</t>
-  </si>
-  <si>
-    <t>h_Mikolow_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/183945016-220 (Katowice, 19 km)</t>
-  </si>
-  <si>
-    <t>h_NowaSol_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/180535363-220 (Lubin, 33 km)</t>
-  </si>
-  <si>
-    <t>h_Nowogard_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- PL8-220 (Szczecin, 29 km)</t>
-  </si>
-  <si>
-    <t>h_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/101915790-220 (Olsztyn, 4 km)</t>
-  </si>
-  <si>
-    <t>h_Opole_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/255277953-400 (Opole, 10 km)</t>
-  </si>
-  <si>
-    <t>h_OstrowMazowiecka_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/121656686-220 (Lomza, 31 km)</t>
-  </si>
-  <si>
-    <t>h_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/254235846-400 (Ostrowiec Swietokrzyski, 4 km)</t>
-  </si>
-  <si>
-    <t>h_Otwock_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- PL26-400 (Warsaw, 53 km)</t>
-  </si>
-  <si>
-    <t>h_PiotrkowTrybunalsk_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/293484891-400 (Piotrkow Trybunalski, 26 km)</t>
-  </si>
-  <si>
-    <t>h_Plock_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/658600169-400 (Plock, 4 km)</t>
-  </si>
-  <si>
-    <t>h_Police_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/39428977-220 (Szczecin, 27 km)</t>
-  </si>
-  <si>
-    <t>h_Pulawy_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/88544449-220 (Lublin, 46 km)</t>
-  </si>
-  <si>
-    <t>h_Radom_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/173582810-400 (Radom, 35 km)</t>
-  </si>
-  <si>
-    <t>h_Radomsko_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/171917072-400 (Czestochowa, 41 km)</t>
-  </si>
-  <si>
-    <t>h_Rumia_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/112614319-400 (Gdansk, 4 km)</t>
-  </si>
-  <si>
-    <t>h_Rybnik_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/139452056-400 (Gliwice, 20 km)</t>
-  </si>
-  <si>
-    <t>h_Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/215282393-400 (Rzeszow, 20 km)</t>
-  </si>
-  <si>
-    <t>h_Sanok_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- PL62-400 (Rzeszow, 32 km)</t>
-  </si>
-  <si>
-    <t>h_SiemianowiceSlaski_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/40946790-220 (Katowice, 19 km)</t>
-  </si>
-  <si>
-    <t>h_Slupsk_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- relation/18085709-400 (Slupsk, 10 km)</t>
-  </si>
-  <si>
-    <t>h_Sosnowiec_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/133537926-220 (Katowice, 22 km)</t>
-  </si>
-  <si>
-    <t>h_Staszow_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/199098053-400 (Mielec, 19 km)</t>
-  </si>
-  <si>
-    <t>h_Swarzedz_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/32036484-220 (Poznan, 11 km)</t>
-  </si>
-  <si>
-    <t>h_Swidnik_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/170249563-220 (Lublin, 6 km)</t>
-  </si>
-  <si>
-    <t>h_Tczew_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/385098015-400 (Gdansk, 45 km)</t>
-  </si>
-  <si>
-    <t>h_TomaszowLubelski_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/170368942-220 (Zamosc, 8 km)</t>
-  </si>
-  <si>
-    <t>h_Torun_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- PL15-400 (Bydgoszcz, 10 km)</t>
-  </si>
-  <si>
     <t>h_Ustka_POL</t>
   </si>
   <si>
     <t>heat at grid node -- way/255314292 (Slupsk, 10 km)</t>
   </si>
   <si>
-    <t>h_Wagrowiec_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/238640596-220 (Pila, 12 km)</t>
-  </si>
-  <si>
-    <t>h_Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/276291999-220 (Walbrzych, 11 km)</t>
+    <t>h_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/29115701-220 (Warsaw, 9 km)</t>
   </si>
   <si>
     <t>h_Wloclawek_POL</t>
@@ -2221,22 +1963,16 @@
     <t>heat at grid node -- way/245964556-220 (Wloclawek, 10 km)</t>
   </si>
   <si>
-    <t>h_Wloszczowa_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/216060722-220 (Czestochowa, 4 km)</t>
-  </si>
-  <si>
     <t>h_Wroclaw_POL</t>
   </si>
   <si>
     <t>heat at grid node -- way/79033485-400 (Wroclaw, 13 km)</t>
   </si>
   <si>
-    <t>h_Zabki_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/29115701-220 (Warsaw, 9 km)</t>
+    <t>h_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/173613665-220 (Zamosc, 3 km)</t>
   </si>
   <si>
     <t>h_ZielonaGora_POL</t>
@@ -2245,13 +1981,7 @@
     <t>heat at grid node -- way/158232924-220 (Zielona Gora, 15 km)</t>
   </si>
   <si>
-    <t>h_Zory_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/139452056-220 (Gliwice, 20 km)</t>
-  </si>
-  <si>
-    <t>co2_Torun_POL</t>
+    <t>co2_Bydgoszcz_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- PL15-400 (Bydgoszcz, 10 km)</t>
@@ -2272,34 +2002,22 @@
     <t>co2 captured at grid node -- PL18-400 (Gorzow Wielkopolski, 15 km)</t>
   </si>
   <si>
-    <t>co2_Otwock_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- PL26-400 (Warsaw, 53 km)</t>
-  </si>
-  <si>
-    <t>co2_Lukow_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- PL27-400 (Siedlce, 8 km)</t>
-  </si>
-  <si>
     <t>co2_Legnica_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- PL34-400 (Wroclaw, 43 km)</t>
   </si>
   <si>
-    <t>co2_Giszowiec_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- PL55-220 (Katowice, 8 km)</t>
-  </si>
-  <si>
-    <t>co2_Sanok_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- PL62-400 (Rzeszow, 32 km)</t>
+    <t>co2_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- PL36-400 (Wroclaw, 46 km)</t>
+  </si>
+  <si>
+    <t>co2_Swidnica_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- PL46-220 (Wroclaw, 58 km)</t>
   </si>
   <si>
     <t>co2_Kwidzyn_POL</t>
@@ -2308,12 +2026,6 @@
     <t>co2 captured at grid node -- PL7-400 (Grudziadz, 8 km)</t>
   </si>
   <si>
-    <t>co2_Nowogard_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- PL8-220 (Szczecin, 29 km)</t>
-  </si>
-  <si>
     <t>co2_Slupsk_POL</t>
   </si>
   <si>
@@ -2332,286 +2044,364 @@
     <t>co2 captured at grid node -- way/111615226-220 (Legnica, 74 km)</t>
   </si>
   <si>
-    <t>co2_Rumia_POL</t>
+    <t>co2_Gdansk_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/112614319-400 (Gdansk, 4 km)</t>
   </si>
   <si>
-    <t>co2_OstrowMazowiecka_POL</t>
+    <t>co2_Lomza_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/121656686-220 (Lomza, 31 km)</t>
   </si>
   <si>
-    <t>co2_Kolno_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/121656686-400 (Lomza, 31 km)</t>
+    <t>co2_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/158232924-220 (Zielona Gora, 15 km)</t>
+  </si>
+  <si>
+    <t>co2_Police_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/165763717-220 (Szczecin, 15 km)</t>
+  </si>
+  <si>
+    <t>co2_Krosno_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/166838338-400 (Rzeszow, 40 km)</t>
+  </si>
+  <si>
+    <t>co2_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/170259740-220 (Elk, 6 km)</t>
+  </si>
+  <si>
+    <t>co2_PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/170316833-220 (Piotrkow Trybunalski, 3 km)</t>
+  </si>
+  <si>
+    <t>co2_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/171917072-400 (Czestochowa, 41 km)</t>
+  </si>
+  <si>
+    <t>co2_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/173613665-220 (Zamosc, 3 km)</t>
+  </si>
+  <si>
+    <t>co2_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/178838661-220 (Koszalin, 40 km)</t>
+  </si>
+  <si>
+    <t>co2_Lubin_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/180535363-220 (Lubin, 33 km)</t>
   </si>
   <si>
     <t>co2_Sosnowiec_POL</t>
   </si>
   <si>
-    <t>co2 captured at grid node -- way/133537926-220 (Katowice, 22 km)</t>
-  </si>
-  <si>
-    <t>co2_Zory_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/139452056-220 (Gliwice, 20 km)</t>
-  </si>
-  <si>
-    <t>co2_Rybnik_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/139452056-400 (Gliwice, 20 km)</t>
-  </si>
-  <si>
-    <t>co2_ZielonaGora_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/158232924-220 (Zielona Gora, 15 km)</t>
-  </si>
-  <si>
-    <t>co2_KamienPomorski_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/165763717-220 (Szczecin, 15 km)</t>
-  </si>
-  <si>
-    <t>co2_Swidnik_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/170249563-220 (Lublin, 6 km)</t>
-  </si>
-  <si>
-    <t>co2_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/170259740-220 (Elk, 6 km)</t>
-  </si>
-  <si>
-    <t>co2_TomaszowLubelski_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/170368942-220 (Zamosc, 8 km)</t>
-  </si>
-  <si>
-    <t>co2_Radomsko_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/171917072-400 (Czestochowa, 41 km)</t>
-  </si>
-  <si>
-    <t>co2_Radom_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/173582810-400 (Radom, 35 km)</t>
-  </si>
-  <si>
-    <t>co2_Koszalin_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/175406958-400 (Koszalin, 10 km)</t>
-  </si>
-  <si>
-    <t>co2_Miastko_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/178838661-220 (Koszalin, 40 km)</t>
-  </si>
-  <si>
-    <t>co2_NowaSol_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/180535363-220 (Lubin, 33 km)</t>
-  </si>
-  <si>
-    <t>co2_Mikolow_POL</t>
-  </si>
-  <si>
     <t>co2 captured at grid node -- way/183945016-220 (Katowice, 19 km)</t>
   </si>
   <si>
+    <t>co2_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/191038569-220 (Tarnow, 5 km)</t>
+  </si>
+  <si>
+    <t>co2_Chelm_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/194903381-400 (Chelm, 4 km)</t>
+  </si>
+  <si>
+    <t>co2_Debica_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/198635989-220 (Rzeszow, 6 km)</t>
+  </si>
+  <si>
+    <t>co2_Kielce_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/199098050-220 (Kielce, 16 km)</t>
+  </si>
+  <si>
+    <t>co2_Mielec_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/199098053-220 (Mielec, 19 km)</t>
+  </si>
+  <si>
+    <t>co2_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/215282393-400 (Rzeszow, 20 km)</t>
+  </si>
+  <si>
+    <t>co2_Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/216060722-220 (Czestochowa, 4 km)</t>
+  </si>
+  <si>
+    <t>co2_Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/245964556-220 (Wloclawek, 10 km)</t>
+  </si>
+  <si>
+    <t>co2_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/254235846-400 (Ostrowiec Swietokrzyski, 4 km)</t>
+  </si>
+  <si>
+    <t>co2_Opole_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/255277953-400 (Opole, 10 km)</t>
+  </si>
+  <si>
+    <t>co2_Konin_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/255284259-220 (Konin, 10 km)</t>
+  </si>
+  <si>
+    <t>co2_Ustka_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/255314292 (Slupsk, 10 km)</t>
+  </si>
+  <si>
+    <t>co2_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/29115701-220 (Warsaw, 9 km)</t>
+  </si>
+  <si>
+    <t>co2_Gliwice_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/293489607-400 (Katowice, 21 km)</t>
+  </si>
+  <si>
+    <t>co2_Elk_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/303870256-400 (Elk, 8 km)</t>
+  </si>
+  <si>
+    <t>co2_Poznan_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/32036484-220 (Poznan, 11 km)</t>
+  </si>
+  <si>
     <t>co2_KedzierzynKozle_POL</t>
   </si>
   <si>
-    <t>co2 captured at grid node -- way/185454704-220 (Gliwice, 28 km)</t>
+    <t>co2 captured at grid node -- way/336990960-220 (Opole, 7 km)</t>
+  </si>
+  <si>
+    <t>co2_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/39428977-400 (Szczecin, 27 km)</t>
+  </si>
+  <si>
+    <t>co2_Katowice_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/40946790-220 (Katowice, 19 km)</t>
+  </si>
+  <si>
+    <t>co2_BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/44389929-220 (Bielsko-Biala, 12 km)</t>
+  </si>
+  <si>
+    <t>co2_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/46092396-400 (Grudziadz, 6 km)</t>
+  </si>
+  <si>
+    <t>co2_Plock_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/658600169-400 (Plock, 4 km)</t>
+  </si>
+  <si>
+    <t>co2_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/79033485-400 (Wroclaw, 13 km)</t>
+  </si>
+  <si>
+    <t>co2_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/86494356-400 (Gdansk, 54 km)</t>
   </si>
   <si>
     <t>co2_Krakow_POL</t>
   </si>
   <si>
-    <t>co2 captured at grid node -- way/189501431-400 (Krakow, 13 km)</t>
-  </si>
-  <si>
-    <t>co2_Debica_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/191038569-220 (Tarnow, 5 km)</t>
-  </si>
-  <si>
-    <t>co2_Chelm_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/194903381-400 (Chelm, 4 km)</t>
-  </si>
-  <si>
-    <t>co2_Kielce_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/199098050-220 (Kielce, 16 km)</t>
-  </si>
-  <si>
-    <t>co2_Staszow_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/199098053-400 (Mielec, 19 km)</t>
-  </si>
-  <si>
-    <t>co2_Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/215282393-400 (Rzeszow, 20 km)</t>
-  </si>
-  <si>
-    <t>co2_Wloszczowa_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/216060722-220 (Czestochowa, 4 km)</t>
-  </si>
-  <si>
-    <t>co2_Wagrowiec_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/238640596-220 (Pila, 12 km)</t>
-  </si>
-  <si>
-    <t>co2_Wloclawek_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/245964556-220 (Wloclawek, 10 km)</t>
-  </si>
-  <si>
-    <t>co2_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/254235846-400 (Ostrowiec Swietokrzyski, 4 km)</t>
-  </si>
-  <si>
-    <t>co2_Opole_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/255277953-400 (Opole, 10 km)</t>
-  </si>
-  <si>
-    <t>co2_Konin_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/255284259-220 (Konin, 10 km)</t>
-  </si>
-  <si>
-    <t>co2_Kalisz_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/255293403-400 (Kalisz, 21 km)</t>
-  </si>
-  <si>
-    <t>co2_Ustka_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/255314292 (Slupsk, 10 km)</t>
-  </si>
-  <si>
-    <t>co2_Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/276291999-220 (Walbrzych, 11 km)</t>
-  </si>
-  <si>
-    <t>co2_Zabki_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/29115701-220 (Warsaw, 9 km)</t>
-  </si>
-  <si>
-    <t>co2_PiotrkowTrybunalsk_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/293484891-400 (Piotrkow Trybunalski, 26 km)</t>
-  </si>
-  <si>
-    <t>co2_Elk_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/303870256-400 (Elk, 8 km)</t>
-  </si>
-  <si>
-    <t>co2_Swarzedz_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/32036484-220 (Poznan, 11 km)</t>
-  </si>
-  <si>
-    <t>co2_Krapkowice_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/336990960-220 (Opole, 7 km)</t>
-  </si>
-  <si>
-    <t>co2_Tczew_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/385098015-400 (Gdansk, 45 km)</t>
-  </si>
-  <si>
-    <t>co2_Police_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/39428977-220 (Szczecin, 27 km)</t>
-  </si>
-  <si>
-    <t>co2_SiemianowiceSlaski_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/40946790-220 (Katowice, 19 km)</t>
-  </si>
-  <si>
-    <t>co2_BielskoBiala_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/44389929-220 (Bielsko-Biala, 12 km)</t>
-  </si>
-  <si>
-    <t>co2_Grudziadz_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/46092396-400 (Grudziadz, 6 km)</t>
-  </si>
-  <si>
-    <t>co2_Plock_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/658600169-400 (Plock, 4 km)</t>
-  </si>
-  <si>
-    <t>co2_Wroclaw_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/79033485-400 (Wroclaw, 13 km)</t>
-  </si>
-  <si>
-    <t>co2_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/86494356-400 (Gdansk, 54 km)</t>
+    <t>co2 captured at grid node -- way/87667718-220 (Krakow, 12 km)</t>
   </si>
   <si>
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/88544449-220 (Lublin, 46 km)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11072_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11072.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11074_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11074.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11075_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11075.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11076_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11076.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11077_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11077.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11078_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11078.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11079_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11079.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11080_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11080.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11081_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11081.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11082_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11082.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11083_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11083.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11084_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11084.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11085_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11085.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11086_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11086.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11087_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11087.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11088_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11088.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11089_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11089.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11090_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11090.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11091_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11091.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11092_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11092.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11093_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11093.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11094_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11094.0 (OGCI/catalogue)</t>
   </si>
   <si>
     <t>co2s_T1_POL</t>
@@ -4692,9 +4482,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4732,7 +4522,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4838,7 +4628,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4980,7 +4770,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4989,15 +4779,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.06640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.9296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.53125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8">
@@ -5054,13 +4844,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE1DB511-6C08-417A-B3CF-DA0D0FA32E5C}">
-  <dimension ref="B3:H72"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0F7B196-FB77-4156-A72F-6197B3013C84}">
+  <dimension ref="B3:H82"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:8">
       <c r="B3" t="s">
-        <v>494</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="2:8">
@@ -5091,19 +4881,19 @@
         <v>192</v>
       </c>
       <c r="C5" t="s">
-        <v>736</v>
+        <v>646</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>737</v>
+        <v>647</v>
       </c>
       <c r="F5" t="s">
         <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H5" t="s">
         <v>195</v>
@@ -5114,19 +4904,19 @@
         <v>192</v>
       </c>
       <c r="C6" t="s">
-        <v>739</v>
+        <v>649</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>740</v>
+        <v>650</v>
       </c>
       <c r="F6" t="s">
         <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H6" t="s">
         <v>195</v>
@@ -5137,19 +4927,19 @@
         <v>192</v>
       </c>
       <c r="C7" t="s">
-        <v>741</v>
+        <v>651</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>742</v>
+        <v>652</v>
       </c>
       <c r="F7" t="s">
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H7" t="s">
         <v>195</v>
@@ -5160,19 +4950,19 @@
         <v>192</v>
       </c>
       <c r="C8" t="s">
-        <v>743</v>
+        <v>653</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>744</v>
+        <v>654</v>
       </c>
       <c r="F8" t="s">
         <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H8" t="s">
         <v>195</v>
@@ -5183,19 +4973,19 @@
         <v>192</v>
       </c>
       <c r="C9" t="s">
-        <v>745</v>
+        <v>655</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>746</v>
+        <v>656</v>
       </c>
       <c r="F9" t="s">
         <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H9" t="s">
         <v>195</v>
@@ -5206,19 +4996,19 @@
         <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>747</v>
+        <v>657</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>748</v>
+        <v>658</v>
       </c>
       <c r="F10" t="s">
         <v>26</v>
       </c>
       <c r="G10" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H10" t="s">
         <v>195</v>
@@ -5229,19 +5019,19 @@
         <v>192</v>
       </c>
       <c r="C11" t="s">
-        <v>749</v>
+        <v>659</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>750</v>
+        <v>660</v>
       </c>
       <c r="F11" t="s">
         <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H11" t="s">
         <v>195</v>
@@ -5252,19 +5042,19 @@
         <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>751</v>
+        <v>661</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>752</v>
+        <v>662</v>
       </c>
       <c r="F12" t="s">
         <v>26</v>
       </c>
       <c r="G12" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H12" t="s">
         <v>195</v>
@@ -5275,19 +5065,19 @@
         <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>753</v>
+        <v>663</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>754</v>
+        <v>664</v>
       </c>
       <c r="F13" t="s">
         <v>26</v>
       </c>
       <c r="G13" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H13" t="s">
         <v>195</v>
@@ -5298,19 +5088,19 @@
         <v>192</v>
       </c>
       <c r="C14" t="s">
-        <v>755</v>
+        <v>665</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>756</v>
+        <v>666</v>
       </c>
       <c r="F14" t="s">
         <v>26</v>
       </c>
       <c r="G14" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H14" t="s">
         <v>195</v>
@@ -5321,19 +5111,19 @@
         <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>757</v>
+        <v>667</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>758</v>
+        <v>668</v>
       </c>
       <c r="F15" t="s">
         <v>26</v>
       </c>
       <c r="G15" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H15" t="s">
         <v>195</v>
@@ -5344,19 +5134,19 @@
         <v>192</v>
       </c>
       <c r="C16" t="s">
-        <v>759</v>
+        <v>669</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>760</v>
+        <v>670</v>
       </c>
       <c r="F16" t="s">
         <v>26</v>
       </c>
       <c r="G16" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H16" t="s">
         <v>195</v>
@@ -5367,19 +5157,19 @@
         <v>192</v>
       </c>
       <c r="C17" t="s">
-        <v>761</v>
+        <v>671</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>762</v>
+        <v>672</v>
       </c>
       <c r="F17" t="s">
         <v>26</v>
       </c>
       <c r="G17" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H17" t="s">
         <v>195</v>
@@ -5390,19 +5180,19 @@
         <v>192</v>
       </c>
       <c r="C18" t="s">
-        <v>763</v>
+        <v>673</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>764</v>
+        <v>674</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
       </c>
       <c r="G18" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H18" t="s">
         <v>195</v>
@@ -5413,19 +5203,19 @@
         <v>192</v>
       </c>
       <c r="C19" t="s">
-        <v>765</v>
+        <v>675</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>766</v>
+        <v>676</v>
       </c>
       <c r="F19" t="s">
         <v>26</v>
       </c>
       <c r="G19" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H19" t="s">
         <v>195</v>
@@ -5436,19 +5226,19 @@
         <v>192</v>
       </c>
       <c r="C20" t="s">
-        <v>767</v>
+        <v>677</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>768</v>
+        <v>678</v>
       </c>
       <c r="F20" t="s">
         <v>26</v>
       </c>
       <c r="G20" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H20" t="s">
         <v>195</v>
@@ -5459,19 +5249,19 @@
         <v>192</v>
       </c>
       <c r="C21" t="s">
-        <v>769</v>
+        <v>679</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>770</v>
+        <v>680</v>
       </c>
       <c r="F21" t="s">
         <v>26</v>
       </c>
       <c r="G21" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H21" t="s">
         <v>195</v>
@@ -5482,19 +5272,19 @@
         <v>192</v>
       </c>
       <c r="C22" t="s">
-        <v>771</v>
+        <v>681</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>772</v>
+        <v>682</v>
       </c>
       <c r="F22" t="s">
         <v>26</v>
       </c>
       <c r="G22" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H22" t="s">
         <v>195</v>
@@ -5505,19 +5295,19 @@
         <v>192</v>
       </c>
       <c r="C23" t="s">
-        <v>773</v>
+        <v>683</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>774</v>
+        <v>684</v>
       </c>
       <c r="F23" t="s">
         <v>26</v>
       </c>
       <c r="G23" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H23" t="s">
         <v>195</v>
@@ -5528,19 +5318,19 @@
         <v>192</v>
       </c>
       <c r="C24" t="s">
-        <v>775</v>
+        <v>685</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>776</v>
+        <v>686</v>
       </c>
       <c r="F24" t="s">
         <v>26</v>
       </c>
       <c r="G24" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H24" t="s">
         <v>195</v>
@@ -5551,19 +5341,19 @@
         <v>192</v>
       </c>
       <c r="C25" t="s">
-        <v>777</v>
+        <v>687</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>778</v>
+        <v>688</v>
       </c>
       <c r="F25" t="s">
         <v>26</v>
       </c>
       <c r="G25" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H25" t="s">
         <v>195</v>
@@ -5574,19 +5364,19 @@
         <v>192</v>
       </c>
       <c r="C26" t="s">
-        <v>779</v>
+        <v>689</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>780</v>
+        <v>690</v>
       </c>
       <c r="F26" t="s">
         <v>26</v>
       </c>
       <c r="G26" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H26" t="s">
         <v>195</v>
@@ -5597,19 +5387,19 @@
         <v>192</v>
       </c>
       <c r="C27" t="s">
-        <v>781</v>
+        <v>691</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>782</v>
+        <v>692</v>
       </c>
       <c r="F27" t="s">
         <v>26</v>
       </c>
       <c r="G27" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H27" t="s">
         <v>195</v>
@@ -5620,19 +5410,19 @@
         <v>192</v>
       </c>
       <c r="C28" t="s">
-        <v>783</v>
+        <v>693</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>784</v>
+        <v>694</v>
       </c>
       <c r="F28" t="s">
         <v>26</v>
       </c>
       <c r="G28" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H28" t="s">
         <v>195</v>
@@ -5643,19 +5433,19 @@
         <v>192</v>
       </c>
       <c r="C29" t="s">
-        <v>785</v>
+        <v>695</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>786</v>
+        <v>696</v>
       </c>
       <c r="F29" t="s">
         <v>26</v>
       </c>
       <c r="G29" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H29" t="s">
         <v>195</v>
@@ -5666,19 +5456,19 @@
         <v>192</v>
       </c>
       <c r="C30" t="s">
-        <v>787</v>
+        <v>697</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>788</v>
+        <v>698</v>
       </c>
       <c r="F30" t="s">
         <v>26</v>
       </c>
       <c r="G30" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H30" t="s">
         <v>195</v>
@@ -5689,19 +5479,19 @@
         <v>192</v>
       </c>
       <c r="C31" t="s">
-        <v>789</v>
+        <v>699</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>790</v>
+        <v>700</v>
       </c>
       <c r="F31" t="s">
         <v>26</v>
       </c>
       <c r="G31" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H31" t="s">
         <v>195</v>
@@ -5712,19 +5502,19 @@
         <v>192</v>
       </c>
       <c r="C32" t="s">
-        <v>791</v>
+        <v>701</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>792</v>
+        <v>702</v>
       </c>
       <c r="F32" t="s">
         <v>26</v>
       </c>
       <c r="G32" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H32" t="s">
         <v>195</v>
@@ -5735,19 +5525,19 @@
         <v>192</v>
       </c>
       <c r="C33" t="s">
-        <v>793</v>
+        <v>703</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>794</v>
+        <v>704</v>
       </c>
       <c r="F33" t="s">
         <v>26</v>
       </c>
       <c r="G33" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H33" t="s">
         <v>195</v>
@@ -5758,19 +5548,19 @@
         <v>192</v>
       </c>
       <c r="C34" t="s">
-        <v>795</v>
+        <v>705</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>796</v>
+        <v>706</v>
       </c>
       <c r="F34" t="s">
         <v>26</v>
       </c>
       <c r="G34" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H34" t="s">
         <v>195</v>
@@ -5781,19 +5571,19 @@
         <v>192</v>
       </c>
       <c r="C35" t="s">
-        <v>797</v>
+        <v>707</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>798</v>
+        <v>708</v>
       </c>
       <c r="F35" t="s">
         <v>26</v>
       </c>
       <c r="G35" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H35" t="s">
         <v>195</v>
@@ -5804,19 +5594,19 @@
         <v>192</v>
       </c>
       <c r="C36" t="s">
-        <v>799</v>
+        <v>709</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>800</v>
+        <v>710</v>
       </c>
       <c r="F36" t="s">
         <v>26</v>
       </c>
       <c r="G36" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H36" t="s">
         <v>195</v>
@@ -5827,19 +5617,19 @@
         <v>192</v>
       </c>
       <c r="C37" t="s">
-        <v>801</v>
+        <v>711</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>802</v>
+        <v>712</v>
       </c>
       <c r="F37" t="s">
         <v>26</v>
       </c>
       <c r="G37" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H37" t="s">
         <v>195</v>
@@ -5850,19 +5640,19 @@
         <v>192</v>
       </c>
       <c r="C38" t="s">
-        <v>803</v>
+        <v>713</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>804</v>
+        <v>714</v>
       </c>
       <c r="F38" t="s">
         <v>26</v>
       </c>
       <c r="G38" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H38" t="s">
         <v>195</v>
@@ -5873,19 +5663,19 @@
         <v>192</v>
       </c>
       <c r="C39" t="s">
-        <v>805</v>
+        <v>715</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>806</v>
+        <v>716</v>
       </c>
       <c r="F39" t="s">
         <v>26</v>
       </c>
       <c r="G39" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H39" t="s">
         <v>195</v>
@@ -5896,19 +5686,19 @@
         <v>192</v>
       </c>
       <c r="C40" t="s">
-        <v>807</v>
+        <v>717</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>808</v>
+        <v>718</v>
       </c>
       <c r="F40" t="s">
         <v>26</v>
       </c>
       <c r="G40" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H40" t="s">
         <v>195</v>
@@ -5919,19 +5709,19 @@
         <v>192</v>
       </c>
       <c r="C41" t="s">
-        <v>809</v>
+        <v>719</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>810</v>
+        <v>720</v>
       </c>
       <c r="F41" t="s">
         <v>26</v>
       </c>
       <c r="G41" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H41" t="s">
         <v>195</v>
@@ -5942,19 +5732,19 @@
         <v>192</v>
       </c>
       <c r="C42" t="s">
-        <v>811</v>
+        <v>721</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>812</v>
+        <v>722</v>
       </c>
       <c r="F42" t="s">
         <v>26</v>
       </c>
       <c r="G42" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H42" t="s">
         <v>195</v>
@@ -5965,19 +5755,19 @@
         <v>192</v>
       </c>
       <c r="C43" t="s">
-        <v>813</v>
+        <v>723</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>814</v>
+        <v>724</v>
       </c>
       <c r="F43" t="s">
         <v>26</v>
       </c>
       <c r="G43" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H43" t="s">
         <v>195</v>
@@ -5988,19 +5778,19 @@
         <v>192</v>
       </c>
       <c r="C44" t="s">
-        <v>815</v>
+        <v>725</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>816</v>
+        <v>726</v>
       </c>
       <c r="F44" t="s">
         <v>26</v>
       </c>
       <c r="G44" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H44" t="s">
         <v>195</v>
@@ -6011,19 +5801,19 @@
         <v>192</v>
       </c>
       <c r="C45" t="s">
-        <v>817</v>
+        <v>727</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>818</v>
+        <v>728</v>
       </c>
       <c r="F45" t="s">
         <v>26</v>
       </c>
       <c r="G45" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H45" t="s">
         <v>195</v>
@@ -6034,19 +5824,19 @@
         <v>192</v>
       </c>
       <c r="C46" t="s">
-        <v>819</v>
+        <v>729</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>820</v>
+        <v>730</v>
       </c>
       <c r="F46" t="s">
         <v>26</v>
       </c>
       <c r="G46" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H46" t="s">
         <v>195</v>
@@ -6057,19 +5847,19 @@
         <v>192</v>
       </c>
       <c r="C47" t="s">
-        <v>821</v>
+        <v>731</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>822</v>
+        <v>732</v>
       </c>
       <c r="F47" t="s">
         <v>26</v>
       </c>
       <c r="G47" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H47" t="s">
         <v>195</v>
@@ -6080,19 +5870,19 @@
         <v>192</v>
       </c>
       <c r="C48" t="s">
-        <v>823</v>
+        <v>733</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>824</v>
+        <v>734</v>
       </c>
       <c r="F48" t="s">
         <v>26</v>
       </c>
       <c r="G48" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H48" t="s">
         <v>195</v>
@@ -6103,19 +5893,19 @@
         <v>192</v>
       </c>
       <c r="C49" t="s">
-        <v>825</v>
+        <v>735</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>826</v>
+        <v>736</v>
       </c>
       <c r="F49" t="s">
         <v>26</v>
       </c>
       <c r="G49" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H49" t="s">
         <v>195</v>
@@ -6126,19 +5916,19 @@
         <v>192</v>
       </c>
       <c r="C50" t="s">
-        <v>827</v>
+        <v>737</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>828</v>
+        <v>738</v>
       </c>
       <c r="F50" t="s">
         <v>26</v>
       </c>
       <c r="G50" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H50" t="s">
         <v>195</v>
@@ -6149,19 +5939,19 @@
         <v>192</v>
       </c>
       <c r="C51" t="s">
-        <v>829</v>
+        <v>739</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>830</v>
+        <v>740</v>
       </c>
       <c r="F51" t="s">
         <v>26</v>
       </c>
       <c r="G51" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H51" t="s">
         <v>195</v>
@@ -6172,19 +5962,19 @@
         <v>192</v>
       </c>
       <c r="C52" t="s">
-        <v>831</v>
+        <v>741</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>832</v>
+        <v>742</v>
       </c>
       <c r="F52" t="s">
         <v>26</v>
       </c>
       <c r="G52" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H52" t="s">
         <v>195</v>
@@ -6195,19 +5985,19 @@
         <v>192</v>
       </c>
       <c r="C53" t="s">
-        <v>833</v>
+        <v>743</v>
       </c>
       <c r="D53" t="s">
         <v>243</v>
       </c>
       <c r="E53" t="s">
-        <v>834</v>
+        <v>744</v>
       </c>
       <c r="F53" t="s">
         <v>26</v>
       </c>
       <c r="G53" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H53" t="s">
         <v>195</v>
@@ -6218,19 +6008,19 @@
         <v>192</v>
       </c>
       <c r="C54" t="s">
-        <v>835</v>
+        <v>745</v>
       </c>
       <c r="D54" t="s">
         <v>243</v>
       </c>
       <c r="E54" t="s">
-        <v>836</v>
+        <v>746</v>
       </c>
       <c r="F54" t="s">
         <v>26</v>
       </c>
       <c r="G54" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H54" t="s">
         <v>195</v>
@@ -6241,19 +6031,19 @@
         <v>192</v>
       </c>
       <c r="C55" t="s">
-        <v>837</v>
+        <v>747</v>
       </c>
       <c r="D55" t="s">
         <v>243</v>
       </c>
       <c r="E55" t="s">
-        <v>838</v>
+        <v>748</v>
       </c>
       <c r="F55" t="s">
         <v>26</v>
       </c>
       <c r="G55" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H55" t="s">
         <v>195</v>
@@ -6264,19 +6054,19 @@
         <v>192</v>
       </c>
       <c r="C56" t="s">
-        <v>839</v>
+        <v>749</v>
       </c>
       <c r="D56" t="s">
         <v>243</v>
       </c>
       <c r="E56" t="s">
-        <v>840</v>
+        <v>750</v>
       </c>
       <c r="F56" t="s">
         <v>26</v>
       </c>
       <c r="G56" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H56" t="s">
         <v>195</v>
@@ -6287,19 +6077,19 @@
         <v>192</v>
       </c>
       <c r="C57" t="s">
-        <v>841</v>
+        <v>751</v>
       </c>
       <c r="D57" t="s">
         <v>243</v>
       </c>
       <c r="E57" t="s">
-        <v>842</v>
+        <v>752</v>
       </c>
       <c r="F57" t="s">
         <v>26</v>
       </c>
       <c r="G57" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H57" t="s">
         <v>195</v>
@@ -6310,19 +6100,19 @@
         <v>192</v>
       </c>
       <c r="C58" t="s">
-        <v>843</v>
+        <v>753</v>
       </c>
       <c r="D58" t="s">
         <v>243</v>
       </c>
       <c r="E58" t="s">
-        <v>844</v>
+        <v>754</v>
       </c>
       <c r="F58" t="s">
         <v>26</v>
       </c>
       <c r="G58" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H58" t="s">
         <v>195</v>
@@ -6333,19 +6123,19 @@
         <v>192</v>
       </c>
       <c r="C59" t="s">
-        <v>845</v>
+        <v>755</v>
       </c>
       <c r="D59" t="s">
         <v>243</v>
       </c>
       <c r="E59" t="s">
-        <v>846</v>
+        <v>756</v>
       </c>
       <c r="F59" t="s">
         <v>26</v>
       </c>
       <c r="G59" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H59" t="s">
         <v>195</v>
@@ -6356,19 +6146,19 @@
         <v>192</v>
       </c>
       <c r="C60" t="s">
-        <v>847</v>
+        <v>757</v>
       </c>
       <c r="D60" t="s">
         <v>243</v>
       </c>
       <c r="E60" t="s">
-        <v>848</v>
+        <v>758</v>
       </c>
       <c r="F60" t="s">
         <v>26</v>
       </c>
       <c r="G60" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H60" t="s">
         <v>195</v>
@@ -6379,19 +6169,19 @@
         <v>192</v>
       </c>
       <c r="C61" t="s">
-        <v>849</v>
+        <v>759</v>
       </c>
       <c r="D61" t="s">
         <v>243</v>
       </c>
       <c r="E61" t="s">
-        <v>850</v>
+        <v>760</v>
       </c>
       <c r="F61" t="s">
         <v>26</v>
       </c>
       <c r="G61" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H61" t="s">
         <v>195</v>
@@ -6402,19 +6192,19 @@
         <v>192</v>
       </c>
       <c r="C62" t="s">
-        <v>851</v>
+        <v>761</v>
       </c>
       <c r="D62" t="s">
         <v>243</v>
       </c>
       <c r="E62" t="s">
-        <v>852</v>
+        <v>762</v>
       </c>
       <c r="F62" t="s">
         <v>26</v>
       </c>
       <c r="G62" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H62" t="s">
         <v>195</v>
@@ -6425,19 +6215,19 @@
         <v>192</v>
       </c>
       <c r="C63" t="s">
-        <v>853</v>
+        <v>763</v>
       </c>
       <c r="D63" t="s">
         <v>243</v>
       </c>
       <c r="E63" t="s">
-        <v>854</v>
+        <v>764</v>
       </c>
       <c r="F63" t="s">
         <v>26</v>
       </c>
       <c r="G63" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H63" t="s">
         <v>195</v>
@@ -6448,19 +6238,19 @@
         <v>192</v>
       </c>
       <c r="C64" t="s">
-        <v>855</v>
+        <v>765</v>
       </c>
       <c r="D64" t="s">
         <v>243</v>
       </c>
       <c r="E64" t="s">
-        <v>856</v>
+        <v>766</v>
       </c>
       <c r="F64" t="s">
         <v>26</v>
       </c>
       <c r="G64" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H64" t="s">
         <v>195</v>
@@ -6471,19 +6261,19 @@
         <v>192</v>
       </c>
       <c r="C65" t="s">
-        <v>857</v>
+        <v>767</v>
       </c>
       <c r="D65" t="s">
         <v>243</v>
       </c>
       <c r="E65" t="s">
-        <v>858</v>
+        <v>768</v>
       </c>
       <c r="F65" t="s">
         <v>26</v>
       </c>
       <c r="G65" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H65" t="s">
         <v>195</v>
@@ -6494,19 +6284,19 @@
         <v>192</v>
       </c>
       <c r="C66" t="s">
-        <v>859</v>
+        <v>769</v>
       </c>
       <c r="D66" t="s">
         <v>243</v>
       </c>
       <c r="E66" t="s">
-        <v>860</v>
+        <v>770</v>
       </c>
       <c r="F66" t="s">
         <v>26</v>
       </c>
       <c r="G66" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H66" t="s">
         <v>195</v>
@@ -6517,19 +6307,19 @@
         <v>192</v>
       </c>
       <c r="C67" t="s">
-        <v>861</v>
+        <v>771</v>
       </c>
       <c r="D67" t="s">
         <v>243</v>
       </c>
       <c r="E67" t="s">
-        <v>862</v>
+        <v>772</v>
       </c>
       <c r="F67" t="s">
         <v>26</v>
       </c>
       <c r="G67" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H67" t="s">
         <v>195</v>
@@ -6540,19 +6330,19 @@
         <v>192</v>
       </c>
       <c r="C68" t="s">
-        <v>863</v>
+        <v>773</v>
       </c>
       <c r="D68" t="s">
         <v>243</v>
       </c>
       <c r="E68" t="s">
-        <v>864</v>
+        <v>774</v>
       </c>
       <c r="F68" t="s">
         <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H68" t="s">
         <v>195</v>
@@ -6563,19 +6353,19 @@
         <v>192</v>
       </c>
       <c r="C69" t="s">
-        <v>865</v>
+        <v>775</v>
       </c>
       <c r="D69" t="s">
         <v>243</v>
       </c>
       <c r="E69" t="s">
-        <v>866</v>
+        <v>776</v>
       </c>
       <c r="F69" t="s">
         <v>26</v>
       </c>
       <c r="G69" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H69" t="s">
         <v>195</v>
@@ -6586,19 +6376,19 @@
         <v>192</v>
       </c>
       <c r="C70" t="s">
-        <v>867</v>
+        <v>777</v>
       </c>
       <c r="D70" t="s">
         <v>243</v>
       </c>
       <c r="E70" t="s">
-        <v>868</v>
+        <v>778</v>
       </c>
       <c r="F70" t="s">
         <v>26</v>
       </c>
       <c r="G70" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H70" t="s">
         <v>195</v>
@@ -6609,19 +6399,19 @@
         <v>192</v>
       </c>
       <c r="C71" t="s">
-        <v>869</v>
+        <v>779</v>
       </c>
       <c r="D71" t="s">
         <v>243</v>
       </c>
       <c r="E71" t="s">
-        <v>870</v>
+        <v>780</v>
       </c>
       <c r="F71" t="s">
         <v>26</v>
       </c>
       <c r="G71" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H71" t="s">
         <v>195</v>
@@ -6632,21 +6422,251 @@
         <v>192</v>
       </c>
       <c r="C72" t="s">
-        <v>871</v>
+        <v>781</v>
       </c>
       <c r="D72" t="s">
         <v>243</v>
       </c>
       <c r="E72" t="s">
-        <v>872</v>
+        <v>782</v>
       </c>
       <c r="F72" t="s">
         <v>26</v>
       </c>
       <c r="G72" t="s">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="H72" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8">
+      <c r="B73" t="s">
+        <v>192</v>
+      </c>
+      <c r="C73" t="s">
+        <v>783</v>
+      </c>
+      <c r="D73" t="s">
+        <v>243</v>
+      </c>
+      <c r="E73" t="s">
+        <v>784</v>
+      </c>
+      <c r="F73" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" t="s">
+        <v>648</v>
+      </c>
+      <c r="H73" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8">
+      <c r="B74" t="s">
+        <v>192</v>
+      </c>
+      <c r="C74" t="s">
+        <v>785</v>
+      </c>
+      <c r="D74" t="s">
+        <v>243</v>
+      </c>
+      <c r="E74" t="s">
+        <v>786</v>
+      </c>
+      <c r="F74" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" t="s">
+        <v>648</v>
+      </c>
+      <c r="H74" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8">
+      <c r="B75" t="s">
+        <v>192</v>
+      </c>
+      <c r="C75" t="s">
+        <v>787</v>
+      </c>
+      <c r="D75" t="s">
+        <v>243</v>
+      </c>
+      <c r="E75" t="s">
+        <v>788</v>
+      </c>
+      <c r="F75" t="s">
+        <v>26</v>
+      </c>
+      <c r="G75" t="s">
+        <v>648</v>
+      </c>
+      <c r="H75" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8">
+      <c r="B76" t="s">
+        <v>192</v>
+      </c>
+      <c r="C76" t="s">
+        <v>789</v>
+      </c>
+      <c r="D76" t="s">
+        <v>243</v>
+      </c>
+      <c r="E76" t="s">
+        <v>790</v>
+      </c>
+      <c r="F76" t="s">
+        <v>26</v>
+      </c>
+      <c r="G76" t="s">
+        <v>648</v>
+      </c>
+      <c r="H76" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8">
+      <c r="B77" t="s">
+        <v>192</v>
+      </c>
+      <c r="C77" t="s">
+        <v>791</v>
+      </c>
+      <c r="D77" t="s">
+        <v>243</v>
+      </c>
+      <c r="E77" t="s">
+        <v>792</v>
+      </c>
+      <c r="F77" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" t="s">
+        <v>648</v>
+      </c>
+      <c r="H77" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8">
+      <c r="B78" t="s">
+        <v>192</v>
+      </c>
+      <c r="C78" t="s">
+        <v>793</v>
+      </c>
+      <c r="D78" t="s">
+        <v>243</v>
+      </c>
+      <c r="E78" t="s">
+        <v>794</v>
+      </c>
+      <c r="F78" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" t="s">
+        <v>648</v>
+      </c>
+      <c r="H78" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8">
+      <c r="B79" t="s">
+        <v>192</v>
+      </c>
+      <c r="C79" t="s">
+        <v>795</v>
+      </c>
+      <c r="D79" t="s">
+        <v>243</v>
+      </c>
+      <c r="E79" t="s">
+        <v>796</v>
+      </c>
+      <c r="F79" t="s">
+        <v>26</v>
+      </c>
+      <c r="G79" t="s">
+        <v>648</v>
+      </c>
+      <c r="H79" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8">
+      <c r="B80" t="s">
+        <v>192</v>
+      </c>
+      <c r="C80" t="s">
+        <v>797</v>
+      </c>
+      <c r="D80" t="s">
+        <v>243</v>
+      </c>
+      <c r="E80" t="s">
+        <v>798</v>
+      </c>
+      <c r="F80" t="s">
+        <v>26</v>
+      </c>
+      <c r="G80" t="s">
+        <v>648</v>
+      </c>
+      <c r="H80" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8">
+      <c r="B81" t="s">
+        <v>192</v>
+      </c>
+      <c r="C81" t="s">
+        <v>799</v>
+      </c>
+      <c r="D81" t="s">
+        <v>243</v>
+      </c>
+      <c r="E81" t="s">
+        <v>800</v>
+      </c>
+      <c r="F81" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" t="s">
+        <v>648</v>
+      </c>
+      <c r="H81" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8">
+      <c r="B82" t="s">
+        <v>192</v>
+      </c>
+      <c r="C82" t="s">
+        <v>801</v>
+      </c>
+      <c r="D82" t="s">
+        <v>243</v>
+      </c>
+      <c r="E82" t="s">
+        <v>802</v>
+      </c>
+      <c r="F82" t="s">
+        <v>26</v>
+      </c>
+      <c r="G82" t="s">
+        <v>648</v>
+      </c>
+      <c r="H82" t="s">
         <v>195</v>
       </c>
     </row>
@@ -6656,13 +6676,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8675A9A-2614-46E3-A9BA-5DAD67EC3D7E}">
-  <dimension ref="B3:I64"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88C1B4F-C4AD-47BE-9F7D-63B8ADA6B425}">
+  <dimension ref="B3:I52"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>494</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -6696,13 +6716,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>616</v>
+        <v>550</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>617</v>
+        <v>551</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -6711,7 +6731,7 @@
         <v>232</v>
       </c>
       <c r="H5" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I5" t="s">
         <v>247</v>
@@ -6722,13 +6742,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>618</v>
+        <v>552</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>619</v>
+        <v>553</v>
       </c>
       <c r="F6" t="s">
         <v>233</v>
@@ -6737,7 +6757,7 @@
         <v>232</v>
       </c>
       <c r="H6" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I6" t="s">
         <v>247</v>
@@ -6748,13 +6768,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>620</v>
+        <v>554</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>621</v>
+        <v>555</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -6763,7 +6783,7 @@
         <v>232</v>
       </c>
       <c r="H7" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I7" t="s">
         <v>247</v>
@@ -6774,13 +6794,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>622</v>
+        <v>556</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>623</v>
+        <v>557</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -6789,7 +6809,7 @@
         <v>232</v>
       </c>
       <c r="H8" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I8" t="s">
         <v>247</v>
@@ -6800,13 +6820,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>624</v>
+        <v>558</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>625</v>
+        <v>559</v>
       </c>
       <c r="F9" t="s">
         <v>233</v>
@@ -6815,7 +6835,7 @@
         <v>232</v>
       </c>
       <c r="H9" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I9" t="s">
         <v>247</v>
@@ -6826,13 +6846,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>626</v>
+        <v>560</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>627</v>
+        <v>561</v>
       </c>
       <c r="F10" t="s">
         <v>233</v>
@@ -6841,7 +6861,7 @@
         <v>232</v>
       </c>
       <c r="H10" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I10" t="s">
         <v>247</v>
@@ -6852,13 +6872,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>628</v>
+        <v>562</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>629</v>
+        <v>563</v>
       </c>
       <c r="F11" t="s">
         <v>233</v>
@@ -6867,7 +6887,7 @@
         <v>232</v>
       </c>
       <c r="H11" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I11" t="s">
         <v>247</v>
@@ -6878,13 +6898,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>630</v>
+        <v>564</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>631</v>
+        <v>565</v>
       </c>
       <c r="F12" t="s">
         <v>233</v>
@@ -6893,7 +6913,7 @@
         <v>232</v>
       </c>
       <c r="H12" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I12" t="s">
         <v>247</v>
@@ -6904,13 +6924,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>632</v>
+        <v>566</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>633</v>
+        <v>567</v>
       </c>
       <c r="F13" t="s">
         <v>233</v>
@@ -6919,7 +6939,7 @@
         <v>232</v>
       </c>
       <c r="H13" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I13" t="s">
         <v>247</v>
@@ -6930,13 +6950,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>634</v>
+        <v>568</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>635</v>
+        <v>569</v>
       </c>
       <c r="F14" t="s">
         <v>233</v>
@@ -6945,7 +6965,7 @@
         <v>232</v>
       </c>
       <c r="H14" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I14" t="s">
         <v>247</v>
@@ -6956,13 +6976,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>636</v>
+        <v>570</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>637</v>
+        <v>571</v>
       </c>
       <c r="F15" t="s">
         <v>233</v>
@@ -6971,7 +6991,7 @@
         <v>232</v>
       </c>
       <c r="H15" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I15" t="s">
         <v>247</v>
@@ -6982,13 +7002,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>638</v>
+        <v>572</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>639</v>
+        <v>573</v>
       </c>
       <c r="F16" t="s">
         <v>233</v>
@@ -6997,7 +7017,7 @@
         <v>232</v>
       </c>
       <c r="H16" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I16" t="s">
         <v>247</v>
@@ -7008,13 +7028,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>640</v>
+        <v>574</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>641</v>
+        <v>575</v>
       </c>
       <c r="F17" t="s">
         <v>233</v>
@@ -7023,7 +7043,7 @@
         <v>232</v>
       </c>
       <c r="H17" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I17" t="s">
         <v>247</v>
@@ -7034,13 +7054,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>642</v>
+        <v>576</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>643</v>
+        <v>577</v>
       </c>
       <c r="F18" t="s">
         <v>233</v>
@@ -7049,7 +7069,7 @@
         <v>232</v>
       </c>
       <c r="H18" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I18" t="s">
         <v>247</v>
@@ -7060,13 +7080,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>644</v>
+        <v>578</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>645</v>
+        <v>579</v>
       </c>
       <c r="F19" t="s">
         <v>233</v>
@@ -7075,7 +7095,7 @@
         <v>232</v>
       </c>
       <c r="H19" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I19" t="s">
         <v>247</v>
@@ -7086,13 +7106,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>646</v>
+        <v>580</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>647</v>
+        <v>581</v>
       </c>
       <c r="F20" t="s">
         <v>233</v>
@@ -7101,7 +7121,7 @@
         <v>232</v>
       </c>
       <c r="H20" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I20" t="s">
         <v>247</v>
@@ -7112,13 +7132,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>648</v>
+        <v>582</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>649</v>
+        <v>583</v>
       </c>
       <c r="F21" t="s">
         <v>233</v>
@@ -7127,7 +7147,7 @@
         <v>232</v>
       </c>
       <c r="H21" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I21" t="s">
         <v>247</v>
@@ -7138,13 +7158,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>650</v>
+        <v>584</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>651</v>
+        <v>585</v>
       </c>
       <c r="F22" t="s">
         <v>233</v>
@@ -7153,7 +7173,7 @@
         <v>232</v>
       </c>
       <c r="H22" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I22" t="s">
         <v>247</v>
@@ -7164,13 +7184,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>652</v>
+        <v>586</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>653</v>
+        <v>587</v>
       </c>
       <c r="F23" t="s">
         <v>233</v>
@@ -7179,7 +7199,7 @@
         <v>232</v>
       </c>
       <c r="H23" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I23" t="s">
         <v>247</v>
@@ -7190,13 +7210,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>654</v>
+        <v>588</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>655</v>
+        <v>589</v>
       </c>
       <c r="F24" t="s">
         <v>233</v>
@@ -7205,7 +7225,7 @@
         <v>232</v>
       </c>
       <c r="H24" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I24" t="s">
         <v>247</v>
@@ -7216,13 +7236,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>656</v>
+        <v>590</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>657</v>
+        <v>591</v>
       </c>
       <c r="F25" t="s">
         <v>233</v>
@@ -7231,7 +7251,7 @@
         <v>232</v>
       </c>
       <c r="H25" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I25" t="s">
         <v>247</v>
@@ -7242,13 +7262,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>658</v>
+        <v>592</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>659</v>
+        <v>593</v>
       </c>
       <c r="F26" t="s">
         <v>233</v>
@@ -7257,7 +7277,7 @@
         <v>232</v>
       </c>
       <c r="H26" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I26" t="s">
         <v>247</v>
@@ -7268,13 +7288,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>660</v>
+        <v>594</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>661</v>
+        <v>595</v>
       </c>
       <c r="F27" t="s">
         <v>233</v>
@@ -7283,7 +7303,7 @@
         <v>232</v>
       </c>
       <c r="H27" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I27" t="s">
         <v>247</v>
@@ -7294,13 +7314,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>662</v>
+        <v>596</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>663</v>
+        <v>597</v>
       </c>
       <c r="F28" t="s">
         <v>233</v>
@@ -7309,7 +7329,7 @@
         <v>232</v>
       </c>
       <c r="H28" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I28" t="s">
         <v>247</v>
@@ -7320,13 +7340,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>664</v>
+        <v>598</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>665</v>
+        <v>599</v>
       </c>
       <c r="F29" t="s">
         <v>233</v>
@@ -7335,7 +7355,7 @@
         <v>232</v>
       </c>
       <c r="H29" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I29" t="s">
         <v>247</v>
@@ -7346,13 +7366,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>666</v>
+        <v>600</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>667</v>
+        <v>601</v>
       </c>
       <c r="F30" t="s">
         <v>233</v>
@@ -7361,7 +7381,7 @@
         <v>232</v>
       </c>
       <c r="H30" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I30" t="s">
         <v>247</v>
@@ -7372,13 +7392,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>668</v>
+        <v>602</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>669</v>
+        <v>603</v>
       </c>
       <c r="F31" t="s">
         <v>233</v>
@@ -7387,7 +7407,7 @@
         <v>232</v>
       </c>
       <c r="H31" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I31" t="s">
         <v>247</v>
@@ -7398,13 +7418,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>670</v>
+        <v>604</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>671</v>
+        <v>605</v>
       </c>
       <c r="F32" t="s">
         <v>233</v>
@@ -7413,7 +7433,7 @@
         <v>232</v>
       </c>
       <c r="H32" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I32" t="s">
         <v>247</v>
@@ -7424,13 +7444,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>672</v>
+        <v>606</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>673</v>
+        <v>607</v>
       </c>
       <c r="F33" t="s">
         <v>233</v>
@@ -7439,7 +7459,7 @@
         <v>232</v>
       </c>
       <c r="H33" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I33" t="s">
         <v>247</v>
@@ -7450,13 +7470,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>674</v>
+        <v>608</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>675</v>
+        <v>609</v>
       </c>
       <c r="F34" t="s">
         <v>233</v>
@@ -7465,7 +7485,7 @@
         <v>232</v>
       </c>
       <c r="H34" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I34" t="s">
         <v>247</v>
@@ -7476,13 +7496,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>676</v>
+        <v>610</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>677</v>
+        <v>611</v>
       </c>
       <c r="F35" t="s">
         <v>233</v>
@@ -7491,7 +7511,7 @@
         <v>232</v>
       </c>
       <c r="H35" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I35" t="s">
         <v>247</v>
@@ -7502,13 +7522,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>678</v>
+        <v>612</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>679</v>
+        <v>613</v>
       </c>
       <c r="F36" t="s">
         <v>233</v>
@@ -7517,7 +7537,7 @@
         <v>232</v>
       </c>
       <c r="H36" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I36" t="s">
         <v>247</v>
@@ -7528,13 +7548,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>680</v>
+        <v>614</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>681</v>
+        <v>615</v>
       </c>
       <c r="F37" t="s">
         <v>233</v>
@@ -7543,7 +7563,7 @@
         <v>232</v>
       </c>
       <c r="H37" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I37" t="s">
         <v>247</v>
@@ -7554,13 +7574,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>682</v>
+        <v>616</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>683</v>
+        <v>617</v>
       </c>
       <c r="F38" t="s">
         <v>233</v>
@@ -7569,7 +7589,7 @@
         <v>232</v>
       </c>
       <c r="H38" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I38" t="s">
         <v>247</v>
@@ -7580,13 +7600,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>684</v>
+        <v>618</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>685</v>
+        <v>619</v>
       </c>
       <c r="F39" t="s">
         <v>233</v>
@@ -7595,7 +7615,7 @@
         <v>232</v>
       </c>
       <c r="H39" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I39" t="s">
         <v>247</v>
@@ -7606,13 +7626,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>686</v>
+        <v>620</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>687</v>
+        <v>621</v>
       </c>
       <c r="F40" t="s">
         <v>233</v>
@@ -7621,7 +7641,7 @@
         <v>232</v>
       </c>
       <c r="H40" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I40" t="s">
         <v>247</v>
@@ -7632,13 +7652,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>688</v>
+        <v>622</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>689</v>
+        <v>623</v>
       </c>
       <c r="F41" t="s">
         <v>233</v>
@@ -7647,7 +7667,7 @@
         <v>232</v>
       </c>
       <c r="H41" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I41" t="s">
         <v>247</v>
@@ -7658,13 +7678,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>690</v>
+        <v>624</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>691</v>
+        <v>625</v>
       </c>
       <c r="F42" t="s">
         <v>233</v>
@@ -7673,7 +7693,7 @@
         <v>232</v>
       </c>
       <c r="H42" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I42" t="s">
         <v>247</v>
@@ -7684,13 +7704,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>692</v>
+        <v>626</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>693</v>
+        <v>627</v>
       </c>
       <c r="F43" t="s">
         <v>233</v>
@@ -7699,7 +7719,7 @@
         <v>232</v>
       </c>
       <c r="H43" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I43" t="s">
         <v>247</v>
@@ -7710,13 +7730,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>694</v>
+        <v>628</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>695</v>
+        <v>629</v>
       </c>
       <c r="F44" t="s">
         <v>233</v>
@@ -7725,7 +7745,7 @@
         <v>232</v>
       </c>
       <c r="H44" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I44" t="s">
         <v>247</v>
@@ -7736,13 +7756,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>696</v>
+        <v>630</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>697</v>
+        <v>631</v>
       </c>
       <c r="F45" t="s">
         <v>233</v>
@@ -7751,7 +7771,7 @@
         <v>232</v>
       </c>
       <c r="H45" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I45" t="s">
         <v>247</v>
@@ -7762,13 +7782,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>698</v>
+        <v>632</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>699</v>
+        <v>633</v>
       </c>
       <c r="F46" t="s">
         <v>233</v>
@@ -7777,7 +7797,7 @@
         <v>232</v>
       </c>
       <c r="H46" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I46" t="s">
         <v>247</v>
@@ -7788,13 +7808,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>700</v>
+        <v>634</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>701</v>
+        <v>635</v>
       </c>
       <c r="F47" t="s">
         <v>233</v>
@@ -7803,7 +7823,7 @@
         <v>232</v>
       </c>
       <c r="H47" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I47" t="s">
         <v>247</v>
@@ -7814,13 +7834,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>702</v>
+        <v>636</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>703</v>
+        <v>637</v>
       </c>
       <c r="F48" t="s">
         <v>233</v>
@@ -7829,7 +7849,7 @@
         <v>232</v>
       </c>
       <c r="H48" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I48" t="s">
         <v>247</v>
@@ -7840,13 +7860,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>704</v>
+        <v>638</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>705</v>
+        <v>639</v>
       </c>
       <c r="F49" t="s">
         <v>233</v>
@@ -7855,7 +7875,7 @@
         <v>232</v>
       </c>
       <c r="H49" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I49" t="s">
         <v>247</v>
@@ -7866,13 +7886,13 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>706</v>
+        <v>640</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>707</v>
+        <v>641</v>
       </c>
       <c r="F50" t="s">
         <v>233</v>
@@ -7881,7 +7901,7 @@
         <v>232</v>
       </c>
       <c r="H50" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I50" t="s">
         <v>247</v>
@@ -7892,13 +7912,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>708</v>
+        <v>642</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>709</v>
+        <v>643</v>
       </c>
       <c r="F51" t="s">
         <v>233</v>
@@ -7907,7 +7927,7 @@
         <v>232</v>
       </c>
       <c r="H51" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I51" t="s">
         <v>247</v>
@@ -7918,13 +7938,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>710</v>
+        <v>644</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>711</v>
+        <v>645</v>
       </c>
       <c r="F52" t="s">
         <v>233</v>
@@ -7933,321 +7953,9 @@
         <v>232</v>
       </c>
       <c r="H52" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I52" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="53" spans="2:9">
-      <c r="B53" t="s">
-        <v>17</v>
-      </c>
-      <c r="C53" t="s">
-        <v>712</v>
-      </c>
-      <c r="D53" t="s">
-        <v>243</v>
-      </c>
-      <c r="E53" t="s">
-        <v>713</v>
-      </c>
-      <c r="F53" t="s">
-        <v>233</v>
-      </c>
-      <c r="G53" t="s">
-        <v>232</v>
-      </c>
-      <c r="H53" t="s">
-        <v>497</v>
-      </c>
-      <c r="I53" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="54" spans="2:9">
-      <c r="B54" t="s">
-        <v>17</v>
-      </c>
-      <c r="C54" t="s">
-        <v>714</v>
-      </c>
-      <c r="D54" t="s">
-        <v>243</v>
-      </c>
-      <c r="E54" t="s">
-        <v>715</v>
-      </c>
-      <c r="F54" t="s">
-        <v>233</v>
-      </c>
-      <c r="G54" t="s">
-        <v>232</v>
-      </c>
-      <c r="H54" t="s">
-        <v>497</v>
-      </c>
-      <c r="I54" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9">
-      <c r="B55" t="s">
-        <v>17</v>
-      </c>
-      <c r="C55" t="s">
-        <v>716</v>
-      </c>
-      <c r="D55" t="s">
-        <v>243</v>
-      </c>
-      <c r="E55" t="s">
-        <v>717</v>
-      </c>
-      <c r="F55" t="s">
-        <v>233</v>
-      </c>
-      <c r="G55" t="s">
-        <v>232</v>
-      </c>
-      <c r="H55" t="s">
-        <v>497</v>
-      </c>
-      <c r="I55" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="56" spans="2:9">
-      <c r="B56" t="s">
-        <v>17</v>
-      </c>
-      <c r="C56" t="s">
-        <v>718</v>
-      </c>
-      <c r="D56" t="s">
-        <v>243</v>
-      </c>
-      <c r="E56" t="s">
-        <v>719</v>
-      </c>
-      <c r="F56" t="s">
-        <v>233</v>
-      </c>
-      <c r="G56" t="s">
-        <v>232</v>
-      </c>
-      <c r="H56" t="s">
-        <v>497</v>
-      </c>
-      <c r="I56" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="57" spans="2:9">
-      <c r="B57" t="s">
-        <v>17</v>
-      </c>
-      <c r="C57" t="s">
-        <v>720</v>
-      </c>
-      <c r="D57" t="s">
-        <v>243</v>
-      </c>
-      <c r="E57" t="s">
-        <v>721</v>
-      </c>
-      <c r="F57" t="s">
-        <v>233</v>
-      </c>
-      <c r="G57" t="s">
-        <v>232</v>
-      </c>
-      <c r="H57" t="s">
-        <v>497</v>
-      </c>
-      <c r="I57" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="58" spans="2:9">
-      <c r="B58" t="s">
-        <v>17</v>
-      </c>
-      <c r="C58" t="s">
-        <v>722</v>
-      </c>
-      <c r="D58" t="s">
-        <v>243</v>
-      </c>
-      <c r="E58" t="s">
-        <v>723</v>
-      </c>
-      <c r="F58" t="s">
-        <v>233</v>
-      </c>
-      <c r="G58" t="s">
-        <v>232</v>
-      </c>
-      <c r="H58" t="s">
-        <v>497</v>
-      </c>
-      <c r="I58" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="59" spans="2:9">
-      <c r="B59" t="s">
-        <v>17</v>
-      </c>
-      <c r="C59" t="s">
-        <v>724</v>
-      </c>
-      <c r="D59" t="s">
-        <v>243</v>
-      </c>
-      <c r="E59" t="s">
-        <v>725</v>
-      </c>
-      <c r="F59" t="s">
-        <v>233</v>
-      </c>
-      <c r="G59" t="s">
-        <v>232</v>
-      </c>
-      <c r="H59" t="s">
-        <v>497</v>
-      </c>
-      <c r="I59" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="60" spans="2:9">
-      <c r="B60" t="s">
-        <v>17</v>
-      </c>
-      <c r="C60" t="s">
-        <v>726</v>
-      </c>
-      <c r="D60" t="s">
-        <v>243</v>
-      </c>
-      <c r="E60" t="s">
-        <v>727</v>
-      </c>
-      <c r="F60" t="s">
-        <v>233</v>
-      </c>
-      <c r="G60" t="s">
-        <v>232</v>
-      </c>
-      <c r="H60" t="s">
-        <v>497</v>
-      </c>
-      <c r="I60" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="61" spans="2:9">
-      <c r="B61" t="s">
-        <v>17</v>
-      </c>
-      <c r="C61" t="s">
-        <v>728</v>
-      </c>
-      <c r="D61" t="s">
-        <v>243</v>
-      </c>
-      <c r="E61" t="s">
-        <v>729</v>
-      </c>
-      <c r="F61" t="s">
-        <v>233</v>
-      </c>
-      <c r="G61" t="s">
-        <v>232</v>
-      </c>
-      <c r="H61" t="s">
-        <v>497</v>
-      </c>
-      <c r="I61" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="62" spans="2:9">
-      <c r="B62" t="s">
-        <v>17</v>
-      </c>
-      <c r="C62" t="s">
-        <v>730</v>
-      </c>
-      <c r="D62" t="s">
-        <v>243</v>
-      </c>
-      <c r="E62" t="s">
-        <v>731</v>
-      </c>
-      <c r="F62" t="s">
-        <v>233</v>
-      </c>
-      <c r="G62" t="s">
-        <v>232</v>
-      </c>
-      <c r="H62" t="s">
-        <v>497</v>
-      </c>
-      <c r="I62" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="63" spans="2:9">
-      <c r="B63" t="s">
-        <v>17</v>
-      </c>
-      <c r="C63" t="s">
-        <v>732</v>
-      </c>
-      <c r="D63" t="s">
-        <v>243</v>
-      </c>
-      <c r="E63" t="s">
-        <v>733</v>
-      </c>
-      <c r="F63" t="s">
-        <v>233</v>
-      </c>
-      <c r="G63" t="s">
-        <v>232</v>
-      </c>
-      <c r="H63" t="s">
-        <v>497</v>
-      </c>
-      <c r="I63" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="64" spans="2:9">
-      <c r="B64" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" t="s">
-        <v>734</v>
-      </c>
-      <c r="D64" t="s">
-        <v>243</v>
-      </c>
-      <c r="E64" t="s">
-        <v>735</v>
-      </c>
-      <c r="F64" t="s">
-        <v>233</v>
-      </c>
-      <c r="G64" t="s">
-        <v>232</v>
-      </c>
-      <c r="H64" t="s">
-        <v>497</v>
-      </c>
-      <c r="I64" t="s">
         <v>247</v>
       </c>
     </row>
@@ -8257,13 +7965,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11AE27F4-6BCB-4E70-944E-6E03C6A66E34}">
-  <dimension ref="B3:I64"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D5B8311-A7E9-42EF-B49B-10C96D5F9BB3}">
+  <dimension ref="B3:I52"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>494</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -8297,13 +8005,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>495</v>
+        <v>453</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>496</v>
+        <v>454</v>
       </c>
       <c r="F5" t="s">
         <v>25</v>
@@ -8312,7 +8020,7 @@
         <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I5" t="s">
         <v>247</v>
@@ -8323,13 +8031,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>498</v>
+        <v>456</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>499</v>
+        <v>457</v>
       </c>
       <c r="F6" t="s">
         <v>25</v>
@@ -8338,7 +8046,7 @@
         <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I6" t="s">
         <v>247</v>
@@ -8349,13 +8057,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>500</v>
+        <v>458</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>501</v>
+        <v>459</v>
       </c>
       <c r="F7" t="s">
         <v>25</v>
@@ -8364,7 +8072,7 @@
         <v>35</v>
       </c>
       <c r="H7" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I7" t="s">
         <v>247</v>
@@ -8375,13 +8083,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>502</v>
+        <v>460</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>503</v>
+        <v>461</v>
       </c>
       <c r="F8" t="s">
         <v>25</v>
@@ -8390,7 +8098,7 @@
         <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I8" t="s">
         <v>247</v>
@@ -8401,13 +8109,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>504</v>
+        <v>462</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>505</v>
+        <v>463</v>
       </c>
       <c r="F9" t="s">
         <v>25</v>
@@ -8416,7 +8124,7 @@
         <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I9" t="s">
         <v>247</v>
@@ -8427,13 +8135,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>506</v>
+        <v>464</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>507</v>
+        <v>465</v>
       </c>
       <c r="F10" t="s">
         <v>25</v>
@@ -8442,7 +8150,7 @@
         <v>35</v>
       </c>
       <c r="H10" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I10" t="s">
         <v>247</v>
@@ -8453,13 +8161,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>508</v>
+        <v>466</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>509</v>
+        <v>467</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
@@ -8468,7 +8176,7 @@
         <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I11" t="s">
         <v>247</v>
@@ -8479,13 +8187,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>510</v>
+        <v>468</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>511</v>
+        <v>469</v>
       </c>
       <c r="F12" t="s">
         <v>25</v>
@@ -8494,7 +8202,7 @@
         <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I12" t="s">
         <v>247</v>
@@ -8505,13 +8213,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>512</v>
+        <v>470</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>513</v>
+        <v>471</v>
       </c>
       <c r="F13" t="s">
         <v>25</v>
@@ -8520,7 +8228,7 @@
         <v>35</v>
       </c>
       <c r="H13" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I13" t="s">
         <v>247</v>
@@ -8531,13 +8239,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>514</v>
+        <v>472</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>515</v>
+        <v>473</v>
       </c>
       <c r="F14" t="s">
         <v>25</v>
@@ -8546,7 +8254,7 @@
         <v>35</v>
       </c>
       <c r="H14" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I14" t="s">
         <v>247</v>
@@ -8557,13 +8265,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>516</v>
+        <v>474</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>517</v>
+        <v>475</v>
       </c>
       <c r="F15" t="s">
         <v>25</v>
@@ -8572,7 +8280,7 @@
         <v>35</v>
       </c>
       <c r="H15" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I15" t="s">
         <v>247</v>
@@ -8583,13 +8291,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>518</v>
+        <v>476</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>519</v>
+        <v>477</v>
       </c>
       <c r="F16" t="s">
         <v>25</v>
@@ -8598,7 +8306,7 @@
         <v>35</v>
       </c>
       <c r="H16" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I16" t="s">
         <v>247</v>
@@ -8609,13 +8317,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>520</v>
+        <v>478</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>521</v>
+        <v>479</v>
       </c>
       <c r="F17" t="s">
         <v>25</v>
@@ -8624,7 +8332,7 @@
         <v>35</v>
       </c>
       <c r="H17" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I17" t="s">
         <v>247</v>
@@ -8635,13 +8343,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>522</v>
+        <v>480</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>523</v>
+        <v>481</v>
       </c>
       <c r="F18" t="s">
         <v>25</v>
@@ -8650,7 +8358,7 @@
         <v>35</v>
       </c>
       <c r="H18" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I18" t="s">
         <v>247</v>
@@ -8661,13 +8369,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>524</v>
+        <v>482</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>525</v>
+        <v>483</v>
       </c>
       <c r="F19" t="s">
         <v>25</v>
@@ -8676,7 +8384,7 @@
         <v>35</v>
       </c>
       <c r="H19" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I19" t="s">
         <v>247</v>
@@ -8687,13 +8395,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>526</v>
+        <v>484</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>527</v>
+        <v>485</v>
       </c>
       <c r="F20" t="s">
         <v>25</v>
@@ -8702,7 +8410,7 @@
         <v>35</v>
       </c>
       <c r="H20" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I20" t="s">
         <v>247</v>
@@ -8713,13 +8421,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>528</v>
+        <v>486</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>529</v>
+        <v>487</v>
       </c>
       <c r="F21" t="s">
         <v>25</v>
@@ -8728,7 +8436,7 @@
         <v>35</v>
       </c>
       <c r="H21" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I21" t="s">
         <v>247</v>
@@ -8739,13 +8447,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>530</v>
+        <v>488</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>531</v>
+        <v>489</v>
       </c>
       <c r="F22" t="s">
         <v>25</v>
@@ -8754,7 +8462,7 @@
         <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I22" t="s">
         <v>247</v>
@@ -8765,13 +8473,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>532</v>
+        <v>490</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>533</v>
+        <v>491</v>
       </c>
       <c r="F23" t="s">
         <v>25</v>
@@ -8780,7 +8488,7 @@
         <v>35</v>
       </c>
       <c r="H23" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I23" t="s">
         <v>247</v>
@@ -8791,13 +8499,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>534</v>
+        <v>492</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>535</v>
+        <v>493</v>
       </c>
       <c r="F24" t="s">
         <v>25</v>
@@ -8806,7 +8514,7 @@
         <v>35</v>
       </c>
       <c r="H24" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I24" t="s">
         <v>247</v>
@@ -8817,13 +8525,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>536</v>
+        <v>494</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>537</v>
+        <v>495</v>
       </c>
       <c r="F25" t="s">
         <v>25</v>
@@ -8832,7 +8540,7 @@
         <v>35</v>
       </c>
       <c r="H25" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I25" t="s">
         <v>247</v>
@@ -8843,13 +8551,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>538</v>
+        <v>496</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>539</v>
+        <v>497</v>
       </c>
       <c r="F26" t="s">
         <v>25</v>
@@ -8858,7 +8566,7 @@
         <v>35</v>
       </c>
       <c r="H26" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I26" t="s">
         <v>247</v>
@@ -8869,13 +8577,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>540</v>
+        <v>498</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>541</v>
+        <v>499</v>
       </c>
       <c r="F27" t="s">
         <v>25</v>
@@ -8884,7 +8592,7 @@
         <v>35</v>
       </c>
       <c r="H27" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I27" t="s">
         <v>247</v>
@@ -8895,13 +8603,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>542</v>
+        <v>500</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>543</v>
+        <v>501</v>
       </c>
       <c r="F28" t="s">
         <v>25</v>
@@ -8910,7 +8618,7 @@
         <v>35</v>
       </c>
       <c r="H28" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I28" t="s">
         <v>247</v>
@@ -8921,13 +8629,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>544</v>
+        <v>502</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>545</v>
+        <v>503</v>
       </c>
       <c r="F29" t="s">
         <v>25</v>
@@ -8936,7 +8644,7 @@
         <v>35</v>
       </c>
       <c r="H29" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I29" t="s">
         <v>247</v>
@@ -8947,13 +8655,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>546</v>
+        <v>504</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>547</v>
+        <v>505</v>
       </c>
       <c r="F30" t="s">
         <v>25</v>
@@ -8962,7 +8670,7 @@
         <v>35</v>
       </c>
       <c r="H30" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I30" t="s">
         <v>247</v>
@@ -8973,13 +8681,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>548</v>
+        <v>506</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>549</v>
+        <v>507</v>
       </c>
       <c r="F31" t="s">
         <v>25</v>
@@ -8988,7 +8696,7 @@
         <v>35</v>
       </c>
       <c r="H31" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I31" t="s">
         <v>247</v>
@@ -8999,13 +8707,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>550</v>
+        <v>508</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>551</v>
+        <v>509</v>
       </c>
       <c r="F32" t="s">
         <v>25</v>
@@ -9014,7 +8722,7 @@
         <v>35</v>
       </c>
       <c r="H32" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I32" t="s">
         <v>247</v>
@@ -9025,13 +8733,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>552</v>
+        <v>510</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>553</v>
+        <v>511</v>
       </c>
       <c r="F33" t="s">
         <v>25</v>
@@ -9040,7 +8748,7 @@
         <v>35</v>
       </c>
       <c r="H33" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I33" t="s">
         <v>247</v>
@@ -9051,13 +8759,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>554</v>
+        <v>512</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>555</v>
+        <v>513</v>
       </c>
       <c r="F34" t="s">
         <v>25</v>
@@ -9066,7 +8774,7 @@
         <v>35</v>
       </c>
       <c r="H34" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I34" t="s">
         <v>247</v>
@@ -9077,13 +8785,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>556</v>
+        <v>514</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>557</v>
+        <v>515</v>
       </c>
       <c r="F35" t="s">
         <v>25</v>
@@ -9092,7 +8800,7 @@
         <v>35</v>
       </c>
       <c r="H35" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I35" t="s">
         <v>247</v>
@@ -9103,13 +8811,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>558</v>
+        <v>516</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>559</v>
+        <v>517</v>
       </c>
       <c r="F36" t="s">
         <v>25</v>
@@ -9118,7 +8826,7 @@
         <v>35</v>
       </c>
       <c r="H36" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I36" t="s">
         <v>247</v>
@@ -9129,13 +8837,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>560</v>
+        <v>518</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>561</v>
+        <v>519</v>
       </c>
       <c r="F37" t="s">
         <v>25</v>
@@ -9144,7 +8852,7 @@
         <v>35</v>
       </c>
       <c r="H37" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I37" t="s">
         <v>247</v>
@@ -9155,13 +8863,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>562</v>
+        <v>520</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>563</v>
+        <v>521</v>
       </c>
       <c r="F38" t="s">
         <v>25</v>
@@ -9170,7 +8878,7 @@
         <v>35</v>
       </c>
       <c r="H38" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I38" t="s">
         <v>247</v>
@@ -9181,13 +8889,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>564</v>
+        <v>522</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>565</v>
+        <v>523</v>
       </c>
       <c r="F39" t="s">
         <v>25</v>
@@ -9196,7 +8904,7 @@
         <v>35</v>
       </c>
       <c r="H39" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I39" t="s">
         <v>247</v>
@@ -9207,13 +8915,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>566</v>
+        <v>524</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>567</v>
+        <v>525</v>
       </c>
       <c r="F40" t="s">
         <v>25</v>
@@ -9222,7 +8930,7 @@
         <v>35</v>
       </c>
       <c r="H40" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I40" t="s">
         <v>247</v>
@@ -9233,13 +8941,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>568</v>
+        <v>526</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>569</v>
+        <v>527</v>
       </c>
       <c r="F41" t="s">
         <v>25</v>
@@ -9248,7 +8956,7 @@
         <v>35</v>
       </c>
       <c r="H41" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I41" t="s">
         <v>247</v>
@@ -9259,13 +8967,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>570</v>
+        <v>528</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>571</v>
+        <v>529</v>
       </c>
       <c r="F42" t="s">
         <v>25</v>
@@ -9274,7 +8982,7 @@
         <v>35</v>
       </c>
       <c r="H42" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I42" t="s">
         <v>247</v>
@@ -9285,13 +8993,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>572</v>
+        <v>530</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>573</v>
+        <v>531</v>
       </c>
       <c r="F43" t="s">
         <v>25</v>
@@ -9300,7 +9008,7 @@
         <v>35</v>
       </c>
       <c r="H43" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I43" t="s">
         <v>247</v>
@@ -9311,13 +9019,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>574</v>
+        <v>532</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>575</v>
+        <v>533</v>
       </c>
       <c r="F44" t="s">
         <v>25</v>
@@ -9326,7 +9034,7 @@
         <v>35</v>
       </c>
       <c r="H44" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I44" t="s">
         <v>247</v>
@@ -9337,13 +9045,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>576</v>
+        <v>534</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>577</v>
+        <v>535</v>
       </c>
       <c r="F45" t="s">
         <v>25</v>
@@ -9352,7 +9060,7 @@
         <v>35</v>
       </c>
       <c r="H45" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I45" t="s">
         <v>247</v>
@@ -9363,13 +9071,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>578</v>
+        <v>536</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>579</v>
+        <v>537</v>
       </c>
       <c r="F46" t="s">
         <v>25</v>
@@ -9378,7 +9086,7 @@
         <v>35</v>
       </c>
       <c r="H46" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I46" t="s">
         <v>247</v>
@@ -9389,13 +9097,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>580</v>
+        <v>538</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>581</v>
+        <v>539</v>
       </c>
       <c r="F47" t="s">
         <v>25</v>
@@ -9404,7 +9112,7 @@
         <v>35</v>
       </c>
       <c r="H47" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I47" t="s">
         <v>247</v>
@@ -9415,13 +9123,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>582</v>
+        <v>540</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>583</v>
+        <v>541</v>
       </c>
       <c r="F48" t="s">
         <v>25</v>
@@ -9430,7 +9138,7 @@
         <v>35</v>
       </c>
       <c r="H48" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I48" t="s">
         <v>247</v>
@@ -9441,13 +9149,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>584</v>
+        <v>542</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>585</v>
+        <v>543</v>
       </c>
       <c r="F49" t="s">
         <v>25</v>
@@ -9456,7 +9164,7 @@
         <v>35</v>
       </c>
       <c r="H49" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I49" t="s">
         <v>247</v>
@@ -9467,13 +9175,13 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>586</v>
+        <v>544</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>587</v>
+        <v>545</v>
       </c>
       <c r="F50" t="s">
         <v>25</v>
@@ -9482,7 +9190,7 @@
         <v>35</v>
       </c>
       <c r="H50" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I50" t="s">
         <v>247</v>
@@ -9493,13 +9201,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>588</v>
+        <v>546</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>589</v>
+        <v>547</v>
       </c>
       <c r="F51" t="s">
         <v>25</v>
@@ -9508,7 +9216,7 @@
         <v>35</v>
       </c>
       <c r="H51" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I51" t="s">
         <v>247</v>
@@ -9519,13 +9227,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>590</v>
+        <v>548</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>591</v>
+        <v>549</v>
       </c>
       <c r="F52" t="s">
         <v>25</v>
@@ -9534,321 +9242,9 @@
         <v>35</v>
       </c>
       <c r="H52" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="I52" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="53" spans="2:9">
-      <c r="B53" t="s">
-        <v>17</v>
-      </c>
-      <c r="C53" t="s">
-        <v>592</v>
-      </c>
-      <c r="D53" t="s">
-        <v>243</v>
-      </c>
-      <c r="E53" t="s">
-        <v>593</v>
-      </c>
-      <c r="F53" t="s">
-        <v>25</v>
-      </c>
-      <c r="G53" t="s">
-        <v>35</v>
-      </c>
-      <c r="H53" t="s">
-        <v>497</v>
-      </c>
-      <c r="I53" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="54" spans="2:9">
-      <c r="B54" t="s">
-        <v>17</v>
-      </c>
-      <c r="C54" t="s">
-        <v>594</v>
-      </c>
-      <c r="D54" t="s">
-        <v>243</v>
-      </c>
-      <c r="E54" t="s">
-        <v>595</v>
-      </c>
-      <c r="F54" t="s">
-        <v>25</v>
-      </c>
-      <c r="G54" t="s">
-        <v>35</v>
-      </c>
-      <c r="H54" t="s">
-        <v>497</v>
-      </c>
-      <c r="I54" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9">
-      <c r="B55" t="s">
-        <v>17</v>
-      </c>
-      <c r="C55" t="s">
-        <v>596</v>
-      </c>
-      <c r="D55" t="s">
-        <v>243</v>
-      </c>
-      <c r="E55" t="s">
-        <v>597</v>
-      </c>
-      <c r="F55" t="s">
-        <v>25</v>
-      </c>
-      <c r="G55" t="s">
-        <v>35</v>
-      </c>
-      <c r="H55" t="s">
-        <v>497</v>
-      </c>
-      <c r="I55" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="56" spans="2:9">
-      <c r="B56" t="s">
-        <v>17</v>
-      </c>
-      <c r="C56" t="s">
-        <v>598</v>
-      </c>
-      <c r="D56" t="s">
-        <v>243</v>
-      </c>
-      <c r="E56" t="s">
-        <v>599</v>
-      </c>
-      <c r="F56" t="s">
-        <v>25</v>
-      </c>
-      <c r="G56" t="s">
-        <v>35</v>
-      </c>
-      <c r="H56" t="s">
-        <v>497</v>
-      </c>
-      <c r="I56" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="57" spans="2:9">
-      <c r="B57" t="s">
-        <v>17</v>
-      </c>
-      <c r="C57" t="s">
-        <v>600</v>
-      </c>
-      <c r="D57" t="s">
-        <v>243</v>
-      </c>
-      <c r="E57" t="s">
-        <v>601</v>
-      </c>
-      <c r="F57" t="s">
-        <v>25</v>
-      </c>
-      <c r="G57" t="s">
-        <v>35</v>
-      </c>
-      <c r="H57" t="s">
-        <v>497</v>
-      </c>
-      <c r="I57" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="58" spans="2:9">
-      <c r="B58" t="s">
-        <v>17</v>
-      </c>
-      <c r="C58" t="s">
-        <v>602</v>
-      </c>
-      <c r="D58" t="s">
-        <v>243</v>
-      </c>
-      <c r="E58" t="s">
-        <v>603</v>
-      </c>
-      <c r="F58" t="s">
-        <v>25</v>
-      </c>
-      <c r="G58" t="s">
-        <v>35</v>
-      </c>
-      <c r="H58" t="s">
-        <v>497</v>
-      </c>
-      <c r="I58" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="59" spans="2:9">
-      <c r="B59" t="s">
-        <v>17</v>
-      </c>
-      <c r="C59" t="s">
-        <v>604</v>
-      </c>
-      <c r="D59" t="s">
-        <v>243</v>
-      </c>
-      <c r="E59" t="s">
-        <v>605</v>
-      </c>
-      <c r="F59" t="s">
-        <v>25</v>
-      </c>
-      <c r="G59" t="s">
-        <v>35</v>
-      </c>
-      <c r="H59" t="s">
-        <v>497</v>
-      </c>
-      <c r="I59" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="60" spans="2:9">
-      <c r="B60" t="s">
-        <v>17</v>
-      </c>
-      <c r="C60" t="s">
-        <v>606</v>
-      </c>
-      <c r="D60" t="s">
-        <v>243</v>
-      </c>
-      <c r="E60" t="s">
-        <v>607</v>
-      </c>
-      <c r="F60" t="s">
-        <v>25</v>
-      </c>
-      <c r="G60" t="s">
-        <v>35</v>
-      </c>
-      <c r="H60" t="s">
-        <v>497</v>
-      </c>
-      <c r="I60" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="61" spans="2:9">
-      <c r="B61" t="s">
-        <v>17</v>
-      </c>
-      <c r="C61" t="s">
-        <v>608</v>
-      </c>
-      <c r="D61" t="s">
-        <v>243</v>
-      </c>
-      <c r="E61" t="s">
-        <v>609</v>
-      </c>
-      <c r="F61" t="s">
-        <v>25</v>
-      </c>
-      <c r="G61" t="s">
-        <v>35</v>
-      </c>
-      <c r="H61" t="s">
-        <v>497</v>
-      </c>
-      <c r="I61" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="62" spans="2:9">
-      <c r="B62" t="s">
-        <v>17</v>
-      </c>
-      <c r="C62" t="s">
-        <v>610</v>
-      </c>
-      <c r="D62" t="s">
-        <v>243</v>
-      </c>
-      <c r="E62" t="s">
-        <v>611</v>
-      </c>
-      <c r="F62" t="s">
-        <v>25</v>
-      </c>
-      <c r="G62" t="s">
-        <v>35</v>
-      </c>
-      <c r="H62" t="s">
-        <v>497</v>
-      </c>
-      <c r="I62" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="63" spans="2:9">
-      <c r="B63" t="s">
-        <v>17</v>
-      </c>
-      <c r="C63" t="s">
-        <v>612</v>
-      </c>
-      <c r="D63" t="s">
-        <v>243</v>
-      </c>
-      <c r="E63" t="s">
-        <v>613</v>
-      </c>
-      <c r="F63" t="s">
-        <v>25</v>
-      </c>
-      <c r="G63" t="s">
-        <v>35</v>
-      </c>
-      <c r="H63" t="s">
-        <v>497</v>
-      </c>
-      <c r="I63" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="64" spans="2:9">
-      <c r="B64" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" t="s">
-        <v>614</v>
-      </c>
-      <c r="D64" t="s">
-        <v>243</v>
-      </c>
-      <c r="E64" t="s">
-        <v>615</v>
-      </c>
-      <c r="F64" t="s">
-        <v>25</v>
-      </c>
-      <c r="G64" t="s">
-        <v>35</v>
-      </c>
-      <c r="H64" t="s">
-        <v>497</v>
-      </c>
-      <c r="I64" t="s">
         <v>247</v>
       </c>
     </row>
@@ -9859,20 +9255,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:S128"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="B3:S107"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.73046875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:19" ht="18" thickBot="1">
+    <row r="3" spans="2:19" ht="17.25" thickBot="1">
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
@@ -9891,7 +9287,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="2:19" ht="16.5" thickTop="1" thickBot="1">
+    <row r="4" spans="2:19" ht="15" thickTop="1" thickBot="1">
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
@@ -10777,7 +10173,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="30" spans="2:19" ht="18" thickBot="1">
+    <row r="30" spans="2:19" ht="17.25" thickBot="1">
       <c r="B30" s="3" t="s">
         <v>212</v>
       </c>
@@ -10805,7 +10201,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="31" spans="2:19" ht="16.5" thickTop="1" thickBot="1">
+    <row r="31" spans="2:19" ht="15" thickTop="1" thickBot="1">
       <c r="B31" s="5" t="s">
         <v>172</v>
       </c>
@@ -10984,7 +10380,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="38" spans="2:19" ht="18" thickBot="1">
+    <row r="38" spans="2:19" ht="17.25" thickBot="1">
       <c r="B38" s="3" t="s">
         <v>8</v>
       </c>
@@ -11012,7 +10408,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="39" spans="2:19" ht="16.5" thickTop="1" thickBot="1">
+    <row r="39" spans="2:19" ht="15" thickTop="1" thickBot="1">
       <c r="B39" s="5" t="s">
         <v>218</v>
       </c>
@@ -12689,489 +12085,6 @@
         <v>35</v>
       </c>
       <c r="S107" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="108" spans="13:19">
-      <c r="M108" t="s">
-        <v>17</v>
-      </c>
-      <c r="N108" t="s">
-        <v>452</v>
-      </c>
-      <c r="O108" t="s">
-        <v>243</v>
-      </c>
-      <c r="P108" t="s">
-        <v>453</v>
-      </c>
-      <c r="Q108" t="s">
-        <v>25</v>
-      </c>
-      <c r="R108" t="s">
-        <v>35</v>
-      </c>
-      <c r="S108" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="109" spans="13:19">
-      <c r="M109" t="s">
-        <v>17</v>
-      </c>
-      <c r="N109" t="s">
-        <v>454</v>
-      </c>
-      <c r="O109" t="s">
-        <v>243</v>
-      </c>
-      <c r="P109" t="s">
-        <v>455</v>
-      </c>
-      <c r="Q109" t="s">
-        <v>25</v>
-      </c>
-      <c r="R109" t="s">
-        <v>35</v>
-      </c>
-      <c r="S109" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="110" spans="13:19">
-      <c r="M110" t="s">
-        <v>17</v>
-      </c>
-      <c r="N110" t="s">
-        <v>456</v>
-      </c>
-      <c r="O110" t="s">
-        <v>243</v>
-      </c>
-      <c r="P110" t="s">
-        <v>457</v>
-      </c>
-      <c r="Q110" t="s">
-        <v>25</v>
-      </c>
-      <c r="R110" t="s">
-        <v>35</v>
-      </c>
-      <c r="S110" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="111" spans="13:19">
-      <c r="M111" t="s">
-        <v>17</v>
-      </c>
-      <c r="N111" t="s">
-        <v>458</v>
-      </c>
-      <c r="O111" t="s">
-        <v>243</v>
-      </c>
-      <c r="P111" t="s">
-        <v>459</v>
-      </c>
-      <c r="Q111" t="s">
-        <v>25</v>
-      </c>
-      <c r="R111" t="s">
-        <v>35</v>
-      </c>
-      <c r="S111" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="112" spans="13:19">
-      <c r="M112" t="s">
-        <v>17</v>
-      </c>
-      <c r="N112" t="s">
-        <v>460</v>
-      </c>
-      <c r="O112" t="s">
-        <v>243</v>
-      </c>
-      <c r="P112" t="s">
-        <v>461</v>
-      </c>
-      <c r="Q112" t="s">
-        <v>25</v>
-      </c>
-      <c r="R112" t="s">
-        <v>35</v>
-      </c>
-      <c r="S112" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="113" spans="13:19">
-      <c r="M113" t="s">
-        <v>17</v>
-      </c>
-      <c r="N113" t="s">
-        <v>462</v>
-      </c>
-      <c r="O113" t="s">
-        <v>243</v>
-      </c>
-      <c r="P113" t="s">
-        <v>463</v>
-      </c>
-      <c r="Q113" t="s">
-        <v>25</v>
-      </c>
-      <c r="R113" t="s">
-        <v>35</v>
-      </c>
-      <c r="S113" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="114" spans="13:19">
-      <c r="M114" t="s">
-        <v>17</v>
-      </c>
-      <c r="N114" t="s">
-        <v>464</v>
-      </c>
-      <c r="O114" t="s">
-        <v>243</v>
-      </c>
-      <c r="P114" t="s">
-        <v>465</v>
-      </c>
-      <c r="Q114" t="s">
-        <v>25</v>
-      </c>
-      <c r="R114" t="s">
-        <v>35</v>
-      </c>
-      <c r="S114" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="115" spans="13:19">
-      <c r="M115" t="s">
-        <v>17</v>
-      </c>
-      <c r="N115" t="s">
-        <v>466</v>
-      </c>
-      <c r="O115" t="s">
-        <v>243</v>
-      </c>
-      <c r="P115" t="s">
-        <v>467</v>
-      </c>
-      <c r="Q115" t="s">
-        <v>25</v>
-      </c>
-      <c r="R115" t="s">
-        <v>35</v>
-      </c>
-      <c r="S115" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="116" spans="13:19">
-      <c r="M116" t="s">
-        <v>17</v>
-      </c>
-      <c r="N116" t="s">
-        <v>468</v>
-      </c>
-      <c r="O116" t="s">
-        <v>243</v>
-      </c>
-      <c r="P116" t="s">
-        <v>469</v>
-      </c>
-      <c r="Q116" t="s">
-        <v>25</v>
-      </c>
-      <c r="R116" t="s">
-        <v>35</v>
-      </c>
-      <c r="S116" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="117" spans="13:19">
-      <c r="M117" t="s">
-        <v>17</v>
-      </c>
-      <c r="N117" t="s">
-        <v>470</v>
-      </c>
-      <c r="O117" t="s">
-        <v>243</v>
-      </c>
-      <c r="P117" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q117" t="s">
-        <v>25</v>
-      </c>
-      <c r="R117" t="s">
-        <v>35</v>
-      </c>
-      <c r="S117" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="118" spans="13:19">
-      <c r="M118" t="s">
-        <v>17</v>
-      </c>
-      <c r="N118" t="s">
-        <v>472</v>
-      </c>
-      <c r="O118" t="s">
-        <v>243</v>
-      </c>
-      <c r="P118" t="s">
-        <v>473</v>
-      </c>
-      <c r="Q118" t="s">
-        <v>25</v>
-      </c>
-      <c r="R118" t="s">
-        <v>35</v>
-      </c>
-      <c r="S118" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="119" spans="13:19">
-      <c r="M119" t="s">
-        <v>17</v>
-      </c>
-      <c r="N119" t="s">
-        <v>474</v>
-      </c>
-      <c r="O119" t="s">
-        <v>243</v>
-      </c>
-      <c r="P119" t="s">
-        <v>475</v>
-      </c>
-      <c r="Q119" t="s">
-        <v>25</v>
-      </c>
-      <c r="R119" t="s">
-        <v>35</v>
-      </c>
-      <c r="S119" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="120" spans="13:19">
-      <c r="M120" t="s">
-        <v>17</v>
-      </c>
-      <c r="N120" t="s">
-        <v>476</v>
-      </c>
-      <c r="O120" t="s">
-        <v>243</v>
-      </c>
-      <c r="P120" t="s">
-        <v>477</v>
-      </c>
-      <c r="Q120" t="s">
-        <v>25</v>
-      </c>
-      <c r="R120" t="s">
-        <v>35</v>
-      </c>
-      <c r="S120" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="121" spans="13:19">
-      <c r="M121" t="s">
-        <v>17</v>
-      </c>
-      <c r="N121" t="s">
-        <v>478</v>
-      </c>
-      <c r="O121" t="s">
-        <v>243</v>
-      </c>
-      <c r="P121" t="s">
-        <v>479</v>
-      </c>
-      <c r="Q121" t="s">
-        <v>25</v>
-      </c>
-      <c r="R121" t="s">
-        <v>35</v>
-      </c>
-      <c r="S121" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="122" spans="13:19">
-      <c r="M122" t="s">
-        <v>17</v>
-      </c>
-      <c r="N122" t="s">
-        <v>480</v>
-      </c>
-      <c r="O122" t="s">
-        <v>243</v>
-      </c>
-      <c r="P122" t="s">
-        <v>481</v>
-      </c>
-      <c r="Q122" t="s">
-        <v>25</v>
-      </c>
-      <c r="R122" t="s">
-        <v>35</v>
-      </c>
-      <c r="S122" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="123" spans="13:19">
-      <c r="M123" t="s">
-        <v>17</v>
-      </c>
-      <c r="N123" t="s">
-        <v>482</v>
-      </c>
-      <c r="O123" t="s">
-        <v>243</v>
-      </c>
-      <c r="P123" t="s">
-        <v>483</v>
-      </c>
-      <c r="Q123" t="s">
-        <v>25</v>
-      </c>
-      <c r="R123" t="s">
-        <v>35</v>
-      </c>
-      <c r="S123" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="124" spans="13:19">
-      <c r="M124" t="s">
-        <v>17</v>
-      </c>
-      <c r="N124" t="s">
-        <v>484</v>
-      </c>
-      <c r="O124" t="s">
-        <v>243</v>
-      </c>
-      <c r="P124" t="s">
-        <v>485</v>
-      </c>
-      <c r="Q124" t="s">
-        <v>25</v>
-      </c>
-      <c r="R124" t="s">
-        <v>35</v>
-      </c>
-      <c r="S124" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="125" spans="13:19">
-      <c r="M125" t="s">
-        <v>17</v>
-      </c>
-      <c r="N125" t="s">
-        <v>486</v>
-      </c>
-      <c r="O125" t="s">
-        <v>243</v>
-      </c>
-      <c r="P125" t="s">
-        <v>487</v>
-      </c>
-      <c r="Q125" t="s">
-        <v>25</v>
-      </c>
-      <c r="R125" t="s">
-        <v>35</v>
-      </c>
-      <c r="S125" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="126" spans="13:19">
-      <c r="M126" t="s">
-        <v>17</v>
-      </c>
-      <c r="N126" t="s">
-        <v>488</v>
-      </c>
-      <c r="O126" t="s">
-        <v>243</v>
-      </c>
-      <c r="P126" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q126" t="s">
-        <v>25</v>
-      </c>
-      <c r="R126" t="s">
-        <v>35</v>
-      </c>
-      <c r="S126" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="127" spans="13:19">
-      <c r="M127" t="s">
-        <v>17</v>
-      </c>
-      <c r="N127" t="s">
-        <v>490</v>
-      </c>
-      <c r="O127" t="s">
-        <v>243</v>
-      </c>
-      <c r="P127" t="s">
-        <v>491</v>
-      </c>
-      <c r="Q127" t="s">
-        <v>25</v>
-      </c>
-      <c r="R127" t="s">
-        <v>35</v>
-      </c>
-      <c r="S127" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="128" spans="13:19">
-      <c r="M128" t="s">
-        <v>17</v>
-      </c>
-      <c r="N128" t="s">
-        <v>492</v>
-      </c>
-      <c r="O128" t="s">
-        <v>243</v>
-      </c>
-      <c r="P128" t="s">
-        <v>493</v>
-      </c>
-      <c r="Q128" t="s">
-        <v>25</v>
-      </c>
-      <c r="R128" t="s">
-        <v>35</v>
-      </c>
-      <c r="S128" t="s">
         <v>247</v>
       </c>
     </row>
@@ -13186,15 +12099,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A39735C-B147-4873-BE33-BF7570891F36}">
   <dimension ref="B3:G33"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="6"/>
-    <col min="4" max="4" width="14.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.42578125" style="6"/>
+    <col min="1" max="1" width="9.1328125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="11.86328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3984375" style="6"/>
+    <col min="4" max="4" width="14.1328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.86328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.86328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.3984375" style="6"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:7">
@@ -13225,7 +12138,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="15">
+    <row r="12" spans="2:7" ht="14.25">
       <c r="B12" s="7" t="s">
         <v>42</v>
       </c>
@@ -13245,7 +12158,7 @@
         <v>msy5_2050</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="15">
+    <row r="13" spans="2:7" ht="14.25">
       <c r="B13" s="9">
         <v>1</v>
       </c>
@@ -13253,7 +12166,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="15">
+    <row r="14" spans="2:7" ht="14.25">
       <c r="B14" s="9">
         <v>5</v>
       </c>
@@ -13273,7 +12186,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="15">
+    <row r="15" spans="2:7" ht="14.25">
       <c r="B15" s="9">
         <v>5</v>
       </c>
@@ -13293,7 +12206,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="15">
+    <row r="16" spans="2:7" ht="14.25">
       <c r="B16" s="9">
         <v>10</v>
       </c>
@@ -13313,7 +12226,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="15">
+    <row r="17" spans="2:7" ht="14.25">
       <c r="B17" s="9">
         <v>10</v>
       </c>
@@ -13333,7 +12246,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="15">
+    <row r="18" spans="2:7" ht="14.25">
       <c r="B18" s="9">
         <v>10</v>
       </c>
@@ -13353,7 +12266,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="15">
+    <row r="19" spans="2:7" ht="14.25">
       <c r="B19" s="9">
         <v>10</v>
       </c>
@@ -13369,7 +12282,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="15">
+    <row r="20" spans="2:7" ht="14.25">
       <c r="B20" s="9">
         <v>10</v>
       </c>
@@ -13381,7 +12294,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="15">
+    <row r="21" spans="2:7" ht="14.25">
       <c r="B21" s="9">
         <v>10</v>
       </c>
@@ -13389,7 +12302,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="15">
+    <row r="22" spans="2:7" ht="14.25">
       <c r="B22" s="9">
         <v>10</v>
       </c>
@@ -13397,7 +12310,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="15">
+    <row r="23" spans="2:7" ht="14.25">
       <c r="B23" s="9">
         <v>10</v>
       </c>
@@ -13405,7 +12318,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="15">
+    <row r="24" spans="2:7" ht="14.25">
       <c r="B24" s="9">
         <v>10</v>
       </c>
@@ -13413,46 +12326,46 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="15">
+    <row r="25" spans="2:7" ht="14.25">
       <c r="B25" s="9"/>
       <c r="D25" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="15">
+    <row r="26" spans="2:7" ht="14.25">
       <c r="B26" s="9"/>
       <c r="D26" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="15">
+    <row r="27" spans="2:7" ht="14.25">
       <c r="B27" s="9"/>
       <c r="D27" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="15">
+    <row r="28" spans="2:7" ht="14.25">
       <c r="B28" s="9"/>
       <c r="D28" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="15">
+    <row r="29" spans="2:7" ht="14.25">
       <c r="B29" s="9"/>
       <c r="D29" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="15">
+    <row r="30" spans="2:7" ht="14.25">
       <c r="B30" s="9"/>
     </row>
-    <row r="31" spans="2:7" ht="15">
+    <row r="31" spans="2:7" ht="14.25">
       <c r="B31" s="9"/>
     </row>
-    <row r="32" spans="2:7" ht="15">
+    <row r="32" spans="2:7" ht="14.25">
       <c r="B32" s="9"/>
     </row>
-    <row r="33" spans="2:2" ht="15">
+    <row r="33" spans="2:2" ht="14.25">
       <c r="B33" s="9"/>
     </row>
   </sheetData>
@@ -13464,21 +12377,21 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
   <dimension ref="B1:N42"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="11"/>
-    <col min="2" max="2" width="8.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" style="11"/>
+    <col min="1" max="1" width="11.3984375" style="11"/>
+    <col min="2" max="2" width="8.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.1328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.46484375" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.46484375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.9296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.9296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.1328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.53125" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.73046875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.3984375" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="12.75">
@@ -13710,7 +12623,7 @@
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
     </row>
-    <row r="21" spans="2:14" ht="15">
+    <row r="21" spans="2:14" ht="14.25">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -13725,7 +12638,7 @@
       <c r="M21"/>
       <c r="N21"/>
     </row>
-    <row r="22" spans="2:14" ht="15">
+    <row r="22" spans="2:14" ht="14.25">
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
@@ -13740,7 +12653,7 @@
       <c r="M22"/>
       <c r="N22"/>
     </row>
-    <row r="23" spans="2:14" ht="15">
+    <row r="23" spans="2:14" ht="14.25">
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
@@ -13755,7 +12668,7 @@
       <c r="M23"/>
       <c r="N23"/>
     </row>
-    <row r="24" spans="2:14" ht="15">
+    <row r="24" spans="2:14" ht="14.25">
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
@@ -13770,7 +12683,7 @@
       <c r="M24"/>
       <c r="N24"/>
     </row>
-    <row r="25" spans="2:14" ht="15">
+    <row r="25" spans="2:14" ht="14.25">
       <c r="B25"/>
       <c r="C25"/>
       <c r="D25"/>
@@ -13785,7 +12698,7 @@
       <c r="M25"/>
       <c r="N25"/>
     </row>
-    <row r="26" spans="2:14" ht="15">
+    <row r="26" spans="2:14" ht="14.25">
       <c r="B26"/>
       <c r="C26"/>
       <c r="D26"/>
@@ -13800,7 +12713,7 @@
       <c r="M26"/>
       <c r="N26"/>
     </row>
-    <row r="27" spans="2:14" ht="15">
+    <row r="27" spans="2:14" ht="14.25">
       <c r="B27"/>
       <c r="C27"/>
       <c r="D27"/>
@@ -13815,7 +12728,7 @@
       <c r="M27"/>
       <c r="N27"/>
     </row>
-    <row r="28" spans="2:14" ht="15">
+    <row r="28" spans="2:14" ht="14.25">
       <c r="B28"/>
       <c r="C28"/>
       <c r="D28"/>
@@ -13830,7 +12743,7 @@
       <c r="M28"/>
       <c r="N28"/>
     </row>
-    <row r="29" spans="2:14" ht="15">
+    <row r="29" spans="2:14" ht="14.25">
       <c r="B29"/>
       <c r="C29"/>
       <c r="D29"/>
@@ -13845,7 +12758,7 @@
       <c r="M29"/>
       <c r="N29"/>
     </row>
-    <row r="30" spans="2:14" ht="15">
+    <row r="30" spans="2:14" ht="14.25">
       <c r="B30"/>
       <c r="C30"/>
       <c r="D30"/>
@@ -13860,7 +12773,7 @@
       <c r="M30"/>
       <c r="N30"/>
     </row>
-    <row r="31" spans="2:14" ht="15">
+    <row r="31" spans="2:14" ht="14.25">
       <c r="B31"/>
       <c r="C31"/>
       <c r="D31"/>
@@ -13875,7 +12788,7 @@
       <c r="M31"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="2:14" ht="15">
+    <row r="32" spans="2:14" ht="14.25">
       <c r="B32"/>
       <c r="C32"/>
       <c r="D32"/>
@@ -13890,7 +12803,7 @@
       <c r="M32"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="2:14" ht="15">
+    <row r="33" spans="2:14" ht="14.25">
       <c r="B33"/>
       <c r="C33"/>
       <c r="D33"/>
@@ -13905,7 +12818,7 @@
       <c r="M33"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="2:14" ht="15">
+    <row r="34" spans="2:14" ht="14.25">
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
@@ -13920,7 +12833,7 @@
       <c r="M34"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="2:14" ht="15">
+    <row r="35" spans="2:14" ht="14.25">
       <c r="B35"/>
       <c r="C35"/>
       <c r="D35"/>
@@ -13935,7 +12848,7 @@
       <c r="M35"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="2:14" ht="15">
+    <row r="36" spans="2:14" ht="14.25">
       <c r="B36"/>
       <c r="C36"/>
       <c r="D36"/>
@@ -13950,7 +12863,7 @@
       <c r="M36"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="2:14" ht="15">
+    <row r="37" spans="2:14" ht="14.25">
       <c r="B37"/>
       <c r="C37"/>
       <c r="D37"/>
@@ -13965,7 +12878,7 @@
       <c r="M37"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="2:14" ht="15">
+    <row r="38" spans="2:14" ht="14.25">
       <c r="B38"/>
       <c r="C38"/>
       <c r="D38"/>
@@ -13980,7 +12893,7 @@
       <c r="M38"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="2:14" ht="15">
+    <row r="39" spans="2:14" ht="14.25">
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
@@ -13995,7 +12908,7 @@
       <c r="M39"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="2:14" ht="15">
+    <row r="40" spans="2:14" ht="14.25">
       <c r="B40"/>
       <c r="C40"/>
       <c r="D40"/>
@@ -14010,7 +12923,7 @@
       <c r="M40"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="2:14" ht="15">
+    <row r="41" spans="2:14" ht="14.25">
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
@@ -14025,7 +12938,7 @@
       <c r="M41"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="2:14" ht="15">
+    <row r="42" spans="2:14" ht="14.25">
       <c r="B42"/>
       <c r="C42"/>
       <c r="D42"/>
@@ -14050,25 +12963,25 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EBD23C-EA82-4040-97D7-F532F0547462}">
   <dimension ref="A2:N102"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="11"/>
-    <col min="2" max="2" width="12.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.42578125" style="11"/>
-    <col min="5" max="5" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="11"/>
-    <col min="12" max="12" width="17.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="11"/>
+    <col min="1" max="1" width="11.3984375" style="11"/>
+    <col min="2" max="2" width="12.73046875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.3984375" style="11"/>
+    <col min="5" max="5" width="13.53125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.3984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.9296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.3984375" style="11"/>
+    <col min="12" max="12" width="17.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.73046875" style="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.3984375" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" ht="18" thickBot="1">
+    <row r="2" spans="1:14" ht="17.25" thickBot="1">
       <c r="A2" s="13"/>
       <c r="B2" s="20" t="s">
         <v>68</v>
@@ -14082,7 +12995,7 @@
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14" ht="16.5" thickTop="1" thickBot="1">
+    <row r="3" spans="1:14" ht="15" thickTop="1" thickBot="1">
       <c r="A3" s="13"/>
       <c r="B3" s="4" t="s">
         <v>70</v>
@@ -14115,7 +13028,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="12.75">
+    <row r="4" spans="1:14" ht="13.15">
       <c r="A4" s="13"/>
       <c r="B4" s="19" t="s">
         <v>134</v>
@@ -14140,7 +13053,7 @@
         <v>1055.55</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="12.75">
+    <row r="5" spans="1:14" ht="13.15">
       <c r="A5" s="13"/>
       <c r="B5" s="19" t="s">
         <v>72</v>
@@ -14167,7 +13080,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="12.75">
+    <row r="6" spans="1:14" ht="13.15">
       <c r="A6" s="13"/>
       <c r="B6" s="19" t="s">
         <v>73</v>
@@ -14188,7 +13101,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="12.75">
+    <row r="7" spans="1:14" ht="13.15">
       <c r="A7" s="13"/>
       <c r="B7" s="19" t="s">
         <v>74</v>
@@ -14209,7 +13122,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="12.75">
+    <row r="8" spans="1:14" ht="13.15">
       <c r="A8" s="13"/>
       <c r="B8" s="19" t="s">
         <v>75</v>
@@ -14236,7 +13149,7 @@
         <v>1.05555</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="12.75">
+    <row r="9" spans="1:14" ht="13.15">
       <c r="A9" s="13"/>
       <c r="B9" s="19" t="s">
         <v>76</v>
@@ -14263,7 +13176,7 @@
         <v>4.1868000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="12.75">
+    <row r="10" spans="1:14" ht="13.15">
       <c r="A10" s="13"/>
       <c r="B10" s="19" t="s">
         <v>78</v>
@@ -14290,7 +13203,7 @@
         <v>41.868000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="12.75">
+    <row r="11" spans="1:14" ht="13.15">
       <c r="A11" s="13"/>
       <c r="B11" s="19" t="s">
         <v>71</v>
@@ -14317,7 +13230,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="12.75">
+    <row r="12" spans="1:14" ht="13.15">
       <c r="A12" s="13"/>
       <c r="B12" s="19" t="s">
         <v>82</v>
@@ -14344,7 +13257,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="12.75">
+    <row r="13" spans="1:14" ht="13.15">
       <c r="A13" s="13"/>
       <c r="B13" s="19" t="s">
         <v>85</v>
@@ -14371,7 +13284,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="12.75">
+    <row r="14" spans="1:14" ht="13.15">
       <c r="A14" s="13"/>
       <c r="B14" s="19" t="s">
         <v>87</v>
@@ -14398,7 +13311,7 @@
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="12.75">
+    <row r="15" spans="1:14" ht="13.15">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
         <v>90</v>
@@ -14425,7 +13338,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="12.75">
+    <row r="16" spans="1:14" ht="13.15">
       <c r="A16" s="13"/>
       <c r="B16" s="19" t="s">
         <v>93</v>
@@ -14452,7 +13365,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="12.75">
+    <row r="17" spans="1:14" ht="13.15">
       <c r="A17" s="13"/>
       <c r="B17" s="19" t="s">
         <v>95</v>
@@ -14479,7 +13392,7 @@
         <v>37.68</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="12.75">
+    <row r="18" spans="1:14" ht="13.15">
       <c r="B18" s="19" t="s">
         <v>97</v>
       </c>
@@ -14505,7 +13418,7 @@
         <v>2139.4548</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="12.75">
+    <row r="19" spans="1:14" ht="13.15">
       <c r="B19" s="19" t="s">
         <v>99</v>
       </c>
@@ -14531,7 +13444,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="12.75">
+    <row r="20" spans="1:14" ht="13.15">
       <c r="B20" s="19" t="s">
         <v>101</v>
       </c>
@@ -14557,7 +13470,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="12.75">
+    <row r="21" spans="1:14" ht="13.15">
       <c r="B21" s="19" t="s">
         <v>103</v>
       </c>
@@ -14583,7 +13496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="12.75">
+    <row r="22" spans="1:14" ht="13.15">
       <c r="B22" s="19" t="s">
         <v>106</v>
       </c>
@@ -14609,7 +13522,7 @@
         <v>31.536000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="12.75">
+    <row r="23" spans="1:14" ht="13.15">
       <c r="B23" s="19" t="s">
         <v>109</v>
       </c>
@@ -14635,7 +13548,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="12.75">
+    <row r="24" spans="1:14" ht="13.15">
       <c r="B24" s="19" t="s">
         <v>112</v>
       </c>
@@ -14661,7 +13574,7 @@
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="12.75">
+    <row r="25" spans="1:14" ht="13.15">
       <c r="B25" s="19" t="s">
         <v>114</v>
       </c>
@@ -14687,7 +13600,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="12.75">
+    <row r="26" spans="1:14" ht="13.15">
       <c r="B26" s="19" t="s">
         <v>116</v>
       </c>
@@ -14704,7 +13617,7 @@
         <v>1.4198999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="12.75">
+    <row r="27" spans="1:14" ht="13.15">
       <c r="B27" s="19" t="s">
         <v>118</v>
       </c>
@@ -14721,7 +13634,7 @@
         <v>1.3986000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="12.75">
+    <row r="28" spans="1:14" ht="13.15">
       <c r="B28" s="19" t="s">
         <v>121</v>
       </c>
@@ -14738,7 +13651,7 @@
         <v>1.3727</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="12.75">
+    <row r="29" spans="1:14" ht="13.15">
       <c r="B29" s="19" t="s">
         <v>123</v>
       </c>
@@ -14755,7 +13668,7 @@
         <v>1.3369</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="12.75">
+    <row r="30" spans="1:14" ht="13.15">
       <c r="B30" s="19" t="s">
         <v>124</v>
       </c>
@@ -14772,7 +13685,7 @@
         <v>1.2967</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="12.75">
+    <row r="31" spans="1:14" ht="13.15">
       <c r="B31" s="19" t="s">
         <v>126</v>
       </c>
@@ -14789,7 +13702,7 @@
         <v>1.2583</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="12.75">
+    <row r="32" spans="1:14" ht="13.15">
       <c r="B32" s="19" t="s">
         <v>128</v>
       </c>
@@ -14806,7 +13719,7 @@
         <v>1.2253000000000001</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="12.75">
+    <row r="33" spans="2:9" ht="13.15">
       <c r="B33" s="19" t="s">
         <v>130</v>
       </c>
@@ -14823,7 +13736,7 @@
         <v>1.2023999999999999</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="12.75">
+    <row r="34" spans="2:9" ht="13.15">
       <c r="B34" s="19" t="s">
         <v>132</v>
       </c>
@@ -14840,7 +13753,7 @@
         <v>1.1931</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="12.75">
+    <row r="35" spans="2:9" ht="13.15">
       <c r="B35" s="19" t="s">
         <v>133</v>
       </c>
@@ -14857,7 +13770,7 @@
         <v>1.1793</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="12.75">
+    <row r="36" spans="2:9" ht="13.15">
       <c r="B36" s="19" t="s">
         <v>134</v>
       </c>
@@ -14874,7 +13787,7 @@
         <v>1.1552</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="12.75">
+    <row r="37" spans="2:9" ht="13.15">
       <c r="B37" s="19" t="s">
         <v>135</v>
       </c>
@@ -14891,7 +13804,7 @@
         <v>1.1334</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="12.75">
+    <row r="38" spans="2:9" ht="13.15">
       <c r="B38" s="19" t="s">
         <v>136</v>
       </c>
@@ -14908,7 +13821,7 @@
         <v>1.1136999999999999</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="12.75">
+    <row r="39" spans="2:9" ht="13.15">
       <c r="B39" s="19" t="s">
         <v>137</v>
       </c>
@@ -14925,7 +13838,7 @@
         <v>1.0934999999999999</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="12.75">
+    <row r="40" spans="2:9" ht="13.15">
       <c r="B40" s="19" t="s">
         <v>138</v>
       </c>
@@ -14942,7 +13855,7 @@
         <v>1.0831</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="12.75">
+    <row r="41" spans="2:9" ht="13.15">
       <c r="B41" s="19" t="s">
         <v>139</v>
       </c>
@@ -14959,7 +13872,7 @@
         <v>1.0719000000000001</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="12.75">
+    <row r="42" spans="2:9" ht="13.15">
       <c r="B42" s="19" t="s">
         <v>140</v>
       </c>
@@ -14976,7 +13889,7 @@
         <v>1.0519000000000001</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="12.75">
+    <row r="43" spans="2:9" ht="13.15">
       <c r="B43" s="19" t="s">
         <v>141</v>
       </c>
@@ -14993,7 +13906,7 @@
         <v>1.0274000000000001</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="12.75">
+    <row r="44" spans="2:9" ht="13.15">
       <c r="B44" s="19" t="s">
         <v>142</v>
       </c>
@@ -15010,7 +13923,7 @@
         <v>1.0091000000000001</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="12.75">
+    <row r="45" spans="2:9" ht="13.15">
       <c r="B45" s="19" t="s">
         <v>143</v>
       </c>
@@ -15027,7 +13940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="12.75">
+    <row r="46" spans="2:9" ht="13.15">
       <c r="B46" s="19" t="s">
         <v>144</v>
       </c>
@@ -15044,7 +13957,7 @@
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="12.75">
+    <row r="47" spans="2:9" ht="13.15">
       <c r="B47" s="19" t="s">
         <v>145</v>
       </c>
@@ -15061,7 +13974,7 @@
         <v>0.97809999999999997</v>
       </c>
     </row>
-    <row r="48" spans="2:9" ht="12.75">
+    <row r="48" spans="2:9" ht="13.15">
       <c r="B48" s="19" t="s">
         <v>146</v>
       </c>
@@ -15078,7 +13991,7 @@
         <v>0.96499999999999997</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="12.75">
+    <row r="49" spans="2:9" ht="13.15">
       <c r="B49" s="19" t="s">
         <v>147</v>
       </c>
@@ -15095,7 +14008,7 @@
         <v>0.94910000000000005</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="12.75">
+    <row r="50" spans="2:9" ht="13.15">
       <c r="B50" s="19" t="s">
         <v>148</v>
       </c>
@@ -15112,7 +14025,7 @@
         <v>0.92969999999999997</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="12.75">
+    <row r="51" spans="2:9" ht="13.15">
       <c r="B51" s="19" t="s">
         <v>149</v>
       </c>
@@ -15132,7 +14045,7 @@
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="12.75">
+    <row r="52" spans="2:9" ht="13.15">
       <c r="B52" s="19" t="s">
         <v>150</v>
       </c>
@@ -15146,7 +14059,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="12.75">
+    <row r="53" spans="2:9" ht="13.15">
       <c r="B53" s="19" t="s">
         <v>151</v>
       </c>
@@ -15160,7 +14073,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="12.75">
+    <row r="54" spans="2:9" ht="13.15">
       <c r="B54" s="19" t="s">
         <v>152</v>
       </c>
@@ -15626,12 +14539,12 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="99" spans="5:10" ht="18" thickBot="1">
+    <row r="99" spans="5:10" ht="17.25" thickBot="1">
       <c r="E99" s="20" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="100" spans="5:10" ht="16.5" thickTop="1" thickBot="1">
+    <row r="100" spans="5:10" ht="15" thickTop="1" thickBot="1">
       <c r="E100" s="4" t="s">
         <v>49</v>
       </c>
@@ -15651,7 +14564,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="101" spans="5:10" ht="15">
+    <row r="101" spans="5:10" ht="14.25">
       <c r="E101"/>
       <c r="F101" s="21" t="s">
         <v>189</v>
@@ -15667,7 +14580,7 @@
         <v>1.201442041042708</v>
       </c>
     </row>
-    <row r="102" spans="5:10" ht="15">
+    <row r="102" spans="5:10" ht="14.25">
       <c r="E102"/>
       <c r="F102" s="21" t="s">
         <v>191</v>
@@ -15690,19 +14603,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE1F0D2-7682-484B-9627-54FDDA96E26C}">
   <dimension ref="B3:D33"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="2" width="8.85546875" style="6"/>
-    <col min="3" max="3" width="20.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.85546875" style="6"/>
+    <col min="1" max="2" width="8.86328125" style="6"/>
+    <col min="3" max="3" width="20.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.86328125" style="6"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" ht="18" thickBot="1">
+    <row r="3" spans="2:4" ht="17.25" thickBot="1">
       <c r="B3" s="20" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
+    <row r="4" spans="2:4" ht="15" thickTop="1" thickBot="1">
       <c r="B4" s="4" t="s">
         <v>51</v>
       </c>
@@ -15894,12 +14807,12 @@
         <v>170</v>
       </c>
     </row>
-    <row r="25" spans="2:4" ht="18" thickBot="1">
+    <row r="25" spans="2:4" ht="17.25" thickBot="1">
       <c r="B25" s="20" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="16.5" thickTop="1" thickBot="1">
+    <row r="26" spans="2:4" ht="15" thickTop="1" thickBot="1">
       <c r="B26" s="4" t="s">
         <v>172</v>
       </c>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D132E7B6-90EB-42E2-B216-D607FBFE2513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42147D7E-FD1B-4685-9592-A646010A2A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2691" uniqueCount="809">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -802,7 +802,7 @@
     <t>elc_spv_POL_004</t>
   </si>
   <si>
-    <t>solar electricity near Wroclaw (cluster 4)</t>
+    <t>solar electricity near Walbrzych (cluster 4)</t>
   </si>
   <si>
     <t>elc_spv_POL_005</t>
@@ -814,7 +814,7 @@
     <t>elc_spv_POL_006</t>
   </si>
   <si>
-    <t>solar electricity near Wroclaw (cluster 6)</t>
+    <t>solar electricity near Walbrzych (cluster 6)</t>
   </si>
   <si>
     <t>elc_spv_POL_007</t>
@@ -838,7 +838,7 @@
     <t>elc_spv_POL_010</t>
   </si>
   <si>
-    <t>solar electricity near Legnica (cluster 10)</t>
+    <t>solar electricity near Jelenia Gora (cluster 10)</t>
   </si>
   <si>
     <t>elc_spv_POL_011</t>
@@ -880,7 +880,7 @@
     <t>elc_spv_POL_017</t>
   </si>
   <si>
-    <t>solar electricity near Lodz (cluster 17)</t>
+    <t>solar electricity near Piotrkow Trybunalski (cluster 17)</t>
   </si>
   <si>
     <t>elc_spv_POL_018</t>
@@ -922,7 +922,7 @@
     <t>elc_spv_POL_024</t>
   </si>
   <si>
-    <t>solar electricity near Lublin (cluster 24)</t>
+    <t>solar electricity near Chelm (cluster 24)</t>
   </si>
   <si>
     <t>elc_spv_POL_025</t>
@@ -946,7 +946,7 @@
     <t>elc_spv_POL_028</t>
   </si>
   <si>
-    <t>solar electricity near Stalowa Wola (cluster 28)</t>
+    <t>solar electricity near Rzeszow (cluster 28)</t>
   </si>
   <si>
     <t>elc_spv_POL_029</t>
@@ -976,7 +976,7 @@
     <t>elc_spv_POL_033</t>
   </si>
   <si>
-    <t>solar electricity near Konin (cluster 33)</t>
+    <t>solar electricity near Kalisz (cluster 33)</t>
   </si>
   <si>
     <t>elc_spv_POL_034</t>
@@ -1000,19 +1000,19 @@
     <t>elc_spv_POL_037</t>
   </si>
   <si>
-    <t>solar electricity near Elk (cluster 37)</t>
+    <t>solar electricity near Suwalki (cluster 37)</t>
   </si>
   <si>
     <t>elc_spv_POL_038</t>
   </si>
   <si>
-    <t>solar electricity near Poznan (cluster 38)</t>
+    <t>solar electricity near Pila (cluster 38)</t>
   </si>
   <si>
     <t>elc_spv_POL_039</t>
   </si>
   <si>
-    <t>solar electricity near Opole (cluster 39)</t>
+    <t>solar electricity near Kedzierzyn-Kozle (cluster 39)</t>
   </si>
   <si>
     <t>elc_spv_POL_040</t>
@@ -1066,7 +1066,7 @@
     <t>elc_spv_POL_048</t>
   </si>
   <si>
-    <t>solar electricity near Lublin (cluster 48)</t>
+    <t>solar electricity near Siedlce (cluster 48)</t>
   </si>
   <si>
     <t>elc_wof_POL_001</t>
@@ -1150,7 +1150,7 @@
     <t>elc_won_POL_004</t>
   </si>
   <si>
-    <t>wind onshore electricity near Legnica (cluster 4)</t>
+    <t>wind onshore electricity near Walbrzych (cluster 4)</t>
   </si>
   <si>
     <t>elc_won_POL_005</t>
@@ -1162,7 +1162,7 @@
     <t>elc_won_POL_006</t>
   </si>
   <si>
-    <t>wind onshore electricity near Wroclaw (cluster 6)</t>
+    <t>wind onshore electricity near Walbrzych (cluster 6)</t>
   </si>
   <si>
     <t>elc_won_POL_007</t>
@@ -1186,7 +1186,7 @@
     <t>elc_won_POL_010</t>
   </si>
   <si>
-    <t>wind onshore electricity near Legnica (cluster 10)</t>
+    <t>wind onshore electricity near Jelenia Gora (cluster 10)</t>
   </si>
   <si>
     <t>elc_won_POL_011</t>
@@ -1216,7 +1216,7 @@
     <t>elc_won_POL_015</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rzeszow (cluster 15)</t>
+    <t>wind onshore electricity near Przemysl (cluster 15)</t>
   </si>
   <si>
     <t>elc_won_POL_016</t>
@@ -1228,7 +1228,7 @@
     <t>elc_won_POL_017</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lodz (cluster 17)</t>
+    <t>wind onshore electricity near Piotrkow Trybunalski (cluster 17)</t>
   </si>
   <si>
     <t>elc_won_POL_018</t>
@@ -1258,145 +1258,163 @@
     <t>elc_won_POL_022</t>
   </si>
   <si>
-    <t>wind onshore electricity near Tarnow (cluster 22)</t>
+    <t>wind onshore electricity near Katowice (cluster 22)</t>
   </si>
   <si>
     <t>elc_won_POL_023</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lublin (cluster 23)</t>
+    <t>wind onshore electricity near Tarnow (cluster 23)</t>
   </si>
   <si>
     <t>elc_won_POL_024</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rzeszow (cluster 24)</t>
+    <t>wind onshore electricity near Chelm (cluster 24)</t>
   </si>
   <si>
     <t>elc_won_POL_025</t>
   </si>
   <si>
-    <t>wind onshore electricity near Radom (cluster 25)</t>
+    <t>wind onshore electricity near Rzeszow (cluster 25)</t>
   </si>
   <si>
     <t>elc_won_POL_026</t>
   </si>
   <si>
-    <t>wind onshore electricity near Mielec (cluster 26)</t>
+    <t>wind onshore electricity near Kielce (cluster 26)</t>
   </si>
   <si>
     <t>elc_won_POL_027</t>
   </si>
   <si>
-    <t>wind onshore electricity near Stalowa Wola (cluster 27)</t>
+    <t>wind onshore electricity near Mielec (cluster 27)</t>
   </si>
   <si>
     <t>elc_won_POL_028</t>
   </si>
   <si>
-    <t>wind onshore electricity near Czestochowa (cluster 28)</t>
+    <t>wind onshore electricity near Rzeszow (cluster 28)</t>
   </si>
   <si>
     <t>elc_won_POL_029</t>
   </si>
   <si>
-    <t>wind onshore electricity near Torun (cluster 29)</t>
+    <t>wind onshore electricity near Czestochowa (cluster 29)</t>
   </si>
   <si>
     <t>elc_won_POL_030</t>
   </si>
   <si>
-    <t>wind onshore electricity near Radom (cluster 30)</t>
+    <t>wind onshore electricity near Torun (cluster 30)</t>
   </si>
   <si>
     <t>elc_won_POL_031</t>
   </si>
   <si>
-    <t>wind onshore electricity near Konin (cluster 31)</t>
+    <t>wind onshore electricity near Ostrowiec Swietokrzyski (cluster 31)</t>
   </si>
   <si>
     <t>elc_won_POL_032</t>
   </si>
   <si>
-    <t>wind onshore electricity near Koszalin (cluster 32)</t>
+    <t>wind onshore electricity near Opole (cluster 32)</t>
   </si>
   <si>
     <t>elc_won_POL_033</t>
   </si>
   <si>
-    <t>wind onshore electricity near Warsaw (cluster 33)</t>
+    <t>wind onshore electricity near Konin (cluster 33)</t>
   </si>
   <si>
     <t>elc_won_POL_034</t>
   </si>
   <si>
-    <t>wind onshore electricity near Katowice (cluster 34)</t>
+    <t>wind onshore electricity near Koszalin (cluster 34)</t>
   </si>
   <si>
     <t>elc_won_POL_035</t>
   </si>
   <si>
-    <t>wind onshore electricity near Elk (cluster 35)</t>
+    <t>wind onshore electricity near Warsaw (cluster 35)</t>
   </si>
   <si>
     <t>elc_won_POL_036</t>
   </si>
   <si>
-    <t>wind onshore electricity near Poznan (cluster 36)</t>
+    <t>wind onshore electricity near Katowice (cluster 36)</t>
   </si>
   <si>
     <t>elc_won_POL_037</t>
   </si>
   <si>
-    <t>wind onshore electricity near Kedzierzyn-Kozle (cluster 37)</t>
+    <t>wind onshore electricity near Suwalki (cluster 37)</t>
   </si>
   <si>
     <t>elc_won_POL_038</t>
   </si>
   <si>
-    <t>wind onshore electricity near Szczecin (cluster 38)</t>
+    <t>wind onshore electricity near Pila (cluster 38)</t>
   </si>
   <si>
     <t>elc_won_POL_039</t>
   </si>
   <si>
-    <t>wind onshore electricity near Krakow (cluster 39)</t>
+    <t>wind onshore electricity near Kedzierzyn-Kozle (cluster 39)</t>
   </si>
   <si>
     <t>elc_won_POL_040</t>
   </si>
   <si>
-    <t>wind onshore electricity near Elblag (cluster 40)</t>
+    <t>wind onshore electricity near Szczecin (cluster 40)</t>
   </si>
   <si>
     <t>elc_won_POL_041</t>
   </si>
   <si>
-    <t>wind onshore electricity near Plock (cluster 41)</t>
+    <t>wind onshore electricity near Krakow (cluster 41)</t>
   </si>
   <si>
     <t>elc_won_POL_042</t>
   </si>
   <si>
-    <t>wind onshore electricity near Kalisz (cluster 42)</t>
+    <t>wind onshore electricity near Krakow (cluster 42)</t>
   </si>
   <si>
     <t>elc_won_POL_043</t>
   </si>
   <si>
-    <t>wind onshore electricity near Gdansk (cluster 43)</t>
+    <t>wind onshore electricity near Elblag (cluster 43)</t>
   </si>
   <si>
     <t>elc_won_POL_044</t>
   </si>
   <si>
-    <t>wind onshore electricity near Krakow (cluster 44)</t>
+    <t>wind onshore electricity near Plock (cluster 44)</t>
   </si>
   <si>
     <t>elc_won_POL_045</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lublin (cluster 45)</t>
+    <t>wind onshore electricity near Wroclaw (cluster 45)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_046</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Gdansk (cluster 46)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_047</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Krakow (cluster 47)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_048</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Siedlce (cluster 48)</t>
   </si>
   <si>
     <t>~fi_comm</t>
@@ -4482,9 +4500,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4522,7 +4540,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4628,7 +4646,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4770,7 +4788,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4844,13 +4862,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0F7B196-FB77-4156-A72F-6197B3013C84}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BB39D3-7AE7-42DD-AB2E-54745AEDE01E}">
   <dimension ref="B3:H82"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:8">
       <c r="B3" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="4" spans="2:8">
@@ -4881,19 +4899,19 @@
         <v>192</v>
       </c>
       <c r="C5" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="F5" t="s">
         <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H5" t="s">
         <v>195</v>
@@ -4904,19 +4922,19 @@
         <v>192</v>
       </c>
       <c r="C6" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="F6" t="s">
         <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H6" t="s">
         <v>195</v>
@@ -4927,19 +4945,19 @@
         <v>192</v>
       </c>
       <c r="C7" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="F7" t="s">
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H7" t="s">
         <v>195</v>
@@ -4950,19 +4968,19 @@
         <v>192</v>
       </c>
       <c r="C8" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="F8" t="s">
         <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H8" t="s">
         <v>195</v>
@@ -4973,19 +4991,19 @@
         <v>192</v>
       </c>
       <c r="C9" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="F9" t="s">
         <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H9" t="s">
         <v>195</v>
@@ -4996,19 +5014,19 @@
         <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="F10" t="s">
         <v>26</v>
       </c>
       <c r="G10" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H10" t="s">
         <v>195</v>
@@ -5019,19 +5037,19 @@
         <v>192</v>
       </c>
       <c r="C11" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="F11" t="s">
         <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H11" t="s">
         <v>195</v>
@@ -5042,19 +5060,19 @@
         <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="F12" t="s">
         <v>26</v>
       </c>
       <c r="G12" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H12" t="s">
         <v>195</v>
@@ -5065,19 +5083,19 @@
         <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="F13" t="s">
         <v>26</v>
       </c>
       <c r="G13" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H13" t="s">
         <v>195</v>
@@ -5088,19 +5106,19 @@
         <v>192</v>
       </c>
       <c r="C14" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="F14" t="s">
         <v>26</v>
       </c>
       <c r="G14" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H14" t="s">
         <v>195</v>
@@ -5111,19 +5129,19 @@
         <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="F15" t="s">
         <v>26</v>
       </c>
       <c r="G15" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H15" t="s">
         <v>195</v>
@@ -5134,19 +5152,19 @@
         <v>192</v>
       </c>
       <c r="C16" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="F16" t="s">
         <v>26</v>
       </c>
       <c r="G16" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H16" t="s">
         <v>195</v>
@@ -5157,19 +5175,19 @@
         <v>192</v>
       </c>
       <c r="C17" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="F17" t="s">
         <v>26</v>
       </c>
       <c r="G17" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H17" t="s">
         <v>195</v>
@@ -5180,19 +5198,19 @@
         <v>192</v>
       </c>
       <c r="C18" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
       </c>
       <c r="G18" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H18" t="s">
         <v>195</v>
@@ -5203,19 +5221,19 @@
         <v>192</v>
       </c>
       <c r="C19" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="F19" t="s">
         <v>26</v>
       </c>
       <c r="G19" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H19" t="s">
         <v>195</v>
@@ -5226,19 +5244,19 @@
         <v>192</v>
       </c>
       <c r="C20" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="F20" t="s">
         <v>26</v>
       </c>
       <c r="G20" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H20" t="s">
         <v>195</v>
@@ -5249,19 +5267,19 @@
         <v>192</v>
       </c>
       <c r="C21" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="F21" t="s">
         <v>26</v>
       </c>
       <c r="G21" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H21" t="s">
         <v>195</v>
@@ -5272,19 +5290,19 @@
         <v>192</v>
       </c>
       <c r="C22" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F22" t="s">
         <v>26</v>
       </c>
       <c r="G22" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H22" t="s">
         <v>195</v>
@@ -5295,19 +5313,19 @@
         <v>192</v>
       </c>
       <c r="C23" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="F23" t="s">
         <v>26</v>
       </c>
       <c r="G23" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H23" t="s">
         <v>195</v>
@@ -5318,19 +5336,19 @@
         <v>192</v>
       </c>
       <c r="C24" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="F24" t="s">
         <v>26</v>
       </c>
       <c r="G24" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H24" t="s">
         <v>195</v>
@@ -5341,19 +5359,19 @@
         <v>192</v>
       </c>
       <c r="C25" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="F25" t="s">
         <v>26</v>
       </c>
       <c r="G25" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H25" t="s">
         <v>195</v>
@@ -5364,19 +5382,19 @@
         <v>192</v>
       </c>
       <c r="C26" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="F26" t="s">
         <v>26</v>
       </c>
       <c r="G26" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H26" t="s">
         <v>195</v>
@@ -5387,19 +5405,19 @@
         <v>192</v>
       </c>
       <c r="C27" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="F27" t="s">
         <v>26</v>
       </c>
       <c r="G27" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H27" t="s">
         <v>195</v>
@@ -5410,19 +5428,19 @@
         <v>192</v>
       </c>
       <c r="C28" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="F28" t="s">
         <v>26</v>
       </c>
       <c r="G28" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H28" t="s">
         <v>195</v>
@@ -5433,19 +5451,19 @@
         <v>192</v>
       </c>
       <c r="C29" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="F29" t="s">
         <v>26</v>
       </c>
       <c r="G29" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H29" t="s">
         <v>195</v>
@@ -5456,19 +5474,19 @@
         <v>192</v>
       </c>
       <c r="C30" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="F30" t="s">
         <v>26</v>
       </c>
       <c r="G30" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H30" t="s">
         <v>195</v>
@@ -5479,19 +5497,19 @@
         <v>192</v>
       </c>
       <c r="C31" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="F31" t="s">
         <v>26</v>
       </c>
       <c r="G31" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H31" t="s">
         <v>195</v>
@@ -5502,19 +5520,19 @@
         <v>192</v>
       </c>
       <c r="C32" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="F32" t="s">
         <v>26</v>
       </c>
       <c r="G32" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H32" t="s">
         <v>195</v>
@@ -5525,19 +5543,19 @@
         <v>192</v>
       </c>
       <c r="C33" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="F33" t="s">
         <v>26</v>
       </c>
       <c r="G33" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H33" t="s">
         <v>195</v>
@@ -5548,19 +5566,19 @@
         <v>192</v>
       </c>
       <c r="C34" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="F34" t="s">
         <v>26</v>
       </c>
       <c r="G34" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H34" t="s">
         <v>195</v>
@@ -5571,19 +5589,19 @@
         <v>192</v>
       </c>
       <c r="C35" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="F35" t="s">
         <v>26</v>
       </c>
       <c r="G35" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H35" t="s">
         <v>195</v>
@@ -5594,19 +5612,19 @@
         <v>192</v>
       </c>
       <c r="C36" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="F36" t="s">
         <v>26</v>
       </c>
       <c r="G36" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H36" t="s">
         <v>195</v>
@@ -5617,19 +5635,19 @@
         <v>192</v>
       </c>
       <c r="C37" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="F37" t="s">
         <v>26</v>
       </c>
       <c r="G37" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H37" t="s">
         <v>195</v>
@@ -5640,19 +5658,19 @@
         <v>192</v>
       </c>
       <c r="C38" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="F38" t="s">
         <v>26</v>
       </c>
       <c r="G38" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H38" t="s">
         <v>195</v>
@@ -5663,19 +5681,19 @@
         <v>192</v>
       </c>
       <c r="C39" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="F39" t="s">
         <v>26</v>
       </c>
       <c r="G39" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H39" t="s">
         <v>195</v>
@@ -5686,19 +5704,19 @@
         <v>192</v>
       </c>
       <c r="C40" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="F40" t="s">
         <v>26</v>
       </c>
       <c r="G40" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H40" t="s">
         <v>195</v>
@@ -5709,19 +5727,19 @@
         <v>192</v>
       </c>
       <c r="C41" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="F41" t="s">
         <v>26</v>
       </c>
       <c r="G41" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H41" t="s">
         <v>195</v>
@@ -5732,19 +5750,19 @@
         <v>192</v>
       </c>
       <c r="C42" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="F42" t="s">
         <v>26</v>
       </c>
       <c r="G42" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H42" t="s">
         <v>195</v>
@@ -5755,19 +5773,19 @@
         <v>192</v>
       </c>
       <c r="C43" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="F43" t="s">
         <v>26</v>
       </c>
       <c r="G43" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H43" t="s">
         <v>195</v>
@@ -5778,19 +5796,19 @@
         <v>192</v>
       </c>
       <c r="C44" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="F44" t="s">
         <v>26</v>
       </c>
       <c r="G44" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H44" t="s">
         <v>195</v>
@@ -5801,19 +5819,19 @@
         <v>192</v>
       </c>
       <c r="C45" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="F45" t="s">
         <v>26</v>
       </c>
       <c r="G45" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H45" t="s">
         <v>195</v>
@@ -5824,19 +5842,19 @@
         <v>192</v>
       </c>
       <c r="C46" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="F46" t="s">
         <v>26</v>
       </c>
       <c r="G46" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H46" t="s">
         <v>195</v>
@@ -5847,19 +5865,19 @@
         <v>192</v>
       </c>
       <c r="C47" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="F47" t="s">
         <v>26</v>
       </c>
       <c r="G47" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H47" t="s">
         <v>195</v>
@@ -5870,19 +5888,19 @@
         <v>192</v>
       </c>
       <c r="C48" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="F48" t="s">
         <v>26</v>
       </c>
       <c r="G48" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H48" t="s">
         <v>195</v>
@@ -5893,19 +5911,19 @@
         <v>192</v>
       </c>
       <c r="C49" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="F49" t="s">
         <v>26</v>
       </c>
       <c r="G49" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H49" t="s">
         <v>195</v>
@@ -5916,19 +5934,19 @@
         <v>192</v>
       </c>
       <c r="C50" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="F50" t="s">
         <v>26</v>
       </c>
       <c r="G50" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H50" t="s">
         <v>195</v>
@@ -5939,19 +5957,19 @@
         <v>192</v>
       </c>
       <c r="C51" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="F51" t="s">
         <v>26</v>
       </c>
       <c r="G51" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H51" t="s">
         <v>195</v>
@@ -5962,19 +5980,19 @@
         <v>192</v>
       </c>
       <c r="C52" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="F52" t="s">
         <v>26</v>
       </c>
       <c r="G52" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H52" t="s">
         <v>195</v>
@@ -5985,19 +6003,19 @@
         <v>192</v>
       </c>
       <c r="C53" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="D53" t="s">
         <v>243</v>
       </c>
       <c r="E53" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="F53" t="s">
         <v>26</v>
       </c>
       <c r="G53" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H53" t="s">
         <v>195</v>
@@ -6008,19 +6026,19 @@
         <v>192</v>
       </c>
       <c r="C54" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="D54" t="s">
         <v>243</v>
       </c>
       <c r="E54" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="F54" t="s">
         <v>26</v>
       </c>
       <c r="G54" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H54" t="s">
         <v>195</v>
@@ -6031,19 +6049,19 @@
         <v>192</v>
       </c>
       <c r="C55" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="D55" t="s">
         <v>243</v>
       </c>
       <c r="E55" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="F55" t="s">
         <v>26</v>
       </c>
       <c r="G55" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H55" t="s">
         <v>195</v>
@@ -6054,19 +6072,19 @@
         <v>192</v>
       </c>
       <c r="C56" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="D56" t="s">
         <v>243</v>
       </c>
       <c r="E56" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="F56" t="s">
         <v>26</v>
       </c>
       <c r="G56" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H56" t="s">
         <v>195</v>
@@ -6077,19 +6095,19 @@
         <v>192</v>
       </c>
       <c r="C57" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="D57" t="s">
         <v>243</v>
       </c>
       <c r="E57" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="F57" t="s">
         <v>26</v>
       </c>
       <c r="G57" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H57" t="s">
         <v>195</v>
@@ -6100,19 +6118,19 @@
         <v>192</v>
       </c>
       <c r="C58" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="D58" t="s">
         <v>243</v>
       </c>
       <c r="E58" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="F58" t="s">
         <v>26</v>
       </c>
       <c r="G58" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H58" t="s">
         <v>195</v>
@@ -6123,19 +6141,19 @@
         <v>192</v>
       </c>
       <c r="C59" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="D59" t="s">
         <v>243</v>
       </c>
       <c r="E59" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="F59" t="s">
         <v>26</v>
       </c>
       <c r="G59" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H59" t="s">
         <v>195</v>
@@ -6146,19 +6164,19 @@
         <v>192</v>
       </c>
       <c r="C60" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="D60" t="s">
         <v>243</v>
       </c>
       <c r="E60" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="F60" t="s">
         <v>26</v>
       </c>
       <c r="G60" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H60" t="s">
         <v>195</v>
@@ -6169,19 +6187,19 @@
         <v>192</v>
       </c>
       <c r="C61" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="D61" t="s">
         <v>243</v>
       </c>
       <c r="E61" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="F61" t="s">
         <v>26</v>
       </c>
       <c r="G61" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H61" t="s">
         <v>195</v>
@@ -6192,19 +6210,19 @@
         <v>192</v>
       </c>
       <c r="C62" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="D62" t="s">
         <v>243</v>
       </c>
       <c r="E62" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="F62" t="s">
         <v>26</v>
       </c>
       <c r="G62" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H62" t="s">
         <v>195</v>
@@ -6215,19 +6233,19 @@
         <v>192</v>
       </c>
       <c r="C63" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="D63" t="s">
         <v>243</v>
       </c>
       <c r="E63" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="F63" t="s">
         <v>26</v>
       </c>
       <c r="G63" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H63" t="s">
         <v>195</v>
@@ -6238,19 +6256,19 @@
         <v>192</v>
       </c>
       <c r="C64" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="D64" t="s">
         <v>243</v>
       </c>
       <c r="E64" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="F64" t="s">
         <v>26</v>
       </c>
       <c r="G64" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H64" t="s">
         <v>195</v>
@@ -6261,19 +6279,19 @@
         <v>192</v>
       </c>
       <c r="C65" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="D65" t="s">
         <v>243</v>
       </c>
       <c r="E65" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="F65" t="s">
         <v>26</v>
       </c>
       <c r="G65" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H65" t="s">
         <v>195</v>
@@ -6284,19 +6302,19 @@
         <v>192</v>
       </c>
       <c r="C66" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="D66" t="s">
         <v>243</v>
       </c>
       <c r="E66" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="F66" t="s">
         <v>26</v>
       </c>
       <c r="G66" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H66" t="s">
         <v>195</v>
@@ -6307,19 +6325,19 @@
         <v>192</v>
       </c>
       <c r="C67" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="D67" t="s">
         <v>243</v>
       </c>
       <c r="E67" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="F67" t="s">
         <v>26</v>
       </c>
       <c r="G67" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H67" t="s">
         <v>195</v>
@@ -6330,19 +6348,19 @@
         <v>192</v>
       </c>
       <c r="C68" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="D68" t="s">
         <v>243</v>
       </c>
       <c r="E68" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="F68" t="s">
         <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H68" t="s">
         <v>195</v>
@@ -6353,19 +6371,19 @@
         <v>192</v>
       </c>
       <c r="C69" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="D69" t="s">
         <v>243</v>
       </c>
       <c r="E69" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="F69" t="s">
         <v>26</v>
       </c>
       <c r="G69" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H69" t="s">
         <v>195</v>
@@ -6376,19 +6394,19 @@
         <v>192</v>
       </c>
       <c r="C70" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="D70" t="s">
         <v>243</v>
       </c>
       <c r="E70" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="F70" t="s">
         <v>26</v>
       </c>
       <c r="G70" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H70" t="s">
         <v>195</v>
@@ -6399,19 +6417,19 @@
         <v>192</v>
       </c>
       <c r="C71" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="D71" t="s">
         <v>243</v>
       </c>
       <c r="E71" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="F71" t="s">
         <v>26</v>
       </c>
       <c r="G71" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H71" t="s">
         <v>195</v>
@@ -6422,19 +6440,19 @@
         <v>192</v>
       </c>
       <c r="C72" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="D72" t="s">
         <v>243</v>
       </c>
       <c r="E72" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="F72" t="s">
         <v>26</v>
       </c>
       <c r="G72" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H72" t="s">
         <v>195</v>
@@ -6445,19 +6463,19 @@
         <v>192</v>
       </c>
       <c r="C73" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="D73" t="s">
         <v>243</v>
       </c>
       <c r="E73" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="F73" t="s">
         <v>26</v>
       </c>
       <c r="G73" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H73" t="s">
         <v>195</v>
@@ -6468,19 +6486,19 @@
         <v>192</v>
       </c>
       <c r="C74" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="D74" t="s">
         <v>243</v>
       </c>
       <c r="E74" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="F74" t="s">
         <v>26</v>
       </c>
       <c r="G74" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H74" t="s">
         <v>195</v>
@@ -6491,19 +6509,19 @@
         <v>192</v>
       </c>
       <c r="C75" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="D75" t="s">
         <v>243</v>
       </c>
       <c r="E75" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="F75" t="s">
         <v>26</v>
       </c>
       <c r="G75" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H75" t="s">
         <v>195</v>
@@ -6514,19 +6532,19 @@
         <v>192</v>
       </c>
       <c r="C76" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="D76" t="s">
         <v>243</v>
       </c>
       <c r="E76" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="F76" t="s">
         <v>26</v>
       </c>
       <c r="G76" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H76" t="s">
         <v>195</v>
@@ -6537,19 +6555,19 @@
         <v>192</v>
       </c>
       <c r="C77" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="D77" t="s">
         <v>243</v>
       </c>
       <c r="E77" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="F77" t="s">
         <v>26</v>
       </c>
       <c r="G77" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H77" t="s">
         <v>195</v>
@@ -6560,19 +6578,19 @@
         <v>192</v>
       </c>
       <c r="C78" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="D78" t="s">
         <v>243</v>
       </c>
       <c r="E78" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="F78" t="s">
         <v>26</v>
       </c>
       <c r="G78" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H78" t="s">
         <v>195</v>
@@ -6583,19 +6601,19 @@
         <v>192</v>
       </c>
       <c r="C79" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="D79" t="s">
         <v>243</v>
       </c>
       <c r="E79" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="F79" t="s">
         <v>26</v>
       </c>
       <c r="G79" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H79" t="s">
         <v>195</v>
@@ -6606,19 +6624,19 @@
         <v>192</v>
       </c>
       <c r="C80" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="D80" t="s">
         <v>243</v>
       </c>
       <c r="E80" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="F80" t="s">
         <v>26</v>
       </c>
       <c r="G80" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H80" t="s">
         <v>195</v>
@@ -6629,19 +6647,19 @@
         <v>192</v>
       </c>
       <c r="C81" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="D81" t="s">
         <v>243</v>
       </c>
       <c r="E81" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="F81" t="s">
         <v>26</v>
       </c>
       <c r="G81" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H81" t="s">
         <v>195</v>
@@ -6652,19 +6670,19 @@
         <v>192</v>
       </c>
       <c r="C82" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="D82" t="s">
         <v>243</v>
       </c>
       <c r="E82" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="F82" t="s">
         <v>26</v>
       </c>
       <c r="G82" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="H82" t="s">
         <v>195</v>
@@ -6676,13 +6694,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88C1B4F-C4AD-47BE-9F7D-63B8ADA6B425}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A46E409C-4182-48B0-B466-C4065EF3FDB5}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -6716,13 +6734,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -6731,7 +6749,7 @@
         <v>232</v>
       </c>
       <c r="H5" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I5" t="s">
         <v>247</v>
@@ -6742,13 +6760,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="F6" t="s">
         <v>233</v>
@@ -6757,7 +6775,7 @@
         <v>232</v>
       </c>
       <c r="H6" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I6" t="s">
         <v>247</v>
@@ -6768,13 +6786,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -6783,7 +6801,7 @@
         <v>232</v>
       </c>
       <c r="H7" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I7" t="s">
         <v>247</v>
@@ -6794,13 +6812,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -6809,7 +6827,7 @@
         <v>232</v>
       </c>
       <c r="H8" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I8" t="s">
         <v>247</v>
@@ -6820,13 +6838,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="F9" t="s">
         <v>233</v>
@@ -6835,7 +6853,7 @@
         <v>232</v>
       </c>
       <c r="H9" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I9" t="s">
         <v>247</v>
@@ -6846,13 +6864,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="F10" t="s">
         <v>233</v>
@@ -6861,7 +6879,7 @@
         <v>232</v>
       </c>
       <c r="H10" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I10" t="s">
         <v>247</v>
@@ -6872,13 +6890,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="F11" t="s">
         <v>233</v>
@@ -6887,7 +6905,7 @@
         <v>232</v>
       </c>
       <c r="H11" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I11" t="s">
         <v>247</v>
@@ -6898,13 +6916,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="F12" t="s">
         <v>233</v>
@@ -6913,7 +6931,7 @@
         <v>232</v>
       </c>
       <c r="H12" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I12" t="s">
         <v>247</v>
@@ -6924,13 +6942,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="F13" t="s">
         <v>233</v>
@@ -6939,7 +6957,7 @@
         <v>232</v>
       </c>
       <c r="H13" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I13" t="s">
         <v>247</v>
@@ -6950,13 +6968,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="F14" t="s">
         <v>233</v>
@@ -6965,7 +6983,7 @@
         <v>232</v>
       </c>
       <c r="H14" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I14" t="s">
         <v>247</v>
@@ -6976,13 +6994,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="F15" t="s">
         <v>233</v>
@@ -6991,7 +7009,7 @@
         <v>232</v>
       </c>
       <c r="H15" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I15" t="s">
         <v>247</v>
@@ -7002,13 +7020,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="F16" t="s">
         <v>233</v>
@@ -7017,7 +7035,7 @@
         <v>232</v>
       </c>
       <c r="H16" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I16" t="s">
         <v>247</v>
@@ -7028,13 +7046,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="F17" t="s">
         <v>233</v>
@@ -7043,7 +7061,7 @@
         <v>232</v>
       </c>
       <c r="H17" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I17" t="s">
         <v>247</v>
@@ -7054,13 +7072,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="F18" t="s">
         <v>233</v>
@@ -7069,7 +7087,7 @@
         <v>232</v>
       </c>
       <c r="H18" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I18" t="s">
         <v>247</v>
@@ -7080,13 +7098,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="F19" t="s">
         <v>233</v>
@@ -7095,7 +7113,7 @@
         <v>232</v>
       </c>
       <c r="H19" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I19" t="s">
         <v>247</v>
@@ -7106,13 +7124,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="F20" t="s">
         <v>233</v>
@@ -7121,7 +7139,7 @@
         <v>232</v>
       </c>
       <c r="H20" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I20" t="s">
         <v>247</v>
@@ -7132,13 +7150,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="F21" t="s">
         <v>233</v>
@@ -7147,7 +7165,7 @@
         <v>232</v>
       </c>
       <c r="H21" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I21" t="s">
         <v>247</v>
@@ -7158,13 +7176,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="F22" t="s">
         <v>233</v>
@@ -7173,7 +7191,7 @@
         <v>232</v>
       </c>
       <c r="H22" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I22" t="s">
         <v>247</v>
@@ -7184,13 +7202,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="F23" t="s">
         <v>233</v>
@@ -7199,7 +7217,7 @@
         <v>232</v>
       </c>
       <c r="H23" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I23" t="s">
         <v>247</v>
@@ -7210,13 +7228,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="F24" t="s">
         <v>233</v>
@@ -7225,7 +7243,7 @@
         <v>232</v>
       </c>
       <c r="H24" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I24" t="s">
         <v>247</v>
@@ -7236,13 +7254,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="F25" t="s">
         <v>233</v>
@@ -7251,7 +7269,7 @@
         <v>232</v>
       </c>
       <c r="H25" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I25" t="s">
         <v>247</v>
@@ -7262,13 +7280,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="F26" t="s">
         <v>233</v>
@@ -7277,7 +7295,7 @@
         <v>232</v>
       </c>
       <c r="H26" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I26" t="s">
         <v>247</v>
@@ -7288,13 +7306,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="F27" t="s">
         <v>233</v>
@@ -7303,7 +7321,7 @@
         <v>232</v>
       </c>
       <c r="H27" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I27" t="s">
         <v>247</v>
@@ -7314,13 +7332,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="F28" t="s">
         <v>233</v>
@@ -7329,7 +7347,7 @@
         <v>232</v>
       </c>
       <c r="H28" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I28" t="s">
         <v>247</v>
@@ -7340,13 +7358,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="F29" t="s">
         <v>233</v>
@@ -7355,7 +7373,7 @@
         <v>232</v>
       </c>
       <c r="H29" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I29" t="s">
         <v>247</v>
@@ -7366,13 +7384,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="F30" t="s">
         <v>233</v>
@@ -7381,7 +7399,7 @@
         <v>232</v>
       </c>
       <c r="H30" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I30" t="s">
         <v>247</v>
@@ -7392,13 +7410,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="F31" t="s">
         <v>233</v>
@@ -7407,7 +7425,7 @@
         <v>232</v>
       </c>
       <c r="H31" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I31" t="s">
         <v>247</v>
@@ -7418,13 +7436,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="F32" t="s">
         <v>233</v>
@@ -7433,7 +7451,7 @@
         <v>232</v>
       </c>
       <c r="H32" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I32" t="s">
         <v>247</v>
@@ -7444,13 +7462,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="F33" t="s">
         <v>233</v>
@@ -7459,7 +7477,7 @@
         <v>232</v>
       </c>
       <c r="H33" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I33" t="s">
         <v>247</v>
@@ -7470,13 +7488,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="F34" t="s">
         <v>233</v>
@@ -7485,7 +7503,7 @@
         <v>232</v>
       </c>
       <c r="H34" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I34" t="s">
         <v>247</v>
@@ -7496,13 +7514,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="F35" t="s">
         <v>233</v>
@@ -7511,7 +7529,7 @@
         <v>232</v>
       </c>
       <c r="H35" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I35" t="s">
         <v>247</v>
@@ -7522,13 +7540,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="F36" t="s">
         <v>233</v>
@@ -7537,7 +7555,7 @@
         <v>232</v>
       </c>
       <c r="H36" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I36" t="s">
         <v>247</v>
@@ -7548,13 +7566,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="F37" t="s">
         <v>233</v>
@@ -7563,7 +7581,7 @@
         <v>232</v>
       </c>
       <c r="H37" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I37" t="s">
         <v>247</v>
@@ -7574,13 +7592,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="F38" t="s">
         <v>233</v>
@@ -7589,7 +7607,7 @@
         <v>232</v>
       </c>
       <c r="H38" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I38" t="s">
         <v>247</v>
@@ -7600,13 +7618,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="F39" t="s">
         <v>233</v>
@@ -7615,7 +7633,7 @@
         <v>232</v>
       </c>
       <c r="H39" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I39" t="s">
         <v>247</v>
@@ -7626,13 +7644,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="F40" t="s">
         <v>233</v>
@@ -7641,7 +7659,7 @@
         <v>232</v>
       </c>
       <c r="H40" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I40" t="s">
         <v>247</v>
@@ -7652,13 +7670,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="F41" t="s">
         <v>233</v>
@@ -7667,7 +7685,7 @@
         <v>232</v>
       </c>
       <c r="H41" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I41" t="s">
         <v>247</v>
@@ -7678,13 +7696,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="F42" t="s">
         <v>233</v>
@@ -7693,7 +7711,7 @@
         <v>232</v>
       </c>
       <c r="H42" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I42" t="s">
         <v>247</v>
@@ -7704,13 +7722,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="F43" t="s">
         <v>233</v>
@@ -7719,7 +7737,7 @@
         <v>232</v>
       </c>
       <c r="H43" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I43" t="s">
         <v>247</v>
@@ -7730,13 +7748,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="F44" t="s">
         <v>233</v>
@@ -7745,7 +7763,7 @@
         <v>232</v>
       </c>
       <c r="H44" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I44" t="s">
         <v>247</v>
@@ -7756,13 +7774,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="F45" t="s">
         <v>233</v>
@@ -7771,7 +7789,7 @@
         <v>232</v>
       </c>
       <c r="H45" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I45" t="s">
         <v>247</v>
@@ -7782,13 +7800,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="F46" t="s">
         <v>233</v>
@@ -7797,7 +7815,7 @@
         <v>232</v>
       </c>
       <c r="H46" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I46" t="s">
         <v>247</v>
@@ -7808,13 +7826,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="F47" t="s">
         <v>233</v>
@@ -7823,7 +7841,7 @@
         <v>232</v>
       </c>
       <c r="H47" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I47" t="s">
         <v>247</v>
@@ -7834,13 +7852,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="F48" t="s">
         <v>233</v>
@@ -7849,7 +7867,7 @@
         <v>232</v>
       </c>
       <c r="H48" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I48" t="s">
         <v>247</v>
@@ -7860,13 +7878,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="F49" t="s">
         <v>233</v>
@@ -7875,7 +7893,7 @@
         <v>232</v>
       </c>
       <c r="H49" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I49" t="s">
         <v>247</v>
@@ -7886,13 +7904,13 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="F50" t="s">
         <v>233</v>
@@ -7901,7 +7919,7 @@
         <v>232</v>
       </c>
       <c r="H50" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I50" t="s">
         <v>247</v>
@@ -7912,13 +7930,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="F51" t="s">
         <v>233</v>
@@ -7927,7 +7945,7 @@
         <v>232</v>
       </c>
       <c r="H51" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I51" t="s">
         <v>247</v>
@@ -7938,13 +7956,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="F52" t="s">
         <v>233</v>
@@ -7953,7 +7971,7 @@
         <v>232</v>
       </c>
       <c r="H52" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I52" t="s">
         <v>247</v>
@@ -7965,13 +7983,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D5B8311-A7E9-42EF-B49B-10C96D5F9BB3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5D17DB3-C2F4-4CBA-BFEB-6A66F35FFD15}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -8005,13 +8023,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="F5" t="s">
         <v>25</v>
@@ -8020,7 +8038,7 @@
         <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I5" t="s">
         <v>247</v>
@@ -8031,13 +8049,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="F6" t="s">
         <v>25</v>
@@ -8046,7 +8064,7 @@
         <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I6" t="s">
         <v>247</v>
@@ -8057,13 +8075,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="F7" t="s">
         <v>25</v>
@@ -8072,7 +8090,7 @@
         <v>35</v>
       </c>
       <c r="H7" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I7" t="s">
         <v>247</v>
@@ -8083,22 +8101,22 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
+        <v>467</v>
+      </c>
+      <c r="F8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" t="s">
         <v>461</v>
-      </c>
-      <c r="F8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" t="s">
-        <v>455</v>
       </c>
       <c r="I8" t="s">
         <v>247</v>
@@ -8109,13 +8127,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="F9" t="s">
         <v>25</v>
@@ -8124,7 +8142,7 @@
         <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I9" t="s">
         <v>247</v>
@@ -8135,13 +8153,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="F10" t="s">
         <v>25</v>
@@ -8150,7 +8168,7 @@
         <v>35</v>
       </c>
       <c r="H10" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I10" t="s">
         <v>247</v>
@@ -8161,13 +8179,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
@@ -8176,7 +8194,7 @@
         <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I11" t="s">
         <v>247</v>
@@ -8187,13 +8205,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F12" t="s">
         <v>25</v>
@@ -8202,7 +8220,7 @@
         <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I12" t="s">
         <v>247</v>
@@ -8213,13 +8231,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="F13" t="s">
         <v>25</v>
@@ -8228,7 +8246,7 @@
         <v>35</v>
       </c>
       <c r="H13" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I13" t="s">
         <v>247</v>
@@ -8239,13 +8257,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F14" t="s">
         <v>25</v>
@@ -8254,7 +8272,7 @@
         <v>35</v>
       </c>
       <c r="H14" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I14" t="s">
         <v>247</v>
@@ -8265,13 +8283,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="F15" t="s">
         <v>25</v>
@@ -8280,7 +8298,7 @@
         <v>35</v>
       </c>
       <c r="H15" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I15" t="s">
         <v>247</v>
@@ -8291,13 +8309,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="F16" t="s">
         <v>25</v>
@@ -8306,7 +8324,7 @@
         <v>35</v>
       </c>
       <c r="H16" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I16" t="s">
         <v>247</v>
@@ -8317,13 +8335,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F17" t="s">
         <v>25</v>
@@ -8332,7 +8350,7 @@
         <v>35</v>
       </c>
       <c r="H17" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I17" t="s">
         <v>247</v>
@@ -8343,13 +8361,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F18" t="s">
         <v>25</v>
@@ -8358,7 +8376,7 @@
         <v>35</v>
       </c>
       <c r="H18" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I18" t="s">
         <v>247</v>
@@ -8369,13 +8387,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="F19" t="s">
         <v>25</v>
@@ -8384,7 +8402,7 @@
         <v>35</v>
       </c>
       <c r="H19" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I19" t="s">
         <v>247</v>
@@ -8395,13 +8413,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="F20" t="s">
         <v>25</v>
@@ -8410,7 +8428,7 @@
         <v>35</v>
       </c>
       <c r="H20" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I20" t="s">
         <v>247</v>
@@ -8421,13 +8439,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="F21" t="s">
         <v>25</v>
@@ -8436,7 +8454,7 @@
         <v>35</v>
       </c>
       <c r="H21" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I21" t="s">
         <v>247</v>
@@ -8447,13 +8465,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="F22" t="s">
         <v>25</v>
@@ -8462,7 +8480,7 @@
         <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I22" t="s">
         <v>247</v>
@@ -8473,13 +8491,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="F23" t="s">
         <v>25</v>
@@ -8488,7 +8506,7 @@
         <v>35</v>
       </c>
       <c r="H23" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I23" t="s">
         <v>247</v>
@@ -8499,13 +8517,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="F24" t="s">
         <v>25</v>
@@ -8514,7 +8532,7 @@
         <v>35</v>
       </c>
       <c r="H24" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I24" t="s">
         <v>247</v>
@@ -8525,13 +8543,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="F25" t="s">
         <v>25</v>
@@ -8540,7 +8558,7 @@
         <v>35</v>
       </c>
       <c r="H25" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I25" t="s">
         <v>247</v>
@@ -8551,13 +8569,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="F26" t="s">
         <v>25</v>
@@ -8566,7 +8584,7 @@
         <v>35</v>
       </c>
       <c r="H26" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I26" t="s">
         <v>247</v>
@@ -8577,13 +8595,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="F27" t="s">
         <v>25</v>
@@ -8592,7 +8610,7 @@
         <v>35</v>
       </c>
       <c r="H27" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I27" t="s">
         <v>247</v>
@@ -8603,13 +8621,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="F28" t="s">
         <v>25</v>
@@ -8618,7 +8636,7 @@
         <v>35</v>
       </c>
       <c r="H28" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I28" t="s">
         <v>247</v>
@@ -8629,13 +8647,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="F29" t="s">
         <v>25</v>
@@ -8644,7 +8662,7 @@
         <v>35</v>
       </c>
       <c r="H29" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I29" t="s">
         <v>247</v>
@@ -8655,13 +8673,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="F30" t="s">
         <v>25</v>
@@ -8670,7 +8688,7 @@
         <v>35</v>
       </c>
       <c r="H30" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I30" t="s">
         <v>247</v>
@@ -8681,13 +8699,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="F31" t="s">
         <v>25</v>
@@ -8696,7 +8714,7 @@
         <v>35</v>
       </c>
       <c r="H31" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I31" t="s">
         <v>247</v>
@@ -8707,13 +8725,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="F32" t="s">
         <v>25</v>
@@ -8722,7 +8740,7 @@
         <v>35</v>
       </c>
       <c r="H32" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I32" t="s">
         <v>247</v>
@@ -8733,13 +8751,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="F33" t="s">
         <v>25</v>
@@ -8748,7 +8766,7 @@
         <v>35</v>
       </c>
       <c r="H33" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I33" t="s">
         <v>247</v>
@@ -8759,13 +8777,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="F34" t="s">
         <v>25</v>
@@ -8774,7 +8792,7 @@
         <v>35</v>
       </c>
       <c r="H34" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I34" t="s">
         <v>247</v>
@@ -8785,13 +8803,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="F35" t="s">
         <v>25</v>
@@ -8800,7 +8818,7 @@
         <v>35</v>
       </c>
       <c r="H35" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I35" t="s">
         <v>247</v>
@@ -8811,13 +8829,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="F36" t="s">
         <v>25</v>
@@ -8826,7 +8844,7 @@
         <v>35</v>
       </c>
       <c r="H36" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I36" t="s">
         <v>247</v>
@@ -8837,13 +8855,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="F37" t="s">
         <v>25</v>
@@ -8852,7 +8870,7 @@
         <v>35</v>
       </c>
       <c r="H37" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I37" t="s">
         <v>247</v>
@@ -8863,13 +8881,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="F38" t="s">
         <v>25</v>
@@ -8878,7 +8896,7 @@
         <v>35</v>
       </c>
       <c r="H38" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I38" t="s">
         <v>247</v>
@@ -8889,13 +8907,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="F39" t="s">
         <v>25</v>
@@ -8904,7 +8922,7 @@
         <v>35</v>
       </c>
       <c r="H39" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I39" t="s">
         <v>247</v>
@@ -8915,13 +8933,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="F40" t="s">
         <v>25</v>
@@ -8930,7 +8948,7 @@
         <v>35</v>
       </c>
       <c r="H40" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I40" t="s">
         <v>247</v>
@@ -8941,13 +8959,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="F41" t="s">
         <v>25</v>
@@ -8956,7 +8974,7 @@
         <v>35</v>
       </c>
       <c r="H41" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I41" t="s">
         <v>247</v>
@@ -8967,13 +8985,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="F42" t="s">
         <v>25</v>
@@ -8982,7 +9000,7 @@
         <v>35</v>
       </c>
       <c r="H42" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I42" t="s">
         <v>247</v>
@@ -8993,13 +9011,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="F43" t="s">
         <v>25</v>
@@ -9008,7 +9026,7 @@
         <v>35</v>
       </c>
       <c r="H43" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I43" t="s">
         <v>247</v>
@@ -9019,13 +9037,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="F44" t="s">
         <v>25</v>
@@ -9034,7 +9052,7 @@
         <v>35</v>
       </c>
       <c r="H44" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I44" t="s">
         <v>247</v>
@@ -9045,13 +9063,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="F45" t="s">
         <v>25</v>
@@ -9060,7 +9078,7 @@
         <v>35</v>
       </c>
       <c r="H45" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I45" t="s">
         <v>247</v>
@@ -9071,13 +9089,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="F46" t="s">
         <v>25</v>
@@ -9086,7 +9104,7 @@
         <v>35</v>
       </c>
       <c r="H46" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I46" t="s">
         <v>247</v>
@@ -9097,13 +9115,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="F47" t="s">
         <v>25</v>
@@ -9112,7 +9130,7 @@
         <v>35</v>
       </c>
       <c r="H47" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I47" t="s">
         <v>247</v>
@@ -9123,13 +9141,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="F48" t="s">
         <v>25</v>
@@ -9138,7 +9156,7 @@
         <v>35</v>
       </c>
       <c r="H48" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I48" t="s">
         <v>247</v>
@@ -9149,13 +9167,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="F49" t="s">
         <v>25</v>
@@ -9164,7 +9182,7 @@
         <v>35</v>
       </c>
       <c r="H49" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I49" t="s">
         <v>247</v>
@@ -9175,13 +9193,13 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="F50" t="s">
         <v>25</v>
@@ -9190,7 +9208,7 @@
         <v>35</v>
       </c>
       <c r="H50" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I50" t="s">
         <v>247</v>
@@ -9201,13 +9219,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="F51" t="s">
         <v>25</v>
@@ -9216,7 +9234,7 @@
         <v>35</v>
       </c>
       <c r="H51" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I51" t="s">
         <v>247</v>
@@ -9227,13 +9245,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="F52" t="s">
         <v>25</v>
@@ -9242,7 +9260,7 @@
         <v>35</v>
       </c>
       <c r="H52" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I52" t="s">
         <v>247</v>
@@ -9255,7 +9273,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:S107"/>
+  <dimension ref="B3:S110"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
@@ -12085,6 +12103,75 @@
         <v>35</v>
       </c>
       <c r="S107" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="108" spans="13:19">
+      <c r="M108" t="s">
+        <v>17</v>
+      </c>
+      <c r="N108" t="s">
+        <v>452</v>
+      </c>
+      <c r="O108" t="s">
+        <v>243</v>
+      </c>
+      <c r="P108" t="s">
+        <v>453</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>25</v>
+      </c>
+      <c r="R108" t="s">
+        <v>35</v>
+      </c>
+      <c r="S108" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="109" spans="13:19">
+      <c r="M109" t="s">
+        <v>17</v>
+      </c>
+      <c r="N109" t="s">
+        <v>454</v>
+      </c>
+      <c r="O109" t="s">
+        <v>243</v>
+      </c>
+      <c r="P109" t="s">
+        <v>455</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>25</v>
+      </c>
+      <c r="R109" t="s">
+        <v>35</v>
+      </c>
+      <c r="S109" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="110" spans="13:19">
+      <c r="M110" t="s">
+        <v>17</v>
+      </c>
+      <c r="N110" t="s">
+        <v>456</v>
+      </c>
+      <c r="O110" t="s">
+        <v>243</v>
+      </c>
+      <c r="P110" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>25</v>
+      </c>
+      <c r="R110" t="s">
+        <v>35</v>
+      </c>
+      <c r="S110" t="s">
         <v>247</v>
       </c>
     </row>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42147D7E-FD1B-4685-9592-A646010A2A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60225B4E-5D77-46C1-98BD-2AF06001E2FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2691" uniqueCount="809">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2892" uniqueCount="863">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -802,91 +802,91 @@
     <t>elc_spv_POL_004</t>
   </si>
   <si>
-    <t>solar electricity near Walbrzych (cluster 4)</t>
+    <t>solar electricity near Warsaw (cluster 4)</t>
   </si>
   <si>
     <t>elc_spv_POL_005</t>
   </si>
   <si>
-    <t>solar electricity near Wroclaw (cluster 5)</t>
+    <t>solar electricity near Siedlce (cluster 5)</t>
   </si>
   <si>
     <t>elc_spv_POL_006</t>
   </si>
   <si>
-    <t>solar electricity near Walbrzych (cluster 6)</t>
+    <t>solar electricity near Wroclaw (cluster 6)</t>
   </si>
   <si>
     <t>elc_spv_POL_007</t>
   </si>
   <si>
-    <t>solar electricity near Olsztyn (cluster 7)</t>
+    <t>solar electricity near Wroclaw (cluster 7)</t>
   </si>
   <si>
     <t>elc_spv_POL_008</t>
   </si>
   <si>
-    <t>solar electricity near Slupsk (cluster 8)</t>
+    <t>solar electricity near Rzeszow (cluster 8)</t>
   </si>
   <si>
     <t>elc_spv_POL_009</t>
   </si>
   <si>
-    <t>solar electricity near Olsztyn (cluster 9)</t>
+    <t>solar electricity near Slupsk (cluster 9)</t>
   </si>
   <si>
     <t>elc_spv_POL_010</t>
   </si>
   <si>
-    <t>solar electricity near Jelenia Gora (cluster 10)</t>
+    <t>solar electricity near Olsztyn (cluster 10)</t>
   </si>
   <si>
     <t>elc_spv_POL_011</t>
   </si>
   <si>
-    <t>solar electricity near Gdansk (cluster 11)</t>
+    <t>solar electricity near Legnica (cluster 11)</t>
   </si>
   <si>
     <t>elc_spv_POL_012</t>
   </si>
   <si>
-    <t>solar electricity near Lomza (cluster 12)</t>
+    <t>solar electricity near Gdansk (cluster 12)</t>
   </si>
   <si>
     <t>elc_spv_POL_013</t>
   </si>
   <si>
-    <t>solar electricity near Zielona Gora (cluster 13)</t>
+    <t>solar electricity near Warsaw (cluster 13)</t>
   </si>
   <si>
     <t>elc_spv_POL_014</t>
   </si>
   <si>
-    <t>solar electricity near Szczecin (cluster 14)</t>
+    <t>solar electricity near Lomza (cluster 14)</t>
   </si>
   <si>
     <t>elc_spv_POL_015</t>
   </si>
   <si>
-    <t>solar electricity near Rzeszow (cluster 15)</t>
+    <t>solar electricity near Zielona Gora (cluster 15)</t>
   </si>
   <si>
     <t>elc_spv_POL_016</t>
   </si>
   <si>
-    <t>solar electricity near Suwalki (cluster 16)</t>
+    <t>solar electricity near Szczecin (cluster 16)</t>
   </si>
   <si>
     <t>elc_spv_POL_017</t>
   </si>
   <si>
-    <t>solar electricity near Piotrkow Trybunalski (cluster 17)</t>
+    <t>solar electricity near Lublin (cluster 17)</t>
   </si>
   <si>
     <t>elc_spv_POL_018</t>
   </si>
   <si>
-    <t>solar electricity near Lodz (cluster 18)</t>
+    <t>solar electricity near Suwalki (cluster 18)</t>
   </si>
   <si>
     <t>elc_spv_POL_019</t>
@@ -898,163 +898,163 @@
     <t>elc_spv_POL_020</t>
   </si>
   <si>
-    <t>solar electricity near Koszalin (cluster 20)</t>
+    <t>solar electricity near Czestochowa (cluster 20)</t>
   </si>
   <si>
     <t>elc_spv_POL_021</t>
   </si>
   <si>
-    <t>solar electricity near Zielona Gora (cluster 21)</t>
+    <t>solar electricity near Warsaw (cluster 21)</t>
   </si>
   <si>
     <t>elc_spv_POL_022</t>
   </si>
   <si>
-    <t>solar electricity near Katowice (cluster 22)</t>
+    <t>solar electricity near Koszalin (cluster 22)</t>
   </si>
   <si>
     <t>elc_spv_POL_023</t>
   </si>
   <si>
-    <t>solar electricity near Tarnow (cluster 23)</t>
+    <t>solar electricity near Lubin (cluster 23)</t>
   </si>
   <si>
     <t>elc_spv_POL_024</t>
   </si>
   <si>
-    <t>solar electricity near Chelm (cluster 24)</t>
+    <t>solar electricity near Gliwice (cluster 24)</t>
   </si>
   <si>
     <t>elc_spv_POL_025</t>
   </si>
   <si>
-    <t>solar electricity near Rzeszow (cluster 25)</t>
+    <t>solar electricity near Tarnow (cluster 25)</t>
   </si>
   <si>
     <t>elc_spv_POL_026</t>
   </si>
   <si>
-    <t>solar electricity near Kielce (cluster 26)</t>
+    <t>solar electricity near Chelm (cluster 26)</t>
   </si>
   <si>
     <t>elc_spv_POL_027</t>
   </si>
   <si>
-    <t>solar electricity near Mielec (cluster 27)</t>
+    <t>solar electricity near Kielce (cluster 27)</t>
   </si>
   <si>
     <t>elc_spv_POL_028</t>
   </si>
   <si>
-    <t>solar electricity near Rzeszow (cluster 28)</t>
+    <t>solar electricity near Tarnow (cluster 28)</t>
   </si>
   <si>
     <t>elc_spv_POL_029</t>
   </si>
   <si>
-    <t>solar electricity near Czestochowa (cluster 29)</t>
+    <t>solar electricity near Rzeszow (cluster 29)</t>
   </si>
   <si>
     <t>elc_spv_POL_030</t>
   </si>
   <si>
-    <t>solar electricity near Torun (cluster 30)</t>
+    <t>solar electricity near Czestochowa (cluster 30)</t>
   </si>
   <si>
     <t>elc_spv_POL_031</t>
   </si>
   <si>
-    <t>solar electricity near Ostrowiec Swietokrzyski (cluster 31)</t>
+    <t>solar electricity near Pila (cluster 31)</t>
   </si>
   <si>
     <t>elc_spv_POL_032</t>
   </si>
   <si>
-    <t>solar electricity near Opole (cluster 32)</t>
+    <t>solar electricity near Torun (cluster 32)</t>
   </si>
   <si>
     <t>elc_spv_POL_033</t>
   </si>
   <si>
-    <t>solar electricity near Kalisz (cluster 33)</t>
+    <t>solar electricity near Ostrowiec Swietokrzyski (cluster 33)</t>
   </si>
   <si>
     <t>elc_spv_POL_034</t>
   </si>
   <si>
-    <t>solar electricity near Koszalin (cluster 34)</t>
+    <t>solar electricity near Wroclaw (cluster 34)</t>
   </si>
   <si>
     <t>elc_spv_POL_035</t>
   </si>
   <si>
-    <t>solar electricity near Warsaw (cluster 35)</t>
+    <t>solar electricity near Konin (cluster 35)</t>
   </si>
   <si>
     <t>elc_spv_POL_036</t>
   </si>
   <si>
-    <t>solar electricity near Katowice (cluster 36)</t>
+    <t>solar electricity near Kalisz (cluster 36)</t>
   </si>
   <si>
     <t>elc_spv_POL_037</t>
   </si>
   <si>
-    <t>solar electricity near Suwalki (cluster 37)</t>
+    <t>solar electricity near Koszalin (cluster 37)</t>
   </si>
   <si>
     <t>elc_spv_POL_038</t>
   </si>
   <si>
-    <t>solar electricity near Pila (cluster 38)</t>
+    <t>solar electricity near Walbrzych (cluster 38)</t>
   </si>
   <si>
     <t>elc_spv_POL_039</t>
   </si>
   <si>
-    <t>solar electricity near Kedzierzyn-Kozle (cluster 39)</t>
+    <t>solar electricity near Warsaw (cluster 39)</t>
   </si>
   <si>
     <t>elc_spv_POL_040</t>
   </si>
   <si>
-    <t>solar electricity near Szczecin (cluster 40)</t>
+    <t>solar electricity near Piotrkow Trybunalski (cluster 40)</t>
   </si>
   <si>
     <t>elc_spv_POL_041</t>
   </si>
   <si>
-    <t>solar electricity near Krakow (cluster 41)</t>
+    <t>solar electricity near Lomza (cluster 41)</t>
   </si>
   <si>
     <t>elc_spv_POL_042</t>
   </si>
   <si>
-    <t>solar electricity near Krakow (cluster 42)</t>
+    <t>solar electricity near Poznan (cluster 42)</t>
   </si>
   <si>
     <t>elc_spv_POL_043</t>
   </si>
   <si>
-    <t>solar electricity near Elblag (cluster 43)</t>
+    <t>solar electricity near Opole (cluster 43)</t>
   </si>
   <si>
     <t>elc_spv_POL_044</t>
   </si>
   <si>
-    <t>solar electricity near Plock (cluster 44)</t>
+    <t>solar electricity near Lodz (cluster 44)</t>
   </si>
   <si>
     <t>elc_spv_POL_045</t>
   </si>
   <si>
-    <t>solar electricity near Wroclaw (cluster 45)</t>
+    <t>solar electricity near Szczecin (cluster 45)</t>
   </si>
   <si>
     <t>elc_spv_POL_046</t>
   </si>
   <si>
-    <t>solar electricity near Gdansk (cluster 46)</t>
+    <t>solar electricity near Krakow (cluster 46)</t>
   </si>
   <si>
     <t>elc_spv_POL_047</t>
@@ -1066,7 +1066,37 @@
     <t>elc_spv_POL_048</t>
   </si>
   <si>
-    <t>solar electricity near Siedlce (cluster 48)</t>
+    <t>solar electricity near Grudziadz (cluster 48)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_049</t>
+  </si>
+  <si>
+    <t>solar electricity near Plock (cluster 49)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_050</t>
+  </si>
+  <si>
+    <t>solar electricity near Wroclaw (cluster 50)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_051</t>
+  </si>
+  <si>
+    <t>solar electricity near Gdansk (cluster 51)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_052</t>
+  </si>
+  <si>
+    <t>solar electricity near Krakow (cluster 52)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_053</t>
+  </si>
+  <si>
+    <t>solar electricity near Lublin (cluster 53)</t>
   </si>
   <si>
     <t>elc_wof_POL_001</t>
@@ -1084,7 +1114,7 @@
     <t>elc_wof_POL_003</t>
   </si>
   <si>
-    <t>wind offshore electricity near Koszalin (cluster 3)</t>
+    <t>wind offshore electricity near Szczecin (cluster 3)</t>
   </si>
   <si>
     <t>elc_wof_POL_004</t>
@@ -1108,7 +1138,7 @@
     <t>elc_wof_POL_007</t>
   </si>
   <si>
-    <t>wind offshore electricity near Koszalin (cluster 7)</t>
+    <t>wind offshore electricity near Slupsk (cluster 7)</t>
   </si>
   <si>
     <t>elc_wof_POL_008</t>
@@ -1150,91 +1180,91 @@
     <t>elc_won_POL_004</t>
   </si>
   <si>
-    <t>wind onshore electricity near Walbrzych (cluster 4)</t>
+    <t>wind onshore electricity near Warsaw (cluster 4)</t>
   </si>
   <si>
     <t>elc_won_POL_005</t>
   </si>
   <si>
-    <t>wind onshore electricity near Wroclaw (cluster 5)</t>
+    <t>wind onshore electricity near Siedlce (cluster 5)</t>
   </si>
   <si>
     <t>elc_won_POL_006</t>
   </si>
   <si>
-    <t>wind onshore electricity near Walbrzych (cluster 6)</t>
+    <t>wind onshore electricity near Legnica (cluster 6)</t>
   </si>
   <si>
     <t>elc_won_POL_007</t>
   </si>
   <si>
-    <t>wind onshore electricity near Olsztyn (cluster 7)</t>
+    <t>wind onshore electricity near Wroclaw (cluster 7)</t>
   </si>
   <si>
     <t>elc_won_POL_008</t>
   </si>
   <si>
-    <t>wind onshore electricity near Slupsk (cluster 8)</t>
+    <t>wind onshore electricity near Rzeszow (cluster 8)</t>
   </si>
   <si>
     <t>elc_won_POL_009</t>
   </si>
   <si>
-    <t>wind onshore electricity near Olsztyn (cluster 9)</t>
+    <t>wind onshore electricity near Slupsk (cluster 9)</t>
   </si>
   <si>
     <t>elc_won_POL_010</t>
   </si>
   <si>
-    <t>wind onshore electricity near Jelenia Gora (cluster 10)</t>
+    <t>wind onshore electricity near Olsztyn (cluster 10)</t>
   </si>
   <si>
     <t>elc_won_POL_011</t>
   </si>
   <si>
-    <t>wind onshore electricity near Gdansk (cluster 11)</t>
+    <t>wind onshore electricity near Legnica (cluster 11)</t>
   </si>
   <si>
     <t>elc_won_POL_012</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lomza (cluster 12)</t>
+    <t>wind onshore electricity near Gdansk (cluster 12)</t>
   </si>
   <si>
     <t>elc_won_POL_013</t>
   </si>
   <si>
-    <t>wind onshore electricity near Zielona Gora (cluster 13)</t>
+    <t>wind onshore electricity near Warsaw (cluster 13)</t>
   </si>
   <si>
     <t>elc_won_POL_014</t>
   </si>
   <si>
-    <t>wind onshore electricity near Szczecin (cluster 14)</t>
+    <t>wind onshore electricity near Lomza (cluster 14)</t>
   </si>
   <si>
     <t>elc_won_POL_015</t>
   </si>
   <si>
-    <t>wind onshore electricity near Przemysl (cluster 15)</t>
+    <t>wind onshore electricity near Zielona Gora (cluster 15)</t>
   </si>
   <si>
     <t>elc_won_POL_016</t>
   </si>
   <si>
-    <t>wind onshore electricity near Suwalki (cluster 16)</t>
+    <t>wind onshore electricity near Szczecin (cluster 16)</t>
   </si>
   <si>
     <t>elc_won_POL_017</t>
   </si>
   <si>
-    <t>wind onshore electricity near Piotrkow Trybunalski (cluster 17)</t>
+    <t>wind onshore electricity near Lublin (cluster 17)</t>
   </si>
   <si>
     <t>elc_won_POL_018</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lodz (cluster 18)</t>
+    <t>wind onshore electricity near Suwalki (cluster 18)</t>
   </si>
   <si>
     <t>elc_won_POL_019</t>
@@ -1246,189 +1276,219 @@
     <t>elc_won_POL_020</t>
   </si>
   <si>
-    <t>wind onshore electricity near Koszalin (cluster 20)</t>
+    <t>wind onshore electricity near Czestochowa (cluster 20)</t>
   </si>
   <si>
     <t>elc_won_POL_021</t>
   </si>
   <si>
-    <t>wind onshore electricity near Zielona Gora (cluster 21)</t>
+    <t>wind onshore electricity near Warsaw (cluster 21)</t>
   </si>
   <si>
     <t>elc_won_POL_022</t>
   </si>
   <si>
-    <t>wind onshore electricity near Katowice (cluster 22)</t>
+    <t>wind onshore electricity near Koszalin (cluster 22)</t>
   </si>
   <si>
     <t>elc_won_POL_023</t>
   </si>
   <si>
-    <t>wind onshore electricity near Tarnow (cluster 23)</t>
+    <t>wind onshore electricity near Glogow (cluster 23)</t>
   </si>
   <si>
     <t>elc_won_POL_024</t>
   </si>
   <si>
-    <t>wind onshore electricity near Chelm (cluster 24)</t>
+    <t>wind onshore electricity near Katowice (cluster 24)</t>
   </si>
   <si>
     <t>elc_won_POL_025</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rzeszow (cluster 25)</t>
+    <t>wind onshore electricity near Tarnow (cluster 25)</t>
   </si>
   <si>
     <t>elc_won_POL_026</t>
   </si>
   <si>
-    <t>wind onshore electricity near Kielce (cluster 26)</t>
+    <t>wind onshore electricity near Chelm (cluster 26)</t>
   </si>
   <si>
     <t>elc_won_POL_027</t>
   </si>
   <si>
-    <t>wind onshore electricity near Mielec (cluster 27)</t>
+    <t>wind onshore electricity near Radom (cluster 27)</t>
   </si>
   <si>
     <t>elc_won_POL_028</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rzeszow (cluster 28)</t>
+    <t>wind onshore electricity near Mielec (cluster 28)</t>
   </si>
   <si>
     <t>elc_won_POL_029</t>
   </si>
   <si>
-    <t>wind onshore electricity near Czestochowa (cluster 29)</t>
+    <t>wind onshore electricity near Rzeszow (cluster 29)</t>
   </si>
   <si>
     <t>elc_won_POL_030</t>
   </si>
   <si>
-    <t>wind onshore electricity near Torun (cluster 30)</t>
+    <t>wind onshore electricity near Czestochowa (cluster 30)</t>
   </si>
   <si>
     <t>elc_won_POL_031</t>
   </si>
   <si>
-    <t>wind onshore electricity near Ostrowiec Swietokrzyski (cluster 31)</t>
+    <t>wind onshore electricity near Pila (cluster 31)</t>
   </si>
   <si>
     <t>elc_won_POL_032</t>
   </si>
   <si>
-    <t>wind onshore electricity near Opole (cluster 32)</t>
+    <t>wind onshore electricity near Torun (cluster 32)</t>
   </si>
   <si>
     <t>elc_won_POL_033</t>
   </si>
   <si>
-    <t>wind onshore electricity near Konin (cluster 33)</t>
+    <t>wind onshore electricity near Radom (cluster 33)</t>
   </si>
   <si>
     <t>elc_won_POL_034</t>
   </si>
   <si>
-    <t>wind onshore electricity near Koszalin (cluster 34)</t>
+    <t>wind onshore electricity near Opole (cluster 34)</t>
   </si>
   <si>
     <t>elc_won_POL_035</t>
   </si>
   <si>
-    <t>wind onshore electricity near Warsaw (cluster 35)</t>
+    <t>wind onshore electricity near Konin (cluster 35)</t>
   </si>
   <si>
     <t>elc_won_POL_036</t>
   </si>
   <si>
-    <t>wind onshore electricity near Katowice (cluster 36)</t>
+    <t>wind onshore electricity near Kalisz (cluster 36)</t>
   </si>
   <si>
     <t>elc_won_POL_037</t>
   </si>
   <si>
-    <t>wind onshore electricity near Suwalki (cluster 37)</t>
+    <t>wind onshore electricity near Koszalin (cluster 37)</t>
   </si>
   <si>
     <t>elc_won_POL_038</t>
   </si>
   <si>
-    <t>wind onshore electricity near Pila (cluster 38)</t>
+    <t>wind onshore electricity near Walbrzych (cluster 38)</t>
   </si>
   <si>
     <t>elc_won_POL_039</t>
   </si>
   <si>
-    <t>wind onshore electricity near Kedzierzyn-Kozle (cluster 39)</t>
+    <t>wind onshore electricity near Warsaw (cluster 39)</t>
   </si>
   <si>
     <t>elc_won_POL_040</t>
   </si>
   <si>
-    <t>wind onshore electricity near Szczecin (cluster 40)</t>
+    <t>wind onshore electricity near Piotrkow Trybunalski (cluster 40)</t>
   </si>
   <si>
     <t>elc_won_POL_041</t>
   </si>
   <si>
-    <t>wind onshore electricity near Krakow (cluster 41)</t>
+    <t>wind onshore electricity near Lomza (cluster 41)</t>
   </si>
   <si>
     <t>elc_won_POL_042</t>
   </si>
   <si>
-    <t>wind onshore electricity near Krakow (cluster 42)</t>
+    <t>wind onshore electricity near Poznan (cluster 42)</t>
   </si>
   <si>
     <t>elc_won_POL_043</t>
   </si>
   <si>
-    <t>wind onshore electricity near Elblag (cluster 43)</t>
+    <t>wind onshore electricity near Kedzierzyn-Kozle (cluster 43)</t>
   </si>
   <si>
     <t>elc_won_POL_044</t>
   </si>
   <si>
-    <t>wind onshore electricity near Plock (cluster 44)</t>
+    <t>wind onshore electricity near Lodz (cluster 44)</t>
   </si>
   <si>
     <t>elc_won_POL_045</t>
   </si>
   <si>
-    <t>wind onshore electricity near Wroclaw (cluster 45)</t>
+    <t>wind onshore electricity near Szczecin (cluster 45)</t>
   </si>
   <si>
     <t>elc_won_POL_046</t>
   </si>
   <si>
-    <t>wind onshore electricity near Gdansk (cluster 46)</t>
+    <t>wind onshore electricity near Krakow (cluster 46)</t>
   </si>
   <si>
     <t>elc_won_POL_047</t>
   </si>
   <si>
-    <t>wind onshore electricity near Krakow (cluster 47)</t>
+    <t>wind onshore electricity near Grudziadz (cluster 47)</t>
   </si>
   <si>
     <t>elc_won_POL_048</t>
   </si>
   <si>
-    <t>wind onshore electricity near Siedlce (cluster 48)</t>
+    <t>wind onshore electricity near Plock (cluster 48)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_049</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Wroclaw (cluster 49)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_050</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Gdansk (cluster 50)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_051</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Krakow (cluster 51)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_052</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Lublin (cluster 52)</t>
   </si>
   <si>
     <t>~fi_comm</t>
   </si>
   <si>
+    <t>e_Belchatow_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/293484891-400 (Piotrkow Trybunalski, 26 km)</t>
+  </si>
+  <si>
+    <t>lo</t>
+  </si>
+  <si>
     <t>e_Bialystok_POL</t>
   </si>
   <si>
     <t>grid node -- PL17-400 (Bialystok, 26 km)</t>
   </si>
   <si>
-    <t>lo</t>
-  </si>
-  <si>
     <t>e_BielskoBiala_POL</t>
   </si>
   <si>
@@ -1459,12 +1519,6 @@
     <t>grid node -- way/216060722-220 (Czestochowa, 4 km)</t>
   </si>
   <si>
-    <t>e_Debica_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/198635989-220 (Rzeszow, 6 km)</t>
-  </si>
-  <si>
     <t>e_Elk_POL</t>
   </si>
   <si>
@@ -1483,12 +1537,6 @@
     <t>grid node -- way/86494356-400 (Gdansk, 54 km)</t>
   </si>
   <si>
-    <t>e_Gliwice_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/293489607-400 (Katowice, 21 km)</t>
-  </si>
-  <si>
     <t>e_GorzowWielkopolski_POL</t>
   </si>
   <si>
@@ -1507,6 +1555,12 @@
     <t>grid node -- way/46092396-400 (Grudziadz, 6 km)</t>
   </si>
   <si>
+    <t>e_Kalisz_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/255293403-400 (Kalisz, 21 km)</t>
+  </si>
+  <si>
     <t>e_Katowice_POL</t>
   </si>
   <si>
@@ -1546,7 +1600,7 @@
     <t>e_Krosno_POL</t>
   </si>
   <si>
-    <t>grid node -- way/166838338-400 (Rzeszow, 40 km)</t>
+    <t>grid node -- PL62-400 (Rzeszow, 32 km)</t>
   </si>
   <si>
     <t>e_Kwidzyn_POL</t>
@@ -1561,52 +1615,70 @@
     <t>grid node -- PL34-400 (Wroclaw, 43 km)</t>
   </si>
   <si>
+    <t>e_Lodz_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/35366436-220 (Lodz, 8 km)</t>
+  </si>
+  <si>
     <t>e_Lomza_POL</t>
   </si>
   <si>
+    <t>grid node -- way/121656686-400 (Lomza, 31 km)</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/180535363-220 (Lubin, 33 km)</t>
+  </si>
+  <si>
+    <t>e_Lublin_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/170249563-220 (Lublin, 6 km)</t>
+  </si>
+  <si>
+    <t>e_Lukow_POL</t>
+  </si>
+  <si>
+    <t>grid node -- PL27-400 (Siedlce, 8 km)</t>
+  </si>
+  <si>
+    <t>e_Mielec_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/199098053-400 (Mielec, 19 km)</t>
+  </si>
+  <si>
+    <t>e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/101915790-220 (Olsztyn, 4 km)</t>
+  </si>
+  <si>
+    <t>e_Opole_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/255277953-400 (Opole, 10 km)</t>
+  </si>
+  <si>
+    <t>e_Ostroleka_POL</t>
+  </si>
+  <si>
     <t>grid node -- way/121656686-220 (Lomza, 31 km)</t>
   </si>
   <si>
-    <t>e_Lubin_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/180535363-220 (Lubin, 33 km)</t>
-  </si>
-  <si>
-    <t>e_Mielec_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/199098053-220 (Mielec, 19 km)</t>
-  </si>
-  <si>
-    <t>e_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>grid node -- PL36-400 (Wroclaw, 46 km)</t>
-  </si>
-  <si>
-    <t>e_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/101915790-220 (Olsztyn, 4 km)</t>
-  </si>
-  <si>
-    <t>e_Opole_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/255277953-400 (Opole, 10 km)</t>
-  </si>
-  <si>
     <t>e_OstrowiecSwietokrz_POL</t>
   </si>
   <si>
     <t>grid node -- way/254235846-400 (Ostrowiec Swietokrzyski, 4 km)</t>
   </si>
   <si>
-    <t>e_PiotrkowTrybunalsk_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/170316833-220 (Piotrkow Trybunalski, 3 km)</t>
+    <t>e_Pila_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/238640596-220 (Pila, 12 km)</t>
   </si>
   <si>
     <t>e_Plock_POL</t>
@@ -1633,6 +1705,12 @@
     <t>grid node -- way/88544449-220 (Lublin, 46 km)</t>
   </si>
   <si>
+    <t>e_Radom_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/173582810-400 (Radom, 35 km)</t>
+  </si>
+  <si>
     <t>e_Radomsko_POL</t>
   </si>
   <si>
@@ -1645,6 +1723,12 @@
     <t>grid node -- way/215282393-400 (Rzeszow, 20 km)</t>
   </si>
   <si>
+    <t>e_Siedlce_POL</t>
+  </si>
+  <si>
+    <t>grid node -- PL26-400 (Warsaw, 53 km)</t>
+  </si>
+  <si>
     <t>e_Slupsk_POL</t>
   </si>
   <si>
@@ -1681,6 +1765,12 @@
     <t>grid node -- way/255314292 (Slupsk, 10 km)</t>
   </si>
   <si>
+    <t>e_Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/276291999-220 (Walbrzych, 11 km)</t>
+  </si>
+  <si>
     <t>e_Warsaw_POL</t>
   </si>
   <si>
@@ -1702,7 +1792,7 @@
     <t>e_Zamosc_POL</t>
   </si>
   <si>
-    <t>grid node -- way/173613665-220 (Zamosc, 3 km)</t>
+    <t>grid node -- way/170368942-220 (Zamosc, 8 km)</t>
   </si>
   <si>
     <t>e_ZielonaGora_POL</t>
@@ -1711,6 +1801,12 @@
     <t>grid node -- way/158232924-220 (Zielona Gora, 15 km)</t>
   </si>
   <si>
+    <t>h_Belchatow_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/293484891-400 (Piotrkow Trybunalski, 26 km)</t>
+  </si>
+  <si>
     <t>h_Bialystok_POL</t>
   </si>
   <si>
@@ -1747,12 +1843,6 @@
     <t>heat at grid node -- way/216060722-220 (Czestochowa, 4 km)</t>
   </si>
   <si>
-    <t>h_Debica_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/198635989-220 (Rzeszow, 6 km)</t>
-  </si>
-  <si>
     <t>h_Elk_POL</t>
   </si>
   <si>
@@ -1771,12 +1861,6 @@
     <t>heat at grid node -- way/86494356-400 (Gdansk, 54 km)</t>
   </si>
   <si>
-    <t>h_Gliwice_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/293489607-400 (Katowice, 21 km)</t>
-  </si>
-  <si>
     <t>h_GorzowWielkopolski_POL</t>
   </si>
   <si>
@@ -1795,6 +1879,12 @@
     <t>heat at grid node -- way/46092396-400 (Grudziadz, 6 km)</t>
   </si>
   <si>
+    <t>h_Kalisz_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/255293403-400 (Kalisz, 21 km)</t>
+  </si>
+  <si>
     <t>h_Katowice_POL</t>
   </si>
   <si>
@@ -1834,7 +1924,7 @@
     <t>h_Krosno_POL</t>
   </si>
   <si>
-    <t>heat at grid node -- way/166838338-400 (Rzeszow, 40 km)</t>
+    <t>heat at grid node -- PL62-400 (Rzeszow, 32 km)</t>
   </si>
   <si>
     <t>h_Kwidzyn_POL</t>
@@ -1849,52 +1939,70 @@
     <t>heat at grid node -- PL34-400 (Wroclaw, 43 km)</t>
   </si>
   <si>
+    <t>h_Lodz_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/35366436-220 (Lodz, 8 km)</t>
+  </si>
+  <si>
     <t>h_Lomza_POL</t>
   </si>
   <si>
+    <t>heat at grid node -- way/121656686-400 (Lomza, 31 km)</t>
+  </si>
+  <si>
+    <t>h_Lubin_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/180535363-220 (Lubin, 33 km)</t>
+  </si>
+  <si>
+    <t>h_Lublin_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/170249563-220 (Lublin, 6 km)</t>
+  </si>
+  <si>
+    <t>h_Lukow_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- PL27-400 (Siedlce, 8 km)</t>
+  </si>
+  <si>
+    <t>h_Mielec_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/199098053-400 (Mielec, 19 km)</t>
+  </si>
+  <si>
+    <t>h_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/101915790-220 (Olsztyn, 4 km)</t>
+  </si>
+  <si>
+    <t>h_Opole_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/255277953-400 (Opole, 10 km)</t>
+  </si>
+  <si>
+    <t>h_Ostroleka_POL</t>
+  </si>
+  <si>
     <t>heat at grid node -- way/121656686-220 (Lomza, 31 km)</t>
   </si>
   <si>
-    <t>h_Lubin_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/180535363-220 (Lubin, 33 km)</t>
-  </si>
-  <si>
-    <t>h_Mielec_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/199098053-220 (Mielec, 19 km)</t>
-  </si>
-  <si>
-    <t>h_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- PL36-400 (Wroclaw, 46 km)</t>
-  </si>
-  <si>
-    <t>h_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/101915790-220 (Olsztyn, 4 km)</t>
-  </si>
-  <si>
-    <t>h_Opole_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/255277953-400 (Opole, 10 km)</t>
-  </si>
-  <si>
     <t>h_OstrowiecSwietokrz_POL</t>
   </si>
   <si>
     <t>heat at grid node -- way/254235846-400 (Ostrowiec Swietokrzyski, 4 km)</t>
   </si>
   <si>
-    <t>h_PiotrkowTrybunalsk_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/170316833-220 (Piotrkow Trybunalski, 3 km)</t>
+    <t>h_Pila_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/238640596-220 (Pila, 12 km)</t>
   </si>
   <si>
     <t>h_Plock_POL</t>
@@ -1921,6 +2029,12 @@
     <t>heat at grid node -- way/88544449-220 (Lublin, 46 km)</t>
   </si>
   <si>
+    <t>h_Radom_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/173582810-400 (Radom, 35 km)</t>
+  </si>
+  <si>
     <t>h_Radomsko_POL</t>
   </si>
   <si>
@@ -1933,6 +2047,12 @@
     <t>heat at grid node -- way/215282393-400 (Rzeszow, 20 km)</t>
   </si>
   <si>
+    <t>h_Siedlce_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- PL26-400 (Warsaw, 53 km)</t>
+  </si>
+  <si>
     <t>h_Slupsk_POL</t>
   </si>
   <si>
@@ -1969,6 +2089,12 @@
     <t>heat at grid node -- way/255314292 (Slupsk, 10 km)</t>
   </si>
   <si>
+    <t>h_Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/276291999-220 (Walbrzych, 11 km)</t>
+  </si>
+  <si>
     <t>h_Warsaw_POL</t>
   </si>
   <si>
@@ -1990,7 +2116,7 @@
     <t>h_Zamosc_POL</t>
   </si>
   <si>
-    <t>heat at grid node -- way/173613665-220 (Zamosc, 3 km)</t>
+    <t>heat at grid node -- way/170368942-220 (Zamosc, 8 km)</t>
   </si>
   <si>
     <t>h_ZielonaGora_POL</t>
@@ -2020,24 +2146,36 @@
     <t>co2 captured at grid node -- PL18-400 (Gorzow Wielkopolski, 15 km)</t>
   </si>
   <si>
+    <t>co2_Siedlce_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- PL26-400 (Warsaw, 53 km)</t>
+  </si>
+  <si>
+    <t>co2_Lukow_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- PL27-400 (Siedlce, 8 km)</t>
+  </si>
+  <si>
     <t>co2_Legnica_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- PL34-400 (Wroclaw, 43 km)</t>
   </si>
   <si>
-    <t>co2_Olesnica_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- PL36-400 (Wroclaw, 46 km)</t>
-  </si>
-  <si>
     <t>co2_Swidnica_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- PL46-220 (Wroclaw, 58 km)</t>
   </si>
   <si>
+    <t>co2_Krosno_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- PL62-400 (Rzeszow, 32 km)</t>
+  </si>
+  <si>
     <t>co2_Kwidzyn_POL</t>
   </si>
   <si>
@@ -2068,10 +2206,16 @@
     <t>co2 captured at grid node -- way/112614319-400 (Gdansk, 4 km)</t>
   </si>
   <si>
+    <t>co2_Ostroleka_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/121656686-220 (Lomza, 31 km)</t>
+  </si>
+  <si>
     <t>co2_Lomza_POL</t>
   </si>
   <si>
-    <t>co2 captured at grid node -- way/121656686-220 (Lomza, 31 km)</t>
+    <t>co2 captured at grid node -- way/121656686-400 (Lomza, 31 km)</t>
   </si>
   <si>
     <t>co2_ZielonaGora_POL</t>
@@ -2086,10 +2230,10 @@
     <t>co2 captured at grid node -- way/165763717-220 (Szczecin, 15 km)</t>
   </si>
   <si>
-    <t>co2_Krosno_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/166838338-400 (Rzeszow, 40 km)</t>
+    <t>co2_Lublin_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/170249563-220 (Lublin, 6 km)</t>
   </si>
   <si>
     <t>co2_Grajewo_POL</t>
@@ -2098,10 +2242,10 @@
     <t>co2 captured at grid node -- way/170259740-220 (Elk, 6 km)</t>
   </si>
   <si>
-    <t>co2_PiotrkowTrybunalsk_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/170316833-220 (Piotrkow Trybunalski, 3 km)</t>
+    <t>co2_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/170368942-220 (Zamosc, 8 km)</t>
   </si>
   <si>
     <t>co2_Radomsko_POL</t>
@@ -2110,10 +2254,10 @@
     <t>co2 captured at grid node -- way/171917072-400 (Czestochowa, 41 km)</t>
   </si>
   <si>
-    <t>co2_Zamosc_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/173613665-220 (Zamosc, 3 km)</t>
+    <t>co2_Radom_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/173582810-400 (Radom, 35 km)</t>
   </si>
   <si>
     <t>co2_Koszalin_POL</t>
@@ -2146,12 +2290,6 @@
     <t>co2 captured at grid node -- way/194903381-400 (Chelm, 4 km)</t>
   </si>
   <si>
-    <t>co2_Debica_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/198635989-220 (Rzeszow, 6 km)</t>
-  </si>
-  <si>
     <t>co2_Kielce_POL</t>
   </si>
   <si>
@@ -2161,7 +2299,7 @@
     <t>co2_Mielec_POL</t>
   </si>
   <si>
-    <t>co2 captured at grid node -- way/199098053-220 (Mielec, 19 km)</t>
+    <t>co2 captured at grid node -- way/199098053-400 (Mielec, 19 km)</t>
   </si>
   <si>
     <t>co2_Rzeszow_POL</t>
@@ -2176,6 +2314,12 @@
     <t>co2 captured at grid node -- way/216060722-220 (Czestochowa, 4 km)</t>
   </si>
   <si>
+    <t>co2_Pila_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/238640596-220 (Pila, 12 km)</t>
+  </si>
+  <si>
     <t>co2_Wloclawek_POL</t>
   </si>
   <si>
@@ -2200,22 +2344,34 @@
     <t>co2 captured at grid node -- way/255284259-220 (Konin, 10 km)</t>
   </si>
   <si>
+    <t>co2_Kalisz_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/255293403-400 (Kalisz, 21 km)</t>
+  </si>
+  <si>
     <t>co2_Ustka_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/255314292 (Slupsk, 10 km)</t>
   </si>
   <si>
+    <t>co2_Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/276291999-220 (Walbrzych, 11 km)</t>
+  </si>
+  <si>
     <t>co2_Warsaw_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/29115701-220 (Warsaw, 9 km)</t>
   </si>
   <si>
-    <t>co2_Gliwice_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/293489607-400 (Katowice, 21 km)</t>
+    <t>co2_Belchatow_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/293484891-400 (Piotrkow Trybunalski, 26 km)</t>
   </si>
   <si>
     <t>co2_Elk_POL</t>
@@ -2234,6 +2390,12 @@
   </si>
   <si>
     <t>co2 captured at grid node -- way/336990960-220 (Opole, 7 km)</t>
+  </si>
+  <si>
+    <t>co2_Lodz_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/35366436-220 (Lodz, 8 km)</t>
   </si>
   <si>
     <t>co2_Szczecin_POL</t>
@@ -4862,13 +5024,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BB39D3-7AE7-42DD-AB2E-54745AEDE01E}">
-  <dimension ref="B3:H82"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41DF7A7-016B-4C5C-8FC8-E80CFBD87664}">
+  <dimension ref="B3:H88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:8">
       <c r="B3" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4" spans="2:8">
@@ -4899,19 +5061,19 @@
         <v>192</v>
       </c>
       <c r="C5" t="s">
-        <v>652</v>
+        <v>694</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>653</v>
+        <v>695</v>
       </c>
       <c r="F5" t="s">
         <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H5" t="s">
         <v>195</v>
@@ -4922,19 +5084,19 @@
         <v>192</v>
       </c>
       <c r="C6" t="s">
-        <v>655</v>
+        <v>697</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>656</v>
+        <v>698</v>
       </c>
       <c r="F6" t="s">
         <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H6" t="s">
         <v>195</v>
@@ -4945,19 +5107,19 @@
         <v>192</v>
       </c>
       <c r="C7" t="s">
-        <v>657</v>
+        <v>699</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>658</v>
+        <v>700</v>
       </c>
       <c r="F7" t="s">
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H7" t="s">
         <v>195</v>
@@ -4968,19 +5130,19 @@
         <v>192</v>
       </c>
       <c r="C8" t="s">
-        <v>659</v>
+        <v>701</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>660</v>
+        <v>702</v>
       </c>
       <c r="F8" t="s">
         <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H8" t="s">
         <v>195</v>
@@ -4991,19 +5153,19 @@
         <v>192</v>
       </c>
       <c r="C9" t="s">
-        <v>661</v>
+        <v>703</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>662</v>
+        <v>704</v>
       </c>
       <c r="F9" t="s">
         <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H9" t="s">
         <v>195</v>
@@ -5014,19 +5176,19 @@
         <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>663</v>
+        <v>705</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>664</v>
+        <v>706</v>
       </c>
       <c r="F10" t="s">
         <v>26</v>
       </c>
       <c r="G10" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H10" t="s">
         <v>195</v>
@@ -5037,19 +5199,19 @@
         <v>192</v>
       </c>
       <c r="C11" t="s">
-        <v>665</v>
+        <v>707</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>666</v>
+        <v>708</v>
       </c>
       <c r="F11" t="s">
         <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H11" t="s">
         <v>195</v>
@@ -5060,19 +5222,19 @@
         <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>667</v>
+        <v>709</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>668</v>
+        <v>710</v>
       </c>
       <c r="F12" t="s">
         <v>26</v>
       </c>
       <c r="G12" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H12" t="s">
         <v>195</v>
@@ -5083,19 +5245,19 @@
         <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>669</v>
+        <v>711</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>670</v>
+        <v>712</v>
       </c>
       <c r="F13" t="s">
         <v>26</v>
       </c>
       <c r="G13" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H13" t="s">
         <v>195</v>
@@ -5106,19 +5268,19 @@
         <v>192</v>
       </c>
       <c r="C14" t="s">
-        <v>671</v>
+        <v>713</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>672</v>
+        <v>714</v>
       </c>
       <c r="F14" t="s">
         <v>26</v>
       </c>
       <c r="G14" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H14" t="s">
         <v>195</v>
@@ -5129,19 +5291,19 @@
         <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>673</v>
+        <v>715</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>674</v>
+        <v>716</v>
       </c>
       <c r="F15" t="s">
         <v>26</v>
       </c>
       <c r="G15" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H15" t="s">
         <v>195</v>
@@ -5152,19 +5314,19 @@
         <v>192</v>
       </c>
       <c r="C16" t="s">
-        <v>675</v>
+        <v>717</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>676</v>
+        <v>718</v>
       </c>
       <c r="F16" t="s">
         <v>26</v>
       </c>
       <c r="G16" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H16" t="s">
         <v>195</v>
@@ -5175,19 +5337,19 @@
         <v>192</v>
       </c>
       <c r="C17" t="s">
-        <v>677</v>
+        <v>719</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>678</v>
+        <v>720</v>
       </c>
       <c r="F17" t="s">
         <v>26</v>
       </c>
       <c r="G17" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H17" t="s">
         <v>195</v>
@@ -5198,19 +5360,19 @@
         <v>192</v>
       </c>
       <c r="C18" t="s">
-        <v>679</v>
+        <v>721</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>680</v>
+        <v>722</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
       </c>
       <c r="G18" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H18" t="s">
         <v>195</v>
@@ -5221,19 +5383,19 @@
         <v>192</v>
       </c>
       <c r="C19" t="s">
-        <v>681</v>
+        <v>723</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>682</v>
+        <v>724</v>
       </c>
       <c r="F19" t="s">
         <v>26</v>
       </c>
       <c r="G19" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H19" t="s">
         <v>195</v>
@@ -5244,19 +5406,19 @@
         <v>192</v>
       </c>
       <c r="C20" t="s">
-        <v>683</v>
+        <v>725</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>684</v>
+        <v>726</v>
       </c>
       <c r="F20" t="s">
         <v>26</v>
       </c>
       <c r="G20" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H20" t="s">
         <v>195</v>
@@ -5267,19 +5429,19 @@
         <v>192</v>
       </c>
       <c r="C21" t="s">
-        <v>685</v>
+        <v>727</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>686</v>
+        <v>728</v>
       </c>
       <c r="F21" t="s">
         <v>26</v>
       </c>
       <c r="G21" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H21" t="s">
         <v>195</v>
@@ -5290,19 +5452,19 @@
         <v>192</v>
       </c>
       <c r="C22" t="s">
-        <v>687</v>
+        <v>729</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>688</v>
+        <v>730</v>
       </c>
       <c r="F22" t="s">
         <v>26</v>
       </c>
       <c r="G22" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H22" t="s">
         <v>195</v>
@@ -5313,19 +5475,19 @@
         <v>192</v>
       </c>
       <c r="C23" t="s">
-        <v>689</v>
+        <v>731</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>690</v>
+        <v>732</v>
       </c>
       <c r="F23" t="s">
         <v>26</v>
       </c>
       <c r="G23" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H23" t="s">
         <v>195</v>
@@ -5336,19 +5498,19 @@
         <v>192</v>
       </c>
       <c r="C24" t="s">
-        <v>691</v>
+        <v>733</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>692</v>
+        <v>734</v>
       </c>
       <c r="F24" t="s">
         <v>26</v>
       </c>
       <c r="G24" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H24" t="s">
         <v>195</v>
@@ -5359,19 +5521,19 @@
         <v>192</v>
       </c>
       <c r="C25" t="s">
-        <v>693</v>
+        <v>735</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>694</v>
+        <v>736</v>
       </c>
       <c r="F25" t="s">
         <v>26</v>
       </c>
       <c r="G25" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H25" t="s">
         <v>195</v>
@@ -5382,19 +5544,19 @@
         <v>192</v>
       </c>
       <c r="C26" t="s">
-        <v>695</v>
+        <v>737</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>696</v>
+        <v>738</v>
       </c>
       <c r="F26" t="s">
         <v>26</v>
       </c>
       <c r="G26" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H26" t="s">
         <v>195</v>
@@ -5405,19 +5567,19 @@
         <v>192</v>
       </c>
       <c r="C27" t="s">
-        <v>697</v>
+        <v>739</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>698</v>
+        <v>740</v>
       </c>
       <c r="F27" t="s">
         <v>26</v>
       </c>
       <c r="G27" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H27" t="s">
         <v>195</v>
@@ -5428,19 +5590,19 @@
         <v>192</v>
       </c>
       <c r="C28" t="s">
-        <v>699</v>
+        <v>741</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>700</v>
+        <v>742</v>
       </c>
       <c r="F28" t="s">
         <v>26</v>
       </c>
       <c r="G28" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H28" t="s">
         <v>195</v>
@@ -5451,19 +5613,19 @@
         <v>192</v>
       </c>
       <c r="C29" t="s">
-        <v>701</v>
+        <v>743</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>702</v>
+        <v>744</v>
       </c>
       <c r="F29" t="s">
         <v>26</v>
       </c>
       <c r="G29" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H29" t="s">
         <v>195</v>
@@ -5474,19 +5636,19 @@
         <v>192</v>
       </c>
       <c r="C30" t="s">
-        <v>703</v>
+        <v>745</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>704</v>
+        <v>746</v>
       </c>
       <c r="F30" t="s">
         <v>26</v>
       </c>
       <c r="G30" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H30" t="s">
         <v>195</v>
@@ -5497,19 +5659,19 @@
         <v>192</v>
       </c>
       <c r="C31" t="s">
-        <v>705</v>
+        <v>747</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>706</v>
+        <v>748</v>
       </c>
       <c r="F31" t="s">
         <v>26</v>
       </c>
       <c r="G31" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H31" t="s">
         <v>195</v>
@@ -5520,19 +5682,19 @@
         <v>192</v>
       </c>
       <c r="C32" t="s">
-        <v>707</v>
+        <v>749</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>708</v>
+        <v>750</v>
       </c>
       <c r="F32" t="s">
         <v>26</v>
       </c>
       <c r="G32" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H32" t="s">
         <v>195</v>
@@ -5543,19 +5705,19 @@
         <v>192</v>
       </c>
       <c r="C33" t="s">
-        <v>709</v>
+        <v>751</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>710</v>
+        <v>752</v>
       </c>
       <c r="F33" t="s">
         <v>26</v>
       </c>
       <c r="G33" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H33" t="s">
         <v>195</v>
@@ -5566,19 +5728,19 @@
         <v>192</v>
       </c>
       <c r="C34" t="s">
-        <v>711</v>
+        <v>753</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>712</v>
+        <v>754</v>
       </c>
       <c r="F34" t="s">
         <v>26</v>
       </c>
       <c r="G34" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H34" t="s">
         <v>195</v>
@@ -5589,19 +5751,19 @@
         <v>192</v>
       </c>
       <c r="C35" t="s">
-        <v>713</v>
+        <v>755</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>714</v>
+        <v>756</v>
       </c>
       <c r="F35" t="s">
         <v>26</v>
       </c>
       <c r="G35" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H35" t="s">
         <v>195</v>
@@ -5612,19 +5774,19 @@
         <v>192</v>
       </c>
       <c r="C36" t="s">
-        <v>715</v>
+        <v>757</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>716</v>
+        <v>758</v>
       </c>
       <c r="F36" t="s">
         <v>26</v>
       </c>
       <c r="G36" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H36" t="s">
         <v>195</v>
@@ -5635,19 +5797,19 @@
         <v>192</v>
       </c>
       <c r="C37" t="s">
-        <v>717</v>
+        <v>759</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>718</v>
+        <v>760</v>
       </c>
       <c r="F37" t="s">
         <v>26</v>
       </c>
       <c r="G37" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H37" t="s">
         <v>195</v>
@@ -5658,19 +5820,19 @@
         <v>192</v>
       </c>
       <c r="C38" t="s">
-        <v>719</v>
+        <v>761</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>720</v>
+        <v>762</v>
       </c>
       <c r="F38" t="s">
         <v>26</v>
       </c>
       <c r="G38" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H38" t="s">
         <v>195</v>
@@ -5681,19 +5843,19 @@
         <v>192</v>
       </c>
       <c r="C39" t="s">
-        <v>721</v>
+        <v>763</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>722</v>
+        <v>764</v>
       </c>
       <c r="F39" t="s">
         <v>26</v>
       </c>
       <c r="G39" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H39" t="s">
         <v>195</v>
@@ -5704,19 +5866,19 @@
         <v>192</v>
       </c>
       <c r="C40" t="s">
-        <v>723</v>
+        <v>765</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>724</v>
+        <v>766</v>
       </c>
       <c r="F40" t="s">
         <v>26</v>
       </c>
       <c r="G40" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H40" t="s">
         <v>195</v>
@@ -5727,19 +5889,19 @@
         <v>192</v>
       </c>
       <c r="C41" t="s">
-        <v>725</v>
+        <v>767</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>726</v>
+        <v>768</v>
       </c>
       <c r="F41" t="s">
         <v>26</v>
       </c>
       <c r="G41" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H41" t="s">
         <v>195</v>
@@ -5750,19 +5912,19 @@
         <v>192</v>
       </c>
       <c r="C42" t="s">
-        <v>727</v>
+        <v>769</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>728</v>
+        <v>770</v>
       </c>
       <c r="F42" t="s">
         <v>26</v>
       </c>
       <c r="G42" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H42" t="s">
         <v>195</v>
@@ -5773,19 +5935,19 @@
         <v>192</v>
       </c>
       <c r="C43" t="s">
-        <v>729</v>
+        <v>771</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>730</v>
+        <v>772</v>
       </c>
       <c r="F43" t="s">
         <v>26</v>
       </c>
       <c r="G43" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H43" t="s">
         <v>195</v>
@@ -5796,19 +5958,19 @@
         <v>192</v>
       </c>
       <c r="C44" t="s">
-        <v>731</v>
+        <v>773</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>732</v>
+        <v>774</v>
       </c>
       <c r="F44" t="s">
         <v>26</v>
       </c>
       <c r="G44" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H44" t="s">
         <v>195</v>
@@ -5819,19 +5981,19 @@
         <v>192</v>
       </c>
       <c r="C45" t="s">
-        <v>733</v>
+        <v>775</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>734</v>
+        <v>776</v>
       </c>
       <c r="F45" t="s">
         <v>26</v>
       </c>
       <c r="G45" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H45" t="s">
         <v>195</v>
@@ -5842,19 +6004,19 @@
         <v>192</v>
       </c>
       <c r="C46" t="s">
-        <v>735</v>
+        <v>777</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>736</v>
+        <v>778</v>
       </c>
       <c r="F46" t="s">
         <v>26</v>
       </c>
       <c r="G46" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H46" t="s">
         <v>195</v>
@@ -5865,19 +6027,19 @@
         <v>192</v>
       </c>
       <c r="C47" t="s">
-        <v>737</v>
+        <v>779</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>738</v>
+        <v>780</v>
       </c>
       <c r="F47" t="s">
         <v>26</v>
       </c>
       <c r="G47" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H47" t="s">
         <v>195</v>
@@ -5888,19 +6050,19 @@
         <v>192</v>
       </c>
       <c r="C48" t="s">
-        <v>739</v>
+        <v>781</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>740</v>
+        <v>782</v>
       </c>
       <c r="F48" t="s">
         <v>26</v>
       </c>
       <c r="G48" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H48" t="s">
         <v>195</v>
@@ -5911,19 +6073,19 @@
         <v>192</v>
       </c>
       <c r="C49" t="s">
-        <v>741</v>
+        <v>783</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>742</v>
+        <v>784</v>
       </c>
       <c r="F49" t="s">
         <v>26</v>
       </c>
       <c r="G49" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H49" t="s">
         <v>195</v>
@@ -5934,19 +6096,19 @@
         <v>192</v>
       </c>
       <c r="C50" t="s">
-        <v>743</v>
+        <v>785</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>744</v>
+        <v>786</v>
       </c>
       <c r="F50" t="s">
         <v>26</v>
       </c>
       <c r="G50" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H50" t="s">
         <v>195</v>
@@ -5957,19 +6119,19 @@
         <v>192</v>
       </c>
       <c r="C51" t="s">
-        <v>745</v>
+        <v>787</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>746</v>
+        <v>788</v>
       </c>
       <c r="F51" t="s">
         <v>26</v>
       </c>
       <c r="G51" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H51" t="s">
         <v>195</v>
@@ -5980,19 +6142,19 @@
         <v>192</v>
       </c>
       <c r="C52" t="s">
-        <v>747</v>
+        <v>789</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>748</v>
+        <v>790</v>
       </c>
       <c r="F52" t="s">
         <v>26</v>
       </c>
       <c r="G52" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H52" t="s">
         <v>195</v>
@@ -6003,19 +6165,19 @@
         <v>192</v>
       </c>
       <c r="C53" t="s">
-        <v>749</v>
+        <v>791</v>
       </c>
       <c r="D53" t="s">
         <v>243</v>
       </c>
       <c r="E53" t="s">
-        <v>750</v>
+        <v>792</v>
       </c>
       <c r="F53" t="s">
         <v>26</v>
       </c>
       <c r="G53" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H53" t="s">
         <v>195</v>
@@ -6026,19 +6188,19 @@
         <v>192</v>
       </c>
       <c r="C54" t="s">
-        <v>751</v>
+        <v>793</v>
       </c>
       <c r="D54" t="s">
         <v>243</v>
       </c>
       <c r="E54" t="s">
-        <v>752</v>
+        <v>794</v>
       </c>
       <c r="F54" t="s">
         <v>26</v>
       </c>
       <c r="G54" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H54" t="s">
         <v>195</v>
@@ -6049,19 +6211,19 @@
         <v>192</v>
       </c>
       <c r="C55" t="s">
-        <v>753</v>
+        <v>795</v>
       </c>
       <c r="D55" t="s">
         <v>243</v>
       </c>
       <c r="E55" t="s">
-        <v>754</v>
+        <v>796</v>
       </c>
       <c r="F55" t="s">
         <v>26</v>
       </c>
       <c r="G55" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H55" t="s">
         <v>195</v>
@@ -6072,19 +6234,19 @@
         <v>192</v>
       </c>
       <c r="C56" t="s">
-        <v>755</v>
+        <v>797</v>
       </c>
       <c r="D56" t="s">
         <v>243</v>
       </c>
       <c r="E56" t="s">
-        <v>756</v>
+        <v>798</v>
       </c>
       <c r="F56" t="s">
         <v>26</v>
       </c>
       <c r="G56" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H56" t="s">
         <v>195</v>
@@ -6095,19 +6257,19 @@
         <v>192</v>
       </c>
       <c r="C57" t="s">
-        <v>757</v>
+        <v>799</v>
       </c>
       <c r="D57" t="s">
         <v>243</v>
       </c>
       <c r="E57" t="s">
-        <v>758</v>
+        <v>800</v>
       </c>
       <c r="F57" t="s">
         <v>26</v>
       </c>
       <c r="G57" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H57" t="s">
         <v>195</v>
@@ -6118,19 +6280,19 @@
         <v>192</v>
       </c>
       <c r="C58" t="s">
-        <v>759</v>
+        <v>801</v>
       </c>
       <c r="D58" t="s">
         <v>243</v>
       </c>
       <c r="E58" t="s">
-        <v>760</v>
+        <v>802</v>
       </c>
       <c r="F58" t="s">
         <v>26</v>
       </c>
       <c r="G58" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H58" t="s">
         <v>195</v>
@@ -6141,19 +6303,19 @@
         <v>192</v>
       </c>
       <c r="C59" t="s">
-        <v>761</v>
+        <v>803</v>
       </c>
       <c r="D59" t="s">
         <v>243</v>
       </c>
       <c r="E59" t="s">
-        <v>762</v>
+        <v>804</v>
       </c>
       <c r="F59" t="s">
         <v>26</v>
       </c>
       <c r="G59" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H59" t="s">
         <v>195</v>
@@ -6164,19 +6326,19 @@
         <v>192</v>
       </c>
       <c r="C60" t="s">
-        <v>763</v>
+        <v>805</v>
       </c>
       <c r="D60" t="s">
         <v>243</v>
       </c>
       <c r="E60" t="s">
-        <v>764</v>
+        <v>806</v>
       </c>
       <c r="F60" t="s">
         <v>26</v>
       </c>
       <c r="G60" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H60" t="s">
         <v>195</v>
@@ -6187,19 +6349,19 @@
         <v>192</v>
       </c>
       <c r="C61" t="s">
-        <v>765</v>
+        <v>807</v>
       </c>
       <c r="D61" t="s">
         <v>243</v>
       </c>
       <c r="E61" t="s">
-        <v>766</v>
+        <v>808</v>
       </c>
       <c r="F61" t="s">
         <v>26</v>
       </c>
       <c r="G61" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H61" t="s">
         <v>195</v>
@@ -6210,19 +6372,19 @@
         <v>192</v>
       </c>
       <c r="C62" t="s">
-        <v>767</v>
+        <v>809</v>
       </c>
       <c r="D62" t="s">
         <v>243</v>
       </c>
       <c r="E62" t="s">
-        <v>768</v>
+        <v>810</v>
       </c>
       <c r="F62" t="s">
         <v>26</v>
       </c>
       <c r="G62" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H62" t="s">
         <v>195</v>
@@ -6233,19 +6395,19 @@
         <v>192</v>
       </c>
       <c r="C63" t="s">
-        <v>769</v>
+        <v>811</v>
       </c>
       <c r="D63" t="s">
         <v>243</v>
       </c>
       <c r="E63" t="s">
-        <v>770</v>
+        <v>812</v>
       </c>
       <c r="F63" t="s">
         <v>26</v>
       </c>
       <c r="G63" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H63" t="s">
         <v>195</v>
@@ -6256,19 +6418,19 @@
         <v>192</v>
       </c>
       <c r="C64" t="s">
-        <v>771</v>
+        <v>813</v>
       </c>
       <c r="D64" t="s">
         <v>243</v>
       </c>
       <c r="E64" t="s">
-        <v>772</v>
+        <v>814</v>
       </c>
       <c r="F64" t="s">
         <v>26</v>
       </c>
       <c r="G64" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H64" t="s">
         <v>195</v>
@@ -6279,19 +6441,19 @@
         <v>192</v>
       </c>
       <c r="C65" t="s">
-        <v>773</v>
+        <v>815</v>
       </c>
       <c r="D65" t="s">
         <v>243</v>
       </c>
       <c r="E65" t="s">
-        <v>774</v>
+        <v>816</v>
       </c>
       <c r="F65" t="s">
         <v>26</v>
       </c>
       <c r="G65" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H65" t="s">
         <v>195</v>
@@ -6302,19 +6464,19 @@
         <v>192</v>
       </c>
       <c r="C66" t="s">
-        <v>775</v>
+        <v>817</v>
       </c>
       <c r="D66" t="s">
         <v>243</v>
       </c>
       <c r="E66" t="s">
-        <v>776</v>
+        <v>818</v>
       </c>
       <c r="F66" t="s">
         <v>26</v>
       </c>
       <c r="G66" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H66" t="s">
         <v>195</v>
@@ -6325,19 +6487,19 @@
         <v>192</v>
       </c>
       <c r="C67" t="s">
-        <v>777</v>
+        <v>819</v>
       </c>
       <c r="D67" t="s">
         <v>243</v>
       </c>
       <c r="E67" t="s">
-        <v>778</v>
+        <v>820</v>
       </c>
       <c r="F67" t="s">
         <v>26</v>
       </c>
       <c r="G67" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H67" t="s">
         <v>195</v>
@@ -6348,19 +6510,19 @@
         <v>192</v>
       </c>
       <c r="C68" t="s">
-        <v>779</v>
+        <v>821</v>
       </c>
       <c r="D68" t="s">
         <v>243</v>
       </c>
       <c r="E68" t="s">
-        <v>780</v>
+        <v>822</v>
       </c>
       <c r="F68" t="s">
         <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H68" t="s">
         <v>195</v>
@@ -6371,19 +6533,19 @@
         <v>192</v>
       </c>
       <c r="C69" t="s">
-        <v>781</v>
+        <v>823</v>
       </c>
       <c r="D69" t="s">
         <v>243</v>
       </c>
       <c r="E69" t="s">
-        <v>782</v>
+        <v>824</v>
       </c>
       <c r="F69" t="s">
         <v>26</v>
       </c>
       <c r="G69" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H69" t="s">
         <v>195</v>
@@ -6394,19 +6556,19 @@
         <v>192</v>
       </c>
       <c r="C70" t="s">
-        <v>783</v>
+        <v>825</v>
       </c>
       <c r="D70" t="s">
         <v>243</v>
       </c>
       <c r="E70" t="s">
-        <v>784</v>
+        <v>826</v>
       </c>
       <c r="F70" t="s">
         <v>26</v>
       </c>
       <c r="G70" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H70" t="s">
         <v>195</v>
@@ -6417,19 +6579,19 @@
         <v>192</v>
       </c>
       <c r="C71" t="s">
-        <v>785</v>
+        <v>827</v>
       </c>
       <c r="D71" t="s">
         <v>243</v>
       </c>
       <c r="E71" t="s">
-        <v>786</v>
+        <v>828</v>
       </c>
       <c r="F71" t="s">
         <v>26</v>
       </c>
       <c r="G71" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H71" t="s">
         <v>195</v>
@@ -6440,19 +6602,19 @@
         <v>192</v>
       </c>
       <c r="C72" t="s">
-        <v>787</v>
+        <v>829</v>
       </c>
       <c r="D72" t="s">
         <v>243</v>
       </c>
       <c r="E72" t="s">
-        <v>788</v>
+        <v>830</v>
       </c>
       <c r="F72" t="s">
         <v>26</v>
       </c>
       <c r="G72" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H72" t="s">
         <v>195</v>
@@ -6463,19 +6625,19 @@
         <v>192</v>
       </c>
       <c r="C73" t="s">
-        <v>789</v>
+        <v>831</v>
       </c>
       <c r="D73" t="s">
         <v>243</v>
       </c>
       <c r="E73" t="s">
-        <v>790</v>
+        <v>832</v>
       </c>
       <c r="F73" t="s">
         <v>26</v>
       </c>
       <c r="G73" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H73" t="s">
         <v>195</v>
@@ -6486,19 +6648,19 @@
         <v>192</v>
       </c>
       <c r="C74" t="s">
-        <v>791</v>
+        <v>833</v>
       </c>
       <c r="D74" t="s">
         <v>243</v>
       </c>
       <c r="E74" t="s">
-        <v>792</v>
+        <v>834</v>
       </c>
       <c r="F74" t="s">
         <v>26</v>
       </c>
       <c r="G74" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H74" t="s">
         <v>195</v>
@@ -6509,19 +6671,19 @@
         <v>192</v>
       </c>
       <c r="C75" t="s">
-        <v>793</v>
+        <v>835</v>
       </c>
       <c r="D75" t="s">
         <v>243</v>
       </c>
       <c r="E75" t="s">
-        <v>794</v>
+        <v>836</v>
       </c>
       <c r="F75" t="s">
         <v>26</v>
       </c>
       <c r="G75" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H75" t="s">
         <v>195</v>
@@ -6532,19 +6694,19 @@
         <v>192</v>
       </c>
       <c r="C76" t="s">
-        <v>795</v>
+        <v>837</v>
       </c>
       <c r="D76" t="s">
         <v>243</v>
       </c>
       <c r="E76" t="s">
-        <v>796</v>
+        <v>838</v>
       </c>
       <c r="F76" t="s">
         <v>26</v>
       </c>
       <c r="G76" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H76" t="s">
         <v>195</v>
@@ -6555,19 +6717,19 @@
         <v>192</v>
       </c>
       <c r="C77" t="s">
-        <v>797</v>
+        <v>839</v>
       </c>
       <c r="D77" t="s">
         <v>243</v>
       </c>
       <c r="E77" t="s">
-        <v>798</v>
+        <v>840</v>
       </c>
       <c r="F77" t="s">
         <v>26</v>
       </c>
       <c r="G77" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H77" t="s">
         <v>195</v>
@@ -6578,19 +6740,19 @@
         <v>192</v>
       </c>
       <c r="C78" t="s">
-        <v>799</v>
+        <v>841</v>
       </c>
       <c r="D78" t="s">
         <v>243</v>
       </c>
       <c r="E78" t="s">
-        <v>800</v>
+        <v>842</v>
       </c>
       <c r="F78" t="s">
         <v>26</v>
       </c>
       <c r="G78" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H78" t="s">
         <v>195</v>
@@ -6601,19 +6763,19 @@
         <v>192</v>
       </c>
       <c r="C79" t="s">
-        <v>801</v>
+        <v>843</v>
       </c>
       <c r="D79" t="s">
         <v>243</v>
       </c>
       <c r="E79" t="s">
-        <v>802</v>
+        <v>844</v>
       </c>
       <c r="F79" t="s">
         <v>26</v>
       </c>
       <c r="G79" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H79" t="s">
         <v>195</v>
@@ -6624,19 +6786,19 @@
         <v>192</v>
       </c>
       <c r="C80" t="s">
-        <v>803</v>
+        <v>845</v>
       </c>
       <c r="D80" t="s">
         <v>243</v>
       </c>
       <c r="E80" t="s">
-        <v>804</v>
+        <v>846</v>
       </c>
       <c r="F80" t="s">
         <v>26</v>
       </c>
       <c r="G80" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H80" t="s">
         <v>195</v>
@@ -6647,19 +6809,19 @@
         <v>192</v>
       </c>
       <c r="C81" t="s">
-        <v>805</v>
+        <v>847</v>
       </c>
       <c r="D81" t="s">
         <v>243</v>
       </c>
       <c r="E81" t="s">
-        <v>806</v>
+        <v>848</v>
       </c>
       <c r="F81" t="s">
         <v>26</v>
       </c>
       <c r="G81" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H81" t="s">
         <v>195</v>
@@ -6670,21 +6832,159 @@
         <v>192</v>
       </c>
       <c r="C82" t="s">
-        <v>807</v>
+        <v>849</v>
       </c>
       <c r="D82" t="s">
         <v>243</v>
       </c>
       <c r="E82" t="s">
-        <v>808</v>
+        <v>850</v>
       </c>
       <c r="F82" t="s">
         <v>26</v>
       </c>
       <c r="G82" t="s">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="H82" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8">
+      <c r="B83" t="s">
+        <v>192</v>
+      </c>
+      <c r="C83" t="s">
+        <v>851</v>
+      </c>
+      <c r="D83" t="s">
+        <v>243</v>
+      </c>
+      <c r="E83" t="s">
+        <v>852</v>
+      </c>
+      <c r="F83" t="s">
+        <v>26</v>
+      </c>
+      <c r="G83" t="s">
+        <v>696</v>
+      </c>
+      <c r="H83" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8">
+      <c r="B84" t="s">
+        <v>192</v>
+      </c>
+      <c r="C84" t="s">
+        <v>853</v>
+      </c>
+      <c r="D84" t="s">
+        <v>243</v>
+      </c>
+      <c r="E84" t="s">
+        <v>854</v>
+      </c>
+      <c r="F84" t="s">
+        <v>26</v>
+      </c>
+      <c r="G84" t="s">
+        <v>696</v>
+      </c>
+      <c r="H84" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8">
+      <c r="B85" t="s">
+        <v>192</v>
+      </c>
+      <c r="C85" t="s">
+        <v>855</v>
+      </c>
+      <c r="D85" t="s">
+        <v>243</v>
+      </c>
+      <c r="E85" t="s">
+        <v>856</v>
+      </c>
+      <c r="F85" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" t="s">
+        <v>696</v>
+      </c>
+      <c r="H85" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8">
+      <c r="B86" t="s">
+        <v>192</v>
+      </c>
+      <c r="C86" t="s">
+        <v>857</v>
+      </c>
+      <c r="D86" t="s">
+        <v>243</v>
+      </c>
+      <c r="E86" t="s">
+        <v>858</v>
+      </c>
+      <c r="F86" t="s">
+        <v>26</v>
+      </c>
+      <c r="G86" t="s">
+        <v>696</v>
+      </c>
+      <c r="H86" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8">
+      <c r="B87" t="s">
+        <v>192</v>
+      </c>
+      <c r="C87" t="s">
+        <v>859</v>
+      </c>
+      <c r="D87" t="s">
+        <v>243</v>
+      </c>
+      <c r="E87" t="s">
+        <v>860</v>
+      </c>
+      <c r="F87" t="s">
+        <v>26</v>
+      </c>
+      <c r="G87" t="s">
+        <v>696</v>
+      </c>
+      <c r="H87" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
+      <c r="B88" t="s">
+        <v>192</v>
+      </c>
+      <c r="C88" t="s">
+        <v>861</v>
+      </c>
+      <c r="D88" t="s">
+        <v>243</v>
+      </c>
+      <c r="E88" t="s">
+        <v>862</v>
+      </c>
+      <c r="F88" t="s">
+        <v>26</v>
+      </c>
+      <c r="G88" t="s">
+        <v>696</v>
+      </c>
+      <c r="H88" t="s">
         <v>195</v>
       </c>
     </row>
@@ -6694,13 +6994,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A46E409C-4182-48B0-B466-C4065EF3FDB5}">
-  <dimension ref="B3:I52"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173D60C4-1EDD-4E33-A5A0-D1B3C9BCA5A5}">
+  <dimension ref="B3:I58"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -6734,13 +7034,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>556</v>
+        <v>586</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>557</v>
+        <v>587</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -6749,7 +7049,7 @@
         <v>232</v>
       </c>
       <c r="H5" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I5" t="s">
         <v>247</v>
@@ -6760,13 +7060,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>558</v>
+        <v>588</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>559</v>
+        <v>589</v>
       </c>
       <c r="F6" t="s">
         <v>233</v>
@@ -6775,7 +7075,7 @@
         <v>232</v>
       </c>
       <c r="H6" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I6" t="s">
         <v>247</v>
@@ -6786,13 +7086,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>560</v>
+        <v>590</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>561</v>
+        <v>591</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -6801,7 +7101,7 @@
         <v>232</v>
       </c>
       <c r="H7" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I7" t="s">
         <v>247</v>
@@ -6812,13 +7112,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>562</v>
+        <v>592</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>563</v>
+        <v>593</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -6827,7 +7127,7 @@
         <v>232</v>
       </c>
       <c r="H8" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I8" t="s">
         <v>247</v>
@@ -6838,13 +7138,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>564</v>
+        <v>594</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>565</v>
+        <v>595</v>
       </c>
       <c r="F9" t="s">
         <v>233</v>
@@ -6853,7 +7153,7 @@
         <v>232</v>
       </c>
       <c r="H9" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I9" t="s">
         <v>247</v>
@@ -6864,13 +7164,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>566</v>
+        <v>596</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>567</v>
+        <v>597</v>
       </c>
       <c r="F10" t="s">
         <v>233</v>
@@ -6879,7 +7179,7 @@
         <v>232</v>
       </c>
       <c r="H10" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I10" t="s">
         <v>247</v>
@@ -6890,13 +7190,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>568</v>
+        <v>598</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>569</v>
+        <v>599</v>
       </c>
       <c r="F11" t="s">
         <v>233</v>
@@ -6905,7 +7205,7 @@
         <v>232</v>
       </c>
       <c r="H11" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I11" t="s">
         <v>247</v>
@@ -6916,13 +7216,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>570</v>
+        <v>600</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>571</v>
+        <v>601</v>
       </c>
       <c r="F12" t="s">
         <v>233</v>
@@ -6931,7 +7231,7 @@
         <v>232</v>
       </c>
       <c r="H12" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I12" t="s">
         <v>247</v>
@@ -6942,13 +7242,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>572</v>
+        <v>602</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>573</v>
+        <v>603</v>
       </c>
       <c r="F13" t="s">
         <v>233</v>
@@ -6957,7 +7257,7 @@
         <v>232</v>
       </c>
       <c r="H13" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I13" t="s">
         <v>247</v>
@@ -6968,13 +7268,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>574</v>
+        <v>604</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>575</v>
+        <v>605</v>
       </c>
       <c r="F14" t="s">
         <v>233</v>
@@ -6983,7 +7283,7 @@
         <v>232</v>
       </c>
       <c r="H14" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I14" t="s">
         <v>247</v>
@@ -6994,13 +7294,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>576</v>
+        <v>606</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>577</v>
+        <v>607</v>
       </c>
       <c r="F15" t="s">
         <v>233</v>
@@ -7009,7 +7309,7 @@
         <v>232</v>
       </c>
       <c r="H15" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I15" t="s">
         <v>247</v>
@@ -7020,13 +7320,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>578</v>
+        <v>608</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>579</v>
+        <v>609</v>
       </c>
       <c r="F16" t="s">
         <v>233</v>
@@ -7035,7 +7335,7 @@
         <v>232</v>
       </c>
       <c r="H16" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I16" t="s">
         <v>247</v>
@@ -7046,13 +7346,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>580</v>
+        <v>610</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>581</v>
+        <v>611</v>
       </c>
       <c r="F17" t="s">
         <v>233</v>
@@ -7061,7 +7361,7 @@
         <v>232</v>
       </c>
       <c r="H17" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I17" t="s">
         <v>247</v>
@@ -7072,13 +7372,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>582</v>
+        <v>612</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>583</v>
+        <v>613</v>
       </c>
       <c r="F18" t="s">
         <v>233</v>
@@ -7087,7 +7387,7 @@
         <v>232</v>
       </c>
       <c r="H18" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I18" t="s">
         <v>247</v>
@@ -7098,13 +7398,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>584</v>
+        <v>614</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>585</v>
+        <v>615</v>
       </c>
       <c r="F19" t="s">
         <v>233</v>
@@ -7113,7 +7413,7 @@
         <v>232</v>
       </c>
       <c r="H19" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I19" t="s">
         <v>247</v>
@@ -7124,13 +7424,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>586</v>
+        <v>616</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>587</v>
+        <v>617</v>
       </c>
       <c r="F20" t="s">
         <v>233</v>
@@ -7139,7 +7439,7 @@
         <v>232</v>
       </c>
       <c r="H20" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I20" t="s">
         <v>247</v>
@@ -7150,13 +7450,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>588</v>
+        <v>618</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>589</v>
+        <v>619</v>
       </c>
       <c r="F21" t="s">
         <v>233</v>
@@ -7165,7 +7465,7 @@
         <v>232</v>
       </c>
       <c r="H21" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I21" t="s">
         <v>247</v>
@@ -7176,13 +7476,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>590</v>
+        <v>620</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>591</v>
+        <v>621</v>
       </c>
       <c r="F22" t="s">
         <v>233</v>
@@ -7191,7 +7491,7 @@
         <v>232</v>
       </c>
       <c r="H22" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I22" t="s">
         <v>247</v>
@@ -7202,13 +7502,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>592</v>
+        <v>622</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>593</v>
+        <v>623</v>
       </c>
       <c r="F23" t="s">
         <v>233</v>
@@ -7217,7 +7517,7 @@
         <v>232</v>
       </c>
       <c r="H23" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I23" t="s">
         <v>247</v>
@@ -7228,13 +7528,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>594</v>
+        <v>624</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>595</v>
+        <v>625</v>
       </c>
       <c r="F24" t="s">
         <v>233</v>
@@ -7243,7 +7543,7 @@
         <v>232</v>
       </c>
       <c r="H24" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I24" t="s">
         <v>247</v>
@@ -7254,13 +7554,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>596</v>
+        <v>626</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>597</v>
+        <v>627</v>
       </c>
       <c r="F25" t="s">
         <v>233</v>
@@ -7269,7 +7569,7 @@
         <v>232</v>
       </c>
       <c r="H25" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I25" t="s">
         <v>247</v>
@@ -7280,13 +7580,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>598</v>
+        <v>628</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>599</v>
+        <v>629</v>
       </c>
       <c r="F26" t="s">
         <v>233</v>
@@ -7295,7 +7595,7 @@
         <v>232</v>
       </c>
       <c r="H26" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I26" t="s">
         <v>247</v>
@@ -7306,13 +7606,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>601</v>
+        <v>631</v>
       </c>
       <c r="F27" t="s">
         <v>233</v>
@@ -7321,7 +7621,7 @@
         <v>232</v>
       </c>
       <c r="H27" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I27" t="s">
         <v>247</v>
@@ -7332,13 +7632,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>602</v>
+        <v>632</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>603</v>
+        <v>633</v>
       </c>
       <c r="F28" t="s">
         <v>233</v>
@@ -7347,7 +7647,7 @@
         <v>232</v>
       </c>
       <c r="H28" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I28" t="s">
         <v>247</v>
@@ -7358,13 +7658,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>604</v>
+        <v>634</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>605</v>
+        <v>635</v>
       </c>
       <c r="F29" t="s">
         <v>233</v>
@@ -7373,7 +7673,7 @@
         <v>232</v>
       </c>
       <c r="H29" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I29" t="s">
         <v>247</v>
@@ -7384,13 +7684,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>606</v>
+        <v>636</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>607</v>
+        <v>637</v>
       </c>
       <c r="F30" t="s">
         <v>233</v>
@@ -7399,7 +7699,7 @@
         <v>232</v>
       </c>
       <c r="H30" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I30" t="s">
         <v>247</v>
@@ -7410,13 +7710,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>608</v>
+        <v>638</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>609</v>
+        <v>639</v>
       </c>
       <c r="F31" t="s">
         <v>233</v>
@@ -7425,7 +7725,7 @@
         <v>232</v>
       </c>
       <c r="H31" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I31" t="s">
         <v>247</v>
@@ -7436,13 +7736,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>610</v>
+        <v>640</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>611</v>
+        <v>641</v>
       </c>
       <c r="F32" t="s">
         <v>233</v>
@@ -7451,7 +7751,7 @@
         <v>232</v>
       </c>
       <c r="H32" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I32" t="s">
         <v>247</v>
@@ -7462,13 +7762,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>612</v>
+        <v>642</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>613</v>
+        <v>643</v>
       </c>
       <c r="F33" t="s">
         <v>233</v>
@@ -7477,7 +7777,7 @@
         <v>232</v>
       </c>
       <c r="H33" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I33" t="s">
         <v>247</v>
@@ -7488,13 +7788,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>614</v>
+        <v>644</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>615</v>
+        <v>645</v>
       </c>
       <c r="F34" t="s">
         <v>233</v>
@@ -7503,7 +7803,7 @@
         <v>232</v>
       </c>
       <c r="H34" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I34" t="s">
         <v>247</v>
@@ -7514,13 +7814,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>616</v>
+        <v>646</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>617</v>
+        <v>647</v>
       </c>
       <c r="F35" t="s">
         <v>233</v>
@@ -7529,7 +7829,7 @@
         <v>232</v>
       </c>
       <c r="H35" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I35" t="s">
         <v>247</v>
@@ -7540,13 +7840,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>618</v>
+        <v>648</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>619</v>
+        <v>649</v>
       </c>
       <c r="F36" t="s">
         <v>233</v>
@@ -7555,7 +7855,7 @@
         <v>232</v>
       </c>
       <c r="H36" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I36" t="s">
         <v>247</v>
@@ -7566,13 +7866,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>620</v>
+        <v>650</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>621</v>
+        <v>651</v>
       </c>
       <c r="F37" t="s">
         <v>233</v>
@@ -7581,7 +7881,7 @@
         <v>232</v>
       </c>
       <c r="H37" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I37" t="s">
         <v>247</v>
@@ -7592,13 +7892,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>622</v>
+        <v>652</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>623</v>
+        <v>653</v>
       </c>
       <c r="F38" t="s">
         <v>233</v>
@@ -7607,7 +7907,7 @@
         <v>232</v>
       </c>
       <c r="H38" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I38" t="s">
         <v>247</v>
@@ -7618,13 +7918,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>624</v>
+        <v>654</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="F39" t="s">
         <v>233</v>
@@ -7633,7 +7933,7 @@
         <v>232</v>
       </c>
       <c r="H39" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I39" t="s">
         <v>247</v>
@@ -7644,13 +7944,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>627</v>
+        <v>657</v>
       </c>
       <c r="F40" t="s">
         <v>233</v>
@@ -7659,7 +7959,7 @@
         <v>232</v>
       </c>
       <c r="H40" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I40" t="s">
         <v>247</v>
@@ -7670,13 +7970,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>628</v>
+        <v>658</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>629</v>
+        <v>659</v>
       </c>
       <c r="F41" t="s">
         <v>233</v>
@@ -7685,7 +7985,7 @@
         <v>232</v>
       </c>
       <c r="H41" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I41" t="s">
         <v>247</v>
@@ -7696,13 +7996,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>630</v>
+        <v>660</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="F42" t="s">
         <v>233</v>
@@ -7711,7 +8011,7 @@
         <v>232</v>
       </c>
       <c r="H42" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I42" t="s">
         <v>247</v>
@@ -7722,13 +8022,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>632</v>
+        <v>662</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>633</v>
+        <v>663</v>
       </c>
       <c r="F43" t="s">
         <v>233</v>
@@ -7737,7 +8037,7 @@
         <v>232</v>
       </c>
       <c r="H43" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I43" t="s">
         <v>247</v>
@@ -7748,13 +8048,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>634</v>
+        <v>664</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>635</v>
+        <v>665</v>
       </c>
       <c r="F44" t="s">
         <v>233</v>
@@ -7763,7 +8063,7 @@
         <v>232</v>
       </c>
       <c r="H44" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I44" t="s">
         <v>247</v>
@@ -7774,13 +8074,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>636</v>
+        <v>666</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>637</v>
+        <v>667</v>
       </c>
       <c r="F45" t="s">
         <v>233</v>
@@ -7789,7 +8089,7 @@
         <v>232</v>
       </c>
       <c r="H45" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I45" t="s">
         <v>247</v>
@@ -7800,13 +8100,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>638</v>
+        <v>668</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>639</v>
+        <v>669</v>
       </c>
       <c r="F46" t="s">
         <v>233</v>
@@ -7815,7 +8115,7 @@
         <v>232</v>
       </c>
       <c r="H46" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I46" t="s">
         <v>247</v>
@@ -7826,13 +8126,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>641</v>
+        <v>671</v>
       </c>
       <c r="F47" t="s">
         <v>233</v>
@@ -7841,7 +8141,7 @@
         <v>232</v>
       </c>
       <c r="H47" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I47" t="s">
         <v>247</v>
@@ -7852,13 +8152,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>642</v>
+        <v>672</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>643</v>
+        <v>673</v>
       </c>
       <c r="F48" t="s">
         <v>233</v>
@@ -7867,7 +8167,7 @@
         <v>232</v>
       </c>
       <c r="H48" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I48" t="s">
         <v>247</v>
@@ -7878,13 +8178,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>644</v>
+        <v>674</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>645</v>
+        <v>675</v>
       </c>
       <c r="F49" t="s">
         <v>233</v>
@@ -7893,7 +8193,7 @@
         <v>232</v>
       </c>
       <c r="H49" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I49" t="s">
         <v>247</v>
@@ -7904,13 +8204,13 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>646</v>
+        <v>676</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>647</v>
+        <v>677</v>
       </c>
       <c r="F50" t="s">
         <v>233</v>
@@ -7919,7 +8219,7 @@
         <v>232</v>
       </c>
       <c r="H50" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I50" t="s">
         <v>247</v>
@@ -7930,13 +8230,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>648</v>
+        <v>678</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>649</v>
+        <v>679</v>
       </c>
       <c r="F51" t="s">
         <v>233</v>
@@ -7945,7 +8245,7 @@
         <v>232</v>
       </c>
       <c r="H51" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I51" t="s">
         <v>247</v>
@@ -7956,13 +8256,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>651</v>
+        <v>681</v>
       </c>
       <c r="F52" t="s">
         <v>233</v>
@@ -7971,9 +8271,165 @@
         <v>232</v>
       </c>
       <c r="H52" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I52" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9">
+      <c r="B53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" t="s">
+        <v>682</v>
+      </c>
+      <c r="D53" t="s">
+        <v>243</v>
+      </c>
+      <c r="E53" t="s">
+        <v>683</v>
+      </c>
+      <c r="F53" t="s">
+        <v>233</v>
+      </c>
+      <c r="G53" t="s">
+        <v>232</v>
+      </c>
+      <c r="H53" t="s">
+        <v>479</v>
+      </c>
+      <c r="I53" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9">
+      <c r="B54" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" t="s">
+        <v>684</v>
+      </c>
+      <c r="D54" t="s">
+        <v>243</v>
+      </c>
+      <c r="E54" t="s">
+        <v>685</v>
+      </c>
+      <c r="F54" t="s">
+        <v>233</v>
+      </c>
+      <c r="G54" t="s">
+        <v>232</v>
+      </c>
+      <c r="H54" t="s">
+        <v>479</v>
+      </c>
+      <c r="I54" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9">
+      <c r="B55" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" t="s">
+        <v>686</v>
+      </c>
+      <c r="D55" t="s">
+        <v>243</v>
+      </c>
+      <c r="E55" t="s">
+        <v>687</v>
+      </c>
+      <c r="F55" t="s">
+        <v>233</v>
+      </c>
+      <c r="G55" t="s">
+        <v>232</v>
+      </c>
+      <c r="H55" t="s">
+        <v>479</v>
+      </c>
+      <c r="I55" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9">
+      <c r="B56" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" t="s">
+        <v>688</v>
+      </c>
+      <c r="D56" t="s">
+        <v>243</v>
+      </c>
+      <c r="E56" t="s">
+        <v>689</v>
+      </c>
+      <c r="F56" t="s">
+        <v>233</v>
+      </c>
+      <c r="G56" t="s">
+        <v>232</v>
+      </c>
+      <c r="H56" t="s">
+        <v>479</v>
+      </c>
+      <c r="I56" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9">
+      <c r="B57" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" t="s">
+        <v>690</v>
+      </c>
+      <c r="D57" t="s">
+        <v>243</v>
+      </c>
+      <c r="E57" t="s">
+        <v>691</v>
+      </c>
+      <c r="F57" t="s">
+        <v>233</v>
+      </c>
+      <c r="G57" t="s">
+        <v>232</v>
+      </c>
+      <c r="H57" t="s">
+        <v>479</v>
+      </c>
+      <c r="I57" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9">
+      <c r="B58" t="s">
+        <v>17</v>
+      </c>
+      <c r="C58" t="s">
+        <v>692</v>
+      </c>
+      <c r="D58" t="s">
+        <v>243</v>
+      </c>
+      <c r="E58" t="s">
+        <v>693</v>
+      </c>
+      <c r="F58" t="s">
+        <v>233</v>
+      </c>
+      <c r="G58" t="s">
+        <v>232</v>
+      </c>
+      <c r="H58" t="s">
+        <v>479</v>
+      </c>
+      <c r="I58" t="s">
         <v>247</v>
       </c>
     </row>
@@ -7983,13 +8439,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5D17DB3-C2F4-4CBA-BFEB-6A66F35FFD15}">
-  <dimension ref="B3:I52"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7C2996D-7C8A-4807-9219-540F0AA625C5}">
+  <dimension ref="B3:I58"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -8023,13 +8479,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>460</v>
+        <v>478</v>
       </c>
       <c r="F5" t="s">
         <v>25</v>
@@ -8038,7 +8494,7 @@
         <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I5" t="s">
         <v>247</v>
@@ -8049,13 +8505,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="F6" t="s">
         <v>25</v>
@@ -8064,7 +8520,7 @@
         <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I6" t="s">
         <v>247</v>
@@ -8075,13 +8531,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="F7" t="s">
         <v>25</v>
@@ -8090,7 +8546,7 @@
         <v>35</v>
       </c>
       <c r="H7" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I7" t="s">
         <v>247</v>
@@ -8101,13 +8557,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="F8" t="s">
         <v>25</v>
@@ -8116,7 +8572,7 @@
         <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I8" t="s">
         <v>247</v>
@@ -8127,13 +8583,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>468</v>
+        <v>486</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="F9" t="s">
         <v>25</v>
@@ -8142,7 +8598,7 @@
         <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I9" t="s">
         <v>247</v>
@@ -8153,13 +8609,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="F10" t="s">
         <v>25</v>
@@ -8168,7 +8624,7 @@
         <v>35</v>
       </c>
       <c r="H10" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I10" t="s">
         <v>247</v>
@@ -8179,13 +8635,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>472</v>
+        <v>490</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
@@ -8194,7 +8650,7 @@
         <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I11" t="s">
         <v>247</v>
@@ -8205,13 +8661,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="F12" t="s">
         <v>25</v>
@@ -8220,7 +8676,7 @@
         <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I12" t="s">
         <v>247</v>
@@ -8231,13 +8687,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="F13" t="s">
         <v>25</v>
@@ -8246,7 +8702,7 @@
         <v>35</v>
       </c>
       <c r="H13" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I13" t="s">
         <v>247</v>
@@ -8257,22 +8713,22 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
+        <v>497</v>
+      </c>
+      <c r="F14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" t="s">
         <v>479</v>
-      </c>
-      <c r="F14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" t="s">
-        <v>35</v>
-      </c>
-      <c r="H14" t="s">
-        <v>461</v>
       </c>
       <c r="I14" t="s">
         <v>247</v>
@@ -8283,13 +8739,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="F15" t="s">
         <v>25</v>
@@ -8298,7 +8754,7 @@
         <v>35</v>
       </c>
       <c r="H15" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I15" t="s">
         <v>247</v>
@@ -8309,13 +8765,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="F16" t="s">
         <v>25</v>
@@ -8324,7 +8780,7 @@
         <v>35</v>
       </c>
       <c r="H16" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I16" t="s">
         <v>247</v>
@@ -8335,13 +8791,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="F17" t="s">
         <v>25</v>
@@ -8350,7 +8806,7 @@
         <v>35</v>
       </c>
       <c r="H17" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I17" t="s">
         <v>247</v>
@@ -8361,13 +8817,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="F18" t="s">
         <v>25</v>
@@ -8376,7 +8832,7 @@
         <v>35</v>
       </c>
       <c r="H18" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I18" t="s">
         <v>247</v>
@@ -8387,13 +8843,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="F19" t="s">
         <v>25</v>
@@ -8402,7 +8858,7 @@
         <v>35</v>
       </c>
       <c r="H19" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I19" t="s">
         <v>247</v>
@@ -8413,13 +8869,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="F20" t="s">
         <v>25</v>
@@ -8428,7 +8884,7 @@
         <v>35</v>
       </c>
       <c r="H20" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I20" t="s">
         <v>247</v>
@@ -8439,13 +8895,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="F21" t="s">
         <v>25</v>
@@ -8454,7 +8910,7 @@
         <v>35</v>
       </c>
       <c r="H21" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I21" t="s">
         <v>247</v>
@@ -8465,13 +8921,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="F22" t="s">
         <v>25</v>
@@ -8480,7 +8936,7 @@
         <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I22" t="s">
         <v>247</v>
@@ -8491,13 +8947,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="F23" t="s">
         <v>25</v>
@@ -8506,7 +8962,7 @@
         <v>35</v>
       </c>
       <c r="H23" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I23" t="s">
         <v>247</v>
@@ -8517,13 +8973,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="F24" t="s">
         <v>25</v>
@@ -8532,7 +8988,7 @@
         <v>35</v>
       </c>
       <c r="H24" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I24" t="s">
         <v>247</v>
@@ -8543,13 +8999,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>500</v>
+        <v>518</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>501</v>
+        <v>519</v>
       </c>
       <c r="F25" t="s">
         <v>25</v>
@@ -8558,7 +9014,7 @@
         <v>35</v>
       </c>
       <c r="H25" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I25" t="s">
         <v>247</v>
@@ -8569,13 +9025,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>502</v>
+        <v>520</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>503</v>
+        <v>521</v>
       </c>
       <c r="F26" t="s">
         <v>25</v>
@@ -8584,7 +9040,7 @@
         <v>35</v>
       </c>
       <c r="H26" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I26" t="s">
         <v>247</v>
@@ -8595,13 +9051,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>504</v>
+        <v>522</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>505</v>
+        <v>523</v>
       </c>
       <c r="F27" t="s">
         <v>25</v>
@@ -8610,7 +9066,7 @@
         <v>35</v>
       </c>
       <c r="H27" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I27" t="s">
         <v>247</v>
@@ -8621,13 +9077,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="F28" t="s">
         <v>25</v>
@@ -8636,7 +9092,7 @@
         <v>35</v>
       </c>
       <c r="H28" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I28" t="s">
         <v>247</v>
@@ -8647,13 +9103,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>508</v>
+        <v>526</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>509</v>
+        <v>527</v>
       </c>
       <c r="F29" t="s">
         <v>25</v>
@@ -8662,7 +9118,7 @@
         <v>35</v>
       </c>
       <c r="H29" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I29" t="s">
         <v>247</v>
@@ -8673,13 +9129,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>511</v>
+        <v>529</v>
       </c>
       <c r="F30" t="s">
         <v>25</v>
@@ -8688,7 +9144,7 @@
         <v>35</v>
       </c>
       <c r="H30" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I30" t="s">
         <v>247</v>
@@ -8699,13 +9155,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>512</v>
+        <v>530</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>513</v>
+        <v>531</v>
       </c>
       <c r="F31" t="s">
         <v>25</v>
@@ -8714,7 +9170,7 @@
         <v>35</v>
       </c>
       <c r="H31" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I31" t="s">
         <v>247</v>
@@ -8725,13 +9181,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="F32" t="s">
         <v>25</v>
@@ -8740,7 +9196,7 @@
         <v>35</v>
       </c>
       <c r="H32" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I32" t="s">
         <v>247</v>
@@ -8751,13 +9207,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="F33" t="s">
         <v>25</v>
@@ -8766,7 +9222,7 @@
         <v>35</v>
       </c>
       <c r="H33" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I33" t="s">
         <v>247</v>
@@ -8777,13 +9233,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="F34" t="s">
         <v>25</v>
@@ -8792,7 +9248,7 @@
         <v>35</v>
       </c>
       <c r="H34" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I34" t="s">
         <v>247</v>
@@ -8803,13 +9259,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="F35" t="s">
         <v>25</v>
@@ -8818,7 +9274,7 @@
         <v>35</v>
       </c>
       <c r="H35" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I35" t="s">
         <v>247</v>
@@ -8829,13 +9285,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="F36" t="s">
         <v>25</v>
@@ -8844,7 +9300,7 @@
         <v>35</v>
       </c>
       <c r="H36" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I36" t="s">
         <v>247</v>
@@ -8855,13 +9311,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>524</v>
+        <v>542</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>525</v>
+        <v>543</v>
       </c>
       <c r="F37" t="s">
         <v>25</v>
@@ -8870,7 +9326,7 @@
         <v>35</v>
       </c>
       <c r="H37" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I37" t="s">
         <v>247</v>
@@ -8881,13 +9337,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>526</v>
+        <v>544</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="F38" t="s">
         <v>25</v>
@@ -8896,7 +9352,7 @@
         <v>35</v>
       </c>
       <c r="H38" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I38" t="s">
         <v>247</v>
@@ -8907,13 +9363,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>528</v>
+        <v>546</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
       <c r="F39" t="s">
         <v>25</v>
@@ -8922,7 +9378,7 @@
         <v>35</v>
       </c>
       <c r="H39" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I39" t="s">
         <v>247</v>
@@ -8933,13 +9389,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>530</v>
+        <v>548</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>531</v>
+        <v>549</v>
       </c>
       <c r="F40" t="s">
         <v>25</v>
@@ -8948,7 +9404,7 @@
         <v>35</v>
       </c>
       <c r="H40" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I40" t="s">
         <v>247</v>
@@ -8959,13 +9415,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>532</v>
+        <v>550</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="F41" t="s">
         <v>25</v>
@@ -8974,7 +9430,7 @@
         <v>35</v>
       </c>
       <c r="H41" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I41" t="s">
         <v>247</v>
@@ -8985,13 +9441,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="F42" t="s">
         <v>25</v>
@@ -9000,7 +9456,7 @@
         <v>35</v>
       </c>
       <c r="H42" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I42" t="s">
         <v>247</v>
@@ -9011,13 +9467,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>536</v>
+        <v>554</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="F43" t="s">
         <v>25</v>
@@ -9026,7 +9482,7 @@
         <v>35</v>
       </c>
       <c r="H43" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I43" t="s">
         <v>247</v>
@@ -9037,13 +9493,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>539</v>
+        <v>557</v>
       </c>
       <c r="F44" t="s">
         <v>25</v>
@@ -9052,7 +9508,7 @@
         <v>35</v>
       </c>
       <c r="H44" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I44" t="s">
         <v>247</v>
@@ -9063,13 +9519,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="F45" t="s">
         <v>25</v>
@@ -9078,7 +9534,7 @@
         <v>35</v>
       </c>
       <c r="H45" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I45" t="s">
         <v>247</v>
@@ -9089,13 +9545,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>542</v>
+        <v>560</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="F46" t="s">
         <v>25</v>
@@ -9104,7 +9560,7 @@
         <v>35</v>
       </c>
       <c r="H46" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I46" t="s">
         <v>247</v>
@@ -9115,13 +9571,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>544</v>
+        <v>562</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>545</v>
+        <v>563</v>
       </c>
       <c r="F47" t="s">
         <v>25</v>
@@ -9130,7 +9586,7 @@
         <v>35</v>
       </c>
       <c r="H47" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I47" t="s">
         <v>247</v>
@@ -9141,13 +9597,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>546</v>
+        <v>564</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="F48" t="s">
         <v>25</v>
@@ -9156,7 +9612,7 @@
         <v>35</v>
       </c>
       <c r="H48" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I48" t="s">
         <v>247</v>
@@ -9167,13 +9623,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>548</v>
+        <v>566</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="F49" t="s">
         <v>25</v>
@@ -9182,7 +9638,7 @@
         <v>35</v>
       </c>
       <c r="H49" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I49" t="s">
         <v>247</v>
@@ -9193,13 +9649,13 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
       <c r="F50" t="s">
         <v>25</v>
@@ -9208,7 +9664,7 @@
         <v>35</v>
       </c>
       <c r="H50" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I50" t="s">
         <v>247</v>
@@ -9219,13 +9675,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>552</v>
+        <v>570</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>553</v>
+        <v>571</v>
       </c>
       <c r="F51" t="s">
         <v>25</v>
@@ -9234,7 +9690,7 @@
         <v>35</v>
       </c>
       <c r="H51" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I51" t="s">
         <v>247</v>
@@ -9245,13 +9701,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
       <c r="F52" t="s">
         <v>25</v>
@@ -9260,9 +9716,165 @@
         <v>35</v>
       </c>
       <c r="H52" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="I52" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9">
+      <c r="B53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" t="s">
+        <v>574</v>
+      </c>
+      <c r="D53" t="s">
+        <v>243</v>
+      </c>
+      <c r="E53" t="s">
+        <v>575</v>
+      </c>
+      <c r="F53" t="s">
+        <v>25</v>
+      </c>
+      <c r="G53" t="s">
+        <v>35</v>
+      </c>
+      <c r="H53" t="s">
+        <v>479</v>
+      </c>
+      <c r="I53" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9">
+      <c r="B54" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" t="s">
+        <v>576</v>
+      </c>
+      <c r="D54" t="s">
+        <v>243</v>
+      </c>
+      <c r="E54" t="s">
+        <v>577</v>
+      </c>
+      <c r="F54" t="s">
+        <v>25</v>
+      </c>
+      <c r="G54" t="s">
+        <v>35</v>
+      </c>
+      <c r="H54" t="s">
+        <v>479</v>
+      </c>
+      <c r="I54" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9">
+      <c r="B55" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" t="s">
+        <v>578</v>
+      </c>
+      <c r="D55" t="s">
+        <v>243</v>
+      </c>
+      <c r="E55" t="s">
+        <v>579</v>
+      </c>
+      <c r="F55" t="s">
+        <v>25</v>
+      </c>
+      <c r="G55" t="s">
+        <v>35</v>
+      </c>
+      <c r="H55" t="s">
+        <v>479</v>
+      </c>
+      <c r="I55" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9">
+      <c r="B56" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" t="s">
+        <v>580</v>
+      </c>
+      <c r="D56" t="s">
+        <v>243</v>
+      </c>
+      <c r="E56" t="s">
+        <v>581</v>
+      </c>
+      <c r="F56" t="s">
+        <v>25</v>
+      </c>
+      <c r="G56" t="s">
+        <v>35</v>
+      </c>
+      <c r="H56" t="s">
+        <v>479</v>
+      </c>
+      <c r="I56" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9">
+      <c r="B57" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" t="s">
+        <v>582</v>
+      </c>
+      <c r="D57" t="s">
+        <v>243</v>
+      </c>
+      <c r="E57" t="s">
+        <v>583</v>
+      </c>
+      <c r="F57" t="s">
+        <v>25</v>
+      </c>
+      <c r="G57" t="s">
+        <v>35</v>
+      </c>
+      <c r="H57" t="s">
+        <v>479</v>
+      </c>
+      <c r="I57" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9">
+      <c r="B58" t="s">
+        <v>17</v>
+      </c>
+      <c r="C58" t="s">
+        <v>584</v>
+      </c>
+      <c r="D58" t="s">
+        <v>243</v>
+      </c>
+      <c r="E58" t="s">
+        <v>585</v>
+      </c>
+      <c r="F58" t="s">
+        <v>25</v>
+      </c>
+      <c r="G58" t="s">
+        <v>35</v>
+      </c>
+      <c r="H58" t="s">
+        <v>479</v>
+      </c>
+      <c r="I58" t="s">
         <v>247</v>
       </c>
     </row>
@@ -9273,7 +9885,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:S110"/>
+  <dimension ref="B3:S119"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
@@ -12172,6 +12784,213 @@
         <v>35</v>
       </c>
       <c r="S110" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="111" spans="13:19">
+      <c r="M111" t="s">
+        <v>17</v>
+      </c>
+      <c r="N111" t="s">
+        <v>458</v>
+      </c>
+      <c r="O111" t="s">
+        <v>243</v>
+      </c>
+      <c r="P111" t="s">
+        <v>459</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>25</v>
+      </c>
+      <c r="R111" t="s">
+        <v>35</v>
+      </c>
+      <c r="S111" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="112" spans="13:19">
+      <c r="M112" t="s">
+        <v>17</v>
+      </c>
+      <c r="N112" t="s">
+        <v>460</v>
+      </c>
+      <c r="O112" t="s">
+        <v>243</v>
+      </c>
+      <c r="P112" t="s">
+        <v>461</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>25</v>
+      </c>
+      <c r="R112" t="s">
+        <v>35</v>
+      </c>
+      <c r="S112" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="113" spans="13:19">
+      <c r="M113" t="s">
+        <v>17</v>
+      </c>
+      <c r="N113" t="s">
+        <v>462</v>
+      </c>
+      <c r="O113" t="s">
+        <v>243</v>
+      </c>
+      <c r="P113" t="s">
+        <v>463</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>25</v>
+      </c>
+      <c r="R113" t="s">
+        <v>35</v>
+      </c>
+      <c r="S113" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="114" spans="13:19">
+      <c r="M114" t="s">
+        <v>17</v>
+      </c>
+      <c r="N114" t="s">
+        <v>464</v>
+      </c>
+      <c r="O114" t="s">
+        <v>243</v>
+      </c>
+      <c r="P114" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>25</v>
+      </c>
+      <c r="R114" t="s">
+        <v>35</v>
+      </c>
+      <c r="S114" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="115" spans="13:19">
+      <c r="M115" t="s">
+        <v>17</v>
+      </c>
+      <c r="N115" t="s">
+        <v>466</v>
+      </c>
+      <c r="O115" t="s">
+        <v>243</v>
+      </c>
+      <c r="P115" t="s">
+        <v>467</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>25</v>
+      </c>
+      <c r="R115" t="s">
+        <v>35</v>
+      </c>
+      <c r="S115" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="116" spans="13:19">
+      <c r="M116" t="s">
+        <v>17</v>
+      </c>
+      <c r="N116" t="s">
+        <v>468</v>
+      </c>
+      <c r="O116" t="s">
+        <v>243</v>
+      </c>
+      <c r="P116" t="s">
+        <v>469</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>25</v>
+      </c>
+      <c r="R116" t="s">
+        <v>35</v>
+      </c>
+      <c r="S116" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="117" spans="13:19">
+      <c r="M117" t="s">
+        <v>17</v>
+      </c>
+      <c r="N117" t="s">
+        <v>470</v>
+      </c>
+      <c r="O117" t="s">
+        <v>243</v>
+      </c>
+      <c r="P117" t="s">
+        <v>471</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>25</v>
+      </c>
+      <c r="R117" t="s">
+        <v>35</v>
+      </c>
+      <c r="S117" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="118" spans="13:19">
+      <c r="M118" t="s">
+        <v>17</v>
+      </c>
+      <c r="N118" t="s">
+        <v>472</v>
+      </c>
+      <c r="O118" t="s">
+        <v>243</v>
+      </c>
+      <c r="P118" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>25</v>
+      </c>
+      <c r="R118" t="s">
+        <v>35</v>
+      </c>
+      <c r="S118" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="119" spans="13:19">
+      <c r="M119" t="s">
+        <v>17</v>
+      </c>
+      <c r="N119" t="s">
+        <v>474</v>
+      </c>
+      <c r="O119" t="s">
+        <v>243</v>
+      </c>
+      <c r="P119" t="s">
+        <v>475</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>25</v>
+      </c>
+      <c r="R119" t="s">
+        <v>35</v>
+      </c>
+      <c r="S119" t="s">
         <v>247</v>
       </c>
     </row>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60225B4E-5D77-46C1-98BD-2AF06001E2FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C33DEAE-2EF3-4DDD-90CE-19B037717A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2892" uniqueCount="863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2713" uniqueCount="813">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -832,7 +832,7 @@
     <t>elc_spv_POL_009</t>
   </si>
   <si>
-    <t>solar electricity near Slupsk (cluster 9)</t>
+    <t>solar electricity near Koszalin (cluster 9)</t>
   </si>
   <si>
     <t>elc_spv_POL_010</t>
@@ -856,295 +856,283 @@
     <t>elc_spv_POL_013</t>
   </si>
   <si>
-    <t>solar electricity near Warsaw (cluster 13)</t>
+    <t>solar electricity near Lomza (cluster 13)</t>
   </si>
   <si>
     <t>elc_spv_POL_014</t>
   </si>
   <si>
-    <t>solar electricity near Lomza (cluster 14)</t>
+    <t>solar electricity near Zielona Gora (cluster 14)</t>
   </si>
   <si>
     <t>elc_spv_POL_015</t>
   </si>
   <si>
-    <t>solar electricity near Zielona Gora (cluster 15)</t>
+    <t>solar electricity near Szczecin (cluster 15)</t>
   </si>
   <si>
     <t>elc_spv_POL_016</t>
   </si>
   <si>
-    <t>solar electricity near Szczecin (cluster 16)</t>
+    <t>solar electricity near Lublin (cluster 16)</t>
   </si>
   <si>
     <t>elc_spv_POL_017</t>
   </si>
   <si>
-    <t>solar electricity near Lublin (cluster 17)</t>
+    <t>solar electricity near Suwalki (cluster 17)</t>
   </si>
   <si>
     <t>elc_spv_POL_018</t>
   </si>
   <si>
-    <t>solar electricity near Suwalki (cluster 18)</t>
+    <t>solar electricity near Zamosc (cluster 18)</t>
   </si>
   <si>
     <t>elc_spv_POL_019</t>
   </si>
   <si>
-    <t>solar electricity near Zamosc (cluster 19)</t>
+    <t>solar electricity near Czestochowa (cluster 19)</t>
   </si>
   <si>
     <t>elc_spv_POL_020</t>
   </si>
   <si>
-    <t>solar electricity near Czestochowa (cluster 20)</t>
+    <t>solar electricity near Warsaw (cluster 20)</t>
   </si>
   <si>
     <t>elc_spv_POL_021</t>
   </si>
   <si>
-    <t>solar electricity near Warsaw (cluster 21)</t>
+    <t>solar electricity near Lubin (cluster 21)</t>
   </si>
   <si>
     <t>elc_spv_POL_022</t>
   </si>
   <si>
-    <t>solar electricity near Koszalin (cluster 22)</t>
+    <t>solar electricity near Bielsko-Biala (cluster 22)</t>
   </si>
   <si>
     <t>elc_spv_POL_023</t>
   </si>
   <si>
-    <t>solar electricity near Lubin (cluster 23)</t>
+    <t>solar electricity near Krakow (cluster 23)</t>
   </si>
   <si>
     <t>elc_spv_POL_024</t>
   </si>
   <si>
-    <t>solar electricity near Gliwice (cluster 24)</t>
+    <t>solar electricity near Tarnow (cluster 24)</t>
   </si>
   <si>
     <t>elc_spv_POL_025</t>
   </si>
   <si>
-    <t>solar electricity near Tarnow (cluster 25)</t>
+    <t>solar electricity near Chelm (cluster 25)</t>
   </si>
   <si>
     <t>elc_spv_POL_026</t>
   </si>
   <si>
-    <t>solar electricity near Chelm (cluster 26)</t>
+    <t>solar electricity near Kielce (cluster 26)</t>
   </si>
   <si>
     <t>elc_spv_POL_027</t>
   </si>
   <si>
-    <t>solar electricity near Kielce (cluster 27)</t>
+    <t>solar electricity near Tarnow (cluster 27)</t>
   </si>
   <si>
     <t>elc_spv_POL_028</t>
   </si>
   <si>
-    <t>solar electricity near Tarnow (cluster 28)</t>
+    <t>solar electricity near Rzeszow (cluster 28)</t>
   </si>
   <si>
     <t>elc_spv_POL_029</t>
   </si>
   <si>
-    <t>solar electricity near Rzeszow (cluster 29)</t>
+    <t>solar electricity near Czestochowa (cluster 29)</t>
   </si>
   <si>
     <t>elc_spv_POL_030</t>
   </si>
   <si>
-    <t>solar electricity near Czestochowa (cluster 30)</t>
+    <t>solar electricity near Pila (cluster 30)</t>
   </si>
   <si>
     <t>elc_spv_POL_031</t>
   </si>
   <si>
-    <t>solar electricity near Pila (cluster 31)</t>
+    <t>solar electricity near Ostrowiec Swietokrzyski (cluster 31)</t>
   </si>
   <si>
     <t>elc_spv_POL_032</t>
   </si>
   <si>
-    <t>solar electricity near Torun (cluster 32)</t>
+    <t>solar electricity near Wroclaw (cluster 32)</t>
   </si>
   <si>
     <t>elc_spv_POL_033</t>
   </si>
   <si>
-    <t>solar electricity near Ostrowiec Swietokrzyski (cluster 33)</t>
+    <t>solar electricity near Konin (cluster 33)</t>
   </si>
   <si>
     <t>elc_spv_POL_034</t>
   </si>
   <si>
-    <t>solar electricity near Wroclaw (cluster 34)</t>
+    <t>solar electricity near Kalisz (cluster 34)</t>
   </si>
   <si>
     <t>elc_spv_POL_035</t>
   </si>
   <si>
-    <t>solar electricity near Konin (cluster 35)</t>
+    <t>solar electricity near Walbrzych (cluster 35)</t>
   </si>
   <si>
     <t>elc_spv_POL_036</t>
   </si>
   <si>
-    <t>solar electricity near Kalisz (cluster 36)</t>
+    <t>solar electricity near Warsaw (cluster 36)</t>
   </si>
   <si>
     <t>elc_spv_POL_037</t>
   </si>
   <si>
-    <t>solar electricity near Koszalin (cluster 37)</t>
+    <t>solar electricity near Piotrkow Trybunalski (cluster 37)</t>
   </si>
   <si>
     <t>elc_spv_POL_038</t>
   </si>
   <si>
-    <t>solar electricity near Walbrzych (cluster 38)</t>
+    <t>solar electricity near Katowice (cluster 38)</t>
   </si>
   <si>
     <t>elc_spv_POL_039</t>
   </si>
   <si>
-    <t>solar electricity near Warsaw (cluster 39)</t>
+    <t>solar electricity near Lomza (cluster 39)</t>
   </si>
   <si>
     <t>elc_spv_POL_040</t>
   </si>
   <si>
-    <t>solar electricity near Piotrkow Trybunalski (cluster 40)</t>
+    <t>solar electricity near Poznan (cluster 40)</t>
   </si>
   <si>
     <t>elc_spv_POL_041</t>
   </si>
   <si>
-    <t>solar electricity near Lomza (cluster 41)</t>
+    <t>solar electricity near Opole (cluster 41)</t>
   </si>
   <si>
     <t>elc_spv_POL_042</t>
   </si>
   <si>
-    <t>solar electricity near Poznan (cluster 42)</t>
+    <t>solar electricity near Lodz (cluster 42)</t>
   </si>
   <si>
     <t>elc_spv_POL_043</t>
   </si>
   <si>
-    <t>solar electricity near Opole (cluster 43)</t>
+    <t>solar electricity near Szczecin (cluster 43)</t>
   </si>
   <si>
     <t>elc_spv_POL_044</t>
   </si>
   <si>
-    <t>solar electricity near Lodz (cluster 44)</t>
+    <t>solar electricity near Krakow (cluster 44)</t>
   </si>
   <si>
     <t>elc_spv_POL_045</t>
   </si>
   <si>
-    <t>solar electricity near Szczecin (cluster 45)</t>
+    <t>solar electricity near Krakow (cluster 45)</t>
   </si>
   <si>
     <t>elc_spv_POL_046</t>
   </si>
   <si>
-    <t>solar electricity near Krakow (cluster 46)</t>
+    <t>solar electricity near Grudziadz (cluster 46)</t>
   </si>
   <si>
     <t>elc_spv_POL_047</t>
   </si>
   <si>
-    <t>solar electricity near Krakow (cluster 47)</t>
+    <t>solar electricity near Plock (cluster 47)</t>
   </si>
   <si>
     <t>elc_spv_POL_048</t>
   </si>
   <si>
-    <t>solar electricity near Grudziadz (cluster 48)</t>
+    <t>solar electricity near Torun (cluster 48)</t>
   </si>
   <si>
     <t>elc_spv_POL_049</t>
   </si>
   <si>
-    <t>solar electricity near Plock (cluster 49)</t>
+    <t>solar electricity near Wroclaw (cluster 49)</t>
   </si>
   <si>
     <t>elc_spv_POL_050</t>
   </si>
   <si>
-    <t>solar electricity near Wroclaw (cluster 50)</t>
+    <t>solar electricity near Gdansk (cluster 50)</t>
   </si>
   <si>
     <t>elc_spv_POL_051</t>
   </si>
   <si>
-    <t>solar electricity near Gdansk (cluster 51)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_052</t>
-  </si>
-  <si>
-    <t>solar electricity near Krakow (cluster 52)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_053</t>
-  </si>
-  <si>
-    <t>solar electricity near Lublin (cluster 53)</t>
+    <t>solar electricity near Lublin (cluster 51)</t>
   </si>
   <si>
     <t>elc_wof_POL_001</t>
   </si>
   <si>
-    <t>wind offshore electricity near Gdansk (cluster 1)</t>
+    <t>wind offshore electricity near Koszalin (cluster 1)</t>
   </si>
   <si>
     <t>elc_wof_POL_002</t>
   </si>
   <si>
-    <t>wind offshore electricity near Gdansk (cluster 2)</t>
+    <t>wind offshore electricity near Koszalin (cluster 2)</t>
   </si>
   <si>
     <t>elc_wof_POL_003</t>
   </si>
   <si>
-    <t>wind offshore electricity near Szczecin (cluster 3)</t>
+    <t>wind offshore electricity near Koszalin (cluster 3)</t>
   </si>
   <si>
     <t>elc_wof_POL_004</t>
   </si>
   <si>
-    <t>wind offshore electricity near Koszalin (cluster 4)</t>
+    <t>wind offshore electricity near Gdansk (cluster 4)</t>
   </si>
   <si>
     <t>elc_wof_POL_005</t>
   </si>
   <si>
-    <t>wind offshore electricity near Koszalin (cluster 5)</t>
+    <t>wind offshore electricity near Gdansk (cluster 5)</t>
   </si>
   <si>
     <t>elc_wof_POL_006</t>
   </si>
   <si>
-    <t>wind offshore electricity near Koszalin (cluster 6)</t>
+    <t>wind offshore electricity near Szczecin (cluster 6)</t>
   </si>
   <si>
     <t>elc_wof_POL_007</t>
   </si>
   <si>
-    <t>wind offshore electricity near Slupsk (cluster 7)</t>
+    <t>wind offshore electricity near Gdynia (cluster 7)</t>
   </si>
   <si>
     <t>elc_wof_POL_008</t>
   </si>
   <si>
-    <t>wind offshore electricity near Gdynia (cluster 8)</t>
+    <t>wind offshore electricity near Gdansk (cluster 8)</t>
   </si>
   <si>
     <t>elc_wof_POL_009</t>
@@ -1210,7 +1198,7 @@
     <t>elc_won_POL_009</t>
   </si>
   <si>
-    <t>wind onshore electricity near Slupsk (cluster 9)</t>
+    <t>wind onshore electricity near Koszalin (cluster 9)</t>
   </si>
   <si>
     <t>elc_won_POL_010</t>
@@ -1234,241 +1222,223 @@
     <t>elc_won_POL_013</t>
   </si>
   <si>
-    <t>wind onshore electricity near Warsaw (cluster 13)</t>
+    <t>wind onshore electricity near Lomza (cluster 13)</t>
   </si>
   <si>
     <t>elc_won_POL_014</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lomza (cluster 14)</t>
+    <t>wind onshore electricity near Zielona Gora (cluster 14)</t>
   </si>
   <si>
     <t>elc_won_POL_015</t>
   </si>
   <si>
-    <t>wind onshore electricity near Zielona Gora (cluster 15)</t>
+    <t>wind onshore electricity near Szczecin (cluster 15)</t>
   </si>
   <si>
     <t>elc_won_POL_016</t>
   </si>
   <si>
-    <t>wind onshore electricity near Szczecin (cluster 16)</t>
+    <t>wind onshore electricity near Lublin (cluster 16)</t>
   </si>
   <si>
     <t>elc_won_POL_017</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lublin (cluster 17)</t>
+    <t>wind onshore electricity near Suwalki (cluster 17)</t>
   </si>
   <si>
     <t>elc_won_POL_018</t>
   </si>
   <si>
-    <t>wind onshore electricity near Suwalki (cluster 18)</t>
+    <t>wind onshore electricity near Zamosc (cluster 18)</t>
   </si>
   <si>
     <t>elc_won_POL_019</t>
   </si>
   <si>
-    <t>wind onshore electricity near Zamosc (cluster 19)</t>
+    <t>wind onshore electricity near Czestochowa (cluster 19)</t>
   </si>
   <si>
     <t>elc_won_POL_020</t>
   </si>
   <si>
-    <t>wind onshore electricity near Czestochowa (cluster 20)</t>
+    <t>wind onshore electricity near Warsaw (cluster 20)</t>
   </si>
   <si>
     <t>elc_won_POL_021</t>
   </si>
   <si>
-    <t>wind onshore electricity near Warsaw (cluster 21)</t>
+    <t>wind onshore electricity near Glogow (cluster 21)</t>
   </si>
   <si>
     <t>elc_won_POL_022</t>
   </si>
   <si>
-    <t>wind onshore electricity near Koszalin (cluster 22)</t>
+    <t>wind onshore electricity near Krakow (cluster 22)</t>
   </si>
   <si>
     <t>elc_won_POL_023</t>
   </si>
   <si>
-    <t>wind onshore electricity near Glogow (cluster 23)</t>
+    <t>wind onshore electricity near Tarnow (cluster 23)</t>
   </si>
   <si>
     <t>elc_won_POL_024</t>
   </si>
   <si>
-    <t>wind onshore electricity near Katowice (cluster 24)</t>
+    <t>wind onshore electricity near Chelm (cluster 24)</t>
   </si>
   <si>
     <t>elc_won_POL_025</t>
   </si>
   <si>
-    <t>wind onshore electricity near Tarnow (cluster 25)</t>
+    <t>wind onshore electricity near Radom (cluster 25)</t>
   </si>
   <si>
     <t>elc_won_POL_026</t>
   </si>
   <si>
-    <t>wind onshore electricity near Chelm (cluster 26)</t>
+    <t>wind onshore electricity near Mielec (cluster 26)</t>
   </si>
   <si>
     <t>elc_won_POL_027</t>
   </si>
   <si>
-    <t>wind onshore electricity near Radom (cluster 27)</t>
+    <t>wind onshore electricity near Rzeszow (cluster 27)</t>
   </si>
   <si>
     <t>elc_won_POL_028</t>
   </si>
   <si>
-    <t>wind onshore electricity near Mielec (cluster 28)</t>
+    <t>wind onshore electricity near Czestochowa (cluster 28)</t>
   </si>
   <si>
     <t>elc_won_POL_029</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rzeszow (cluster 29)</t>
+    <t>wind onshore electricity near Pila (cluster 29)</t>
   </si>
   <si>
     <t>elc_won_POL_030</t>
   </si>
   <si>
-    <t>wind onshore electricity near Czestochowa (cluster 30)</t>
+    <t>wind onshore electricity near Radom (cluster 30)</t>
   </si>
   <si>
     <t>elc_won_POL_031</t>
   </si>
   <si>
-    <t>wind onshore electricity near Pila (cluster 31)</t>
+    <t>wind onshore electricity near Opole (cluster 31)</t>
   </si>
   <si>
     <t>elc_won_POL_032</t>
   </si>
   <si>
-    <t>wind onshore electricity near Torun (cluster 32)</t>
+    <t>wind onshore electricity near Konin (cluster 32)</t>
   </si>
   <si>
     <t>elc_won_POL_033</t>
   </si>
   <si>
-    <t>wind onshore electricity near Radom (cluster 33)</t>
+    <t>wind onshore electricity near Kalisz (cluster 33)</t>
   </si>
   <si>
     <t>elc_won_POL_034</t>
   </si>
   <si>
-    <t>wind onshore electricity near Opole (cluster 34)</t>
+    <t>wind onshore electricity near Walbrzych (cluster 34)</t>
   </si>
   <si>
     <t>elc_won_POL_035</t>
   </si>
   <si>
-    <t>wind onshore electricity near Konin (cluster 35)</t>
+    <t>wind onshore electricity near Warsaw (cluster 35)</t>
   </si>
   <si>
     <t>elc_won_POL_036</t>
   </si>
   <si>
-    <t>wind onshore electricity near Kalisz (cluster 36)</t>
+    <t>wind onshore electricity near Piotrkow Trybunalski (cluster 36)</t>
   </si>
   <si>
     <t>elc_won_POL_037</t>
   </si>
   <si>
-    <t>wind onshore electricity near Koszalin (cluster 37)</t>
+    <t>wind onshore electricity near Katowice (cluster 37)</t>
   </si>
   <si>
     <t>elc_won_POL_038</t>
   </si>
   <si>
-    <t>wind onshore electricity near Walbrzych (cluster 38)</t>
+    <t>wind onshore electricity near Lomza (cluster 38)</t>
   </si>
   <si>
     <t>elc_won_POL_039</t>
   </si>
   <si>
-    <t>wind onshore electricity near Warsaw (cluster 39)</t>
+    <t>wind onshore electricity near Poznan (cluster 39)</t>
   </si>
   <si>
     <t>elc_won_POL_040</t>
   </si>
   <si>
-    <t>wind onshore electricity near Piotrkow Trybunalski (cluster 40)</t>
+    <t>wind onshore electricity near Kedzierzyn-Kozle (cluster 40)</t>
   </si>
   <si>
     <t>elc_won_POL_041</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lomza (cluster 41)</t>
+    <t>wind onshore electricity near Lodz (cluster 41)</t>
   </si>
   <si>
     <t>elc_won_POL_042</t>
   </si>
   <si>
-    <t>wind onshore electricity near Poznan (cluster 42)</t>
+    <t>wind onshore electricity near Szczecin (cluster 42)</t>
   </si>
   <si>
     <t>elc_won_POL_043</t>
   </si>
   <si>
-    <t>wind onshore electricity near Kedzierzyn-Kozle (cluster 43)</t>
+    <t>wind onshore electricity near Krakow (cluster 43)</t>
   </si>
   <si>
     <t>elc_won_POL_044</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lodz (cluster 44)</t>
+    <t>wind onshore electricity near Grudziadz (cluster 44)</t>
   </si>
   <si>
     <t>elc_won_POL_045</t>
   </si>
   <si>
-    <t>wind onshore electricity near Szczecin (cluster 45)</t>
+    <t>wind onshore electricity near Plock (cluster 45)</t>
   </si>
   <si>
     <t>elc_won_POL_046</t>
   </si>
   <si>
-    <t>wind onshore electricity near Krakow (cluster 46)</t>
+    <t>wind onshore electricity near Torun (cluster 46)</t>
   </si>
   <si>
     <t>elc_won_POL_047</t>
   </si>
   <si>
-    <t>wind onshore electricity near Grudziadz (cluster 47)</t>
+    <t>wind onshore electricity near Wroclaw (cluster 47)</t>
   </si>
   <si>
     <t>elc_won_POL_048</t>
   </si>
   <si>
-    <t>wind onshore electricity near Plock (cluster 48)</t>
+    <t>wind onshore electricity near Gdansk (cluster 48)</t>
   </si>
   <si>
     <t>elc_won_POL_049</t>
   </si>
   <si>
-    <t>wind onshore electricity near Wroclaw (cluster 49)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_050</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Gdansk (cluster 50)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_051</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Krakow (cluster 51)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_052</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Lublin (cluster 52)</t>
+    <t>wind onshore electricity near Lublin (cluster 49)</t>
   </si>
   <si>
     <t>~fi_comm</t>
@@ -1585,18 +1555,6 @@
     <t>grid node -- way/255284259-220 (Konin, 10 km)</t>
   </si>
   <si>
-    <t>e_Koszalin_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/178838661-220 (Koszalin, 40 km)</t>
-  </si>
-  <si>
-    <t>e_Krakow_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/87667718-220 (Krakow, 12 km)</t>
-  </si>
-  <si>
     <t>e_Krosno_POL</t>
   </si>
   <si>
@@ -1663,12 +1621,6 @@
     <t>grid node -- way/255277953-400 (Opole, 10 km)</t>
   </si>
   <si>
-    <t>e_Ostroleka_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/121656686-220 (Lomza, 31 km)</t>
-  </si>
-  <si>
     <t>e_OstrowiecSwietokrz_POL</t>
   </si>
   <si>
@@ -1729,6 +1681,12 @@
     <t>grid node -- PL26-400 (Warsaw, 53 km)</t>
   </si>
   <si>
+    <t>e_Skawina_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/189501431-400 (Krakow, 13 km)</t>
+  </si>
+  <si>
     <t>e_Slupsk_POL</t>
   </si>
   <si>
@@ -1759,12 +1717,6 @@
     <t>grid node -- way/191038569-220 (Tarnow, 5 km)</t>
   </si>
   <si>
-    <t>e_Ustka_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/255314292 (Slupsk, 10 km)</t>
-  </si>
-  <si>
     <t>e_Walbrzych_POL</t>
   </si>
   <si>
@@ -1780,7 +1732,7 @@
     <t>e_Wloclawek_POL</t>
   </si>
   <si>
-    <t>grid node -- way/245964556-220 (Wloclawek, 10 km)</t>
+    <t>grid node -- way/72879943-220 (Wloclawek, 9 km)</t>
   </si>
   <si>
     <t>e_Wroclaw_POL</t>
@@ -1789,6 +1741,12 @@
     <t>grid node -- way/79033485-400 (Wroclaw, 13 km)</t>
   </si>
   <si>
+    <t>e_Zabrze_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/293489607-400 (Katowice, 21 km)</t>
+  </si>
+  <si>
     <t>e_Zamosc_POL</t>
   </si>
   <si>
@@ -1909,18 +1867,6 @@
     <t>heat at grid node -- way/255284259-220 (Konin, 10 km)</t>
   </si>
   <si>
-    <t>h_Koszalin_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/178838661-220 (Koszalin, 40 km)</t>
-  </si>
-  <si>
-    <t>h_Krakow_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/87667718-220 (Krakow, 12 km)</t>
-  </si>
-  <si>
     <t>h_Krosno_POL</t>
   </si>
   <si>
@@ -1987,12 +1933,6 @@
     <t>heat at grid node -- way/255277953-400 (Opole, 10 km)</t>
   </si>
   <si>
-    <t>h_Ostroleka_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/121656686-220 (Lomza, 31 km)</t>
-  </si>
-  <si>
     <t>h_OstrowiecSwietokrz_POL</t>
   </si>
   <si>
@@ -2053,6 +1993,12 @@
     <t>heat at grid node -- PL26-400 (Warsaw, 53 km)</t>
   </si>
   <si>
+    <t>h_Skawina_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/189501431-400 (Krakow, 13 km)</t>
+  </si>
+  <si>
     <t>h_Slupsk_POL</t>
   </si>
   <si>
@@ -2083,12 +2029,6 @@
     <t>heat at grid node -- way/191038569-220 (Tarnow, 5 km)</t>
   </si>
   <si>
-    <t>h_Ustka_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/255314292 (Slupsk, 10 km)</t>
-  </si>
-  <si>
     <t>h_Walbrzych_POL</t>
   </si>
   <si>
@@ -2104,7 +2044,7 @@
     <t>h_Wloclawek_POL</t>
   </si>
   <si>
-    <t>heat at grid node -- way/245964556-220 (Wloclawek, 10 km)</t>
+    <t>heat at grid node -- way/72879943-220 (Wloclawek, 9 km)</t>
   </si>
   <si>
     <t>h_Wroclaw_POL</t>
@@ -2113,6 +2053,12 @@
     <t>heat at grid node -- way/79033485-400 (Wroclaw, 13 km)</t>
   </si>
   <si>
+    <t>h_Zabrze_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/293489607-400 (Katowice, 21 km)</t>
+  </si>
+  <si>
     <t>h_Zamosc_POL</t>
   </si>
   <si>
@@ -2206,12 +2152,6 @@
     <t>co2 captured at grid node -- way/112614319-400 (Gdansk, 4 km)</t>
   </si>
   <si>
-    <t>co2_Ostroleka_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/121656686-220 (Lomza, 31 km)</t>
-  </si>
-  <si>
     <t>co2_Lomza_POL</t>
   </si>
   <si>
@@ -2260,12 +2200,6 @@
     <t>co2 captured at grid node -- way/173582810-400 (Radom, 35 km)</t>
   </si>
   <si>
-    <t>co2_Koszalin_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/178838661-220 (Koszalin, 40 km)</t>
-  </si>
-  <si>
     <t>co2_Lubin_POL</t>
   </si>
   <si>
@@ -2278,6 +2212,12 @@
     <t>co2 captured at grid node -- way/183945016-220 (Katowice, 19 km)</t>
   </si>
   <si>
+    <t>co2_Skawina_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/189501431-400 (Krakow, 13 km)</t>
+  </si>
+  <si>
     <t>co2_Tarnow_POL</t>
   </si>
   <si>
@@ -2320,112 +2260,112 @@
     <t>co2 captured at grid node -- way/238640596-220 (Pila, 12 km)</t>
   </si>
   <si>
+    <t>co2_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/254235846-400 (Ostrowiec Swietokrzyski, 4 km)</t>
+  </si>
+  <si>
+    <t>co2_Opole_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/255277953-400 (Opole, 10 km)</t>
+  </si>
+  <si>
+    <t>co2_Konin_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/255284259-220 (Konin, 10 km)</t>
+  </si>
+  <si>
+    <t>co2_Kalisz_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/255293403-400 (Kalisz, 21 km)</t>
+  </si>
+  <si>
+    <t>co2_Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/276291999-220 (Walbrzych, 11 km)</t>
+  </si>
+  <si>
+    <t>co2_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/29115701-220 (Warsaw, 9 km)</t>
+  </si>
+  <si>
+    <t>co2_Belchatow_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/293484891-400 (Piotrkow Trybunalski, 26 km)</t>
+  </si>
+  <si>
+    <t>co2_Zabrze_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/293489607-400 (Katowice, 21 km)</t>
+  </si>
+  <si>
+    <t>co2_Elk_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/303870256-400 (Elk, 8 km)</t>
+  </si>
+  <si>
+    <t>co2_Poznan_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/32036484-220 (Poznan, 11 km)</t>
+  </si>
+  <si>
+    <t>co2_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/336990960-220 (Opole, 7 km)</t>
+  </si>
+  <si>
+    <t>co2_Lodz_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/35366436-220 (Lodz, 8 km)</t>
+  </si>
+  <si>
+    <t>co2_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/39428977-400 (Szczecin, 27 km)</t>
+  </si>
+  <si>
+    <t>co2_Katowice_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/40946790-220 (Katowice, 19 km)</t>
+  </si>
+  <si>
+    <t>co2_BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/44389929-220 (Bielsko-Biala, 12 km)</t>
+  </si>
+  <si>
+    <t>co2_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/46092396-400 (Grudziadz, 6 km)</t>
+  </si>
+  <si>
+    <t>co2_Plock_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/658600169-400 (Plock, 4 km)</t>
+  </si>
+  <si>
     <t>co2_Wloclawek_POL</t>
   </si>
   <si>
-    <t>co2 captured at grid node -- way/245964556-220 (Wloclawek, 10 km)</t>
-  </si>
-  <si>
-    <t>co2_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/254235846-400 (Ostrowiec Swietokrzyski, 4 km)</t>
-  </si>
-  <si>
-    <t>co2_Opole_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/255277953-400 (Opole, 10 km)</t>
-  </si>
-  <si>
-    <t>co2_Konin_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/255284259-220 (Konin, 10 km)</t>
-  </si>
-  <si>
-    <t>co2_Kalisz_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/255293403-400 (Kalisz, 21 km)</t>
-  </si>
-  <si>
-    <t>co2_Ustka_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/255314292 (Slupsk, 10 km)</t>
-  </si>
-  <si>
-    <t>co2_Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/276291999-220 (Walbrzych, 11 km)</t>
-  </si>
-  <si>
-    <t>co2_Warsaw_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/29115701-220 (Warsaw, 9 km)</t>
-  </si>
-  <si>
-    <t>co2_Belchatow_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/293484891-400 (Piotrkow Trybunalski, 26 km)</t>
-  </si>
-  <si>
-    <t>co2_Elk_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/303870256-400 (Elk, 8 km)</t>
-  </si>
-  <si>
-    <t>co2_Poznan_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/32036484-220 (Poznan, 11 km)</t>
-  </si>
-  <si>
-    <t>co2_KedzierzynKozle_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/336990960-220 (Opole, 7 km)</t>
-  </si>
-  <si>
-    <t>co2_Lodz_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/35366436-220 (Lodz, 8 km)</t>
-  </si>
-  <si>
-    <t>co2_Szczecin_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/39428977-400 (Szczecin, 27 km)</t>
-  </si>
-  <si>
-    <t>co2_Katowice_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/40946790-220 (Katowice, 19 km)</t>
-  </si>
-  <si>
-    <t>co2_BielskoBiala_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/44389929-220 (Bielsko-Biala, 12 km)</t>
-  </si>
-  <si>
-    <t>co2_Grudziadz_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/46092396-400 (Grudziadz, 6 km)</t>
-  </si>
-  <si>
-    <t>co2_Plock_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/658600169-400 (Plock, 4 km)</t>
+    <t>co2 captured at grid node -- way/72879943-220 (Wloclawek, 9 km)</t>
   </si>
   <si>
     <t>co2_Wroclaw_POL</t>
@@ -2440,196 +2380,106 @@
     <t>co2 captured at grid node -- way/86494356-400 (Gdansk, 54 km)</t>
   </si>
   <si>
-    <t>co2_Krakow_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/87667718-220 (Krakow, 12 km)</t>
-  </si>
-  <si>
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/88544449-220 (Lublin, 46 km)</t>
   </si>
   <si>
-    <t>co2s_ogci11072_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11072.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11074_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11074.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11075_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11075.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11076_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11076.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11077_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11077.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11078_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11078.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11079_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11079.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11080_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11080.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11081_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11081.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11082_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11082.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11083_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11083.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11084_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11084.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11085_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11085.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11086_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11086.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11087_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11087.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11088_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11088.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11089_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11089.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11090_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11090.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11091_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11091.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11092_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11092.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11093_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11093.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_ogci11094_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- ogci_11094.0 (OGCI/catalogue)</t>
-  </si>
-  <si>
-    <t>co2s_T1_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- T1 (national overlay)</t>
-  </si>
-  <si>
-    <t>co2s_T2_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- T2 (national overlay)</t>
-  </si>
-  <si>
-    <t>co2s_T3_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- T3 (national overlay)</t>
-  </si>
-  <si>
-    <t>co2s_T4_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- T4 (national overlay)</t>
-  </si>
-  <si>
-    <t>co2s_T5_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- T5 (national overlay)</t>
-  </si>
-  <si>
-    <t>co2s_T6_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- T6 (national overlay)</t>
-  </si>
-  <si>
-    <t>co2s_T7_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- T7 (national overlay)</t>
-  </si>
-  <si>
-    <t>co2s_T8_POL</t>
-  </si>
-  <si>
-    <t>co2 delivered to sink -- T8 (national overlay)</t>
+    <t>co2s_PGI005_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- PGI005 (national overlay)</t>
+  </si>
+  <si>
+    <t>co2s_PGI038_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- PGI038 (national overlay)</t>
+  </si>
+  <si>
+    <t>co2s_PGI011_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- PGI011 (national overlay)</t>
+  </si>
+  <si>
+    <t>co2s_PGI014_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- PGI014 (national overlay)</t>
+  </si>
+  <si>
+    <t>co2s_PGI015_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- PGI015 (national overlay)</t>
+  </si>
+  <si>
+    <t>co2s_PGI013_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- PGI013 (national overlay)</t>
+  </si>
+  <si>
+    <t>co2s_PGI003_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- PGI003 (national overlay)</t>
+  </si>
+  <si>
+    <t>co2s_PGI020_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- PGI020 (national overlay)</t>
+  </si>
+  <si>
+    <t>co2s_PGI012_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- PGI012 (national overlay)</t>
+  </si>
+  <si>
+    <t>co2s_PGI019_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- PGI019 (national overlay)</t>
+  </si>
+  <si>
+    <t>co2s_PGI016_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- PGI016 (national overlay)</t>
+  </si>
+  <si>
+    <t>co2s_PGI032_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- PGI032 (national overlay)</t>
+  </si>
+  <si>
+    <t>co2s_PGI035_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- PGI035 (national overlay)</t>
+  </si>
+  <si>
+    <t>co2s_PGI033_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- PGI033 (national overlay)</t>
+  </si>
+  <si>
+    <t>co2s_PGI027_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- PGI027 (national overlay)</t>
+  </si>
+  <si>
+    <t>co2s_ExportNL_POL</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ExportNL (export terminal)</t>
   </si>
 </sst>
 </file>
@@ -5024,13 +4874,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41DF7A7-016B-4C5C-8FC8-E80CFBD87664}">
-  <dimension ref="B3:H88"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E08842F-D8C0-4CAD-A464-46B9B3431BF4}">
+  <dimension ref="B3:H72"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:8">
       <c r="B3" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
     </row>
     <row r="4" spans="2:8">
@@ -5061,19 +4911,19 @@
         <v>192</v>
       </c>
       <c r="C5" t="s">
-        <v>694</v>
+        <v>676</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>695</v>
+        <v>677</v>
       </c>
       <c r="F5" t="s">
         <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H5" t="s">
         <v>195</v>
@@ -5084,19 +4934,19 @@
         <v>192</v>
       </c>
       <c r="C6" t="s">
-        <v>697</v>
+        <v>679</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>698</v>
+        <v>680</v>
       </c>
       <c r="F6" t="s">
         <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H6" t="s">
         <v>195</v>
@@ -5107,19 +4957,19 @@
         <v>192</v>
       </c>
       <c r="C7" t="s">
-        <v>699</v>
+        <v>681</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>700</v>
+        <v>682</v>
       </c>
       <c r="F7" t="s">
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H7" t="s">
         <v>195</v>
@@ -5130,19 +4980,19 @@
         <v>192</v>
       </c>
       <c r="C8" t="s">
-        <v>701</v>
+        <v>683</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
       <c r="F8" t="s">
         <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H8" t="s">
         <v>195</v>
@@ -5153,19 +5003,19 @@
         <v>192</v>
       </c>
       <c r="C9" t="s">
-        <v>703</v>
+        <v>685</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>704</v>
+        <v>686</v>
       </c>
       <c r="F9" t="s">
         <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H9" t="s">
         <v>195</v>
@@ -5176,19 +5026,19 @@
         <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>706</v>
+        <v>688</v>
       </c>
       <c r="F10" t="s">
         <v>26</v>
       </c>
       <c r="G10" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H10" t="s">
         <v>195</v>
@@ -5199,19 +5049,19 @@
         <v>192</v>
       </c>
       <c r="C11" t="s">
-        <v>707</v>
+        <v>689</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>708</v>
+        <v>690</v>
       </c>
       <c r="F11" t="s">
         <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H11" t="s">
         <v>195</v>
@@ -5222,19 +5072,19 @@
         <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>709</v>
+        <v>691</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
       <c r="F12" t="s">
         <v>26</v>
       </c>
       <c r="G12" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H12" t="s">
         <v>195</v>
@@ -5245,19 +5095,19 @@
         <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>711</v>
+        <v>693</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>712</v>
+        <v>694</v>
       </c>
       <c r="F13" t="s">
         <v>26</v>
       </c>
       <c r="G13" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H13" t="s">
         <v>195</v>
@@ -5268,19 +5118,19 @@
         <v>192</v>
       </c>
       <c r="C14" t="s">
-        <v>713</v>
+        <v>695</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>714</v>
+        <v>696</v>
       </c>
       <c r="F14" t="s">
         <v>26</v>
       </c>
       <c r="G14" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H14" t="s">
         <v>195</v>
@@ -5291,19 +5141,19 @@
         <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>715</v>
+        <v>697</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>716</v>
+        <v>698</v>
       </c>
       <c r="F15" t="s">
         <v>26</v>
       </c>
       <c r="G15" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H15" t="s">
         <v>195</v>
@@ -5314,19 +5164,19 @@
         <v>192</v>
       </c>
       <c r="C16" t="s">
-        <v>717</v>
+        <v>699</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>718</v>
+        <v>700</v>
       </c>
       <c r="F16" t="s">
         <v>26</v>
       </c>
       <c r="G16" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H16" t="s">
         <v>195</v>
@@ -5337,19 +5187,19 @@
         <v>192</v>
       </c>
       <c r="C17" t="s">
-        <v>719</v>
+        <v>701</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>720</v>
+        <v>702</v>
       </c>
       <c r="F17" t="s">
         <v>26</v>
       </c>
       <c r="G17" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H17" t="s">
         <v>195</v>
@@ -5360,19 +5210,19 @@
         <v>192</v>
       </c>
       <c r="C18" t="s">
-        <v>721</v>
+        <v>703</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>722</v>
+        <v>704</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
       </c>
       <c r="G18" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H18" t="s">
         <v>195</v>
@@ -5383,19 +5233,19 @@
         <v>192</v>
       </c>
       <c r="C19" t="s">
-        <v>723</v>
+        <v>705</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
       <c r="F19" t="s">
         <v>26</v>
       </c>
       <c r="G19" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H19" t="s">
         <v>195</v>
@@ -5406,19 +5256,19 @@
         <v>192</v>
       </c>
       <c r="C20" t="s">
-        <v>725</v>
+        <v>707</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>726</v>
+        <v>708</v>
       </c>
       <c r="F20" t="s">
         <v>26</v>
       </c>
       <c r="G20" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H20" t="s">
         <v>195</v>
@@ -5429,19 +5279,19 @@
         <v>192</v>
       </c>
       <c r="C21" t="s">
-        <v>727</v>
+        <v>709</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>728</v>
+        <v>710</v>
       </c>
       <c r="F21" t="s">
         <v>26</v>
       </c>
       <c r="G21" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H21" t="s">
         <v>195</v>
@@ -5452,19 +5302,19 @@
         <v>192</v>
       </c>
       <c r="C22" t="s">
-        <v>729</v>
+        <v>711</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>730</v>
+        <v>712</v>
       </c>
       <c r="F22" t="s">
         <v>26</v>
       </c>
       <c r="G22" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H22" t="s">
         <v>195</v>
@@ -5475,19 +5325,19 @@
         <v>192</v>
       </c>
       <c r="C23" t="s">
-        <v>731</v>
+        <v>713</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>732</v>
+        <v>714</v>
       </c>
       <c r="F23" t="s">
         <v>26</v>
       </c>
       <c r="G23" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H23" t="s">
         <v>195</v>
@@ -5498,19 +5348,19 @@
         <v>192</v>
       </c>
       <c r="C24" t="s">
-        <v>733</v>
+        <v>715</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>734</v>
+        <v>716</v>
       </c>
       <c r="F24" t="s">
         <v>26</v>
       </c>
       <c r="G24" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H24" t="s">
         <v>195</v>
@@ -5521,19 +5371,19 @@
         <v>192</v>
       </c>
       <c r="C25" t="s">
-        <v>735</v>
+        <v>717</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>736</v>
+        <v>718</v>
       </c>
       <c r="F25" t="s">
         <v>26</v>
       </c>
       <c r="G25" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H25" t="s">
         <v>195</v>
@@ -5544,19 +5394,19 @@
         <v>192</v>
       </c>
       <c r="C26" t="s">
-        <v>737</v>
+        <v>719</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>738</v>
+        <v>720</v>
       </c>
       <c r="F26" t="s">
         <v>26</v>
       </c>
       <c r="G26" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H26" t="s">
         <v>195</v>
@@ -5567,19 +5417,19 @@
         <v>192</v>
       </c>
       <c r="C27" t="s">
-        <v>739</v>
+        <v>721</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>740</v>
+        <v>722</v>
       </c>
       <c r="F27" t="s">
         <v>26</v>
       </c>
       <c r="G27" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H27" t="s">
         <v>195</v>
@@ -5590,19 +5440,19 @@
         <v>192</v>
       </c>
       <c r="C28" t="s">
-        <v>741</v>
+        <v>723</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>742</v>
+        <v>724</v>
       </c>
       <c r="F28" t="s">
         <v>26</v>
       </c>
       <c r="G28" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H28" t="s">
         <v>195</v>
@@ -5613,19 +5463,19 @@
         <v>192</v>
       </c>
       <c r="C29" t="s">
-        <v>743</v>
+        <v>725</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>744</v>
+        <v>726</v>
       </c>
       <c r="F29" t="s">
         <v>26</v>
       </c>
       <c r="G29" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H29" t="s">
         <v>195</v>
@@ -5636,19 +5486,19 @@
         <v>192</v>
       </c>
       <c r="C30" t="s">
-        <v>745</v>
+        <v>727</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>746</v>
+        <v>728</v>
       </c>
       <c r="F30" t="s">
         <v>26</v>
       </c>
       <c r="G30" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H30" t="s">
         <v>195</v>
@@ -5659,19 +5509,19 @@
         <v>192</v>
       </c>
       <c r="C31" t="s">
-        <v>747</v>
+        <v>729</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>748</v>
+        <v>730</v>
       </c>
       <c r="F31" t="s">
         <v>26</v>
       </c>
       <c r="G31" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H31" t="s">
         <v>195</v>
@@ -5682,19 +5532,19 @@
         <v>192</v>
       </c>
       <c r="C32" t="s">
-        <v>749</v>
+        <v>731</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>750</v>
+        <v>732</v>
       </c>
       <c r="F32" t="s">
         <v>26</v>
       </c>
       <c r="G32" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H32" t="s">
         <v>195</v>
@@ -5705,19 +5555,19 @@
         <v>192</v>
       </c>
       <c r="C33" t="s">
-        <v>751</v>
+        <v>733</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>752</v>
+        <v>734</v>
       </c>
       <c r="F33" t="s">
         <v>26</v>
       </c>
       <c r="G33" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H33" t="s">
         <v>195</v>
@@ -5728,19 +5578,19 @@
         <v>192</v>
       </c>
       <c r="C34" t="s">
-        <v>753</v>
+        <v>735</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>754</v>
+        <v>736</v>
       </c>
       <c r="F34" t="s">
         <v>26</v>
       </c>
       <c r="G34" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H34" t="s">
         <v>195</v>
@@ -5751,19 +5601,19 @@
         <v>192</v>
       </c>
       <c r="C35" t="s">
-        <v>755</v>
+        <v>737</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>756</v>
+        <v>738</v>
       </c>
       <c r="F35" t="s">
         <v>26</v>
       </c>
       <c r="G35" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H35" t="s">
         <v>195</v>
@@ -5774,19 +5624,19 @@
         <v>192</v>
       </c>
       <c r="C36" t="s">
-        <v>757</v>
+        <v>739</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>758</v>
+        <v>740</v>
       </c>
       <c r="F36" t="s">
         <v>26</v>
       </c>
       <c r="G36" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H36" t="s">
         <v>195</v>
@@ -5797,19 +5647,19 @@
         <v>192</v>
       </c>
       <c r="C37" t="s">
-        <v>759</v>
+        <v>741</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>760</v>
+        <v>742</v>
       </c>
       <c r="F37" t="s">
         <v>26</v>
       </c>
       <c r="G37" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H37" t="s">
         <v>195</v>
@@ -5820,19 +5670,19 @@
         <v>192</v>
       </c>
       <c r="C38" t="s">
-        <v>761</v>
+        <v>743</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="F38" t="s">
         <v>26</v>
       </c>
       <c r="G38" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H38" t="s">
         <v>195</v>
@@ -5843,19 +5693,19 @@
         <v>192</v>
       </c>
       <c r="C39" t="s">
-        <v>763</v>
+        <v>745</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>764</v>
+        <v>746</v>
       </c>
       <c r="F39" t="s">
         <v>26</v>
       </c>
       <c r="G39" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H39" t="s">
         <v>195</v>
@@ -5866,19 +5716,19 @@
         <v>192</v>
       </c>
       <c r="C40" t="s">
-        <v>765</v>
+        <v>747</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>766</v>
+        <v>748</v>
       </c>
       <c r="F40" t="s">
         <v>26</v>
       </c>
       <c r="G40" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H40" t="s">
         <v>195</v>
@@ -5889,19 +5739,19 @@
         <v>192</v>
       </c>
       <c r="C41" t="s">
-        <v>767</v>
+        <v>749</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>768</v>
+        <v>750</v>
       </c>
       <c r="F41" t="s">
         <v>26</v>
       </c>
       <c r="G41" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H41" t="s">
         <v>195</v>
@@ -5912,19 +5762,19 @@
         <v>192</v>
       </c>
       <c r="C42" t="s">
-        <v>769</v>
+        <v>751</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="F42" t="s">
         <v>26</v>
       </c>
       <c r="G42" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H42" t="s">
         <v>195</v>
@@ -5935,19 +5785,19 @@
         <v>192</v>
       </c>
       <c r="C43" t="s">
-        <v>771</v>
+        <v>753</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>772</v>
+        <v>754</v>
       </c>
       <c r="F43" t="s">
         <v>26</v>
       </c>
       <c r="G43" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H43" t="s">
         <v>195</v>
@@ -5958,19 +5808,19 @@
         <v>192</v>
       </c>
       <c r="C44" t="s">
-        <v>773</v>
+        <v>755</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>774</v>
+        <v>756</v>
       </c>
       <c r="F44" t="s">
         <v>26</v>
       </c>
       <c r="G44" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H44" t="s">
         <v>195</v>
@@ -5981,19 +5831,19 @@
         <v>192</v>
       </c>
       <c r="C45" t="s">
-        <v>775</v>
+        <v>757</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>776</v>
+        <v>758</v>
       </c>
       <c r="F45" t="s">
         <v>26</v>
       </c>
       <c r="G45" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H45" t="s">
         <v>195</v>
@@ -6004,19 +5854,19 @@
         <v>192</v>
       </c>
       <c r="C46" t="s">
-        <v>777</v>
+        <v>759</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>778</v>
+        <v>760</v>
       </c>
       <c r="F46" t="s">
         <v>26</v>
       </c>
       <c r="G46" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H46" t="s">
         <v>195</v>
@@ -6027,19 +5877,19 @@
         <v>192</v>
       </c>
       <c r="C47" t="s">
-        <v>779</v>
+        <v>761</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>780</v>
+        <v>762</v>
       </c>
       <c r="F47" t="s">
         <v>26</v>
       </c>
       <c r="G47" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H47" t="s">
         <v>195</v>
@@ -6050,19 +5900,19 @@
         <v>192</v>
       </c>
       <c r="C48" t="s">
-        <v>781</v>
+        <v>763</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>782</v>
+        <v>764</v>
       </c>
       <c r="F48" t="s">
         <v>26</v>
       </c>
       <c r="G48" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H48" t="s">
         <v>195</v>
@@ -6073,19 +5923,19 @@
         <v>192</v>
       </c>
       <c r="C49" t="s">
-        <v>783</v>
+        <v>765</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>784</v>
+        <v>766</v>
       </c>
       <c r="F49" t="s">
         <v>26</v>
       </c>
       <c r="G49" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H49" t="s">
         <v>195</v>
@@ -6096,19 +5946,19 @@
         <v>192</v>
       </c>
       <c r="C50" t="s">
-        <v>785</v>
+        <v>767</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>786</v>
+        <v>768</v>
       </c>
       <c r="F50" t="s">
         <v>26</v>
       </c>
       <c r="G50" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H50" t="s">
         <v>195</v>
@@ -6119,19 +5969,19 @@
         <v>192</v>
       </c>
       <c r="C51" t="s">
-        <v>787</v>
+        <v>769</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>788</v>
+        <v>770</v>
       </c>
       <c r="F51" t="s">
         <v>26</v>
       </c>
       <c r="G51" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H51" t="s">
         <v>195</v>
@@ -6142,19 +5992,19 @@
         <v>192</v>
       </c>
       <c r="C52" t="s">
-        <v>789</v>
+        <v>771</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>790</v>
+        <v>772</v>
       </c>
       <c r="F52" t="s">
         <v>26</v>
       </c>
       <c r="G52" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H52" t="s">
         <v>195</v>
@@ -6165,19 +6015,19 @@
         <v>192</v>
       </c>
       <c r="C53" t="s">
-        <v>791</v>
+        <v>773</v>
       </c>
       <c r="D53" t="s">
         <v>243</v>
       </c>
       <c r="E53" t="s">
-        <v>792</v>
+        <v>774</v>
       </c>
       <c r="F53" t="s">
         <v>26</v>
       </c>
       <c r="G53" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H53" t="s">
         <v>195</v>
@@ -6188,19 +6038,19 @@
         <v>192</v>
       </c>
       <c r="C54" t="s">
-        <v>793</v>
+        <v>775</v>
       </c>
       <c r="D54" t="s">
         <v>243</v>
       </c>
       <c r="E54" t="s">
-        <v>794</v>
+        <v>776</v>
       </c>
       <c r="F54" t="s">
         <v>26</v>
       </c>
       <c r="G54" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H54" t="s">
         <v>195</v>
@@ -6211,19 +6061,19 @@
         <v>192</v>
       </c>
       <c r="C55" t="s">
-        <v>795</v>
+        <v>777</v>
       </c>
       <c r="D55" t="s">
         <v>243</v>
       </c>
       <c r="E55" t="s">
-        <v>796</v>
+        <v>778</v>
       </c>
       <c r="F55" t="s">
         <v>26</v>
       </c>
       <c r="G55" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H55" t="s">
         <v>195</v>
@@ -6234,19 +6084,19 @@
         <v>192</v>
       </c>
       <c r="C56" t="s">
-        <v>797</v>
+        <v>779</v>
       </c>
       <c r="D56" t="s">
         <v>243</v>
       </c>
       <c r="E56" t="s">
-        <v>798</v>
+        <v>780</v>
       </c>
       <c r="F56" t="s">
         <v>26</v>
       </c>
       <c r="G56" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H56" t="s">
         <v>195</v>
@@ -6257,19 +6107,19 @@
         <v>192</v>
       </c>
       <c r="C57" t="s">
-        <v>799</v>
+        <v>781</v>
       </c>
       <c r="D57" t="s">
         <v>243</v>
       </c>
       <c r="E57" t="s">
-        <v>800</v>
+        <v>782</v>
       </c>
       <c r="F57" t="s">
         <v>26</v>
       </c>
       <c r="G57" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H57" t="s">
         <v>195</v>
@@ -6280,19 +6130,19 @@
         <v>192</v>
       </c>
       <c r="C58" t="s">
-        <v>801</v>
+        <v>783</v>
       </c>
       <c r="D58" t="s">
         <v>243</v>
       </c>
       <c r="E58" t="s">
-        <v>802</v>
+        <v>784</v>
       </c>
       <c r="F58" t="s">
         <v>26</v>
       </c>
       <c r="G58" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H58" t="s">
         <v>195</v>
@@ -6303,19 +6153,19 @@
         <v>192</v>
       </c>
       <c r="C59" t="s">
-        <v>803</v>
+        <v>785</v>
       </c>
       <c r="D59" t="s">
         <v>243</v>
       </c>
       <c r="E59" t="s">
-        <v>804</v>
+        <v>786</v>
       </c>
       <c r="F59" t="s">
         <v>26</v>
       </c>
       <c r="G59" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H59" t="s">
         <v>195</v>
@@ -6326,19 +6176,19 @@
         <v>192</v>
       </c>
       <c r="C60" t="s">
-        <v>805</v>
+        <v>787</v>
       </c>
       <c r="D60" t="s">
         <v>243</v>
       </c>
       <c r="E60" t="s">
-        <v>806</v>
+        <v>788</v>
       </c>
       <c r="F60" t="s">
         <v>26</v>
       </c>
       <c r="G60" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H60" t="s">
         <v>195</v>
@@ -6349,19 +6199,19 @@
         <v>192</v>
       </c>
       <c r="C61" t="s">
-        <v>807</v>
+        <v>789</v>
       </c>
       <c r="D61" t="s">
         <v>243</v>
       </c>
       <c r="E61" t="s">
-        <v>808</v>
+        <v>790</v>
       </c>
       <c r="F61" t="s">
         <v>26</v>
       </c>
       <c r="G61" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H61" t="s">
         <v>195</v>
@@ -6372,19 +6222,19 @@
         <v>192</v>
       </c>
       <c r="C62" t="s">
-        <v>809</v>
+        <v>791</v>
       </c>
       <c r="D62" t="s">
         <v>243</v>
       </c>
       <c r="E62" t="s">
-        <v>810</v>
+        <v>792</v>
       </c>
       <c r="F62" t="s">
         <v>26</v>
       </c>
       <c r="G62" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H62" t="s">
         <v>195</v>
@@ -6395,19 +6245,19 @@
         <v>192</v>
       </c>
       <c r="C63" t="s">
-        <v>811</v>
+        <v>793</v>
       </c>
       <c r="D63" t="s">
         <v>243</v>
       </c>
       <c r="E63" t="s">
-        <v>812</v>
+        <v>794</v>
       </c>
       <c r="F63" t="s">
         <v>26</v>
       </c>
       <c r="G63" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H63" t="s">
         <v>195</v>
@@ -6418,19 +6268,19 @@
         <v>192</v>
       </c>
       <c r="C64" t="s">
-        <v>813</v>
+        <v>795</v>
       </c>
       <c r="D64" t="s">
         <v>243</v>
       </c>
       <c r="E64" t="s">
-        <v>814</v>
+        <v>796</v>
       </c>
       <c r="F64" t="s">
         <v>26</v>
       </c>
       <c r="G64" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H64" t="s">
         <v>195</v>
@@ -6441,19 +6291,19 @@
         <v>192</v>
       </c>
       <c r="C65" t="s">
-        <v>815</v>
+        <v>797</v>
       </c>
       <c r="D65" t="s">
         <v>243</v>
       </c>
       <c r="E65" t="s">
-        <v>816</v>
+        <v>798</v>
       </c>
       <c r="F65" t="s">
         <v>26</v>
       </c>
       <c r="G65" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H65" t="s">
         <v>195</v>
@@ -6464,19 +6314,19 @@
         <v>192</v>
       </c>
       <c r="C66" t="s">
-        <v>817</v>
+        <v>799</v>
       </c>
       <c r="D66" t="s">
         <v>243</v>
       </c>
       <c r="E66" t="s">
-        <v>818</v>
+        <v>800</v>
       </c>
       <c r="F66" t="s">
         <v>26</v>
       </c>
       <c r="G66" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H66" t="s">
         <v>195</v>
@@ -6487,19 +6337,19 @@
         <v>192</v>
       </c>
       <c r="C67" t="s">
-        <v>819</v>
+        <v>801</v>
       </c>
       <c r="D67" t="s">
         <v>243</v>
       </c>
       <c r="E67" t="s">
-        <v>820</v>
+        <v>802</v>
       </c>
       <c r="F67" t="s">
         <v>26</v>
       </c>
       <c r="G67" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H67" t="s">
         <v>195</v>
@@ -6510,19 +6360,19 @@
         <v>192</v>
       </c>
       <c r="C68" t="s">
-        <v>821</v>
+        <v>803</v>
       </c>
       <c r="D68" t="s">
         <v>243</v>
       </c>
       <c r="E68" t="s">
-        <v>822</v>
+        <v>804</v>
       </c>
       <c r="F68" t="s">
         <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H68" t="s">
         <v>195</v>
@@ -6533,19 +6383,19 @@
         <v>192</v>
       </c>
       <c r="C69" t="s">
-        <v>823</v>
+        <v>805</v>
       </c>
       <c r="D69" t="s">
         <v>243</v>
       </c>
       <c r="E69" t="s">
-        <v>824</v>
+        <v>806</v>
       </c>
       <c r="F69" t="s">
         <v>26</v>
       </c>
       <c r="G69" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H69" t="s">
         <v>195</v>
@@ -6556,19 +6406,19 @@
         <v>192</v>
       </c>
       <c r="C70" t="s">
-        <v>825</v>
+        <v>807</v>
       </c>
       <c r="D70" t="s">
         <v>243</v>
       </c>
       <c r="E70" t="s">
-        <v>826</v>
+        <v>808</v>
       </c>
       <c r="F70" t="s">
         <v>26</v>
       </c>
       <c r="G70" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H70" t="s">
         <v>195</v>
@@ -6579,19 +6429,19 @@
         <v>192</v>
       </c>
       <c r="C71" t="s">
-        <v>827</v>
+        <v>809</v>
       </c>
       <c r="D71" t="s">
         <v>243</v>
       </c>
       <c r="E71" t="s">
-        <v>828</v>
+        <v>810</v>
       </c>
       <c r="F71" t="s">
         <v>26</v>
       </c>
       <c r="G71" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H71" t="s">
         <v>195</v>
@@ -6602,389 +6452,21 @@
         <v>192</v>
       </c>
       <c r="C72" t="s">
-        <v>829</v>
+        <v>811</v>
       </c>
       <c r="D72" t="s">
         <v>243</v>
       </c>
       <c r="E72" t="s">
-        <v>830</v>
+        <v>812</v>
       </c>
       <c r="F72" t="s">
         <v>26</v>
       </c>
       <c r="G72" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="H72" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="73" spans="2:8">
-      <c r="B73" t="s">
-        <v>192</v>
-      </c>
-      <c r="C73" t="s">
-        <v>831</v>
-      </c>
-      <c r="D73" t="s">
-        <v>243</v>
-      </c>
-      <c r="E73" t="s">
-        <v>832</v>
-      </c>
-      <c r="F73" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" t="s">
-        <v>696</v>
-      </c>
-      <c r="H73" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="74" spans="2:8">
-      <c r="B74" t="s">
-        <v>192</v>
-      </c>
-      <c r="C74" t="s">
-        <v>833</v>
-      </c>
-      <c r="D74" t="s">
-        <v>243</v>
-      </c>
-      <c r="E74" t="s">
-        <v>834</v>
-      </c>
-      <c r="F74" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" t="s">
-        <v>696</v>
-      </c>
-      <c r="H74" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="75" spans="2:8">
-      <c r="B75" t="s">
-        <v>192</v>
-      </c>
-      <c r="C75" t="s">
-        <v>835</v>
-      </c>
-      <c r="D75" t="s">
-        <v>243</v>
-      </c>
-      <c r="E75" t="s">
-        <v>836</v>
-      </c>
-      <c r="F75" t="s">
-        <v>26</v>
-      </c>
-      <c r="G75" t="s">
-        <v>696</v>
-      </c>
-      <c r="H75" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="76" spans="2:8">
-      <c r="B76" t="s">
-        <v>192</v>
-      </c>
-      <c r="C76" t="s">
-        <v>837</v>
-      </c>
-      <c r="D76" t="s">
-        <v>243</v>
-      </c>
-      <c r="E76" t="s">
-        <v>838</v>
-      </c>
-      <c r="F76" t="s">
-        <v>26</v>
-      </c>
-      <c r="G76" t="s">
-        <v>696</v>
-      </c>
-      <c r="H76" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="77" spans="2:8">
-      <c r="B77" t="s">
-        <v>192</v>
-      </c>
-      <c r="C77" t="s">
-        <v>839</v>
-      </c>
-      <c r="D77" t="s">
-        <v>243</v>
-      </c>
-      <c r="E77" t="s">
-        <v>840</v>
-      </c>
-      <c r="F77" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" t="s">
-        <v>696</v>
-      </c>
-      <c r="H77" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="78" spans="2:8">
-      <c r="B78" t="s">
-        <v>192</v>
-      </c>
-      <c r="C78" t="s">
-        <v>841</v>
-      </c>
-      <c r="D78" t="s">
-        <v>243</v>
-      </c>
-      <c r="E78" t="s">
-        <v>842</v>
-      </c>
-      <c r="F78" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" t="s">
-        <v>696</v>
-      </c>
-      <c r="H78" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="79" spans="2:8">
-      <c r="B79" t="s">
-        <v>192</v>
-      </c>
-      <c r="C79" t="s">
-        <v>843</v>
-      </c>
-      <c r="D79" t="s">
-        <v>243</v>
-      </c>
-      <c r="E79" t="s">
-        <v>844</v>
-      </c>
-      <c r="F79" t="s">
-        <v>26</v>
-      </c>
-      <c r="G79" t="s">
-        <v>696</v>
-      </c>
-      <c r="H79" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="80" spans="2:8">
-      <c r="B80" t="s">
-        <v>192</v>
-      </c>
-      <c r="C80" t="s">
-        <v>845</v>
-      </c>
-      <c r="D80" t="s">
-        <v>243</v>
-      </c>
-      <c r="E80" t="s">
-        <v>846</v>
-      </c>
-      <c r="F80" t="s">
-        <v>26</v>
-      </c>
-      <c r="G80" t="s">
-        <v>696</v>
-      </c>
-      <c r="H80" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8">
-      <c r="B81" t="s">
-        <v>192</v>
-      </c>
-      <c r="C81" t="s">
-        <v>847</v>
-      </c>
-      <c r="D81" t="s">
-        <v>243</v>
-      </c>
-      <c r="E81" t="s">
-        <v>848</v>
-      </c>
-      <c r="F81" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" t="s">
-        <v>696</v>
-      </c>
-      <c r="H81" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="82" spans="2:8">
-      <c r="B82" t="s">
-        <v>192</v>
-      </c>
-      <c r="C82" t="s">
-        <v>849</v>
-      </c>
-      <c r="D82" t="s">
-        <v>243</v>
-      </c>
-      <c r="E82" t="s">
-        <v>850</v>
-      </c>
-      <c r="F82" t="s">
-        <v>26</v>
-      </c>
-      <c r="G82" t="s">
-        <v>696</v>
-      </c>
-      <c r="H82" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="83" spans="2:8">
-      <c r="B83" t="s">
-        <v>192</v>
-      </c>
-      <c r="C83" t="s">
-        <v>851</v>
-      </c>
-      <c r="D83" t="s">
-        <v>243</v>
-      </c>
-      <c r="E83" t="s">
-        <v>852</v>
-      </c>
-      <c r="F83" t="s">
-        <v>26</v>
-      </c>
-      <c r="G83" t="s">
-        <v>696</v>
-      </c>
-      <c r="H83" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8">
-      <c r="B84" t="s">
-        <v>192</v>
-      </c>
-      <c r="C84" t="s">
-        <v>853</v>
-      </c>
-      <c r="D84" t="s">
-        <v>243</v>
-      </c>
-      <c r="E84" t="s">
-        <v>854</v>
-      </c>
-      <c r="F84" t="s">
-        <v>26</v>
-      </c>
-      <c r="G84" t="s">
-        <v>696</v>
-      </c>
-      <c r="H84" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="85" spans="2:8">
-      <c r="B85" t="s">
-        <v>192</v>
-      </c>
-      <c r="C85" t="s">
-        <v>855</v>
-      </c>
-      <c r="D85" t="s">
-        <v>243</v>
-      </c>
-      <c r="E85" t="s">
-        <v>856</v>
-      </c>
-      <c r="F85" t="s">
-        <v>26</v>
-      </c>
-      <c r="G85" t="s">
-        <v>696</v>
-      </c>
-      <c r="H85" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8">
-      <c r="B86" t="s">
-        <v>192</v>
-      </c>
-      <c r="C86" t="s">
-        <v>857</v>
-      </c>
-      <c r="D86" t="s">
-        <v>243</v>
-      </c>
-      <c r="E86" t="s">
-        <v>858</v>
-      </c>
-      <c r="F86" t="s">
-        <v>26</v>
-      </c>
-      <c r="G86" t="s">
-        <v>696</v>
-      </c>
-      <c r="H86" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="87" spans="2:8">
-      <c r="B87" t="s">
-        <v>192</v>
-      </c>
-      <c r="C87" t="s">
-        <v>859</v>
-      </c>
-      <c r="D87" t="s">
-        <v>243</v>
-      </c>
-      <c r="E87" t="s">
-        <v>860</v>
-      </c>
-      <c r="F87" t="s">
-        <v>26</v>
-      </c>
-      <c r="G87" t="s">
-        <v>696</v>
-      </c>
-      <c r="H87" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8">
-      <c r="B88" t="s">
-        <v>192</v>
-      </c>
-      <c r="C88" t="s">
-        <v>861</v>
-      </c>
-      <c r="D88" t="s">
-        <v>243</v>
-      </c>
-      <c r="E88" t="s">
-        <v>862</v>
-      </c>
-      <c r="F88" t="s">
-        <v>26</v>
-      </c>
-      <c r="G88" t="s">
-        <v>696</v>
-      </c>
-      <c r="H88" t="s">
         <v>195</v>
       </c>
     </row>
@@ -6994,13 +6476,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173D60C4-1EDD-4E33-A5A0-D1B3C9BCA5A5}">
-  <dimension ref="B3:I58"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AED2135F-F4A1-467A-BDDD-8AFF29B53C80}">
+  <dimension ref="B3:I56"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -7034,13 +6516,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>586</v>
+        <v>572</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -7049,7 +6531,7 @@
         <v>232</v>
       </c>
       <c r="H5" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I5" t="s">
         <v>247</v>
@@ -7060,13 +6542,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="F6" t="s">
         <v>233</v>
@@ -7075,7 +6557,7 @@
         <v>232</v>
       </c>
       <c r="H6" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I6" t="s">
         <v>247</v>
@@ -7086,13 +6568,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -7101,7 +6583,7 @@
         <v>232</v>
       </c>
       <c r="H7" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I7" t="s">
         <v>247</v>
@@ -7112,13 +6594,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -7127,7 +6609,7 @@
         <v>232</v>
       </c>
       <c r="H8" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I8" t="s">
         <v>247</v>
@@ -7138,13 +6620,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="F9" t="s">
         <v>233</v>
@@ -7153,7 +6635,7 @@
         <v>232</v>
       </c>
       <c r="H9" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I9" t="s">
         <v>247</v>
@@ -7164,13 +6646,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="F10" t="s">
         <v>233</v>
@@ -7179,7 +6661,7 @@
         <v>232</v>
       </c>
       <c r="H10" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I10" t="s">
         <v>247</v>
@@ -7190,13 +6672,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="F11" t="s">
         <v>233</v>
@@ -7205,7 +6687,7 @@
         <v>232</v>
       </c>
       <c r="H11" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I11" t="s">
         <v>247</v>
@@ -7216,13 +6698,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>600</v>
+        <v>586</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>601</v>
+        <v>587</v>
       </c>
       <c r="F12" t="s">
         <v>233</v>
@@ -7231,7 +6713,7 @@
         <v>232</v>
       </c>
       <c r="H12" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I12" t="s">
         <v>247</v>
@@ -7242,13 +6724,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>602</v>
+        <v>588</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>603</v>
+        <v>589</v>
       </c>
       <c r="F13" t="s">
         <v>233</v>
@@ -7257,7 +6739,7 @@
         <v>232</v>
       </c>
       <c r="H13" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I13" t="s">
         <v>247</v>
@@ -7268,13 +6750,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>604</v>
+        <v>590</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="F14" t="s">
         <v>233</v>
@@ -7283,7 +6765,7 @@
         <v>232</v>
       </c>
       <c r="H14" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I14" t="s">
         <v>247</v>
@@ -7294,13 +6776,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>606</v>
+        <v>592</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="F15" t="s">
         <v>233</v>
@@ -7309,7 +6791,7 @@
         <v>232</v>
       </c>
       <c r="H15" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I15" t="s">
         <v>247</v>
@@ -7320,13 +6802,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>608</v>
+        <v>594</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>609</v>
+        <v>595</v>
       </c>
       <c r="F16" t="s">
         <v>233</v>
@@ -7335,7 +6817,7 @@
         <v>232</v>
       </c>
       <c r="H16" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I16" t="s">
         <v>247</v>
@@ -7346,13 +6828,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>611</v>
+        <v>597</v>
       </c>
       <c r="F17" t="s">
         <v>233</v>
@@ -7361,7 +6843,7 @@
         <v>232</v>
       </c>
       <c r="H17" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I17" t="s">
         <v>247</v>
@@ -7372,13 +6854,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>612</v>
+        <v>598</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>613</v>
+        <v>599</v>
       </c>
       <c r="F18" t="s">
         <v>233</v>
@@ -7387,7 +6869,7 @@
         <v>232</v>
       </c>
       <c r="H18" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I18" t="s">
         <v>247</v>
@@ -7398,13 +6880,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>614</v>
+        <v>600</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>615</v>
+        <v>601</v>
       </c>
       <c r="F19" t="s">
         <v>233</v>
@@ -7413,7 +6895,7 @@
         <v>232</v>
       </c>
       <c r="H19" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I19" t="s">
         <v>247</v>
@@ -7424,13 +6906,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>616</v>
+        <v>602</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>617</v>
+        <v>603</v>
       </c>
       <c r="F20" t="s">
         <v>233</v>
@@ -7439,7 +6921,7 @@
         <v>232</v>
       </c>
       <c r="H20" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I20" t="s">
         <v>247</v>
@@ -7450,13 +6932,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>618</v>
+        <v>604</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="F21" t="s">
         <v>233</v>
@@ -7465,7 +6947,7 @@
         <v>232</v>
       </c>
       <c r="H21" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I21" t="s">
         <v>247</v>
@@ -7476,13 +6958,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>620</v>
+        <v>606</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>621</v>
+        <v>607</v>
       </c>
       <c r="F22" t="s">
         <v>233</v>
@@ -7491,7 +6973,7 @@
         <v>232</v>
       </c>
       <c r="H22" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I22" t="s">
         <v>247</v>
@@ -7502,13 +6984,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>622</v>
+        <v>608</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>623</v>
+        <v>609</v>
       </c>
       <c r="F23" t="s">
         <v>233</v>
@@ -7517,7 +6999,7 @@
         <v>232</v>
       </c>
       <c r="H23" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I23" t="s">
         <v>247</v>
@@ -7528,13 +7010,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>624</v>
+        <v>610</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>625</v>
+        <v>611</v>
       </c>
       <c r="F24" t="s">
         <v>233</v>
@@ -7543,7 +7025,7 @@
         <v>232</v>
       </c>
       <c r="H24" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I24" t="s">
         <v>247</v>
@@ -7554,13 +7036,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>626</v>
+        <v>612</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>627</v>
+        <v>613</v>
       </c>
       <c r="F25" t="s">
         <v>233</v>
@@ -7569,7 +7051,7 @@
         <v>232</v>
       </c>
       <c r="H25" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I25" t="s">
         <v>247</v>
@@ -7580,13 +7062,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>628</v>
+        <v>614</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>629</v>
+        <v>615</v>
       </c>
       <c r="F26" t="s">
         <v>233</v>
@@ -7595,7 +7077,7 @@
         <v>232</v>
       </c>
       <c r="H26" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I26" t="s">
         <v>247</v>
@@ -7606,13 +7088,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>630</v>
+        <v>616</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>631</v>
+        <v>617</v>
       </c>
       <c r="F27" t="s">
         <v>233</v>
@@ -7621,7 +7103,7 @@
         <v>232</v>
       </c>
       <c r="H27" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I27" t="s">
         <v>247</v>
@@ -7632,13 +7114,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>632</v>
+        <v>618</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>633</v>
+        <v>619</v>
       </c>
       <c r="F28" t="s">
         <v>233</v>
@@ -7647,7 +7129,7 @@
         <v>232</v>
       </c>
       <c r="H28" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I28" t="s">
         <v>247</v>
@@ -7658,13 +7140,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>634</v>
+        <v>620</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>635</v>
+        <v>621</v>
       </c>
       <c r="F29" t="s">
         <v>233</v>
@@ -7673,7 +7155,7 @@
         <v>232</v>
       </c>
       <c r="H29" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I29" t="s">
         <v>247</v>
@@ -7684,13 +7166,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>636</v>
+        <v>622</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>637</v>
+        <v>623</v>
       </c>
       <c r="F30" t="s">
         <v>233</v>
@@ -7699,7 +7181,7 @@
         <v>232</v>
       </c>
       <c r="H30" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I30" t="s">
         <v>247</v>
@@ -7710,13 +7192,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>638</v>
+        <v>624</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>639</v>
+        <v>625</v>
       </c>
       <c r="F31" t="s">
         <v>233</v>
@@ -7725,7 +7207,7 @@
         <v>232</v>
       </c>
       <c r="H31" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I31" t="s">
         <v>247</v>
@@ -7736,13 +7218,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>640</v>
+        <v>626</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>641</v>
+        <v>627</v>
       </c>
       <c r="F32" t="s">
         <v>233</v>
@@ -7751,7 +7233,7 @@
         <v>232</v>
       </c>
       <c r="H32" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I32" t="s">
         <v>247</v>
@@ -7762,13 +7244,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>642</v>
+        <v>628</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>643</v>
+        <v>629</v>
       </c>
       <c r="F33" t="s">
         <v>233</v>
@@ -7777,7 +7259,7 @@
         <v>232</v>
       </c>
       <c r="H33" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I33" t="s">
         <v>247</v>
@@ -7788,13 +7270,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>644</v>
+        <v>630</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>645</v>
+        <v>631</v>
       </c>
       <c r="F34" t="s">
         <v>233</v>
@@ -7803,7 +7285,7 @@
         <v>232</v>
       </c>
       <c r="H34" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I34" t="s">
         <v>247</v>
@@ -7814,13 +7296,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>646</v>
+        <v>632</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>647</v>
+        <v>633</v>
       </c>
       <c r="F35" t="s">
         <v>233</v>
@@ -7829,7 +7311,7 @@
         <v>232</v>
       </c>
       <c r="H35" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I35" t="s">
         <v>247</v>
@@ -7840,13 +7322,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>648</v>
+        <v>634</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>649</v>
+        <v>635</v>
       </c>
       <c r="F36" t="s">
         <v>233</v>
@@ -7855,7 +7337,7 @@
         <v>232</v>
       </c>
       <c r="H36" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I36" t="s">
         <v>247</v>
@@ -7866,13 +7348,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>650</v>
+        <v>636</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>651</v>
+        <v>637</v>
       </c>
       <c r="F37" t="s">
         <v>233</v>
@@ -7881,7 +7363,7 @@
         <v>232</v>
       </c>
       <c r="H37" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I37" t="s">
         <v>247</v>
@@ -7892,13 +7374,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>652</v>
+        <v>638</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>653</v>
+        <v>639</v>
       </c>
       <c r="F38" t="s">
         <v>233</v>
@@ -7907,7 +7389,7 @@
         <v>232</v>
       </c>
       <c r="H38" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I38" t="s">
         <v>247</v>
@@ -7918,13 +7400,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>654</v>
+        <v>640</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>655</v>
+        <v>641</v>
       </c>
       <c r="F39" t="s">
         <v>233</v>
@@ -7933,7 +7415,7 @@
         <v>232</v>
       </c>
       <c r="H39" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I39" t="s">
         <v>247</v>
@@ -7944,13 +7426,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>656</v>
+        <v>642</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>657</v>
+        <v>643</v>
       </c>
       <c r="F40" t="s">
         <v>233</v>
@@ -7959,7 +7441,7 @@
         <v>232</v>
       </c>
       <c r="H40" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I40" t="s">
         <v>247</v>
@@ -7970,13 +7452,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>658</v>
+        <v>644</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>659</v>
+        <v>645</v>
       </c>
       <c r="F41" t="s">
         <v>233</v>
@@ -7985,7 +7467,7 @@
         <v>232</v>
       </c>
       <c r="H41" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I41" t="s">
         <v>247</v>
@@ -7996,13 +7478,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>660</v>
+        <v>646</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>661</v>
+        <v>647</v>
       </c>
       <c r="F42" t="s">
         <v>233</v>
@@ -8011,7 +7493,7 @@
         <v>232</v>
       </c>
       <c r="H42" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I42" t="s">
         <v>247</v>
@@ -8022,13 +7504,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>662</v>
+        <v>648</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>663</v>
+        <v>649</v>
       </c>
       <c r="F43" t="s">
         <v>233</v>
@@ -8037,7 +7519,7 @@
         <v>232</v>
       </c>
       <c r="H43" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I43" t="s">
         <v>247</v>
@@ -8048,13 +7530,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>664</v>
+        <v>650</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>665</v>
+        <v>651</v>
       </c>
       <c r="F44" t="s">
         <v>233</v>
@@ -8063,7 +7545,7 @@
         <v>232</v>
       </c>
       <c r="H44" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I44" t="s">
         <v>247</v>
@@ -8074,13 +7556,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>666</v>
+        <v>652</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>667</v>
+        <v>653</v>
       </c>
       <c r="F45" t="s">
         <v>233</v>
@@ -8089,7 +7571,7 @@
         <v>232</v>
       </c>
       <c r="H45" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I45" t="s">
         <v>247</v>
@@ -8100,13 +7582,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>669</v>
+        <v>655</v>
       </c>
       <c r="F46" t="s">
         <v>233</v>
@@ -8115,7 +7597,7 @@
         <v>232</v>
       </c>
       <c r="H46" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I46" t="s">
         <v>247</v>
@@ -8126,13 +7608,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>670</v>
+        <v>656</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>671</v>
+        <v>657</v>
       </c>
       <c r="F47" t="s">
         <v>233</v>
@@ -8141,7 +7623,7 @@
         <v>232</v>
       </c>
       <c r="H47" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I47" t="s">
         <v>247</v>
@@ -8152,13 +7634,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>672</v>
+        <v>658</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>673</v>
+        <v>659</v>
       </c>
       <c r="F48" t="s">
         <v>233</v>
@@ -8167,7 +7649,7 @@
         <v>232</v>
       </c>
       <c r="H48" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I48" t="s">
         <v>247</v>
@@ -8178,13 +7660,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>675</v>
+        <v>661</v>
       </c>
       <c r="F49" t="s">
         <v>233</v>
@@ -8193,7 +7675,7 @@
         <v>232</v>
       </c>
       <c r="H49" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I49" t="s">
         <v>247</v>
@@ -8204,13 +7686,13 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>676</v>
+        <v>662</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
       <c r="F50" t="s">
         <v>233</v>
@@ -8219,7 +7701,7 @@
         <v>232</v>
       </c>
       <c r="H50" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I50" t="s">
         <v>247</v>
@@ -8230,13 +7712,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>678</v>
+        <v>664</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="F51" t="s">
         <v>233</v>
@@ -8245,7 +7727,7 @@
         <v>232</v>
       </c>
       <c r="H51" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I51" t="s">
         <v>247</v>
@@ -8256,13 +7738,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>680</v>
+        <v>666</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="F52" t="s">
         <v>233</v>
@@ -8271,7 +7753,7 @@
         <v>232</v>
       </c>
       <c r="H52" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I52" t="s">
         <v>247</v>
@@ -8282,13 +7764,13 @@
         <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="D53" t="s">
         <v>243</v>
       </c>
       <c r="E53" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="F53" t="s">
         <v>233</v>
@@ -8297,7 +7779,7 @@
         <v>232</v>
       </c>
       <c r="H53" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I53" t="s">
         <v>247</v>
@@ -8308,13 +7790,13 @@
         <v>17</v>
       </c>
       <c r="C54" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
       <c r="D54" t="s">
         <v>243</v>
       </c>
       <c r="E54" t="s">
-        <v>685</v>
+        <v>671</v>
       </c>
       <c r="F54" t="s">
         <v>233</v>
@@ -8323,7 +7805,7 @@
         <v>232</v>
       </c>
       <c r="H54" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I54" t="s">
         <v>247</v>
@@ -8334,13 +7816,13 @@
         <v>17</v>
       </c>
       <c r="C55" t="s">
-        <v>686</v>
+        <v>672</v>
       </c>
       <c r="D55" t="s">
         <v>243</v>
       </c>
       <c r="E55" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="F55" t="s">
         <v>233</v>
@@ -8349,7 +7831,7 @@
         <v>232</v>
       </c>
       <c r="H55" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I55" t="s">
         <v>247</v>
@@ -8360,13 +7842,13 @@
         <v>17</v>
       </c>
       <c r="C56" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="D56" t="s">
         <v>243</v>
       </c>
       <c r="E56" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="F56" t="s">
         <v>233</v>
@@ -8375,61 +7857,9 @@
         <v>232</v>
       </c>
       <c r="H56" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I56" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="57" spans="2:9">
-      <c r="B57" t="s">
-        <v>17</v>
-      </c>
-      <c r="C57" t="s">
-        <v>690</v>
-      </c>
-      <c r="D57" t="s">
-        <v>243</v>
-      </c>
-      <c r="E57" t="s">
-        <v>691</v>
-      </c>
-      <c r="F57" t="s">
-        <v>233</v>
-      </c>
-      <c r="G57" t="s">
-        <v>232</v>
-      </c>
-      <c r="H57" t="s">
-        <v>479</v>
-      </c>
-      <c r="I57" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="58" spans="2:9">
-      <c r="B58" t="s">
-        <v>17</v>
-      </c>
-      <c r="C58" t="s">
-        <v>692</v>
-      </c>
-      <c r="D58" t="s">
-        <v>243</v>
-      </c>
-      <c r="E58" t="s">
-        <v>693</v>
-      </c>
-      <c r="F58" t="s">
-        <v>233</v>
-      </c>
-      <c r="G58" t="s">
-        <v>232</v>
-      </c>
-      <c r="H58" t="s">
-        <v>479</v>
-      </c>
-      <c r="I58" t="s">
         <v>247</v>
       </c>
     </row>
@@ -8439,13 +7869,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7C2996D-7C8A-4807-9219-540F0AA625C5}">
-  <dimension ref="B3:I58"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7149CC08-25C3-4149-BF05-D194B036136F}">
+  <dimension ref="B3:I56"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -8479,13 +7909,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="F5" t="s">
         <v>25</v>
@@ -8494,7 +7924,7 @@
         <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I5" t="s">
         <v>247</v>
@@ -8505,13 +7935,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="F6" t="s">
         <v>25</v>
@@ -8520,7 +7950,7 @@
         <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I6" t="s">
         <v>247</v>
@@ -8531,13 +7961,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="F7" t="s">
         <v>25</v>
@@ -8546,7 +7976,7 @@
         <v>35</v>
       </c>
       <c r="H7" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I7" t="s">
         <v>247</v>
@@ -8557,13 +7987,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="F8" t="s">
         <v>25</v>
@@ -8572,7 +8002,7 @@
         <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I8" t="s">
         <v>247</v>
@@ -8583,13 +8013,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="F9" t="s">
         <v>25</v>
@@ -8598,7 +8028,7 @@
         <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I9" t="s">
         <v>247</v>
@@ -8609,13 +8039,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="F10" t="s">
         <v>25</v>
@@ -8624,7 +8054,7 @@
         <v>35</v>
       </c>
       <c r="H10" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I10" t="s">
         <v>247</v>
@@ -8635,13 +8065,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
@@ -8650,7 +8080,7 @@
         <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I11" t="s">
         <v>247</v>
@@ -8661,13 +8091,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="F12" t="s">
         <v>25</v>
@@ -8676,7 +8106,7 @@
         <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I12" t="s">
         <v>247</v>
@@ -8687,13 +8117,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="F13" t="s">
         <v>25</v>
@@ -8702,7 +8132,7 @@
         <v>35</v>
       </c>
       <c r="H13" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I13" t="s">
         <v>247</v>
@@ -8713,13 +8143,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="F14" t="s">
         <v>25</v>
@@ -8728,7 +8158,7 @@
         <v>35</v>
       </c>
       <c r="H14" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I14" t="s">
         <v>247</v>
@@ -8739,13 +8169,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="F15" t="s">
         <v>25</v>
@@ -8754,7 +8184,7 @@
         <v>35</v>
       </c>
       <c r="H15" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I15" t="s">
         <v>247</v>
@@ -8765,13 +8195,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="F16" t="s">
         <v>25</v>
@@ -8780,7 +8210,7 @@
         <v>35</v>
       </c>
       <c r="H16" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I16" t="s">
         <v>247</v>
@@ -8791,13 +8221,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="F17" t="s">
         <v>25</v>
@@ -8806,7 +8236,7 @@
         <v>35</v>
       </c>
       <c r="H17" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I17" t="s">
         <v>247</v>
@@ -8817,13 +8247,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="F18" t="s">
         <v>25</v>
@@ -8832,7 +8262,7 @@
         <v>35</v>
       </c>
       <c r="H18" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I18" t="s">
         <v>247</v>
@@ -8843,13 +8273,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="F19" t="s">
         <v>25</v>
@@ -8858,7 +8288,7 @@
         <v>35</v>
       </c>
       <c r="H19" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I19" t="s">
         <v>247</v>
@@ -8869,13 +8299,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="F20" t="s">
         <v>25</v>
@@ -8884,7 +8314,7 @@
         <v>35</v>
       </c>
       <c r="H20" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I20" t="s">
         <v>247</v>
@@ -8895,13 +8325,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="F21" t="s">
         <v>25</v>
@@ -8910,7 +8340,7 @@
         <v>35</v>
       </c>
       <c r="H21" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I21" t="s">
         <v>247</v>
@@ -8921,13 +8351,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="F22" t="s">
         <v>25</v>
@@ -8936,7 +8366,7 @@
         <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I22" t="s">
         <v>247</v>
@@ -8947,13 +8377,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="F23" t="s">
         <v>25</v>
@@ -8962,7 +8392,7 @@
         <v>35</v>
       </c>
       <c r="H23" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I23" t="s">
         <v>247</v>
@@ -8973,13 +8403,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="F24" t="s">
         <v>25</v>
@@ -8988,7 +8418,7 @@
         <v>35</v>
       </c>
       <c r="H24" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I24" t="s">
         <v>247</v>
@@ -8999,13 +8429,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="F25" t="s">
         <v>25</v>
@@ -9014,7 +8444,7 @@
         <v>35</v>
       </c>
       <c r="H25" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I25" t="s">
         <v>247</v>
@@ -9025,13 +8455,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="F26" t="s">
         <v>25</v>
@@ -9040,7 +8470,7 @@
         <v>35</v>
       </c>
       <c r="H26" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I26" t="s">
         <v>247</v>
@@ -9051,13 +8481,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="F27" t="s">
         <v>25</v>
@@ -9066,7 +8496,7 @@
         <v>35</v>
       </c>
       <c r="H27" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I27" t="s">
         <v>247</v>
@@ -9077,13 +8507,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="F28" t="s">
         <v>25</v>
@@ -9092,7 +8522,7 @@
         <v>35</v>
       </c>
       <c r="H28" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I28" t="s">
         <v>247</v>
@@ -9103,13 +8533,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="F29" t="s">
         <v>25</v>
@@ -9118,7 +8548,7 @@
         <v>35</v>
       </c>
       <c r="H29" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I29" t="s">
         <v>247</v>
@@ -9129,13 +8559,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="F30" t="s">
         <v>25</v>
@@ -9144,7 +8574,7 @@
         <v>35</v>
       </c>
       <c r="H30" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I30" t="s">
         <v>247</v>
@@ -9155,13 +8585,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="F31" t="s">
         <v>25</v>
@@ -9170,7 +8600,7 @@
         <v>35</v>
       </c>
       <c r="H31" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I31" t="s">
         <v>247</v>
@@ -9181,13 +8611,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="F32" t="s">
         <v>25</v>
@@ -9196,7 +8626,7 @@
         <v>35</v>
       </c>
       <c r="H32" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I32" t="s">
         <v>247</v>
@@ -9207,13 +8637,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="F33" t="s">
         <v>25</v>
@@ -9222,7 +8652,7 @@
         <v>35</v>
       </c>
       <c r="H33" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I33" t="s">
         <v>247</v>
@@ -9233,13 +8663,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="F34" t="s">
         <v>25</v>
@@ -9248,7 +8678,7 @@
         <v>35</v>
       </c>
       <c r="H34" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I34" t="s">
         <v>247</v>
@@ -9259,13 +8689,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="F35" t="s">
         <v>25</v>
@@ -9274,7 +8704,7 @@
         <v>35</v>
       </c>
       <c r="H35" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I35" t="s">
         <v>247</v>
@@ -9285,13 +8715,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="F36" t="s">
         <v>25</v>
@@ -9300,7 +8730,7 @@
         <v>35</v>
       </c>
       <c r="H36" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I36" t="s">
         <v>247</v>
@@ -9311,13 +8741,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="F37" t="s">
         <v>25</v>
@@ -9326,7 +8756,7 @@
         <v>35</v>
       </c>
       <c r="H37" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I37" t="s">
         <v>247</v>
@@ -9337,13 +8767,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="F38" t="s">
         <v>25</v>
@@ -9352,7 +8782,7 @@
         <v>35</v>
       </c>
       <c r="H38" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I38" t="s">
         <v>247</v>
@@ -9363,13 +8793,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="F39" t="s">
         <v>25</v>
@@ -9378,7 +8808,7 @@
         <v>35</v>
       </c>
       <c r="H39" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I39" t="s">
         <v>247</v>
@@ -9389,13 +8819,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="F40" t="s">
         <v>25</v>
@@ -9404,7 +8834,7 @@
         <v>35</v>
       </c>
       <c r="H40" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I40" t="s">
         <v>247</v>
@@ -9415,13 +8845,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="F41" t="s">
         <v>25</v>
@@ -9430,7 +8860,7 @@
         <v>35</v>
       </c>
       <c r="H41" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I41" t="s">
         <v>247</v>
@@ -9441,13 +8871,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="F42" t="s">
         <v>25</v>
@@ -9456,7 +8886,7 @@
         <v>35</v>
       </c>
       <c r="H42" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I42" t="s">
         <v>247</v>
@@ -9467,13 +8897,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="F43" t="s">
         <v>25</v>
@@ -9482,7 +8912,7 @@
         <v>35</v>
       </c>
       <c r="H43" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I43" t="s">
         <v>247</v>
@@ -9493,13 +8923,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="F44" t="s">
         <v>25</v>
@@ -9508,7 +8938,7 @@
         <v>35</v>
       </c>
       <c r="H44" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I44" t="s">
         <v>247</v>
@@ -9519,13 +8949,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="F45" t="s">
         <v>25</v>
@@ -9534,7 +8964,7 @@
         <v>35</v>
       </c>
       <c r="H45" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I45" t="s">
         <v>247</v>
@@ -9545,13 +8975,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="F46" t="s">
         <v>25</v>
@@ -9560,7 +8990,7 @@
         <v>35</v>
       </c>
       <c r="H46" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I46" t="s">
         <v>247</v>
@@ -9571,13 +9001,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="F47" t="s">
         <v>25</v>
@@ -9586,7 +9016,7 @@
         <v>35</v>
       </c>
       <c r="H47" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I47" t="s">
         <v>247</v>
@@ -9597,13 +9027,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="F48" t="s">
         <v>25</v>
@@ -9612,7 +9042,7 @@
         <v>35</v>
       </c>
       <c r="H48" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I48" t="s">
         <v>247</v>
@@ -9623,13 +9053,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="F49" t="s">
         <v>25</v>
@@ -9638,7 +9068,7 @@
         <v>35</v>
       </c>
       <c r="H49" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I49" t="s">
         <v>247</v>
@@ -9649,13 +9079,13 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="F50" t="s">
         <v>25</v>
@@ -9664,7 +9094,7 @@
         <v>35</v>
       </c>
       <c r="H50" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I50" t="s">
         <v>247</v>
@@ -9675,13 +9105,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="F51" t="s">
         <v>25</v>
@@ -9690,7 +9120,7 @@
         <v>35</v>
       </c>
       <c r="H51" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I51" t="s">
         <v>247</v>
@@ -9701,13 +9131,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="F52" t="s">
         <v>25</v>
@@ -9716,7 +9146,7 @@
         <v>35</v>
       </c>
       <c r="H52" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I52" t="s">
         <v>247</v>
@@ -9727,13 +9157,13 @@
         <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="D53" t="s">
         <v>243</v>
       </c>
       <c r="E53" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="F53" t="s">
         <v>25</v>
@@ -9742,7 +9172,7 @@
         <v>35</v>
       </c>
       <c r="H53" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I53" t="s">
         <v>247</v>
@@ -9753,13 +9183,13 @@
         <v>17</v>
       </c>
       <c r="C54" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="D54" t="s">
         <v>243</v>
       </c>
       <c r="E54" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="F54" t="s">
         <v>25</v>
@@ -9768,7 +9198,7 @@
         <v>35</v>
       </c>
       <c r="H54" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I54" t="s">
         <v>247</v>
@@ -9779,13 +9209,13 @@
         <v>17</v>
       </c>
       <c r="C55" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="D55" t="s">
         <v>243</v>
       </c>
       <c r="E55" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="F55" t="s">
         <v>25</v>
@@ -9794,7 +9224,7 @@
         <v>35</v>
       </c>
       <c r="H55" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I55" t="s">
         <v>247</v>
@@ -9805,13 +9235,13 @@
         <v>17</v>
       </c>
       <c r="C56" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="D56" t="s">
         <v>243</v>
       </c>
       <c r="E56" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="F56" t="s">
         <v>25</v>
@@ -9820,61 +9250,9 @@
         <v>35</v>
       </c>
       <c r="H56" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I56" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="57" spans="2:9">
-      <c r="B57" t="s">
-        <v>17</v>
-      </c>
-      <c r="C57" t="s">
-        <v>582</v>
-      </c>
-      <c r="D57" t="s">
-        <v>243</v>
-      </c>
-      <c r="E57" t="s">
-        <v>583</v>
-      </c>
-      <c r="F57" t="s">
-        <v>25</v>
-      </c>
-      <c r="G57" t="s">
-        <v>35</v>
-      </c>
-      <c r="H57" t="s">
-        <v>479</v>
-      </c>
-      <c r="I57" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="58" spans="2:9">
-      <c r="B58" t="s">
-        <v>17</v>
-      </c>
-      <c r="C58" t="s">
-        <v>584</v>
-      </c>
-      <c r="D58" t="s">
-        <v>243</v>
-      </c>
-      <c r="E58" t="s">
-        <v>585</v>
-      </c>
-      <c r="F58" t="s">
-        <v>25</v>
-      </c>
-      <c r="G58" t="s">
-        <v>35</v>
-      </c>
-      <c r="H58" t="s">
-        <v>479</v>
-      </c>
-      <c r="I58" t="s">
         <v>247</v>
       </c>
     </row>
@@ -9885,7 +9263,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:S119"/>
+  <dimension ref="B3:S114"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
@@ -12876,121 +12254,6 @@
         <v>35</v>
       </c>
       <c r="S114" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="115" spans="13:19">
-      <c r="M115" t="s">
-        <v>17</v>
-      </c>
-      <c r="N115" t="s">
-        <v>466</v>
-      </c>
-      <c r="O115" t="s">
-        <v>243</v>
-      </c>
-      <c r="P115" t="s">
-        <v>467</v>
-      </c>
-      <c r="Q115" t="s">
-        <v>25</v>
-      </c>
-      <c r="R115" t="s">
-        <v>35</v>
-      </c>
-      <c r="S115" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="116" spans="13:19">
-      <c r="M116" t="s">
-        <v>17</v>
-      </c>
-      <c r="N116" t="s">
-        <v>468</v>
-      </c>
-      <c r="O116" t="s">
-        <v>243</v>
-      </c>
-      <c r="P116" t="s">
-        <v>469</v>
-      </c>
-      <c r="Q116" t="s">
-        <v>25</v>
-      </c>
-      <c r="R116" t="s">
-        <v>35</v>
-      </c>
-      <c r="S116" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="117" spans="13:19">
-      <c r="M117" t="s">
-        <v>17</v>
-      </c>
-      <c r="N117" t="s">
-        <v>470</v>
-      </c>
-      <c r="O117" t="s">
-        <v>243</v>
-      </c>
-      <c r="P117" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q117" t="s">
-        <v>25</v>
-      </c>
-      <c r="R117" t="s">
-        <v>35</v>
-      </c>
-      <c r="S117" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="118" spans="13:19">
-      <c r="M118" t="s">
-        <v>17</v>
-      </c>
-      <c r="N118" t="s">
-        <v>472</v>
-      </c>
-      <c r="O118" t="s">
-        <v>243</v>
-      </c>
-      <c r="P118" t="s">
-        <v>473</v>
-      </c>
-      <c r="Q118" t="s">
-        <v>25</v>
-      </c>
-      <c r="R118" t="s">
-        <v>35</v>
-      </c>
-      <c r="S118" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="119" spans="13:19">
-      <c r="M119" t="s">
-        <v>17</v>
-      </c>
-      <c r="N119" t="s">
-        <v>474</v>
-      </c>
-      <c r="O119" t="s">
-        <v>243</v>
-      </c>
-      <c r="P119" t="s">
-        <v>475</v>
-      </c>
-      <c r="Q119" t="s">
-        <v>25</v>
-      </c>
-      <c r="R119" t="s">
-        <v>35</v>
-      </c>
-      <c r="S119" t="s">
         <v>247</v>
       </c>
     </row>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C33DEAE-2EF3-4DDD-90CE-19B037717A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F666984-9EB1-4E00-AE5C-56584D295BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4874,7 +4874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E08842F-D8C0-4CAD-A464-46B9B3431BF4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5103988C-832D-4A4F-A925-D417AE5B7559}">
   <dimension ref="B3:H72"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6476,7 +6476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AED2135F-F4A1-467A-BDDD-8AFF29B53C80}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309DE399-D4ED-4496-B792-5ADFF83778CE}">
   <dimension ref="B3:I56"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7869,7 +7869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7149CC08-25C3-4149-BF05-D194B036136F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4E265F0-8B20-4B93-B85A-49F204D02938}">
   <dimension ref="B3:I56"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F666984-9EB1-4E00-AE5C-56584D295BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F9C707-4410-4EA2-82E2-008FCE7EC602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4874,7 +4874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5103988C-832D-4A4F-A925-D417AE5B7559}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EF3935E-B84E-4BC2-ACAE-7B9983E522FC}">
   <dimension ref="B3:H72"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6476,7 +6476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309DE399-D4ED-4496-B792-5ADFF83778CE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01F380BB-4E9A-41A9-BAFA-DE92093C5A5C}">
   <dimension ref="B3:I56"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7869,7 +7869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4E265F0-8B20-4B93-B85A-49F204D02938}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E761568-5538-4918-A5E8-CC58B1A6B2E5}">
   <dimension ref="B3:I56"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F9C707-4410-4EA2-82E2-008FCE7EC602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF45F24-2041-4CC6-A6AE-D69AB5609AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4874,7 +4874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EF3935E-B84E-4BC2-ACAE-7B9983E522FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFEF567A-CE6F-4964-AF1B-52C2777396A5}">
   <dimension ref="B3:H72"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6476,7 +6476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01F380BB-4E9A-41A9-BAFA-DE92093C5A5C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45F5D0E7-3364-4684-B3F7-99DA5B71DAEE}">
   <dimension ref="B3:I56"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7869,7 +7869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E761568-5538-4918-A5E8-CC58B1A6B2E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90D586E2-D4F5-4F64-878C-838F7EEA3889}">
   <dimension ref="B3:I56"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF45F24-2041-4CC6-A6AE-D69AB5609AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42AAAACF-5785-4FCA-94BC-38338F7022BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4874,7 +4874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFEF567A-CE6F-4964-AF1B-52C2777396A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78168406-C527-438D-B974-2BEB2D7C7C7B}">
   <dimension ref="B3:H72"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6476,7 +6476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45F5D0E7-3364-4684-B3F7-99DA5B71DAEE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CB9FA8A-FE23-49A8-B477-B033B8BED6D7}">
   <dimension ref="B3:I56"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7869,7 +7869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90D586E2-D4F5-4F64-878C-838F7EEA3889}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD2E467-A31F-4FCE-967D-8B3C04533755}">
   <dimension ref="B3:I56"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42AAAACF-5785-4FCA-94BC-38338F7022BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA44BBCB-AD5F-409F-9D22-0C80CB925DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4874,7 +4874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78168406-C527-438D-B974-2BEB2D7C7C7B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF2F93EB-D29A-494C-9C24-12D6D1834BB3}">
   <dimension ref="B3:H72"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6476,7 +6476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CB9FA8A-FE23-49A8-B477-B033B8BED6D7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E06CFBBB-AC5E-47E2-86AE-5908EC7B30AC}">
   <dimension ref="B3:I56"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7869,7 +7869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD2E467-A31F-4FCE-967D-8B3C04533755}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA586A0-5895-4D03-94A2-101EA6D2E5FF}">
   <dimension ref="B3:I56"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA44BBCB-AD5F-409F-9D22-0C80CB925DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD4AF2F3-46BD-40D2-9F77-B6020D6027BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4874,7 +4874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF2F93EB-D29A-494C-9C24-12D6D1834BB3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCDA9BB7-9B34-4D70-BD5C-858B0930D76A}">
   <dimension ref="B3:H72"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6476,7 +6476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E06CFBBB-AC5E-47E2-86AE-5908EC7B30AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22357F66-C810-4CAA-91B5-1E3D9F2F5104}">
   <dimension ref="B3:I56"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7869,7 +7869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA586A0-5895-4D03-94A2-101EA6D2E5FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8770A68-E93B-449B-BC59-9E769872D332}">
   <dimension ref="B3:I56"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD4AF2F3-46BD-40D2-9F77-B6020D6027BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6E6274-466A-4769-9E30-18C6D8E2953E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4874,7 +4874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCDA9BB7-9B34-4D70-BD5C-858B0930D76A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B68B14-F380-4553-9AC8-0C9AA32D32CC}">
   <dimension ref="B3:H72"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6476,7 +6476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22357F66-C810-4CAA-91B5-1E3D9F2F5104}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49DA0315-56DC-4F35-BFED-F97E39FFE28D}">
   <dimension ref="B3:I56"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7869,7 +7869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8770A68-E93B-449B-BC59-9E769872D332}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{313FCC87-1E8D-4C65-8B8C-ACDEB29F2D8A}">
   <dimension ref="B3:I56"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
